--- a/report-vis.xlsx
+++ b/report-vis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\! CS\Y2\AI is taking over\cw\ai-garbage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF458BD7-08A4-4DDB-B380-A772A12D567F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B037B311-49D5-42FC-82BA-677DCFB74D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-12645" windowWidth="29040" windowHeight="15840" xr2:uid="{82DBE9BC-AC51-4988-B415-6B972F3134D5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="72">
   <si>
     <t>sub-01</t>
   </si>
@@ -178,12 +178,115 @@
   <si>
     <t>TESTING is performed using the TEST SAMPLES for the TEST SUBJECT</t>
   </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>SV</t>
+  </si>
+  <si>
+    <t>STt</t>
+  </si>
+  <si>
+    <t>STr1</t>
+  </si>
+  <si>
+    <t>STr2</t>
+  </si>
+  <si>
+    <t>STr3</t>
+  </si>
+  <si>
+    <t>STr4</t>
+  </si>
+  <si>
+    <t>STr5</t>
+  </si>
+  <si>
+    <t>STr6</t>
+  </si>
+  <si>
+    <t>STr7</t>
+  </si>
+  <si>
+    <t>STr8</t>
+  </si>
+  <si>
+    <t>Fit Preprocessors</t>
+  </si>
+  <si>
+    <t>Apply Preprocessors</t>
+  </si>
+  <si>
+    <t>Fit Subject-Specific Classifiers</t>
+  </si>
+  <si>
+    <t>W1</t>
+  </si>
+  <si>
+    <t>W2</t>
+  </si>
+  <si>
+    <t>W7</t>
+  </si>
+  <si>
+    <t>W8</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>Fine-Tune using
+Validation Set</t>
+  </si>
+  <si>
+    <t>Test Final Model</t>
+  </si>
+  <si>
+    <t>TRAINING</t>
+  </si>
+  <si>
+    <t>VALIDATION</t>
+  </si>
+  <si>
+    <t>TESTING</t>
+  </si>
+  <si>
+    <r>
+      <t>Initialise Generalised Classifier
+with</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> W</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>avg</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +324,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -249,8 +359,59 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="23"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,8 +472,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -373,11 +540,51 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -661,11 +868,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -678,7 +916,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -699,12 +937,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -712,19 +951,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -737,7 +979,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -747,8 +989,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -762,10 +1004,16 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -788,89 +1036,233 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -879,9 +1271,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFBA9F7"/>
       <color rgb="FFEF7F7F"/>
       <color rgb="FF7DF977"/>
-      <color rgb="FFFBA9F7"/>
       <color rgb="FFECF6AE"/>
     </mruColors>
   </colors>
@@ -995,6 +1387,2406 @@
             <a:gd name="adj1" fmla="val 22910"/>
             <a:gd name="adj2" fmla="val 50000"/>
           </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>45180</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>47217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>535702</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>49696</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Arrow: Down 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E329CE2-8B9D-4513-6647-49367A01B626}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="36265028" y="16993434"/>
+          <a:ext cx="490522" cy="549132"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>63650</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>49122</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>550362</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>55411</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Arrow: Down 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F318B5D-DE8E-44E6-B514-F7EB9CB688DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37509324" y="16995339"/>
+          <a:ext cx="486712" cy="552942"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>59840</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>39821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>554172</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>48015</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Arrow: Down 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2440B1A1-F465-4DE1-8C5A-D1D2DBB096FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37039252" y="16758997"/>
+          <a:ext cx="494332" cy="546077"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>64356</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>554878</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Arrow: Down 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7006C5B7-F0F3-47A7-8C9D-B14A03644B15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38254003" y="16761476"/>
+          <a:ext cx="490522" cy="538457"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>54168</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>544690</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>42875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Arrow: Down 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{969F5363-FAE2-4DA1-8923-5005C00BAB54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="39454050" y="16761477"/>
+          <a:ext cx="490522" cy="538457"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>74544</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42963</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>555541</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>53062</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Arrow: Down 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E67B18E8-10C2-47EB-8BAD-DA5ECA2C1D60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40684662" y="16762139"/>
+          <a:ext cx="480997" cy="547982"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>64356</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>554878</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>53061</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Arrow: Down 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9BF4701-B6D3-4856-8AD2-CD4D12125236}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="41884709" y="16762138"/>
+          <a:ext cx="490522" cy="547982"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>48322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>551730</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>62231</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Arrow: Down 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68CACEB9-E3D9-42A7-AAF8-5113D8FEAE35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="43105131" y="16767498"/>
+          <a:ext cx="477187" cy="551792"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Arrow: Down 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A880E7-8195-4B17-A8EA-E0A0C0ADCCDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44315367" y="16761476"/>
+          <a:ext cx="480997" cy="538457"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Arrow: Down 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E154CE0E-475E-4608-A22A-77A665A9E341}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44315367" y="16761476"/>
+          <a:ext cx="480997" cy="538457"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>56029</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>50539</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>533216</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Arrow: Down 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E418E8A-F902-4CD9-B3E5-16B7C4315E2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="45833179" y="17081239"/>
+          <a:ext cx="477187" cy="2883161"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>55806</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>48634</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>550138</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Arrow: Down 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FBCCA0F-065C-4E93-9F9F-DF894EC990C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47052156" y="17079334"/>
+          <a:ext cx="494332" cy="2885066"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>45180</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>47217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>535702</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>49696</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Arrow: Down 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0B69B83-0B33-40A7-A963-0B036AA2EEA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="35816261" y="16947593"/>
+          <a:ext cx="488617" cy="542266"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>63650</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>49122</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>550362</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>55411</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Arrow: Down 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{214A81C1-9101-43CB-B9F2-D0DD2D373C81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37039252" y="16949498"/>
+          <a:ext cx="494332" cy="546076"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>59840</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>39821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>554172</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>48015</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Arrow: Down 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC3F0056-8156-46BA-BB74-75902B75F94C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37035442" y="16938292"/>
+          <a:ext cx="494332" cy="547981"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>64356</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>554878</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Arrow: Down 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0655101C-42D4-4625-8557-C428DA8F6DB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38250193" y="16942676"/>
+          <a:ext cx="490522" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>54168</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>544690</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>42875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Arrow: Down 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7286F74-6F29-4CC0-8A5A-E9540391AB06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="39457860" y="16942677"/>
+          <a:ext cx="488617" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>74544</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42963</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>555541</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>53062</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Arrow: Down 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D64B3F08-2666-49D9-A64B-137E3406D185}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40684662" y="16943339"/>
+          <a:ext cx="477187" cy="549886"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>64356</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>554878</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>53061</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Arrow: Down 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DD3B443-DAE1-484D-A7C3-28B0C5BF5585}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="41880899" y="16943338"/>
+          <a:ext cx="490522" cy="549886"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>48322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>551730</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>62231</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Arrow: Down 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A3B608A-C664-48E3-A2E8-6CC4DB9AEE59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="43105131" y="16948698"/>
+          <a:ext cx="480997" cy="546076"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Arrow: Down 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F23C083-BFBA-4DCA-B010-926B15832937}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44315367" y="16942676"/>
+          <a:ext cx="477187" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Arrow: Down 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9963327C-9D71-433A-947A-07A854E2A716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44315367" y="16942676"/>
+          <a:ext cx="477187" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>45180</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>47217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>535702</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>49696</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Arrow: Down 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89545B30-E079-4ACE-BD93-939A09E90B64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="35816261" y="16947593"/>
+          <a:ext cx="488617" cy="542266"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>63650</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>49122</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>550362</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>55411</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Arrow: Down 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA3E353A-F396-4785-9108-7E26353365B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37039252" y="16949498"/>
+          <a:ext cx="494332" cy="546076"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>59840</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>39821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>554172</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>48015</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Arrow: Down 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD3201E3-A2F6-4F51-8573-40DF10D57D5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37035442" y="16938292"/>
+          <a:ext cx="494332" cy="547981"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>64356</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>554878</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Arrow: Down 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0E40B13-2B21-4338-A59F-E96C94C22677}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38250193" y="16942676"/>
+          <a:ext cx="490522" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>66</xdr:col>
+      <xdr:colOff>69588</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>66</xdr:col>
+      <xdr:colOff>542965</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>117230</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Arrow: Down 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC862714-2830-484A-B797-BF481FE21587}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40360338" y="23726775"/>
+          <a:ext cx="473377" cy="479180"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>54168</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>65</xdr:col>
+      <xdr:colOff>544690</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>42875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Arrow: Down 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ADE2FB2-770B-4F54-A52B-ECE252AB5940}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="39457860" y="16942677"/>
+          <a:ext cx="488617" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>74544</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42963</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>555541</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>53062</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Arrow: Down 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E49C5BF-D783-4655-9DD7-9742EC5C7F69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40684662" y="16943339"/>
+          <a:ext cx="477187" cy="549886"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>64356</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>554878</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>53061</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Arrow: Down 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F06DFD6-131E-4987-9D6A-803C0B7B9E2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="41880899" y="16943338"/>
+          <a:ext cx="490522" cy="549886"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>48322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>551730</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>62231</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Arrow: Down 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A04FBB9-D686-4B24-B969-3483FFFAA68D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="43105131" y="16948698"/>
+          <a:ext cx="480997" cy="546076"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Arrow: Down 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{010D87D4-1BA5-44D7-98AD-84ACCE4572B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44315367" y="16942676"/>
+          <a:ext cx="477187" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Arrow: Down 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD004A44-5303-42FF-BA0C-172BBCCEBA99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44315367" y="16942676"/>
+          <a:ext cx="477187" cy="538456"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>18378</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>174025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>77390</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B7B22BA-2508-EB8C-402B-E6227FEC2551}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="35903816" y="23456697"/>
+          <a:ext cx="9089903" cy="81959"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>16654</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>88103</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>59</xdr:col>
+      <xdr:colOff>91834</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>167301</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Rectangle 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90E74824-898B-4A8E-8B5B-78707354DA58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="36156509" y="23574748"/>
+          <a:ext cx="75180" cy="79198"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>535782</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>1838</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>168733</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Rectangle 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E165342-6755-44E9-91A7-9416785351B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44922282" y="23377922"/>
+          <a:ext cx="73275" cy="73483"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>59839</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>46728</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>533216</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Arrow: Down 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD63406D-853F-4EDF-9FB3-2CC68C1A24B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="45510898" y="21606846"/>
+          <a:ext cx="473377" cy="2384948"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>69</xdr:col>
+      <xdr:colOff>57667</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>58202</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>503468</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>169181</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Arrow: Down 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08719D98-5C85-46F7-B8F1-680FD1B9F610}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="43883596" y="22703166"/>
+          <a:ext cx="464764" cy="3507408"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>74743</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>51227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>551930</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>99637</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Arrow: Down 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE49285-461A-4257-988B-A399549137A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="49114886" y="21373620"/>
+          <a:ext cx="477187" cy="2361624"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>54432</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>40786</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>550005</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Arrow: Down 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BDD8F75-8BA8-4503-8063-BD1C45DE56D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="47878669" y="24157513"/>
+          <a:ext cx="478100" cy="495573"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
@@ -1344,7 +4136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{318B4486-90DF-4557-8364-585FD469B441}">
-  <dimension ref="B31:BC78"/>
+  <dimension ref="B31:AVI143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="20" max="20" width="8.88671875" customWidth="1"/>
@@ -1499,8 +4291,8 @@
       <c r="S34" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
+      <c r="T34" s="23"/>
+      <c r="U34" s="23"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
@@ -1525,8 +4317,8 @@
       <c r="AQ34" s="15"/>
       <c r="AR34" s="7"/>
       <c r="AS34" s="15"/>
-      <c r="AT34" s="21"/>
-      <c r="AU34" s="21"/>
+      <c r="AT34" s="23"/>
+      <c r="AU34" s="23"/>
       <c r="AV34" s="7"/>
       <c r="AW34" s="7"/>
       <c r="AX34" s="7"/>
@@ -1658,20 +4450,20 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
-      <c r="O37" s="33" t="s">
+      <c r="O37" s="35" t="s">
         <v>13</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="34" t="s">
+      <c r="T37" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="U37" s="35" t="s">
+      <c r="U37" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="V37" s="35"/>
+      <c r="V37" s="37"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -1688,16 +4480,16 @@
       <c r="AL37" s="7"/>
       <c r="AM37" s="7"/>
       <c r="AN37" s="7"/>
-      <c r="AO37" s="33" t="s">
+      <c r="AO37" s="35" t="s">
         <v>29</v>
       </c>
       <c r="AP37" s="7"/>
       <c r="AQ37" s="7"/>
       <c r="AR37" s="7"/>
       <c r="AS37" s="7"/>
-      <c r="AT37" s="27"/>
-      <c r="AU37" s="35"/>
-      <c r="AV37" s="35"/>
+      <c r="AT37" s="29"/>
+      <c r="AU37" s="37"/>
+      <c r="AV37" s="37"/>
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
       <c r="AY37" s="7"/>
@@ -1730,16 +4522,16 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
-      <c r="O38" s="32"/>
+      <c r="O38" s="34"/>
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="38" t="s">
+      <c r="T38" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="U38" s="35"/>
-      <c r="V38" s="35"/>
+      <c r="U38" s="37"/>
+      <c r="V38" s="37"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
@@ -1766,14 +4558,14 @@
       <c r="AL38" s="7"/>
       <c r="AM38" s="7"/>
       <c r="AN38" s="7"/>
-      <c r="AO38" s="68"/>
+      <c r="AO38" s="72"/>
       <c r="AP38" s="7"/>
       <c r="AQ38" s="7"/>
       <c r="AR38" s="7"/>
       <c r="AS38" s="7"/>
-      <c r="AT38" s="47"/>
-      <c r="AU38" s="35"/>
-      <c r="AV38" s="35"/>
+      <c r="AT38" s="51"/>
+      <c r="AU38" s="37"/>
+      <c r="AV38" s="37"/>
       <c r="AW38" s="7"/>
       <c r="AX38" s="7"/>
       <c r="AY38" s="7"/>
@@ -1796,37 +4588,37 @@
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
-      <c r="O39" s="32"/>
+      <c r="O39" s="34"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
-      <c r="T39" s="39"/>
-      <c r="U39" s="35"/>
-      <c r="V39" s="35"/>
+      <c r="T39" s="41"/>
+      <c r="U39" s="37"/>
+      <c r="V39" s="37"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="AB39" s="7"/>
-      <c r="AC39" s="45"/>
+      <c r="AC39" s="49"/>
       <c r="AD39" s="6"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="6"/>
-      <c r="AG39" s="40"/>
+      <c r="AG39" s="43"/>
       <c r="AH39" s="6"/>
-      <c r="AI39" s="40"/>
+      <c r="AI39" s="43"/>
       <c r="AJ39" s="6"/>
-      <c r="AK39" s="38"/>
+      <c r="AK39" s="40"/>
       <c r="AL39" s="7"/>
       <c r="AM39" s="7"/>
       <c r="AN39" s="7"/>
-      <c r="AO39" s="68"/>
+      <c r="AO39" s="72"/>
       <c r="AP39" s="7"/>
       <c r="AQ39" s="7"/>
       <c r="AR39" s="7"/>
       <c r="AS39" s="7"/>
-      <c r="AT39" s="47"/>
-      <c r="AU39" s="35"/>
-      <c r="AV39" s="35"/>
+      <c r="AT39" s="51"/>
+      <c r="AU39" s="37"/>
+      <c r="AV39" s="37"/>
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
@@ -1856,34 +4648,34 @@
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="35"/>
-      <c r="V40" s="35"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="37"/>
+      <c r="V40" s="37"/>
       <c r="W40" s="7"/>
       <c r="X40" s="7"/>
       <c r="AB40" s="7"/>
-      <c r="AC40" s="45"/>
+      <c r="AC40" s="49"/>
       <c r="AD40" s="6"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="6"/>
-      <c r="AG40" s="40"/>
+      <c r="AG40" s="43"/>
       <c r="AH40" s="6"/>
-      <c r="AI40" s="40"/>
+      <c r="AI40" s="43"/>
       <c r="AJ40" s="6"/>
-      <c r="AK40" s="38"/>
+      <c r="AK40" s="40"/>
       <c r="AL40" s="7"/>
       <c r="AM40" s="7"/>
       <c r="AN40" s="7"/>
-      <c r="AO40" s="69" t="s">
+      <c r="AO40" s="73" t="s">
         <v>14</v>
       </c>
       <c r="AP40" s="7"/>
       <c r="AQ40" s="7"/>
       <c r="AR40" s="7"/>
       <c r="AS40" s="7"/>
-      <c r="AT40" s="46"/>
-      <c r="AU40" s="35"/>
-      <c r="AV40" s="35"/>
+      <c r="AT40" s="50"/>
+      <c r="AU40" s="37"/>
+      <c r="AV40" s="37"/>
       <c r="AW40" s="7"/>
       <c r="AX40" s="7"/>
       <c r="AY40" s="7"/>
@@ -1913,32 +4705,32 @@
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
-      <c r="T41" s="28"/>
+      <c r="T41" s="30"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="AB41" s="7"/>
-      <c r="AC41" s="42"/>
+      <c r="AC41" s="46"/>
       <c r="AD41" s="6"/>
       <c r="AE41" s="3"/>
       <c r="AF41" s="6"/>
-      <c r="AG41" s="40"/>
+      <c r="AG41" s="43"/>
       <c r="AH41" s="6"/>
-      <c r="AI41" s="40"/>
+      <c r="AI41" s="43"/>
       <c r="AJ41" s="6"/>
-      <c r="AK41" s="40"/>
+      <c r="AK41" s="43"/>
       <c r="AL41" s="7"/>
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
-      <c r="AO41" s="70" t="s">
+      <c r="AO41" s="74" t="s">
         <v>15</v>
       </c>
       <c r="AP41" s="7"/>
       <c r="AQ41" s="7"/>
       <c r="AR41" s="7"/>
       <c r="AS41" s="7"/>
-      <c r="AT41" s="46"/>
+      <c r="AT41" s="50"/>
       <c r="AU41" s="7"/>
       <c r="AV41" s="7"/>
       <c r="AW41" s="7"/>
@@ -1968,30 +4760,30 @@
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
-      <c r="T42" s="28"/>
+      <c r="T42" s="30"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
       <c r="X42" s="7"/>
       <c r="AB42" s="7"/>
-      <c r="AC42" s="42"/>
+      <c r="AC42" s="46"/>
       <c r="AD42" s="6"/>
       <c r="AE42" s="3"/>
       <c r="AF42" s="6"/>
-      <c r="AG42" s="40"/>
+      <c r="AG42" s="43"/>
       <c r="AH42" s="6"/>
-      <c r="AI42" s="40"/>
+      <c r="AI42" s="43"/>
       <c r="AJ42" s="6"/>
-      <c r="AK42" s="40"/>
+      <c r="AK42" s="43"/>
       <c r="AL42" s="7"/>
       <c r="AM42" s="7"/>
       <c r="AN42" s="7"/>
-      <c r="AO42" s="70"/>
+      <c r="AO42" s="74"/>
       <c r="AP42" s="7"/>
       <c r="AQ42" s="7"/>
       <c r="AR42" s="7"/>
       <c r="AS42" s="7"/>
-      <c r="AT42" s="46"/>
+      <c r="AT42" s="50"/>
       <c r="AU42" s="7"/>
       <c r="AV42" s="7"/>
       <c r="AW42" s="7"/>
@@ -2023,34 +4815,34 @@
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
-      <c r="T43" s="28"/>
+      <c r="T43" s="30"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="AB43" s="7"/>
-      <c r="AC43" s="42"/>
+      <c r="AC43" s="46"/>
       <c r="AD43" s="6"/>
       <c r="AE43" s="3"/>
       <c r="AF43" s="6"/>
-      <c r="AG43" s="40"/>
+      <c r="AG43" s="43"/>
       <c r="AH43" s="6"/>
-      <c r="AI43" s="40"/>
+      <c r="AI43" s="43"/>
       <c r="AJ43" s="6"/>
-      <c r="AK43" s="40"/>
+      <c r="AK43" s="43"/>
       <c r="AL43" s="7"/>
       <c r="AM43" s="7"/>
       <c r="AN43" s="7"/>
-      <c r="AO43" s="71" t="s">
+      <c r="AO43" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="AP43" s="48" t="s">
+      <c r="AP43" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="AQ43" s="48"/>
-      <c r="AR43" s="48"/>
-      <c r="AS43" s="48"/>
-      <c r="AT43" s="46"/>
+      <c r="AQ43" s="52"/>
+      <c r="AR43" s="52"/>
+      <c r="AS43" s="52"/>
+      <c r="AT43" s="50"/>
       <c r="AU43" s="7"/>
       <c r="AV43" s="7"/>
       <c r="AW43" s="7"/>
@@ -2080,36 +4872,36 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
-      <c r="T44" s="28"/>
-      <c r="U44" s="29" t="s">
+      <c r="T44" s="30"/>
+      <c r="U44" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
-      <c r="X44" s="30"/>
+      <c r="V44" s="32"/>
+      <c r="W44" s="32"/>
+      <c r="X44" s="32"/>
       <c r="AB44" s="7"/>
-      <c r="AC44" s="42"/>
+      <c r="AC44" s="46"/>
       <c r="AD44" s="6"/>
       <c r="AE44" s="3"/>
       <c r="AF44" s="6"/>
-      <c r="AG44" s="40"/>
+      <c r="AG44" s="43"/>
       <c r="AH44" s="6"/>
-      <c r="AI44" s="40"/>
+      <c r="AI44" s="43"/>
       <c r="AJ44" s="6"/>
-      <c r="AK44" s="40"/>
+      <c r="AK44" s="43"/>
       <c r="AL44" s="7"/>
       <c r="AM44" s="7"/>
       <c r="AN44" s="7"/>
-      <c r="AO44" s="72"/>
-      <c r="AP44" s="48"/>
-      <c r="AQ44" s="48"/>
-      <c r="AR44" s="48"/>
-      <c r="AS44" s="48"/>
-      <c r="AT44" s="46"/>
-      <c r="AU44" s="30"/>
-      <c r="AV44" s="30"/>
-      <c r="AW44" s="30"/>
-      <c r="AX44" s="30"/>
+      <c r="AO44" s="76"/>
+      <c r="AP44" s="52"/>
+      <c r="AQ44" s="52"/>
+      <c r="AR44" s="52"/>
+      <c r="AS44" s="52"/>
+      <c r="AT44" s="50"/>
+      <c r="AU44" s="32"/>
+      <c r="AV44" s="32"/>
+      <c r="AW44" s="32"/>
+      <c r="AX44" s="32"/>
       <c r="AY44" s="7"/>
       <c r="AZ44" s="7"/>
       <c r="BA44" s="7"/>
@@ -2137,36 +4929,36 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
-      <c r="T45" s="28"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
-      <c r="X45" s="30"/>
+      <c r="T45" s="30"/>
+      <c r="U45" s="31"/>
+      <c r="V45" s="32"/>
+      <c r="W45" s="32"/>
+      <c r="X45" s="32"/>
       <c r="AB45" s="7"/>
-      <c r="AC45" s="42"/>
+      <c r="AC45" s="46"/>
       <c r="AD45" s="6"/>
       <c r="AE45" s="3"/>
       <c r="AF45" s="6"/>
-      <c r="AG45" s="40"/>
+      <c r="AG45" s="43"/>
       <c r="AH45" s="6"/>
-      <c r="AI45" s="40"/>
+      <c r="AI45" s="43"/>
       <c r="AJ45" s="6"/>
-      <c r="AK45" s="40"/>
+      <c r="AK45" s="43"/>
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
       <c r="AN45" s="7"/>
-      <c r="AO45" s="71" t="s">
+      <c r="AO45" s="75" t="s">
         <v>22</v>
       </c>
       <c r="AP45" s="7"/>
       <c r="AQ45" s="7"/>
       <c r="AR45" s="7"/>
       <c r="AS45" s="7"/>
-      <c r="AT45" s="46"/>
-      <c r="AU45" s="30"/>
-      <c r="AV45" s="30"/>
-      <c r="AW45" s="30"/>
-      <c r="AX45" s="30"/>
+      <c r="AT45" s="50"/>
+      <c r="AU45" s="32"/>
+      <c r="AV45" s="32"/>
+      <c r="AW45" s="32"/>
+      <c r="AX45" s="32"/>
       <c r="AY45" s="7"/>
       <c r="AZ45" s="7"/>
       <c r="BA45" s="7"/>
@@ -2202,15 +4994,15 @@
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="22" t="s">
+      <c r="T46" s="30"/>
+      <c r="U46" s="24" t="s">
         <v>32</v>
       </c>
       <c r="V46" s="16"/>
       <c r="W46" s="16"/>
       <c r="X46" s="7"/>
       <c r="AB46" s="7"/>
-      <c r="AC46" s="43">
+      <c r="AC46" s="47">
         <v>1654</v>
       </c>
       <c r="AD46" s="6"/>
@@ -2218,27 +5010,27 @@
         <v>1654</v>
       </c>
       <c r="AF46" s="6"/>
-      <c r="AG46" s="40">
+      <c r="AG46" s="43">
         <v>1654</v>
       </c>
       <c r="AH46" s="6"/>
-      <c r="AI46" s="40">
+      <c r="AI46" s="43">
         <v>1654</v>
       </c>
       <c r="AJ46" s="6"/>
-      <c r="AK46" s="40">
+      <c r="AK46" s="43">
         <v>1654</v>
       </c>
       <c r="AL46" s="7"/>
       <c r="AM46" s="7"/>
       <c r="AN46" s="7"/>
-      <c r="AO46" s="72"/>
+      <c r="AO46" s="76"/>
       <c r="AP46" s="7"/>
       <c r="AQ46" s="7"/>
       <c r="AR46" s="7"/>
       <c r="AS46" s="7"/>
-      <c r="AT46" s="46"/>
-      <c r="AU46" s="46"/>
+      <c r="AT46" s="50"/>
+      <c r="AU46" s="50"/>
       <c r="AV46" s="16"/>
       <c r="AW46" s="16"/>
       <c r="AX46" s="7"/>
@@ -2279,13 +5071,13 @@
       <c r="Q47" s="7"/>
       <c r="R47" s="7"/>
       <c r="S47" s="7"/>
-      <c r="T47" s="28"/>
+      <c r="T47" s="30"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
       <c r="AB47" s="7"/>
-      <c r="AC47" s="43" t="s">
+      <c r="AC47" s="47" t="s">
         <v>10</v>
       </c>
       <c r="AD47" s="6"/>
@@ -2293,28 +5085,28 @@
         <v>10</v>
       </c>
       <c r="AF47" s="6"/>
-      <c r="AG47" s="40" t="s">
+      <c r="AG47" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AH47" s="6"/>
-      <c r="AI47" s="40" t="s">
+      <c r="AI47" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AJ47" s="6"/>
-      <c r="AK47" s="40" t="s">
+      <c r="AK47" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AL47" s="7"/>
       <c r="AM47" s="7"/>
       <c r="AN47" s="7"/>
-      <c r="AO47" s="70" t="s">
+      <c r="AO47" s="74" t="s">
         <v>21</v>
       </c>
       <c r="AP47" s="7"/>
       <c r="AQ47" s="7"/>
       <c r="AR47" s="7"/>
       <c r="AS47" s="7"/>
-      <c r="AT47" s="46"/>
+      <c r="AT47" s="50"/>
       <c r="AU47" s="7"/>
       <c r="AV47" s="7"/>
       <c r="AW47" s="7"/>
@@ -2350,19 +5142,19 @@
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
       <c r="O48" s="10"/>
-      <c r="P48" s="25" t="s">
+      <c r="P48" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="26"/>
-      <c r="S48" s="27"/>
-      <c r="T48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="30"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
       <c r="X48" s="7"/>
       <c r="AB48" s="7"/>
-      <c r="AC48" s="43" t="s">
+      <c r="AC48" s="47" t="s">
         <v>11</v>
       </c>
       <c r="AD48" s="6"/>
@@ -2370,26 +5162,26 @@
         <v>11</v>
       </c>
       <c r="AF48" s="6"/>
-      <c r="AG48" s="40" t="s">
+      <c r="AG48" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AH48" s="6"/>
-      <c r="AI48" s="40" t="s">
+      <c r="AI48" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AJ48" s="6"/>
-      <c r="AK48" s="40" t="s">
+      <c r="AK48" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AL48" s="7"/>
       <c r="AM48" s="7"/>
       <c r="AN48" s="7"/>
-      <c r="AO48" s="70"/>
-      <c r="AP48" s="25"/>
-      <c r="AQ48" s="26"/>
-      <c r="AR48" s="26"/>
-      <c r="AS48" s="27"/>
-      <c r="AT48" s="46"/>
+      <c r="AO48" s="74"/>
+      <c r="AP48" s="27"/>
+      <c r="AQ48" s="28"/>
+      <c r="AR48" s="28"/>
+      <c r="AS48" s="29"/>
+      <c r="AT48" s="50"/>
       <c r="AU48" s="7"/>
       <c r="AV48" s="7"/>
       <c r="AW48" s="7"/>
@@ -2417,42 +5209,42 @@
       <c r="O49" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="26"/>
-      <c r="Q49" s="26"/>
-      <c r="R49" s="26"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="24" t="s">
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="V49" s="31"/>
-      <c r="W49" s="31"/>
-      <c r="X49" s="31"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="33"/>
       <c r="AB49" s="7"/>
-      <c r="AC49" s="42"/>
+      <c r="AC49" s="46"/>
       <c r="AD49" s="6"/>
       <c r="AE49" s="3"/>
       <c r="AF49" s="6"/>
-      <c r="AG49" s="40"/>
+      <c r="AG49" s="43"/>
       <c r="AH49" s="6"/>
-      <c r="AI49" s="40"/>
+      <c r="AI49" s="43"/>
       <c r="AJ49" s="6"/>
-      <c r="AK49" s="40"/>
+      <c r="AK49" s="43"/>
       <c r="AL49" s="7"/>
       <c r="AM49" s="7"/>
       <c r="AN49" s="7"/>
-      <c r="AO49" s="73" t="s">
+      <c r="AO49" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="AP49" s="26"/>
-      <c r="AQ49" s="26"/>
-      <c r="AR49" s="26"/>
-      <c r="AS49" s="27"/>
-      <c r="AT49" s="46"/>
-      <c r="AU49" s="25"/>
-      <c r="AV49" s="31"/>
-      <c r="AW49" s="31"/>
-      <c r="AX49" s="31"/>
+      <c r="AP49" s="28"/>
+      <c r="AQ49" s="28"/>
+      <c r="AR49" s="28"/>
+      <c r="AS49" s="29"/>
+      <c r="AT49" s="50"/>
+      <c r="AU49" s="27"/>
+      <c r="AV49" s="33"/>
+      <c r="AW49" s="33"/>
+      <c r="AX49" s="33"/>
       <c r="AY49" s="7"/>
       <c r="AZ49" s="7"/>
       <c r="BA49" s="7"/>
@@ -2478,34 +5270,34 @@
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
-      <c r="T50" s="19"/>
-      <c r="U50" s="24"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
-      <c r="X50" s="31"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="26"/>
+      <c r="V50" s="33"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="33"/>
       <c r="AB50" s="7"/>
-      <c r="AC50" s="42"/>
+      <c r="AC50" s="46"/>
       <c r="AD50" s="6"/>
       <c r="AE50" s="3"/>
       <c r="AF50" s="6"/>
-      <c r="AG50" s="40"/>
+      <c r="AG50" s="43"/>
       <c r="AH50" s="6"/>
-      <c r="AI50" s="40"/>
+      <c r="AI50" s="43"/>
       <c r="AJ50" s="6"/>
-      <c r="AK50" s="40"/>
+      <c r="AK50" s="43"/>
       <c r="AL50" s="7"/>
       <c r="AM50" s="7"/>
       <c r="AN50" s="7"/>
-      <c r="AO50" s="73"/>
+      <c r="AO50" s="77"/>
       <c r="AP50" s="7"/>
       <c r="AQ50" s="7"/>
       <c r="AR50" s="7"/>
       <c r="AS50" s="7"/>
-      <c r="AT50" s="27"/>
-      <c r="AU50" s="25"/>
-      <c r="AV50" s="31"/>
-      <c r="AW50" s="31"/>
-      <c r="AX50" s="31"/>
+      <c r="AT50" s="29"/>
+      <c r="AU50" s="27"/>
+      <c r="AV50" s="33"/>
+      <c r="AW50" s="33"/>
+      <c r="AX50" s="33"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="7"/>
       <c r="BA50" s="7"/>
@@ -2533,38 +5325,38 @@
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
       <c r="S51" s="7"/>
-      <c r="T51" s="17"/>
-      <c r="U51" s="24"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31"/>
-      <c r="X51" s="31"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="26"/>
+      <c r="V51" s="33"/>
+      <c r="W51" s="33"/>
+      <c r="X51" s="33"/>
       <c r="AB51" s="7"/>
-      <c r="AC51" s="42"/>
+      <c r="AC51" s="46"/>
       <c r="AD51" s="6"/>
       <c r="AE51" s="3"/>
       <c r="AF51" s="6"/>
-      <c r="AG51" s="40"/>
+      <c r="AG51" s="43"/>
       <c r="AH51" s="6"/>
-      <c r="AI51" s="40"/>
+      <c r="AI51" s="43"/>
       <c r="AJ51" s="6"/>
-      <c r="AK51" s="40"/>
+      <c r="AK51" s="43"/>
       <c r="AL51" s="7"/>
       <c r="AM51" s="7"/>
       <c r="AN51" s="7"/>
-      <c r="AO51" s="74" t="s">
+      <c r="AO51" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="AP51" s="48" t="s">
+      <c r="AP51" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="AQ51" s="35"/>
-      <c r="AR51" s="35"/>
-      <c r="AS51" s="35"/>
-      <c r="AT51" s="46"/>
-      <c r="AU51" s="25"/>
-      <c r="AV51" s="31"/>
-      <c r="AW51" s="31"/>
-      <c r="AX51" s="31"/>
+      <c r="AQ51" s="37"/>
+      <c r="AR51" s="37"/>
+      <c r="AS51" s="37"/>
+      <c r="AT51" s="50"/>
+      <c r="AU51" s="27"/>
+      <c r="AV51" s="33"/>
+      <c r="AW51" s="33"/>
+      <c r="AX51" s="33"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="7"/>
       <c r="BA51" s="7"/>
@@ -2590,36 +5382,36 @@
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="24" t="s">
+      <c r="T52" s="18"/>
+      <c r="U52" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="V52" s="31"/>
-      <c r="W52" s="31"/>
-      <c r="X52" s="31"/>
+      <c r="V52" s="33"/>
+      <c r="W52" s="33"/>
+      <c r="X52" s="33"/>
       <c r="AB52" s="7"/>
-      <c r="AC52" s="42"/>
+      <c r="AC52" s="46"/>
       <c r="AD52" s="6"/>
       <c r="AE52" s="3"/>
       <c r="AF52" s="6"/>
-      <c r="AG52" s="40"/>
+      <c r="AG52" s="43"/>
       <c r="AH52" s="6"/>
-      <c r="AI52" s="40"/>
+      <c r="AI52" s="43"/>
       <c r="AJ52" s="6"/>
-      <c r="AK52" s="40"/>
+      <c r="AK52" s="43"/>
       <c r="AL52" s="7"/>
       <c r="AM52" s="7"/>
       <c r="AN52" s="7"/>
-      <c r="AO52" s="75"/>
-      <c r="AP52" s="48"/>
-      <c r="AQ52" s="35"/>
-      <c r="AR52" s="35"/>
-      <c r="AS52" s="35"/>
-      <c r="AT52" s="46"/>
-      <c r="AU52" s="25"/>
-      <c r="AV52" s="31"/>
-      <c r="AW52" s="31"/>
-      <c r="AX52" s="31"/>
+      <c r="AO52" s="79"/>
+      <c r="AP52" s="52"/>
+      <c r="AQ52" s="37"/>
+      <c r="AR52" s="37"/>
+      <c r="AS52" s="37"/>
+      <c r="AT52" s="50"/>
+      <c r="AU52" s="27"/>
+      <c r="AV52" s="33"/>
+      <c r="AW52" s="33"/>
+      <c r="AX52" s="33"/>
       <c r="AY52" s="7"/>
       <c r="AZ52" s="7"/>
       <c r="BA52" s="7"/>
@@ -2647,36 +5439,36 @@
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
       <c r="S53" s="7"/>
-      <c r="T53" s="17"/>
-      <c r="U53" s="24"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
-      <c r="X53" s="31"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="26"/>
+      <c r="V53" s="33"/>
+      <c r="W53" s="33"/>
+      <c r="X53" s="33"/>
       <c r="AB53" s="7"/>
-      <c r="AC53" s="42"/>
+      <c r="AC53" s="46"/>
       <c r="AD53" s="6"/>
       <c r="AE53" s="3"/>
       <c r="AF53" s="6"/>
-      <c r="AG53" s="40"/>
+      <c r="AG53" s="43"/>
       <c r="AH53" s="6"/>
-      <c r="AI53" s="40"/>
+      <c r="AI53" s="43"/>
       <c r="AJ53" s="6"/>
-      <c r="AK53" s="40"/>
+      <c r="AK53" s="43"/>
       <c r="AL53" s="7"/>
       <c r="AM53" s="7"/>
       <c r="AN53" s="7"/>
-      <c r="AO53" s="74" t="s">
+      <c r="AO53" s="78" t="s">
         <v>16</v>
       </c>
       <c r="AP53" s="7"/>
       <c r="AQ53" s="7"/>
       <c r="AR53" s="7"/>
       <c r="AS53" s="7"/>
-      <c r="AT53" s="46"/>
-      <c r="AU53" s="25"/>
-      <c r="AV53" s="31"/>
-      <c r="AW53" s="31"/>
-      <c r="AX53" s="31"/>
+      <c r="AT53" s="50"/>
+      <c r="AU53" s="27"/>
+      <c r="AV53" s="33"/>
+      <c r="AW53" s="33"/>
+      <c r="AX53" s="33"/>
       <c r="AY53" s="7"/>
       <c r="AZ53" s="7"/>
       <c r="BA53" s="7"/>
@@ -2702,34 +5494,34 @@
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
-      <c r="T54" s="17"/>
-      <c r="U54" s="24"/>
-      <c r="V54" s="31"/>
-      <c r="W54" s="31"/>
-      <c r="X54" s="31"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="26"/>
+      <c r="V54" s="33"/>
+      <c r="W54" s="33"/>
+      <c r="X54" s="33"/>
       <c r="AB54" s="7"/>
-      <c r="AC54" s="44"/>
+      <c r="AC54" s="48"/>
       <c r="AD54" s="6"/>
       <c r="AE54" s="5"/>
       <c r="AF54" s="6"/>
-      <c r="AG54" s="41"/>
+      <c r="AG54" s="44"/>
       <c r="AH54" s="6"/>
-      <c r="AI54" s="41"/>
+      <c r="AI54" s="44"/>
       <c r="AJ54" s="6"/>
-      <c r="AK54" s="41"/>
+      <c r="AK54" s="44"/>
       <c r="AL54" s="7"/>
       <c r="AM54" s="7"/>
       <c r="AN54" s="7"/>
-      <c r="AO54" s="75"/>
+      <c r="AO54" s="79"/>
       <c r="AP54" s="7"/>
       <c r="AQ54" s="7"/>
       <c r="AR54" s="7"/>
       <c r="AS54" s="7"/>
-      <c r="AT54" s="46"/>
-      <c r="AU54" s="25"/>
-      <c r="AV54" s="31"/>
-      <c r="AW54" s="31"/>
-      <c r="AX54" s="31"/>
+      <c r="AT54" s="50"/>
+      <c r="AU54" s="27"/>
+      <c r="AV54" s="33"/>
+      <c r="AW54" s="33"/>
+      <c r="AX54" s="33"/>
       <c r="AY54" s="7"/>
       <c r="AZ54" s="7"/>
       <c r="BA54" s="7"/>
@@ -2757,7 +5549,7 @@
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
       <c r="S55" s="7"/>
-      <c r="T55" s="18"/>
+      <c r="T55" s="19"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
       <c r="W55" s="7"/>
@@ -2775,14 +5567,14 @@
       <c r="AL55" s="7"/>
       <c r="AM55" s="7"/>
       <c r="AN55" s="7"/>
-      <c r="AO55" s="76" t="s">
+      <c r="AO55" s="80" t="s">
         <v>17</v>
       </c>
       <c r="AP55" s="7"/>
       <c r="AQ55" s="7"/>
       <c r="AR55" s="7"/>
       <c r="AS55" s="7"/>
-      <c r="AT55" s="46"/>
+      <c r="AT55" s="50"/>
       <c r="AU55" s="7"/>
       <c r="AV55" s="7"/>
       <c r="AW55" s="7"/>
@@ -2830,13 +5622,13 @@
       <c r="AL56" s="7"/>
       <c r="AM56" s="7"/>
       <c r="AN56" s="7"/>
-      <c r="AO56" s="77"/>
-      <c r="AP56" s="48" t="s">
+      <c r="AO56" s="81"/>
+      <c r="AP56" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="AQ56" s="23"/>
-      <c r="AR56" s="23"/>
-      <c r="AS56" s="23"/>
+      <c r="AQ56" s="25"/>
+      <c r="AR56" s="25"/>
+      <c r="AS56" s="25"/>
       <c r="AT56" s="7"/>
       <c r="AU56" s="7"/>
       <c r="AV56" s="7"/>
@@ -2907,13 +5699,13 @@
       <c r="AL57" s="7"/>
       <c r="AM57" s="7"/>
       <c r="AN57" s="7"/>
-      <c r="AO57" s="76" t="s">
+      <c r="AO57" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="AP57" s="26"/>
-      <c r="AQ57" s="23"/>
-      <c r="AR57" s="23"/>
-      <c r="AS57" s="23"/>
+      <c r="AP57" s="28"/>
+      <c r="AQ57" s="25"/>
+      <c r="AR57" s="25"/>
+      <c r="AS57" s="25"/>
       <c r="AT57" s="7"/>
       <c r="AU57" s="7"/>
       <c r="AV57" s="7"/>
@@ -2950,19 +5742,19 @@
       <c r="W58" s="7"/>
       <c r="X58" s="7"/>
       <c r="AB58" s="7"/>
-      <c r="AC58" s="40"/>
+      <c r="AC58" s="43"/>
       <c r="AD58" s="6"/>
-      <c r="AE58" s="40"/>
+      <c r="AE58" s="43"/>
       <c r="AF58" s="6"/>
-      <c r="AG58" s="40"/>
+      <c r="AG58" s="43"/>
       <c r="AH58" s="6"/>
-      <c r="AI58" s="40"/>
+      <c r="AI58" s="43"/>
       <c r="AJ58" s="6"/>
-      <c r="AK58" s="40"/>
+      <c r="AK58" s="43"/>
       <c r="AL58" s="7"/>
       <c r="AM58" s="7"/>
       <c r="AN58" s="7"/>
-      <c r="AO58" s="78"/>
+      <c r="AO58" s="82"/>
       <c r="AP58" s="7"/>
       <c r="AQ58" s="7"/>
       <c r="AR58" s="7"/>
@@ -3003,15 +5795,15 @@
       <c r="W59" s="7"/>
       <c r="X59" s="7"/>
       <c r="AB59" s="7"/>
-      <c r="AC59" s="40"/>
+      <c r="AC59" s="43"/>
       <c r="AD59" s="6"/>
-      <c r="AE59" s="40"/>
+      <c r="AE59" s="43"/>
       <c r="AF59" s="6"/>
-      <c r="AG59" s="40"/>
+      <c r="AG59" s="43"/>
       <c r="AH59" s="6"/>
-      <c r="AI59" s="40"/>
+      <c r="AI59" s="43"/>
       <c r="AJ59" s="6"/>
-      <c r="AK59" s="40"/>
+      <c r="AK59" s="43"/>
       <c r="AL59" s="7"/>
       <c r="AM59" s="7"/>
       <c r="AN59" s="7"/>
@@ -3044,42 +5836,42 @@
       <c r="K60" s="3"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-      <c r="N60" s="20" t="s">
+      <c r="N60" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="O60" s="20"/>
-      <c r="P60" s="20"/>
+      <c r="O60" s="22"/>
+      <c r="P60" s="22"/>
       <c r="Q60" s="7"/>
-      <c r="R60" s="20" t="s">
+      <c r="R60" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="S60" s="20"/>
-      <c r="T60" s="20"/>
-      <c r="U60" s="20"/>
-      <c r="V60" s="20"/>
+      <c r="S60" s="22"/>
+      <c r="T60" s="22"/>
+      <c r="U60" s="22"/>
+      <c r="V60" s="22"/>
       <c r="W60" s="7"/>
       <c r="X60" s="7"/>
       <c r="AB60" s="7"/>
-      <c r="AC60" s="40"/>
+      <c r="AC60" s="43"/>
       <c r="AD60" s="6"/>
-      <c r="AE60" s="40"/>
+      <c r="AE60" s="43"/>
       <c r="AF60" s="6"/>
-      <c r="AG60" s="40"/>
+      <c r="AG60" s="43"/>
       <c r="AH60" s="6"/>
-      <c r="AI60" s="40"/>
+      <c r="AI60" s="43"/>
       <c r="AJ60" s="6"/>
-      <c r="AK60" s="40"/>
+      <c r="AK60" s="43"/>
       <c r="AL60" s="7"/>
       <c r="AM60" s="7"/>
-      <c r="AN60" s="36"/>
-      <c r="AO60" s="36"/>
-      <c r="AP60" s="36"/>
+      <c r="AN60" s="38"/>
+      <c r="AO60" s="38"/>
+      <c r="AP60" s="38"/>
       <c r="AQ60" s="7"/>
-      <c r="AR60" s="36"/>
-      <c r="AS60" s="36"/>
-      <c r="AT60" s="36"/>
-      <c r="AU60" s="36"/>
-      <c r="AV60" s="36"/>
+      <c r="AR60" s="38"/>
+      <c r="AS60" s="38"/>
+      <c r="AT60" s="38"/>
+      <c r="AU60" s="38"/>
+      <c r="AV60" s="38"/>
       <c r="AW60" s="7"/>
       <c r="AX60" s="7"/>
       <c r="AY60" s="7"/>
@@ -3101,42 +5893,42 @@
       <c r="K61" s="3"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-      <c r="N61" s="20"/>
-      <c r="O61" s="20"/>
-      <c r="P61" s="20"/>
+      <c r="N61" s="22"/>
+      <c r="O61" s="22"/>
+      <c r="P61" s="22"/>
       <c r="Q61" s="7"/>
-      <c r="R61" s="20"/>
-      <c r="S61" s="20"/>
-      <c r="T61" s="20"/>
-      <c r="U61" s="20"/>
-      <c r="V61" s="20"/>
+      <c r="R61" s="22"/>
+      <c r="S61" s="22"/>
+      <c r="T61" s="22"/>
+      <c r="U61" s="22"/>
+      <c r="V61" s="22"/>
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
       <c r="AB61" s="7"/>
-      <c r="AC61" s="40"/>
+      <c r="AC61" s="43"/>
       <c r="AD61" s="6"/>
-      <c r="AE61" s="40"/>
+      <c r="AE61" s="43"/>
       <c r="AF61" s="6"/>
-      <c r="AG61" s="40"/>
+      <c r="AG61" s="43"/>
       <c r="AH61" s="6"/>
-      <c r="AI61" s="40"/>
+      <c r="AI61" s="43"/>
       <c r="AJ61" s="6"/>
-      <c r="AK61" s="40"/>
+      <c r="AK61" s="43"/>
       <c r="AL61" s="7"/>
       <c r="AM61" s="7"/>
-      <c r="AN61" s="50" t="s">
+      <c r="AN61" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="AO61" s="51"/>
-      <c r="AP61" s="51"/>
-      <c r="AQ61" s="51"/>
-      <c r="AR61" s="51"/>
-      <c r="AS61" s="51"/>
-      <c r="AT61" s="51"/>
-      <c r="AU61" s="51"/>
-      <c r="AV61" s="51"/>
-      <c r="AW61" s="51"/>
-      <c r="AX61" s="52"/>
+      <c r="AO61" s="55"/>
+      <c r="AP61" s="55"/>
+      <c r="AQ61" s="55"/>
+      <c r="AR61" s="55"/>
+      <c r="AS61" s="55"/>
+      <c r="AT61" s="55"/>
+      <c r="AU61" s="55"/>
+      <c r="AV61" s="55"/>
+      <c r="AW61" s="55"/>
+      <c r="AX61" s="56"/>
       <c r="AY61" s="7"/>
       <c r="AZ61" s="7"/>
       <c r="BA61" s="7"/>
@@ -3160,38 +5952,38 @@
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
       <c r="Q62" s="7"/>
-      <c r="R62" s="37" t="s">
+      <c r="R62" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="S62" s="37"/>
-      <c r="T62" s="37"/>
-      <c r="U62" s="37"/>
-      <c r="V62" s="37"/>
+      <c r="S62" s="39"/>
+      <c r="T62" s="39"/>
+      <c r="U62" s="39"/>
+      <c r="V62" s="39"/>
       <c r="W62" s="7"/>
       <c r="X62" s="7"/>
       <c r="AB62" s="7"/>
-      <c r="AC62" s="40"/>
+      <c r="AC62" s="43"/>
       <c r="AD62" s="6"/>
-      <c r="AE62" s="40"/>
+      <c r="AE62" s="43"/>
       <c r="AF62" s="6"/>
-      <c r="AG62" s="40"/>
+      <c r="AG62" s="43"/>
       <c r="AH62" s="6"/>
-      <c r="AI62" s="40"/>
+      <c r="AI62" s="43"/>
       <c r="AJ62" s="6"/>
-      <c r="AK62" s="40"/>
+      <c r="AK62" s="43"/>
       <c r="AL62" s="7"/>
       <c r="AM62" s="7"/>
-      <c r="AN62" s="53"/>
-      <c r="AO62" s="49"/>
-      <c r="AP62" s="49"/>
-      <c r="AQ62" s="49"/>
-      <c r="AR62" s="49"/>
-      <c r="AS62" s="49"/>
-      <c r="AT62" s="49"/>
-      <c r="AU62" s="49"/>
-      <c r="AV62" s="49"/>
-      <c r="AW62" s="49"/>
-      <c r="AX62" s="54"/>
+      <c r="AN62" s="57"/>
+      <c r="AO62" s="53"/>
+      <c r="AP62" s="53"/>
+      <c r="AQ62" s="53"/>
+      <c r="AR62" s="53"/>
+      <c r="AS62" s="53"/>
+      <c r="AT62" s="53"/>
+      <c r="AU62" s="53"/>
+      <c r="AV62" s="53"/>
+      <c r="AW62" s="53"/>
+      <c r="AX62" s="58"/>
       <c r="AY62" s="7"/>
       <c r="AZ62" s="7"/>
       <c r="BA62" s="7"/>
@@ -3223,30 +6015,30 @@
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
       <c r="AB63" s="7"/>
-      <c r="AC63" s="40"/>
+      <c r="AC63" s="43"/>
       <c r="AD63" s="6"/>
-      <c r="AE63" s="40"/>
+      <c r="AE63" s="43"/>
       <c r="AF63" s="6"/>
-      <c r="AG63" s="40"/>
+      <c r="AG63" s="43"/>
       <c r="AH63" s="6"/>
-      <c r="AI63" s="40"/>
+      <c r="AI63" s="43"/>
       <c r="AJ63" s="6"/>
-      <c r="AK63" s="40"/>
+      <c r="AK63" s="43"/>
       <c r="AL63" s="7"/>
       <c r="AM63" s="7"/>
-      <c r="AN63" s="61" t="s">
+      <c r="AN63" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="AO63" s="62"/>
-      <c r="AP63" s="62"/>
-      <c r="AQ63" s="62"/>
-      <c r="AR63" s="62"/>
-      <c r="AS63" s="62"/>
-      <c r="AT63" s="62"/>
-      <c r="AU63" s="62"/>
-      <c r="AV63" s="62"/>
-      <c r="AW63" s="62"/>
-      <c r="AX63" s="63"/>
+      <c r="AO63" s="66"/>
+      <c r="AP63" s="66"/>
+      <c r="AQ63" s="66"/>
+      <c r="AR63" s="66"/>
+      <c r="AS63" s="66"/>
+      <c r="AT63" s="66"/>
+      <c r="AU63" s="66"/>
+      <c r="AV63" s="66"/>
+      <c r="AW63" s="66"/>
+      <c r="AX63" s="67"/>
       <c r="AY63" s="7"/>
       <c r="AZ63" s="7"/>
       <c r="BA63" s="7"/>
@@ -3288,45 +6080,45 @@
       <c r="W64" s="7"/>
       <c r="X64" s="7"/>
       <c r="AB64" s="7"/>
-      <c r="AC64" s="40">
+      <c r="AC64" s="43">
         <v>1654</v>
       </c>
       <c r="AD64" s="6"/>
-      <c r="AE64" s="40">
+      <c r="AE64" s="43">
         <v>1654</v>
       </c>
       <c r="AF64" s="6"/>
-      <c r="AG64" s="40">
+      <c r="AG64" s="43">
         <v>1654</v>
       </c>
       <c r="AH64" s="6"/>
-      <c r="AI64" s="40">
+      <c r="AI64" s="43">
         <v>1654</v>
       </c>
       <c r="AJ64" s="6"/>
-      <c r="AK64" s="40">
+      <c r="AK64" s="43">
         <v>1654</v>
       </c>
       <c r="AL64" s="7"/>
       <c r="AM64" s="7"/>
-      <c r="AN64" s="61"/>
-      <c r="AO64" s="62"/>
-      <c r="AP64" s="62"/>
-      <c r="AQ64" s="62"/>
-      <c r="AR64" s="62"/>
-      <c r="AS64" s="62"/>
-      <c r="AT64" s="62"/>
-      <c r="AU64" s="62"/>
-      <c r="AV64" s="62"/>
-      <c r="AW64" s="62"/>
-      <c r="AX64" s="63"/>
+      <c r="AN64" s="65"/>
+      <c r="AO64" s="66"/>
+      <c r="AP64" s="66"/>
+      <c r="AQ64" s="66"/>
+      <c r="AR64" s="66"/>
+      <c r="AS64" s="66"/>
+      <c r="AT64" s="66"/>
+      <c r="AU64" s="66"/>
+      <c r="AV64" s="66"/>
+      <c r="AW64" s="66"/>
+      <c r="AX64" s="67"/>
       <c r="AY64" s="7"/>
       <c r="AZ64" s="7"/>
       <c r="BA64" s="7"/>
       <c r="BB64" s="7"/>
       <c r="BC64" s="7"/>
     </row>
-    <row r="65" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:84" x14ac:dyDescent="0.3">
       <c r="B65" s="7"/>
       <c r="C65" s="3" t="s">
         <v>10</v>
@@ -3361,47 +6153,47 @@
       <c r="W65" s="7"/>
       <c r="X65" s="7"/>
       <c r="AB65" s="7"/>
-      <c r="AC65" s="40" t="s">
+      <c r="AC65" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AD65" s="6"/>
-      <c r="AE65" s="40" t="s">
+      <c r="AE65" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AF65" s="6"/>
-      <c r="AG65" s="40" t="s">
+      <c r="AG65" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AH65" s="6"/>
-      <c r="AI65" s="40" t="s">
+      <c r="AI65" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AJ65" s="6"/>
-      <c r="AK65" s="40" t="s">
+      <c r="AK65" s="43" t="s">
         <v>10</v>
       </c>
       <c r="AL65" s="7"/>
       <c r="AM65" s="7"/>
-      <c r="AN65" s="55" t="s">
+      <c r="AN65" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="AO65" s="56"/>
-      <c r="AP65" s="56"/>
-      <c r="AQ65" s="56"/>
-      <c r="AR65" s="56"/>
-      <c r="AS65" s="56"/>
-      <c r="AT65" s="56"/>
-      <c r="AU65" s="56"/>
-      <c r="AV65" s="56"/>
-      <c r="AW65" s="56"/>
-      <c r="AX65" s="57"/>
+      <c r="AO65" s="60"/>
+      <c r="AP65" s="60"/>
+      <c r="AQ65" s="60"/>
+      <c r="AR65" s="60"/>
+      <c r="AS65" s="60"/>
+      <c r="AT65" s="60"/>
+      <c r="AU65" s="60"/>
+      <c r="AV65" s="60"/>
+      <c r="AW65" s="60"/>
+      <c r="AX65" s="61"/>
       <c r="AY65" s="7"/>
       <c r="AZ65" s="7"/>
       <c r="BA65" s="7"/>
       <c r="BB65" s="7"/>
       <c r="BC65" s="7"/>
     </row>
-    <row r="66" spans="2:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:84" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="7"/>
       <c r="C66" s="3" t="s">
         <v>11</v>
@@ -3436,45 +6228,45 @@
       <c r="W66" s="7"/>
       <c r="X66" s="7"/>
       <c r="AB66" s="7"/>
-      <c r="AC66" s="40" t="s">
+      <c r="AC66" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AD66" s="6"/>
-      <c r="AE66" s="40" t="s">
+      <c r="AE66" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AF66" s="6"/>
-      <c r="AG66" s="40" t="s">
+      <c r="AG66" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AH66" s="6"/>
-      <c r="AI66" s="40" t="s">
+      <c r="AI66" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AJ66" s="6"/>
-      <c r="AK66" s="40" t="s">
+      <c r="AK66" s="43" t="s">
         <v>11</v>
       </c>
       <c r="AL66" s="7"/>
       <c r="AM66" s="7"/>
-      <c r="AN66" s="58"/>
-      <c r="AO66" s="59"/>
-      <c r="AP66" s="59"/>
-      <c r="AQ66" s="59"/>
-      <c r="AR66" s="59"/>
-      <c r="AS66" s="59"/>
-      <c r="AT66" s="59"/>
-      <c r="AU66" s="59"/>
-      <c r="AV66" s="59"/>
-      <c r="AW66" s="59"/>
-      <c r="AX66" s="60"/>
+      <c r="AN66" s="62"/>
+      <c r="AO66" s="63"/>
+      <c r="AP66" s="63"/>
+      <c r="AQ66" s="63"/>
+      <c r="AR66" s="63"/>
+      <c r="AS66" s="63"/>
+      <c r="AT66" s="63"/>
+      <c r="AU66" s="63"/>
+      <c r="AV66" s="63"/>
+      <c r="AW66" s="63"/>
+      <c r="AX66" s="64"/>
       <c r="AY66" s="7"/>
       <c r="AZ66" s="7"/>
       <c r="BA66" s="7"/>
       <c r="BB66" s="7"/>
       <c r="BC66" s="7"/>
     </row>
-    <row r="67" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:84" x14ac:dyDescent="0.3">
       <c r="B67" s="7"/>
       <c r="C67" s="3"/>
       <c r="D67" s="6"/>
@@ -3499,15 +6291,15 @@
       <c r="W67" s="7"/>
       <c r="X67" s="7"/>
       <c r="AB67" s="7"/>
-      <c r="AC67" s="40"/>
+      <c r="AC67" s="43"/>
       <c r="AD67" s="6"/>
-      <c r="AE67" s="40"/>
+      <c r="AE67" s="43"/>
       <c r="AF67" s="6"/>
-      <c r="AG67" s="40"/>
+      <c r="AG67" s="43"/>
       <c r="AH67" s="6"/>
-      <c r="AI67" s="40"/>
+      <c r="AI67" s="43"/>
       <c r="AJ67" s="6"/>
-      <c r="AK67" s="40"/>
+      <c r="AK67" s="43"/>
       <c r="AL67" s="7"/>
       <c r="AM67" s="7"/>
       <c r="AN67" s="7"/>
@@ -3527,7 +6319,7 @@
       <c r="BB67" s="7"/>
       <c r="BC67" s="7"/>
     </row>
-    <row r="68" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:84" x14ac:dyDescent="0.3">
       <c r="B68" s="7"/>
       <c r="C68" s="3"/>
       <c r="D68" s="6"/>
@@ -3552,15 +6344,15 @@
       <c r="W68" s="7"/>
       <c r="X68" s="7"/>
       <c r="AB68" s="7"/>
-      <c r="AC68" s="40"/>
+      <c r="AC68" s="43"/>
       <c r="AD68" s="6"/>
-      <c r="AE68" s="40"/>
+      <c r="AE68" s="43"/>
       <c r="AF68" s="6"/>
-      <c r="AG68" s="40"/>
+      <c r="AG68" s="43"/>
       <c r="AH68" s="6"/>
-      <c r="AI68" s="40"/>
+      <c r="AI68" s="43"/>
       <c r="AJ68" s="6"/>
-      <c r="AK68" s="40"/>
+      <c r="AK68" s="43"/>
       <c r="AL68" s="7"/>
       <c r="AM68" s="7"/>
       <c r="AN68" s="7"/>
@@ -3580,7 +6372,7 @@
       <c r="BB68" s="7"/>
       <c r="BC68" s="7"/>
     </row>
-    <row r="69" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:84" x14ac:dyDescent="0.3">
       <c r="B69" s="7"/>
       <c r="C69" s="3"/>
       <c r="D69" s="6"/>
@@ -3605,15 +6397,15 @@
       <c r="W69" s="7"/>
       <c r="X69" s="7"/>
       <c r="AB69" s="7"/>
-      <c r="AC69" s="40"/>
+      <c r="AC69" s="43"/>
       <c r="AD69" s="6"/>
-      <c r="AE69" s="40"/>
+      <c r="AE69" s="43"/>
       <c r="AF69" s="6"/>
-      <c r="AG69" s="40"/>
+      <c r="AG69" s="43"/>
       <c r="AH69" s="6"/>
-      <c r="AI69" s="40"/>
+      <c r="AI69" s="43"/>
       <c r="AJ69" s="6"/>
-      <c r="AK69" s="40"/>
+      <c r="AK69" s="43"/>
       <c r="AL69" s="7"/>
       <c r="AM69" s="7"/>
       <c r="AN69" s="7"/>
@@ -3633,7 +6425,7 @@
       <c r="BB69" s="7"/>
       <c r="BC69" s="7"/>
     </row>
-    <row r="70" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:84" x14ac:dyDescent="0.3">
       <c r="B70" s="7"/>
       <c r="C70" s="3"/>
       <c r="D70" s="6"/>
@@ -3658,15 +6450,15 @@
       <c r="W70" s="7"/>
       <c r="X70" s="7"/>
       <c r="AB70" s="7"/>
-      <c r="AC70" s="40"/>
+      <c r="AC70" s="43"/>
       <c r="AD70" s="6"/>
-      <c r="AE70" s="40"/>
+      <c r="AE70" s="43"/>
       <c r="AF70" s="6"/>
-      <c r="AG70" s="40"/>
+      <c r="AG70" s="43"/>
       <c r="AH70" s="6"/>
-      <c r="AI70" s="40"/>
+      <c r="AI70" s="43"/>
       <c r="AJ70" s="6"/>
-      <c r="AK70" s="40"/>
+      <c r="AK70" s="43"/>
       <c r="AL70" s="7"/>
       <c r="AM70" s="7"/>
       <c r="AN70" s="7"/>
@@ -3686,7 +6478,7 @@
       <c r="BB70" s="7"/>
       <c r="BC70" s="7"/>
     </row>
-    <row r="71" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:84" x14ac:dyDescent="0.3">
       <c r="B71" s="7"/>
       <c r="C71" s="3"/>
       <c r="D71" s="6"/>
@@ -3711,15 +6503,15 @@
       <c r="W71" s="7"/>
       <c r="X71" s="7"/>
       <c r="AB71" s="7"/>
-      <c r="AC71" s="40"/>
+      <c r="AC71" s="43"/>
       <c r="AD71" s="6"/>
-      <c r="AE71" s="40"/>
+      <c r="AE71" s="43"/>
       <c r="AF71" s="6"/>
-      <c r="AG71" s="40"/>
+      <c r="AG71" s="43"/>
       <c r="AH71" s="6"/>
-      <c r="AI71" s="40"/>
+      <c r="AI71" s="43"/>
       <c r="AJ71" s="6"/>
-      <c r="AK71" s="40"/>
+      <c r="AK71" s="43"/>
       <c r="AL71" s="7"/>
       <c r="AM71" s="7"/>
       <c r="AN71" s="7"/>
@@ -3739,7 +6531,7 @@
       <c r="BB71" s="7"/>
       <c r="BC71" s="7"/>
     </row>
-    <row r="72" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:84" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
       <c r="C72" s="5"/>
       <c r="D72" s="6"/>
@@ -3764,15 +6556,15 @@
       <c r="W72" s="7"/>
       <c r="X72" s="7"/>
       <c r="AB72" s="7"/>
-      <c r="AC72" s="41"/>
+      <c r="AC72" s="44"/>
       <c r="AD72" s="6"/>
-      <c r="AE72" s="41"/>
+      <c r="AE72" s="44"/>
       <c r="AF72" s="6"/>
-      <c r="AG72" s="41"/>
+      <c r="AG72" s="44"/>
       <c r="AH72" s="6"/>
-      <c r="AI72" s="41"/>
+      <c r="AI72" s="44"/>
       <c r="AJ72" s="6"/>
-      <c r="AK72" s="41"/>
+      <c r="AK72" s="44"/>
       <c r="AL72" s="7"/>
       <c r="AM72" s="7"/>
       <c r="AN72" s="7"/>
@@ -3792,7 +6584,7 @@
       <c r="BB72" s="7"/>
       <c r="BC72" s="7"/>
     </row>
-    <row r="73" spans="2:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:84" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B73" s="7"/>
       <c r="F73" s="7"/>
       <c r="H73" s="7"/>
@@ -3837,7 +6629,7 @@
       <c r="BB73" s="7"/>
       <c r="BC73" s="7"/>
     </row>
-    <row r="74" spans="2:55" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:84" ht="23.4" x14ac:dyDescent="0.45">
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
       <c r="O74" s="7"/>
@@ -3851,12 +6643,12 @@
       <c r="W74" s="7"/>
       <c r="X74" s="7"/>
       <c r="AB74" s="7"/>
-      <c r="AC74" s="64" t="s">
+      <c r="AC74" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="AD74" s="79"/>
-      <c r="AE74" s="79"/>
-      <c r="AF74" s="80"/>
+      <c r="AD74" s="83"/>
+      <c r="AE74" s="83"/>
+      <c r="AF74" s="84"/>
       <c r="AG74" s="7"/>
       <c r="AH74" s="7"/>
       <c r="AI74" s="7"/>
@@ -3881,14 +6673,14 @@
       <c r="BB74" s="7"/>
       <c r="BC74" s="7"/>
     </row>
-    <row r="75" spans="2:55" ht="21" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:84" ht="21" x14ac:dyDescent="0.4">
       <c r="AB75" s="7"/>
-      <c r="AC75" s="65"/>
-      <c r="AD75" s="81" t="s">
+      <c r="AC75" s="69"/>
+      <c r="AD75" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="AE75" s="81"/>
-      <c r="AF75" s="82"/>
+      <c r="AE75" s="85"/>
+      <c r="AF75" s="86"/>
       <c r="AG75" s="7"/>
       <c r="AH75" s="7"/>
       <c r="AI75" s="7"/>
@@ -3913,14 +6705,14 @@
       <c r="BB75" s="7"/>
       <c r="BC75" s="7"/>
     </row>
-    <row r="76" spans="2:55" ht="21" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:84" ht="21" x14ac:dyDescent="0.4">
       <c r="AB76" s="7"/>
-      <c r="AC76" s="66"/>
-      <c r="AD76" s="81" t="s">
+      <c r="AC76" s="70"/>
+      <c r="AD76" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="AE76" s="81"/>
-      <c r="AF76" s="82"/>
+      <c r="AE76" s="85"/>
+      <c r="AF76" s="86"/>
       <c r="AG76" s="7"/>
       <c r="AH76" s="7"/>
       <c r="AI76" s="7"/>
@@ -3944,15 +6736,51 @@
       <c r="BA76" s="7"/>
       <c r="BB76" s="7"/>
       <c r="BC76" s="7"/>
-    </row>
-    <row r="77" spans="2:55" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="BG76" s="7"/>
+      <c r="BH76" s="151" t="s">
+        <v>68</v>
+      </c>
+      <c r="BI76" s="151"/>
+      <c r="BJ76" s="151"/>
+      <c r="BK76" s="151"/>
+      <c r="BL76" s="151"/>
+      <c r="BM76" s="151"/>
+      <c r="BN76" s="151"/>
+      <c r="BO76" s="151"/>
+      <c r="BP76" s="151"/>
+      <c r="BQ76" s="151"/>
+      <c r="BR76" s="151"/>
+      <c r="BS76" s="151"/>
+      <c r="BT76" s="151"/>
+      <c r="BU76" s="151"/>
+      <c r="BV76" s="151"/>
+      <c r="BW76" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX76" s="151" t="s">
+        <v>69</v>
+      </c>
+      <c r="BY76" s="151"/>
+      <c r="BZ76" s="151"/>
+      <c r="CA76" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB76" s="151" t="s">
+        <v>70</v>
+      </c>
+      <c r="CC76" s="151"/>
+      <c r="CD76" s="151"/>
+      <c r="CE76" s="7"/>
+      <c r="CF76" s="7"/>
+    </row>
+    <row r="77" spans="2:84" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="AB77" s="7"/>
-      <c r="AC77" s="67"/>
-      <c r="AD77" s="83" t="s">
+      <c r="AC77" s="71"/>
+      <c r="AD77" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="AE77" s="83"/>
-      <c r="AF77" s="84"/>
+      <c r="AE77" s="87"/>
+      <c r="AF77" s="88"/>
       <c r="AG77" s="7"/>
       <c r="AH77" s="7"/>
       <c r="AI77" s="7"/>
@@ -3976,16 +6804,2225 @@
       <c r="BA77" s="7"/>
       <c r="BB77" s="7"/>
       <c r="BC77" s="7"/>
-    </row>
-    <row r="78" spans="2:55" x14ac:dyDescent="0.3">
+      <c r="BG77" s="7"/>
+      <c r="BH77" s="151"/>
+      <c r="BI77" s="151"/>
+      <c r="BJ77" s="151"/>
+      <c r="BK77" s="151"/>
+      <c r="BL77" s="151"/>
+      <c r="BM77" s="151"/>
+      <c r="BN77" s="151"/>
+      <c r="BO77" s="151"/>
+      <c r="BP77" s="151"/>
+      <c r="BQ77" s="151"/>
+      <c r="BR77" s="151"/>
+      <c r="BS77" s="151"/>
+      <c r="BT77" s="151"/>
+      <c r="BU77" s="151"/>
+      <c r="BV77" s="151"/>
+      <c r="BW77" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX77" s="151"/>
+      <c r="BY77" s="151"/>
+      <c r="BZ77" s="151"/>
+      <c r="CA77" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB77" s="151"/>
+      <c r="CC77" s="151"/>
+      <c r="CD77" s="151"/>
+      <c r="CE77" s="7"/>
+      <c r="CF77" s="7"/>
+    </row>
+    <row r="78" spans="2:84" x14ac:dyDescent="0.3">
       <c r="AY78" s="7"/>
       <c r="AZ78" s="7"/>
       <c r="BA78" s="7"/>
       <c r="BB78" s="7"/>
       <c r="BC78" s="7"/>
+      <c r="BG78" s="7"/>
+      <c r="BH78" s="151"/>
+      <c r="BI78" s="151"/>
+      <c r="BJ78" s="151"/>
+      <c r="BK78" s="151"/>
+      <c r="BL78" s="151"/>
+      <c r="BM78" s="151"/>
+      <c r="BN78" s="151"/>
+      <c r="BO78" s="151"/>
+      <c r="BP78" s="151"/>
+      <c r="BQ78" s="151"/>
+      <c r="BR78" s="151"/>
+      <c r="BS78" s="151"/>
+      <c r="BT78" s="151"/>
+      <c r="BU78" s="151"/>
+      <c r="BV78" s="151"/>
+      <c r="BW78" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX78" s="151"/>
+      <c r="BY78" s="151"/>
+      <c r="BZ78" s="151"/>
+      <c r="CA78" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB78" s="151"/>
+      <c r="CC78" s="151"/>
+      <c r="CD78" s="151"/>
+      <c r="CE78" s="7"/>
+      <c r="CF78" s="7"/>
+    </row>
+    <row r="79" spans="2:84" x14ac:dyDescent="0.3">
+      <c r="BG79" s="7"/>
+      <c r="BH79" s="7"/>
+      <c r="BI79" s="7"/>
+      <c r="BJ79" s="7"/>
+      <c r="BK79" s="7"/>
+      <c r="BL79" s="7"/>
+      <c r="BM79" s="7"/>
+      <c r="BN79" s="7"/>
+      <c r="BO79" s="7"/>
+      <c r="BP79" s="7"/>
+      <c r="BQ79" s="7"/>
+      <c r="BR79" s="7"/>
+      <c r="BS79" s="7"/>
+      <c r="BT79" s="7"/>
+      <c r="BU79" s="7"/>
+      <c r="BV79" s="7"/>
+      <c r="BW79" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX79" s="7"/>
+      <c r="BY79" s="7"/>
+      <c r="BZ79" s="7"/>
+      <c r="CA79" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB79" s="7"/>
+      <c r="CC79" s="7"/>
+      <c r="CD79" s="7"/>
+      <c r="CE79" s="7"/>
+      <c r="CF79" s="7"/>
+    </row>
+    <row r="80" spans="2:84" x14ac:dyDescent="0.3">
+      <c r="BG80" s="7"/>
+      <c r="BH80" s="7"/>
+      <c r="BI80" s="7"/>
+      <c r="BJ80" s="7"/>
+      <c r="BK80" s="7"/>
+      <c r="BL80" s="7"/>
+      <c r="BM80" s="7"/>
+      <c r="BN80" s="7"/>
+      <c r="BO80" s="7"/>
+      <c r="BP80" s="7"/>
+      <c r="BQ80" s="7"/>
+      <c r="BR80" s="7"/>
+      <c r="BS80" s="7"/>
+      <c r="BT80" s="7"/>
+      <c r="BU80" s="7"/>
+      <c r="BV80" s="7"/>
+      <c r="BW80" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX80" s="7"/>
+      <c r="BY80" s="7"/>
+      <c r="BZ80" s="7"/>
+      <c r="CA80" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB80" s="7"/>
+      <c r="CC80" s="7"/>
+      <c r="CD80" s="7"/>
+      <c r="CE80" s="7"/>
+      <c r="CF80" s="7"/>
+    </row>
+    <row r="81" spans="57:94" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="BE81" s="6"/>
+      <c r="BG81" s="6"/>
+      <c r="BH81" s="93" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI81" s="6"/>
+      <c r="BJ81" s="93" t="s">
+        <v>51</v>
+      </c>
+      <c r="BK81" s="6"/>
+      <c r="BL81" s="93" t="s">
+        <v>52</v>
+      </c>
+      <c r="BM81" s="7"/>
+      <c r="BN81" s="93" t="s">
+        <v>53</v>
+      </c>
+      <c r="BO81" s="6"/>
+      <c r="BP81" s="93" t="s">
+        <v>54</v>
+      </c>
+      <c r="BQ81" s="6"/>
+      <c r="BR81" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="BS81" s="6"/>
+      <c r="BT81" s="93" t="s">
+        <v>56</v>
+      </c>
+      <c r="BU81" s="6"/>
+      <c r="BV81" s="93" t="s">
+        <v>57</v>
+      </c>
+      <c r="BW81" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX81" s="7"/>
+      <c r="BY81" s="93" t="s">
+        <v>48</v>
+      </c>
+      <c r="BZ81" s="7"/>
+      <c r="CA81" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB81" s="7"/>
+      <c r="CC81" s="93" t="s">
+        <v>49</v>
+      </c>
+      <c r="CD81" s="7"/>
+      <c r="CE81" s="7"/>
+      <c r="CF81" s="7"/>
+    </row>
+    <row r="82" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE82" s="6"/>
+      <c r="BG82" s="6"/>
+      <c r="BH82" s="43"/>
+      <c r="BI82" s="6"/>
+      <c r="BJ82" s="43"/>
+      <c r="BK82" s="6"/>
+      <c r="BL82" s="40"/>
+      <c r="BM82" s="7"/>
+      <c r="BN82" s="43"/>
+      <c r="BO82" s="6"/>
+      <c r="BP82" s="43"/>
+      <c r="BQ82" s="6"/>
+      <c r="BR82" s="43"/>
+      <c r="BS82" s="6"/>
+      <c r="BT82" s="43"/>
+      <c r="BU82" s="6"/>
+      <c r="BV82" s="43"/>
+      <c r="BW82" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX82" s="7"/>
+      <c r="BY82" s="89"/>
+      <c r="BZ82" s="7"/>
+      <c r="CA82" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB82" s="7"/>
+      <c r="CC82" s="91"/>
+      <c r="CD82" s="7"/>
+      <c r="CE82" s="7"/>
+      <c r="CF82" s="7"/>
+    </row>
+    <row r="83" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE83" s="6"/>
+      <c r="BG83" s="6"/>
+      <c r="BH83" s="43"/>
+      <c r="BI83" s="6"/>
+      <c r="BJ83" s="43"/>
+      <c r="BK83" s="6"/>
+      <c r="BL83" s="40"/>
+      <c r="BM83" s="7"/>
+      <c r="BN83" s="43"/>
+      <c r="BO83" s="6"/>
+      <c r="BP83" s="43"/>
+      <c r="BQ83" s="6"/>
+      <c r="BR83" s="43"/>
+      <c r="BS83" s="6"/>
+      <c r="BT83" s="43"/>
+      <c r="BU83" s="6"/>
+      <c r="BV83" s="43"/>
+      <c r="BW83" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX83" s="7"/>
+      <c r="BY83" s="89"/>
+      <c r="BZ83" s="7"/>
+      <c r="CA83" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB83" s="7"/>
+      <c r="CC83" s="91"/>
+      <c r="CD83" s="7"/>
+      <c r="CE83" s="7"/>
+      <c r="CF83" s="7"/>
+    </row>
+    <row r="84" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE84" s="6"/>
+      <c r="BG84" s="6"/>
+      <c r="BH84" s="43"/>
+      <c r="BI84" s="6"/>
+      <c r="BJ84" s="43"/>
+      <c r="BK84" s="6"/>
+      <c r="BL84" s="43"/>
+      <c r="BM84" s="7"/>
+      <c r="BN84" s="43"/>
+      <c r="BO84" s="6"/>
+      <c r="BP84" s="43"/>
+      <c r="BQ84" s="6"/>
+      <c r="BR84" s="43"/>
+      <c r="BS84" s="6"/>
+      <c r="BT84" s="43"/>
+      <c r="BU84" s="6"/>
+      <c r="BV84" s="43"/>
+      <c r="BW84" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX84" s="7"/>
+      <c r="BY84" s="89"/>
+      <c r="BZ84" s="7"/>
+      <c r="CA84" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB84" s="7"/>
+      <c r="CC84" s="92"/>
+      <c r="CD84" s="7"/>
+      <c r="CE84" s="7"/>
+      <c r="CF84" s="7"/>
+    </row>
+    <row r="85" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE85" s="6"/>
+      <c r="BG85" s="6"/>
+      <c r="BH85" s="43"/>
+      <c r="BI85" s="6"/>
+      <c r="BJ85" s="43"/>
+      <c r="BK85" s="6"/>
+      <c r="BL85" s="43"/>
+      <c r="BM85" s="7"/>
+      <c r="BN85" s="43"/>
+      <c r="BO85" s="6"/>
+      <c r="BP85" s="43"/>
+      <c r="BQ85" s="6"/>
+      <c r="BR85" s="43"/>
+      <c r="BS85" s="6"/>
+      <c r="BT85" s="43"/>
+      <c r="BU85" s="6"/>
+      <c r="BV85" s="43"/>
+      <c r="BW85" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX85" s="7"/>
+      <c r="BY85" s="89"/>
+      <c r="BZ85" s="7"/>
+      <c r="CA85" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB85" s="7"/>
+      <c r="CC85" s="92"/>
+      <c r="CD85" s="7"/>
+      <c r="CE85" s="7"/>
+      <c r="CF85" s="7"/>
+      <c r="CI85" s="7"/>
+    </row>
+    <row r="86" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE86" s="6"/>
+      <c r="BG86" s="6"/>
+      <c r="BH86" s="43"/>
+      <c r="BI86" s="6"/>
+      <c r="BJ86" s="43"/>
+      <c r="BK86" s="6"/>
+      <c r="BL86" s="43"/>
+      <c r="BM86" s="7"/>
+      <c r="BN86" s="43"/>
+      <c r="BO86" s="6"/>
+      <c r="BP86" s="43"/>
+      <c r="BQ86" s="6"/>
+      <c r="BR86" s="43"/>
+      <c r="BS86" s="6"/>
+      <c r="BT86" s="43"/>
+      <c r="BU86" s="6"/>
+      <c r="BV86" s="43"/>
+      <c r="BW86" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX86" s="7"/>
+      <c r="BY86" s="89"/>
+      <c r="BZ86" s="7"/>
+      <c r="CA86" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB86" s="7"/>
+      <c r="CC86" s="92"/>
+      <c r="CD86" s="7"/>
+      <c r="CE86" s="7"/>
+      <c r="CF86" s="7"/>
+    </row>
+    <row r="87" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE87" s="6"/>
+      <c r="BG87" s="6"/>
+      <c r="BH87" s="89"/>
+      <c r="BI87" s="6"/>
+      <c r="BJ87" s="89"/>
+      <c r="BK87" s="6"/>
+      <c r="BL87" s="89"/>
+      <c r="BM87" s="7"/>
+      <c r="BN87" s="89"/>
+      <c r="BO87" s="6"/>
+      <c r="BP87" s="89"/>
+      <c r="BQ87" s="6"/>
+      <c r="BR87" s="89"/>
+      <c r="BS87" s="6"/>
+      <c r="BT87" s="89"/>
+      <c r="BU87" s="6"/>
+      <c r="BV87" s="89"/>
+      <c r="BW87" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX87" s="7"/>
+      <c r="BY87" s="3"/>
+      <c r="BZ87" s="7"/>
+      <c r="CA87" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB87" s="7"/>
+      <c r="CC87" s="92"/>
+      <c r="CD87" s="7"/>
+      <c r="CE87" s="7"/>
+      <c r="CF87" s="7"/>
+    </row>
+    <row r="88" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE88" s="6"/>
+      <c r="BG88" s="6"/>
+      <c r="BH88" s="89"/>
+      <c r="BI88" s="6"/>
+      <c r="BJ88" s="89"/>
+      <c r="BK88" s="6"/>
+      <c r="BL88" s="89"/>
+      <c r="BM88" s="7"/>
+      <c r="BN88" s="89"/>
+      <c r="BO88" s="6"/>
+      <c r="BP88" s="89"/>
+      <c r="BQ88" s="6"/>
+      <c r="BR88" s="89"/>
+      <c r="BS88" s="6"/>
+      <c r="BT88" s="89"/>
+      <c r="BU88" s="6"/>
+      <c r="BV88" s="89"/>
+      <c r="BW88" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX88" s="7"/>
+      <c r="BY88" s="3"/>
+      <c r="BZ88" s="7"/>
+      <c r="CA88" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB88" s="7"/>
+      <c r="CC88" s="92"/>
+      <c r="CD88" s="7"/>
+      <c r="CE88" s="7"/>
+      <c r="CF88" s="7"/>
+    </row>
+    <row r="89" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE89" s="6"/>
+      <c r="BG89" s="6"/>
+      <c r="BH89" s="89"/>
+      <c r="BI89" s="6"/>
+      <c r="BJ89" s="89"/>
+      <c r="BK89" s="6"/>
+      <c r="BL89" s="89"/>
+      <c r="BM89" s="7"/>
+      <c r="BN89" s="89"/>
+      <c r="BO89" s="6"/>
+      <c r="BP89" s="89"/>
+      <c r="BQ89" s="6"/>
+      <c r="BR89" s="89"/>
+      <c r="BS89" s="6"/>
+      <c r="BT89" s="89"/>
+      <c r="BU89" s="6"/>
+      <c r="BV89" s="89"/>
+      <c r="BW89" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX89" s="7"/>
+      <c r="BY89" s="3"/>
+      <c r="BZ89" s="7"/>
+      <c r="CA89" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB89" s="7"/>
+      <c r="CC89" s="89"/>
+      <c r="CD89" s="7"/>
+      <c r="CE89" s="7"/>
+      <c r="CF89" s="7"/>
+      <c r="CJ89" t="s">
+        <v>47</v>
+      </c>
+      <c r="CP89" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE90" s="6"/>
+      <c r="BG90" s="6"/>
+      <c r="BH90" s="89"/>
+      <c r="BI90" s="6"/>
+      <c r="BJ90" s="89"/>
+      <c r="BK90" s="6"/>
+      <c r="BL90" s="89"/>
+      <c r="BM90" s="7"/>
+      <c r="BN90" s="89"/>
+      <c r="BO90" s="6"/>
+      <c r="BP90" s="89"/>
+      <c r="BQ90" s="6"/>
+      <c r="BR90" s="89"/>
+      <c r="BS90" s="6"/>
+      <c r="BT90" s="89"/>
+      <c r="BU90" s="6"/>
+      <c r="BV90" s="89"/>
+      <c r="BW90" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX90" s="7"/>
+      <c r="BY90" s="89"/>
+      <c r="BZ90" s="7"/>
+      <c r="CA90" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB90" s="7"/>
+      <c r="CC90" s="47"/>
+      <c r="CD90" s="7"/>
+      <c r="CE90" s="7"/>
+      <c r="CF90" s="7"/>
+    </row>
+    <row r="91" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE91" s="6"/>
+      <c r="BG91" s="6"/>
+      <c r="BH91" s="90"/>
+      <c r="BI91" s="6"/>
+      <c r="BJ91" s="90"/>
+      <c r="BK91" s="6"/>
+      <c r="BL91" s="90"/>
+      <c r="BM91" s="7"/>
+      <c r="BN91" s="90"/>
+      <c r="BO91" s="6"/>
+      <c r="BP91" s="90"/>
+      <c r="BQ91" s="6"/>
+      <c r="BR91" s="90"/>
+      <c r="BS91" s="6"/>
+      <c r="BT91" s="90"/>
+      <c r="BU91" s="6"/>
+      <c r="BV91" s="90"/>
+      <c r="BW91" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX91" s="7"/>
+      <c r="BY91" s="90"/>
+      <c r="BZ91" s="7"/>
+      <c r="CA91" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB91" s="7"/>
+      <c r="CC91" s="48"/>
+      <c r="CD91" s="7"/>
+      <c r="CE91" s="7"/>
+      <c r="CF91" s="7"/>
+    </row>
+    <row r="92" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE92" s="6"/>
+      <c r="BG92" s="6"/>
+      <c r="BH92" s="7"/>
+      <c r="BI92" s="7"/>
+      <c r="BJ92" s="7"/>
+      <c r="BK92" s="7"/>
+      <c r="BL92" s="7"/>
+      <c r="BM92" s="7"/>
+      <c r="BN92" s="7"/>
+      <c r="BO92" s="7"/>
+      <c r="BP92" s="7"/>
+      <c r="BQ92" s="7"/>
+      <c r="BR92" s="7"/>
+      <c r="BS92" s="7"/>
+      <c r="BT92" s="7"/>
+      <c r="BU92" s="7"/>
+      <c r="BV92" s="7"/>
+      <c r="BW92" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX92" s="7"/>
+      <c r="BY92" s="7"/>
+      <c r="BZ92" s="7"/>
+      <c r="CA92" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB92" s="7"/>
+      <c r="CC92" s="7"/>
+      <c r="CD92" s="7"/>
+      <c r="CE92" s="7"/>
+      <c r="CF92" s="7"/>
+    </row>
+    <row r="93" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE93" s="6"/>
+      <c r="BG93" s="6"/>
+      <c r="BH93" s="7"/>
+      <c r="BI93" s="7"/>
+      <c r="BJ93" s="7"/>
+      <c r="BK93" s="7"/>
+      <c r="BL93" s="7"/>
+      <c r="BM93" s="7"/>
+      <c r="BN93" s="7"/>
+      <c r="BO93" s="7"/>
+      <c r="BP93" s="7"/>
+      <c r="BQ93" s="7"/>
+      <c r="BR93" s="7"/>
+      <c r="BS93" s="7"/>
+      <c r="BT93" s="7"/>
+      <c r="BU93" s="7"/>
+      <c r="BV93" s="7"/>
+      <c r="BW93" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX93" s="7"/>
+      <c r="BY93" s="7"/>
+      <c r="BZ93" s="7"/>
+      <c r="CA93" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB93" s="7"/>
+      <c r="CC93" s="7"/>
+      <c r="CD93" s="7"/>
+      <c r="CE93" s="7"/>
+      <c r="CF93" s="7"/>
+    </row>
+    <row r="94" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE94" s="6"/>
+      <c r="BG94" s="6"/>
+      <c r="BH94" s="7"/>
+      <c r="BI94" s="7"/>
+      <c r="BJ94" s="7"/>
+      <c r="BK94" s="7"/>
+      <c r="BL94" s="7"/>
+      <c r="BM94" s="7"/>
+      <c r="BN94" s="7"/>
+      <c r="BO94" s="7"/>
+      <c r="BP94" s="7"/>
+      <c r="BQ94" s="7"/>
+      <c r="BR94" s="7"/>
+      <c r="BS94" s="7"/>
+      <c r="BT94" s="7"/>
+      <c r="BU94" s="7"/>
+      <c r="BV94" s="7"/>
+      <c r="BW94" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX94" s="7"/>
+      <c r="BY94" s="7"/>
+      <c r="BZ94" s="7"/>
+      <c r="CA94" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB94" s="7"/>
+      <c r="CC94" s="7"/>
+      <c r="CD94" s="7"/>
+      <c r="CE94" s="7"/>
+      <c r="CF94" s="7"/>
+    </row>
+    <row r="95" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE95" s="6"/>
+      <c r="BG95" s="6"/>
+      <c r="BH95" s="7"/>
+      <c r="BI95" s="7"/>
+      <c r="BJ95" s="7"/>
+      <c r="BK95" s="7"/>
+      <c r="BL95" s="7"/>
+      <c r="BM95" s="7"/>
+      <c r="BN95" s="7"/>
+      <c r="BO95" s="7"/>
+      <c r="BP95" s="7"/>
+      <c r="BQ95" s="7"/>
+      <c r="BR95" s="7"/>
+      <c r="BS95" s="7"/>
+      <c r="BT95" s="7"/>
+      <c r="BU95" s="7"/>
+      <c r="BV95" s="7"/>
+      <c r="BW95" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX95" s="7"/>
+      <c r="BY95" s="7"/>
+      <c r="BZ95" s="7"/>
+      <c r="CA95" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB95" s="7"/>
+      <c r="CC95" s="7"/>
+      <c r="CD95" s="7"/>
+      <c r="CE95" s="7"/>
+      <c r="CF95" s="7"/>
+    </row>
+    <row r="96" spans="57:94" x14ac:dyDescent="0.3">
+      <c r="BE96" s="6"/>
+      <c r="BG96" s="6"/>
+      <c r="BH96" s="97"/>
+      <c r="BI96" s="98"/>
+      <c r="BJ96" s="98"/>
+      <c r="BK96" s="98"/>
+      <c r="BL96" s="98"/>
+      <c r="BM96" s="98"/>
+      <c r="BN96" s="98"/>
+      <c r="BO96" s="98"/>
+      <c r="BP96" s="98"/>
+      <c r="BQ96" s="98"/>
+      <c r="BR96" s="98"/>
+      <c r="BS96" s="98"/>
+      <c r="BT96" s="98"/>
+      <c r="BU96" s="98"/>
+      <c r="BV96" s="99"/>
+      <c r="BW96" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX96" s="7"/>
+      <c r="BY96" s="7"/>
+      <c r="BZ96" s="7"/>
+      <c r="CA96" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB96" s="7"/>
+      <c r="CC96" s="7"/>
+      <c r="CD96" s="7"/>
+      <c r="CE96" s="7"/>
+      <c r="CF96" s="7"/>
+    </row>
+    <row r="97" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BH97" s="100"/>
+      <c r="BI97" s="101"/>
+      <c r="BJ97" s="101"/>
+      <c r="BK97" s="101"/>
+      <c r="BL97" s="101"/>
+      <c r="BM97" s="101"/>
+      <c r="BN97" s="101"/>
+      <c r="BO97" s="101"/>
+      <c r="BP97" s="101"/>
+      <c r="BQ97" s="101"/>
+      <c r="BR97" s="101"/>
+      <c r="BS97" s="101"/>
+      <c r="BT97" s="101"/>
+      <c r="BU97" s="101"/>
+      <c r="BV97" s="102"/>
+      <c r="BW97" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX97" s="7"/>
+      <c r="BY97" s="7"/>
+      <c r="BZ97" s="7"/>
+      <c r="CA97" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB97" s="7"/>
+      <c r="CC97" s="7"/>
+      <c r="CD97" s="7"/>
+      <c r="CE97" s="7"/>
+      <c r="CF97" s="7"/>
+    </row>
+    <row r="98" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG98" s="7"/>
+      <c r="BH98" s="100"/>
+      <c r="BI98" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="BJ98" s="103"/>
+      <c r="BK98" s="103"/>
+      <c r="BL98" s="103"/>
+      <c r="BM98" s="103"/>
+      <c r="BN98" s="103"/>
+      <c r="BO98" s="103"/>
+      <c r="BP98" s="103"/>
+      <c r="BQ98" s="103"/>
+      <c r="BR98" s="103"/>
+      <c r="BS98" s="103"/>
+      <c r="BT98" s="103"/>
+      <c r="BU98" s="103"/>
+      <c r="BV98" s="102"/>
+      <c r="BW98" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX98" s="7"/>
+      <c r="BY98" s="7"/>
+      <c r="BZ98" s="7"/>
+      <c r="CA98" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB98" s="7"/>
+      <c r="CC98" s="7"/>
+      <c r="CD98" s="7"/>
+      <c r="CE98" s="7"/>
+      <c r="CF98" s="7"/>
+    </row>
+    <row r="99" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG99" s="7"/>
+      <c r="BH99" s="100"/>
+      <c r="BI99" s="103"/>
+      <c r="BJ99" s="103"/>
+      <c r="BK99" s="103"/>
+      <c r="BL99" s="103"/>
+      <c r="BM99" s="103"/>
+      <c r="BN99" s="103"/>
+      <c r="BO99" s="103"/>
+      <c r="BP99" s="103"/>
+      <c r="BQ99" s="103"/>
+      <c r="BR99" s="103"/>
+      <c r="BS99" s="103"/>
+      <c r="BT99" s="103"/>
+      <c r="BU99" s="103"/>
+      <c r="BV99" s="102"/>
+      <c r="BW99" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX99" s="7"/>
+      <c r="BY99" s="7"/>
+      <c r="BZ99" s="7"/>
+      <c r="CA99" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB99" s="7"/>
+      <c r="CC99" s="7"/>
+      <c r="CD99" s="7"/>
+      <c r="CE99" s="7"/>
+      <c r="CF99" s="7"/>
+    </row>
+    <row r="100" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG100" s="7"/>
+      <c r="BH100" s="100"/>
+      <c r="BI100" s="103"/>
+      <c r="BJ100" s="103"/>
+      <c r="BK100" s="103"/>
+      <c r="BL100" s="103"/>
+      <c r="BM100" s="103"/>
+      <c r="BN100" s="103"/>
+      <c r="BO100" s="103"/>
+      <c r="BP100" s="103"/>
+      <c r="BQ100" s="103"/>
+      <c r="BR100" s="103"/>
+      <c r="BS100" s="103"/>
+      <c r="BT100" s="103"/>
+      <c r="BU100" s="103"/>
+      <c r="BV100" s="102"/>
+      <c r="BW100" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX100" s="7"/>
+      <c r="BY100" s="7"/>
+      <c r="BZ100" s="7"/>
+      <c r="CA100" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB100" s="7"/>
+      <c r="CC100" s="7"/>
+      <c r="CD100" s="7"/>
+      <c r="CE100" s="7"/>
+      <c r="CF100" s="7"/>
+    </row>
+    <row r="101" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG101" s="7"/>
+      <c r="BH101" s="100"/>
+      <c r="BI101" s="103"/>
+      <c r="BJ101" s="103"/>
+      <c r="BK101" s="103"/>
+      <c r="BL101" s="103"/>
+      <c r="BM101" s="103"/>
+      <c r="BN101" s="103"/>
+      <c r="BO101" s="103"/>
+      <c r="BP101" s="103"/>
+      <c r="BQ101" s="103"/>
+      <c r="BR101" s="103"/>
+      <c r="BS101" s="103"/>
+      <c r="BT101" s="103"/>
+      <c r="BU101" s="103"/>
+      <c r="BV101" s="102"/>
+      <c r="BW101" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX101" s="7"/>
+      <c r="BY101" s="7"/>
+      <c r="BZ101" s="7"/>
+      <c r="CA101" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB101" s="7"/>
+      <c r="CC101" s="7"/>
+      <c r="CD101" s="7"/>
+      <c r="CE101" s="7"/>
+      <c r="CF101" s="7"/>
+    </row>
+    <row r="102" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG102" s="7"/>
+      <c r="BH102" s="100"/>
+      <c r="BI102" s="103"/>
+      <c r="BJ102" s="103"/>
+      <c r="BK102" s="103"/>
+      <c r="BL102" s="103"/>
+      <c r="BM102" s="103"/>
+      <c r="BN102" s="103"/>
+      <c r="BO102" s="103"/>
+      <c r="BP102" s="103"/>
+      <c r="BQ102" s="103"/>
+      <c r="BR102" s="103"/>
+      <c r="BS102" s="103"/>
+      <c r="BT102" s="103"/>
+      <c r="BU102" s="103"/>
+      <c r="BV102" s="102"/>
+      <c r="BW102" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX102" s="7"/>
+      <c r="BY102" s="7"/>
+      <c r="BZ102" s="7"/>
+      <c r="CA102" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB102" s="7"/>
+      <c r="CC102" s="7"/>
+      <c r="CD102" s="7"/>
+      <c r="CE102" s="7"/>
+      <c r="CF102" s="7"/>
+    </row>
+    <row r="103" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG103" s="7"/>
+      <c r="BH103" s="100"/>
+      <c r="BI103" s="101"/>
+      <c r="BJ103" s="101"/>
+      <c r="BK103" s="101"/>
+      <c r="BL103" s="101"/>
+      <c r="BM103" s="101"/>
+      <c r="BN103" s="101"/>
+      <c r="BO103" s="101"/>
+      <c r="BP103" s="101"/>
+      <c r="BQ103" s="101"/>
+      <c r="BR103" s="101"/>
+      <c r="BS103" s="101"/>
+      <c r="BT103" s="101"/>
+      <c r="BU103" s="101"/>
+      <c r="BV103" s="102"/>
+      <c r="BW103" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX103" s="7"/>
+      <c r="BY103" s="7"/>
+      <c r="BZ103" s="7"/>
+      <c r="CA103" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB103" s="7"/>
+      <c r="CC103" s="7"/>
+      <c r="CD103" s="7"/>
+      <c r="CE103" s="7"/>
+      <c r="CF103" s="7"/>
+    </row>
+    <row r="104" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG104" s="7"/>
+      <c r="BH104" s="104"/>
+      <c r="BI104" s="105"/>
+      <c r="BJ104" s="105"/>
+      <c r="BK104" s="105"/>
+      <c r="BL104" s="105"/>
+      <c r="BM104" s="105"/>
+      <c r="BN104" s="105"/>
+      <c r="BO104" s="105"/>
+      <c r="BP104" s="105"/>
+      <c r="BQ104" s="105"/>
+      <c r="BR104" s="105"/>
+      <c r="BS104" s="105"/>
+      <c r="BT104" s="105"/>
+      <c r="BU104" s="105"/>
+      <c r="BV104" s="106"/>
+      <c r="BW104" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX104" s="7"/>
+      <c r="BY104" s="7"/>
+      <c r="BZ104" s="7"/>
+      <c r="CA104" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB104" s="7"/>
+      <c r="CC104" s="7"/>
+      <c r="CD104" s="7"/>
+      <c r="CE104" s="7"/>
+      <c r="CF104" s="7"/>
+    </row>
+    <row r="105" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG105" s="7"/>
+      <c r="BH105" s="7"/>
+      <c r="BI105" s="7"/>
+      <c r="BJ105" s="7"/>
+      <c r="BK105" s="7"/>
+      <c r="BL105" s="7"/>
+      <c r="BM105" s="7"/>
+      <c r="BN105" s="7"/>
+      <c r="BO105" s="7"/>
+      <c r="BP105" s="7"/>
+      <c r="BQ105" s="7"/>
+      <c r="BR105" s="7"/>
+      <c r="BS105" s="7"/>
+      <c r="BT105" s="7"/>
+      <c r="BU105" s="7"/>
+      <c r="BV105" s="7"/>
+      <c r="BW105" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX105" s="7"/>
+      <c r="BY105" s="7"/>
+      <c r="BZ105" s="7"/>
+      <c r="CA105" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB105" s="7"/>
+      <c r="CC105" s="7"/>
+      <c r="CD105" s="7"/>
+      <c r="CE105" s="7"/>
+      <c r="CF105" s="7"/>
+    </row>
+    <row r="106" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG106" s="7"/>
+      <c r="BH106" s="7"/>
+      <c r="BI106" s="7"/>
+      <c r="BJ106" s="7"/>
+      <c r="BK106" s="7"/>
+      <c r="BL106" s="7"/>
+      <c r="BM106" s="7"/>
+      <c r="BN106" s="7"/>
+      <c r="BO106" s="7"/>
+      <c r="BP106" s="7"/>
+      <c r="BQ106" s="7"/>
+      <c r="BR106" s="7"/>
+      <c r="BS106" s="7"/>
+      <c r="BT106" s="7"/>
+      <c r="BU106" s="7"/>
+      <c r="BV106" s="7"/>
+      <c r="BW106" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX106" s="7"/>
+      <c r="BY106" s="7"/>
+      <c r="BZ106" s="7"/>
+      <c r="CA106" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB106" s="7"/>
+      <c r="CC106" s="7"/>
+      <c r="CD106" s="7"/>
+      <c r="CE106" s="7"/>
+      <c r="CF106" s="7"/>
+    </row>
+    <row r="107" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG107" s="7"/>
+      <c r="BH107" s="7"/>
+      <c r="BI107" s="7"/>
+      <c r="BJ107" s="7"/>
+      <c r="BK107" s="7"/>
+      <c r="BL107" s="7"/>
+      <c r="BM107" s="7"/>
+      <c r="BN107" s="7"/>
+      <c r="BO107" s="7"/>
+      <c r="BP107" s="7"/>
+      <c r="BQ107" s="7"/>
+      <c r="BR107" s="7"/>
+      <c r="BS107" s="7"/>
+      <c r="BT107" s="7"/>
+      <c r="BU107" s="7"/>
+      <c r="BV107" s="7"/>
+      <c r="BW107" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX107" s="7"/>
+      <c r="BY107" s="7"/>
+      <c r="BZ107" s="7"/>
+      <c r="CA107" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB107" s="7"/>
+      <c r="CC107" s="7"/>
+      <c r="CD107" s="7"/>
+      <c r="CE107" s="7"/>
+      <c r="CF107" s="7"/>
+    </row>
+    <row r="108" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG108" s="7"/>
+      <c r="BH108" s="7"/>
+      <c r="BI108" s="7"/>
+      <c r="BJ108" s="7"/>
+      <c r="BK108" s="7"/>
+      <c r="BL108" s="7"/>
+      <c r="BM108" s="7"/>
+      <c r="BN108" s="7"/>
+      <c r="BO108" s="7"/>
+      <c r="BP108" s="7"/>
+      <c r="BQ108" s="7"/>
+      <c r="BR108" s="7"/>
+      <c r="BS108" s="7"/>
+      <c r="BT108" s="7"/>
+      <c r="BU108" s="7"/>
+      <c r="BV108" s="7"/>
+      <c r="BW108" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX108" s="7"/>
+      <c r="BY108" s="7"/>
+      <c r="BZ108" s="7"/>
+      <c r="CA108" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB108" s="7"/>
+      <c r="CC108" s="7"/>
+      <c r="CD108" s="7"/>
+      <c r="CE108" s="7"/>
+      <c r="CF108" s="7"/>
+    </row>
+    <row r="109" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG109" s="7"/>
+      <c r="BH109" s="109"/>
+      <c r="BI109" s="107"/>
+      <c r="BJ109" s="107"/>
+      <c r="BK109" s="107"/>
+      <c r="BL109" s="107"/>
+      <c r="BM109" s="107"/>
+      <c r="BN109" s="107"/>
+      <c r="BO109" s="107"/>
+      <c r="BP109" s="107"/>
+      <c r="BQ109" s="107"/>
+      <c r="BR109" s="107"/>
+      <c r="BS109" s="107"/>
+      <c r="BT109" s="107"/>
+      <c r="BU109" s="107"/>
+      <c r="BV109" s="107"/>
+      <c r="BW109" s="124" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX109" s="114"/>
+      <c r="BY109" s="107"/>
+      <c r="BZ109" s="114"/>
+      <c r="CA109" s="148" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB109" s="114"/>
+      <c r="CC109" s="115"/>
+      <c r="CD109" s="7"/>
+      <c r="CE109" s="7"/>
+      <c r="CF109" s="7"/>
+    </row>
+    <row r="110" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG110" s="7"/>
+      <c r="BH110" s="110"/>
+      <c r="BI110" s="108"/>
+      <c r="BJ110" s="108"/>
+      <c r="BK110" s="108"/>
+      <c r="BL110" s="108"/>
+      <c r="BM110" s="108"/>
+      <c r="BN110" s="108"/>
+      <c r="BO110" s="108"/>
+      <c r="BP110" s="108"/>
+      <c r="BQ110" s="108"/>
+      <c r="BR110" s="108"/>
+      <c r="BS110" s="108"/>
+      <c r="BT110" s="108"/>
+      <c r="BU110" s="108"/>
+      <c r="BV110" s="108"/>
+      <c r="BW110" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX110" s="17"/>
+      <c r="BY110" s="108"/>
+      <c r="BZ110" s="17"/>
+      <c r="CA110" s="149" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB110" s="17"/>
+      <c r="CC110" s="135"/>
+      <c r="CD110" s="7"/>
+      <c r="CE110" s="7"/>
+      <c r="CF110" s="7"/>
+    </row>
+    <row r="111" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG111" s="7"/>
+      <c r="BH111" s="110"/>
+      <c r="BI111" s="108"/>
+      <c r="BJ111" s="108"/>
+      <c r="BK111" s="108"/>
+      <c r="BL111" s="108"/>
+      <c r="BM111" s="108"/>
+      <c r="BN111" s="108"/>
+      <c r="BO111" s="108"/>
+      <c r="BP111" s="136" t="s">
+        <v>59</v>
+      </c>
+      <c r="BQ111" s="136"/>
+      <c r="BR111" s="136"/>
+      <c r="BS111" s="136"/>
+      <c r="BT111" s="136"/>
+      <c r="BU111" s="136"/>
+      <c r="BV111" s="136"/>
+      <c r="BW111" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX111" s="17"/>
+      <c r="BY111" s="108"/>
+      <c r="BZ111" s="17"/>
+      <c r="CA111" s="149" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB111" s="17"/>
+      <c r="CC111" s="135"/>
+      <c r="CD111" s="7"/>
+      <c r="CE111" s="7"/>
+      <c r="CF111" s="7"/>
+    </row>
+    <row r="112" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG112" s="7"/>
+      <c r="BH112" s="110"/>
+      <c r="BI112" s="108"/>
+      <c r="BJ112" s="108"/>
+      <c r="BK112" s="108"/>
+      <c r="BL112" s="108"/>
+      <c r="BM112" s="108"/>
+      <c r="BN112" s="108"/>
+      <c r="BO112" s="108"/>
+      <c r="BP112" s="136"/>
+      <c r="BQ112" s="136"/>
+      <c r="BR112" s="136"/>
+      <c r="BS112" s="136"/>
+      <c r="BT112" s="136"/>
+      <c r="BU112" s="136"/>
+      <c r="BV112" s="136"/>
+      <c r="BW112" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX112" s="17"/>
+      <c r="BY112" s="108"/>
+      <c r="BZ112" s="17"/>
+      <c r="CA112" s="149" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB112" s="17"/>
+      <c r="CC112" s="135"/>
+      <c r="CD112" s="7"/>
+      <c r="CE112" s="7"/>
+      <c r="CF112" s="7"/>
+    </row>
+    <row r="113" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG113" s="7"/>
+      <c r="BH113" s="110"/>
+      <c r="BI113" s="108"/>
+      <c r="BJ113" s="108"/>
+      <c r="BK113" s="108"/>
+      <c r="BL113" s="108"/>
+      <c r="BM113" s="108"/>
+      <c r="BN113" s="108"/>
+      <c r="BO113" s="108"/>
+      <c r="BP113" s="136"/>
+      <c r="BQ113" s="136"/>
+      <c r="BR113" s="136"/>
+      <c r="BS113" s="136"/>
+      <c r="BT113" s="136"/>
+      <c r="BU113" s="136"/>
+      <c r="BV113" s="136"/>
+      <c r="BW113" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX113" s="17"/>
+      <c r="BY113" s="108"/>
+      <c r="BZ113" s="17"/>
+      <c r="CA113" s="149" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB113" s="17"/>
+      <c r="CC113" s="135"/>
+      <c r="CD113" s="7"/>
+      <c r="CE113" s="7"/>
+      <c r="CF113" s="7"/>
+    </row>
+    <row r="114" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG114" s="7"/>
+      <c r="BH114" s="110"/>
+      <c r="BI114" s="108"/>
+      <c r="BJ114" s="108"/>
+      <c r="BK114" s="108"/>
+      <c r="BL114" s="108"/>
+      <c r="BM114" s="108"/>
+      <c r="BN114" s="108"/>
+      <c r="BO114" s="108"/>
+      <c r="BP114" s="136"/>
+      <c r="BQ114" s="136"/>
+      <c r="BR114" s="136"/>
+      <c r="BS114" s="136"/>
+      <c r="BT114" s="136"/>
+      <c r="BU114" s="136"/>
+      <c r="BV114" s="136"/>
+      <c r="BW114" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX114" s="17"/>
+      <c r="BY114" s="108"/>
+      <c r="BZ114" s="17"/>
+      <c r="CA114" s="149" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB114" s="17"/>
+      <c r="CC114" s="135"/>
+      <c r="CD114" s="7"/>
+      <c r="CE114" s="7"/>
+      <c r="CF114" s="7"/>
+    </row>
+    <row r="115" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG115" s="7"/>
+      <c r="BH115" s="110"/>
+      <c r="BI115" s="108"/>
+      <c r="BJ115" s="108"/>
+      <c r="BK115" s="108"/>
+      <c r="BL115" s="108"/>
+      <c r="BM115" s="108"/>
+      <c r="BN115" s="108"/>
+      <c r="BO115" s="108"/>
+      <c r="BP115" s="136"/>
+      <c r="BQ115" s="136"/>
+      <c r="BR115" s="136"/>
+      <c r="BS115" s="136"/>
+      <c r="BT115" s="136"/>
+      <c r="BU115" s="136"/>
+      <c r="BV115" s="136"/>
+      <c r="BW115" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX115" s="17"/>
+      <c r="BY115" s="108"/>
+      <c r="BZ115" s="17"/>
+      <c r="CA115" s="149" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB115" s="17"/>
+      <c r="CC115" s="135"/>
+      <c r="CD115" s="7"/>
+      <c r="CE115" s="7"/>
+      <c r="CF115" s="7"/>
+    </row>
+    <row r="116" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG116" s="7"/>
+      <c r="BH116" s="110"/>
+      <c r="BI116" s="108"/>
+      <c r="BJ116" s="108"/>
+      <c r="BK116" s="108"/>
+      <c r="BL116" s="108"/>
+      <c r="BM116" s="108"/>
+      <c r="BN116" s="108"/>
+      <c r="BO116" s="108"/>
+      <c r="BP116" s="108"/>
+      <c r="BQ116" s="108"/>
+      <c r="BR116" s="108"/>
+      <c r="BS116" s="108"/>
+      <c r="BT116" s="108"/>
+      <c r="BU116" s="108"/>
+      <c r="BV116" s="108"/>
+      <c r="BW116" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX116" s="17"/>
+      <c r="BY116" s="108"/>
+      <c r="BZ116" s="17"/>
+      <c r="CA116" s="149" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB116" s="17"/>
+      <c r="CC116" s="135"/>
+      <c r="CD116" s="7"/>
+      <c r="CE116" s="7"/>
+      <c r="CF116" s="7"/>
+    </row>
+    <row r="117" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG117" s="7"/>
+      <c r="BH117" s="111"/>
+      <c r="BI117" s="112"/>
+      <c r="BJ117" s="112"/>
+      <c r="BK117" s="112"/>
+      <c r="BL117" s="112"/>
+      <c r="BM117" s="112"/>
+      <c r="BN117" s="112"/>
+      <c r="BO117" s="112"/>
+      <c r="BP117" s="112"/>
+      <c r="BQ117" s="112"/>
+      <c r="BR117" s="112"/>
+      <c r="BS117" s="112"/>
+      <c r="BT117" s="112"/>
+      <c r="BU117" s="112"/>
+      <c r="BV117" s="112"/>
+      <c r="BW117" s="125" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX117" s="120"/>
+      <c r="BY117" s="112"/>
+      <c r="BZ117" s="120"/>
+      <c r="CA117" s="150" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB117" s="120"/>
+      <c r="CC117" s="121"/>
+      <c r="CD117" s="7"/>
+      <c r="CE117" s="7"/>
+      <c r="CF117" s="7"/>
+    </row>
+    <row r="118" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG118" s="7"/>
+      <c r="BH118" s="7"/>
+      <c r="BI118" s="7"/>
+      <c r="BJ118" s="7"/>
+      <c r="BK118" s="7"/>
+      <c r="BL118" s="7"/>
+      <c r="BM118" s="7"/>
+      <c r="BN118" s="7"/>
+      <c r="BO118" s="7"/>
+      <c r="BP118" s="7"/>
+      <c r="BQ118" s="7"/>
+      <c r="BR118" s="7"/>
+      <c r="BS118" s="7"/>
+      <c r="BT118" s="7"/>
+      <c r="BU118" s="7"/>
+      <c r="BV118" s="7"/>
+      <c r="BW118" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX118" s="7"/>
+      <c r="BY118" s="7"/>
+      <c r="BZ118" s="7"/>
+      <c r="CA118" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB118" s="7"/>
+      <c r="CC118" s="7"/>
+      <c r="CD118" s="7"/>
+      <c r="CE118" s="7"/>
+      <c r="CF118" s="7"/>
+    </row>
+    <row r="119" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG119" s="7"/>
+      <c r="BH119" s="7"/>
+      <c r="BI119" s="7"/>
+      <c r="BJ119" s="7"/>
+      <c r="BK119" s="7"/>
+      <c r="BL119" s="7"/>
+      <c r="BM119" s="7"/>
+      <c r="BN119" s="7"/>
+      <c r="BO119" s="7"/>
+      <c r="BP119" s="7"/>
+      <c r="BQ119" s="7"/>
+      <c r="BR119" s="7"/>
+      <c r="BS119" s="7"/>
+      <c r="BT119" s="7"/>
+      <c r="BU119" s="7"/>
+      <c r="BV119" s="7"/>
+      <c r="BW119" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX119" s="7"/>
+      <c r="BY119" s="7"/>
+      <c r="BZ119" s="7"/>
+      <c r="CA119" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB119" s="7"/>
+      <c r="CC119" s="7"/>
+      <c r="CD119" s="7"/>
+      <c r="CE119" s="7"/>
+      <c r="CF119" s="7"/>
+    </row>
+    <row r="120" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG120" s="7"/>
+      <c r="BH120" s="7"/>
+      <c r="BI120" s="7"/>
+      <c r="BJ120" s="7"/>
+      <c r="BK120" s="7"/>
+      <c r="BL120" s="7"/>
+      <c r="BM120" s="7"/>
+      <c r="BN120" s="7"/>
+      <c r="BO120" s="7"/>
+      <c r="BP120" s="7"/>
+      <c r="BQ120" s="7"/>
+      <c r="BR120" s="7"/>
+      <c r="BS120" s="7"/>
+      <c r="BT120" s="7"/>
+      <c r="BU120" s="7"/>
+      <c r="BV120" s="7"/>
+      <c r="BW120" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX120" s="7"/>
+      <c r="BY120" s="7"/>
+      <c r="BZ120" s="7"/>
+      <c r="CA120" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB120" s="7"/>
+      <c r="CC120" s="7"/>
+      <c r="CD120" s="7"/>
+      <c r="CE120" s="7"/>
+      <c r="CF120" s="7"/>
+    </row>
+    <row r="121" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG121" s="7"/>
+      <c r="BH121" s="7"/>
+      <c r="BI121" s="7"/>
+      <c r="BJ121" s="7"/>
+      <c r="BK121" s="7"/>
+      <c r="BL121" s="7"/>
+      <c r="BM121" s="7"/>
+      <c r="BN121" s="7"/>
+      <c r="BO121" s="7"/>
+      <c r="BP121" s="7"/>
+      <c r="BQ121" s="7"/>
+      <c r="BR121" s="7"/>
+      <c r="BS121" s="7"/>
+      <c r="BT121" s="7"/>
+      <c r="BU121" s="7"/>
+      <c r="BV121" s="7"/>
+      <c r="BW121" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX121" s="7"/>
+      <c r="BY121" s="7"/>
+      <c r="BZ121" s="7"/>
+      <c r="CA121" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB121" s="7"/>
+      <c r="CC121" s="7"/>
+      <c r="CD121" s="7"/>
+      <c r="CE121" s="7"/>
+      <c r="CF121" s="7"/>
+    </row>
+    <row r="122" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG122" s="7"/>
+      <c r="BH122" s="96"/>
+      <c r="BI122" s="6"/>
+      <c r="BJ122" s="96"/>
+      <c r="BK122" s="6"/>
+      <c r="BL122" s="96"/>
+      <c r="BM122" s="7"/>
+      <c r="BN122" s="96"/>
+      <c r="BO122" s="6"/>
+      <c r="BP122" s="96"/>
+      <c r="BQ122" s="6"/>
+      <c r="BR122" s="96"/>
+      <c r="BS122" s="6"/>
+      <c r="BT122" s="96"/>
+      <c r="BU122" s="6"/>
+      <c r="BV122" s="96"/>
+      <c r="BW122" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX122" s="7"/>
+      <c r="BY122" s="7"/>
+      <c r="BZ122" s="7"/>
+      <c r="CA122" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB122" s="7"/>
+      <c r="CC122" s="7"/>
+      <c r="CD122" s="7"/>
+      <c r="CE122" s="7"/>
+      <c r="CF122" s="7"/>
+    </row>
+    <row r="123" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG123" s="7"/>
+      <c r="BH123" s="147" t="s">
+        <v>61</v>
+      </c>
+      <c r="BI123" s="6"/>
+      <c r="BJ123" s="147" t="s">
+        <v>62</v>
+      </c>
+      <c r="BK123" s="6"/>
+      <c r="BL123" s="43"/>
+      <c r="BM123" s="7"/>
+      <c r="BN123" s="43"/>
+      <c r="BO123" s="6"/>
+      <c r="BP123" s="43"/>
+      <c r="BQ123" s="6"/>
+      <c r="BR123" s="43"/>
+      <c r="BS123" s="6"/>
+      <c r="BT123" s="147" t="s">
+        <v>63</v>
+      </c>
+      <c r="BU123" s="6"/>
+      <c r="BV123" s="147" t="s">
+        <v>64</v>
+      </c>
+      <c r="BW123" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX123" s="7"/>
+      <c r="BY123" s="7"/>
+      <c r="BZ123" s="7"/>
+      <c r="CA123" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB123" s="7"/>
+      <c r="CC123" s="7"/>
+      <c r="CD123" s="7"/>
+      <c r="CE123" s="7"/>
+      <c r="CF123" s="7"/>
+    </row>
+    <row r="124" spans="59:84" ht="25.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="BG124" s="7"/>
+      <c r="BH124" s="147"/>
+      <c r="BI124" s="6"/>
+      <c r="BJ124" s="147"/>
+      <c r="BK124" s="6"/>
+      <c r="BL124" s="43"/>
+      <c r="BM124" s="95"/>
+      <c r="BN124" s="43"/>
+      <c r="BO124" s="94" t="s">
+        <v>60</v>
+      </c>
+      <c r="BP124" s="43"/>
+      <c r="BQ124" s="6"/>
+      <c r="BR124" s="43"/>
+      <c r="BS124" s="6"/>
+      <c r="BT124" s="147"/>
+      <c r="BU124" s="6"/>
+      <c r="BV124" s="147"/>
+      <c r="BW124" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX124" s="7"/>
+      <c r="BY124" s="7"/>
+      <c r="BZ124" s="7"/>
+      <c r="CA124" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB124" s="7"/>
+      <c r="CC124" s="7"/>
+      <c r="CD124" s="7"/>
+      <c r="CE124" s="7"/>
+      <c r="CF124" s="7"/>
+    </row>
+    <row r="125" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BG125" s="7"/>
+      <c r="BH125" s="147"/>
+      <c r="BI125" s="6"/>
+      <c r="BJ125" s="147"/>
+      <c r="BK125" s="6"/>
+      <c r="BL125" s="43"/>
+      <c r="BM125" s="7"/>
+      <c r="BN125" s="43"/>
+      <c r="BO125" s="6"/>
+      <c r="BP125" s="43"/>
+      <c r="BQ125" s="6"/>
+      <c r="BR125" s="43"/>
+      <c r="BS125" s="6"/>
+      <c r="BT125" s="147"/>
+      <c r="BU125" s="6"/>
+      <c r="BV125" s="147"/>
+      <c r="BW125" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX125" s="7"/>
+      <c r="BY125" s="7"/>
+      <c r="BZ125" s="7"/>
+      <c r="CA125" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB125" s="7"/>
+      <c r="CC125" s="7"/>
+      <c r="CD125" s="7"/>
+      <c r="CE125" s="7"/>
+      <c r="CF125" s="7"/>
+    </row>
+    <row r="126" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG126" s="7"/>
+      <c r="BH126" s="44"/>
+      <c r="BI126" s="6"/>
+      <c r="BJ126" s="44"/>
+      <c r="BK126" s="6"/>
+      <c r="BL126" s="44"/>
+      <c r="BM126" s="7"/>
+      <c r="BN126" s="44"/>
+      <c r="BO126" s="6"/>
+      <c r="BP126" s="44"/>
+      <c r="BQ126" s="6"/>
+      <c r="BR126" s="44"/>
+      <c r="BS126" s="6"/>
+      <c r="BT126" s="44"/>
+      <c r="BU126" s="6"/>
+      <c r="BV126" s="44"/>
+      <c r="BW126" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX126" s="7"/>
+      <c r="BY126" s="7"/>
+      <c r="BZ126" s="7"/>
+      <c r="CA126" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB126" s="7"/>
+      <c r="CC126" s="7"/>
+      <c r="CD126" s="7"/>
+      <c r="CE126" s="7"/>
+      <c r="CF126" s="7"/>
+    </row>
+    <row r="127" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG127" s="7"/>
+      <c r="BH127" s="7"/>
+      <c r="BI127" s="7"/>
+      <c r="BJ127" s="7"/>
+      <c r="BK127" s="7"/>
+      <c r="BL127" s="7"/>
+      <c r="BM127" s="7"/>
+      <c r="BN127" s="7"/>
+      <c r="BO127" s="7"/>
+      <c r="BP127" s="7"/>
+      <c r="BQ127" s="7"/>
+      <c r="BR127" s="7"/>
+      <c r="BS127" s="7"/>
+      <c r="BT127" s="7"/>
+      <c r="BU127" s="7"/>
+      <c r="BV127" s="7"/>
+      <c r="BW127" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX127" s="7"/>
+      <c r="BY127" s="7"/>
+      <c r="BZ127" s="7"/>
+      <c r="CA127" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB127" s="7"/>
+      <c r="CC127" s="7"/>
+      <c r="CD127" s="7"/>
+      <c r="CE127" s="7"/>
+      <c r="CF127" s="7"/>
+    </row>
+    <row r="128" spans="59:84" x14ac:dyDescent="0.3">
+      <c r="BG128" s="7"/>
+      <c r="BH128" s="7"/>
+      <c r="BI128" s="7"/>
+      <c r="BJ128" s="7"/>
+      <c r="BK128" s="7"/>
+      <c r="BL128" s="7"/>
+      <c r="BM128" s="7"/>
+      <c r="BN128" s="7"/>
+      <c r="BO128" s="7"/>
+      <c r="BP128" s="7"/>
+      <c r="BQ128" s="7"/>
+      <c r="BR128" s="7"/>
+      <c r="BS128" s="7"/>
+      <c r="BT128" s="7"/>
+      <c r="BU128" s="7"/>
+      <c r="BV128" s="7"/>
+      <c r="BW128" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX128" s="7"/>
+      <c r="BY128" s="7"/>
+      <c r="BZ128" s="7"/>
+      <c r="CA128" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB128" s="7"/>
+      <c r="CC128" s="7"/>
+      <c r="CD128" s="7"/>
+      <c r="CE128" s="7"/>
+      <c r="CF128" s="7"/>
+    </row>
+    <row r="129" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG129" s="7"/>
+      <c r="BH129" s="7"/>
+      <c r="BI129" s="7"/>
+      <c r="BJ129" s="7"/>
+      <c r="BK129" s="7"/>
+      <c r="BL129" s="7"/>
+      <c r="BM129" s="7"/>
+      <c r="BN129" s="7"/>
+      <c r="BO129" s="7"/>
+      <c r="BP129" s="7"/>
+      <c r="BQ129" s="7"/>
+      <c r="BR129" s="7"/>
+      <c r="BS129" s="7"/>
+      <c r="BT129" s="7"/>
+      <c r="BU129" s="7"/>
+      <c r="BV129" s="7"/>
+      <c r="BW129" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX129" s="7"/>
+      <c r="BY129" s="7"/>
+      <c r="BZ129" s="7"/>
+      <c r="CA129" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB129" s="7"/>
+      <c r="CC129" s="7"/>
+      <c r="CD129" s="7"/>
+      <c r="CE129" s="7"/>
+      <c r="CF129" s="7"/>
+    </row>
+    <row r="130" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG130" s="7"/>
+      <c r="BH130" s="7"/>
+      <c r="BI130" s="7"/>
+      <c r="BJ130" s="7"/>
+      <c r="BK130" s="7"/>
+      <c r="BL130" s="7"/>
+      <c r="BM130" s="7"/>
+      <c r="BN130" s="7"/>
+      <c r="BO130" s="7"/>
+      <c r="BP130" s="7"/>
+      <c r="BQ130" s="7"/>
+      <c r="BR130" s="7"/>
+      <c r="BS130" s="7"/>
+      <c r="BT130" s="7"/>
+      <c r="BU130" s="7"/>
+      <c r="BV130" s="7"/>
+      <c r="BW130" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX130" s="7"/>
+      <c r="BY130" s="7"/>
+      <c r="BZ130" s="7"/>
+      <c r="CA130" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB130" s="7"/>
+      <c r="CC130" s="7"/>
+      <c r="CD130" s="7"/>
+      <c r="CE130" s="7"/>
+      <c r="CF130" s="7"/>
+    </row>
+    <row r="131" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG131" s="7"/>
+      <c r="BH131" s="7"/>
+      <c r="BI131" s="7"/>
+      <c r="BJ131" s="7"/>
+      <c r="BK131" s="7"/>
+      <c r="BL131" s="7"/>
+      <c r="BM131" s="113"/>
+      <c r="BN131" s="114"/>
+      <c r="BO131" s="114"/>
+      <c r="BP131" s="114"/>
+      <c r="BQ131" s="115"/>
+      <c r="BR131" s="7"/>
+      <c r="BS131" s="7"/>
+      <c r="BT131" s="7"/>
+      <c r="BU131" s="7"/>
+      <c r="BV131" s="7"/>
+      <c r="BW131" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX131" s="126" t="s">
+        <v>66</v>
+      </c>
+      <c r="BY131" s="127"/>
+      <c r="BZ131" s="128"/>
+      <c r="CA131" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB131" s="138"/>
+      <c r="CC131" s="139"/>
+      <c r="CD131" s="140"/>
+      <c r="CE131" s="7"/>
+      <c r="CF131" s="7"/>
+    </row>
+    <row r="132" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG132" s="7"/>
+      <c r="BH132" s="7"/>
+      <c r="BI132" s="7"/>
+      <c r="BJ132" s="7"/>
+      <c r="BK132" s="7"/>
+      <c r="BL132" s="7"/>
+      <c r="BM132" s="137" t="s">
+        <v>71</v>
+      </c>
+      <c r="BN132" s="117"/>
+      <c r="BO132" s="117"/>
+      <c r="BP132" s="117"/>
+      <c r="BQ132" s="118"/>
+      <c r="BR132" s="7"/>
+      <c r="BS132" s="7"/>
+      <c r="BT132" s="7"/>
+      <c r="BU132" s="7"/>
+      <c r="BV132" s="7"/>
+      <c r="BW132" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX132" s="129"/>
+      <c r="BY132" s="130"/>
+      <c r="BZ132" s="131"/>
+      <c r="CA132" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB132" s="144" t="s">
+        <v>67</v>
+      </c>
+      <c r="CC132" s="145"/>
+      <c r="CD132" s="146"/>
+      <c r="CE132" s="7"/>
+      <c r="CF132" s="7"/>
+    </row>
+    <row r="133" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG133" s="7"/>
+      <c r="BH133" s="7"/>
+      <c r="BI133" s="7"/>
+      <c r="BJ133" s="7"/>
+      <c r="BK133" s="7"/>
+      <c r="BL133" s="7"/>
+      <c r="BM133" s="116"/>
+      <c r="BN133" s="117"/>
+      <c r="BO133" s="117"/>
+      <c r="BP133" s="117"/>
+      <c r="BQ133" s="118"/>
+      <c r="BR133" s="7"/>
+      <c r="BS133" s="7"/>
+      <c r="BT133" s="7"/>
+      <c r="BU133" s="7"/>
+      <c r="BV133" s="7"/>
+      <c r="BW133" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX133" s="129"/>
+      <c r="BY133" s="130"/>
+      <c r="BZ133" s="131"/>
+      <c r="CA133" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB133" s="144"/>
+      <c r="CC133" s="145"/>
+      <c r="CD133" s="146"/>
+      <c r="CE133" s="7"/>
+      <c r="CF133" s="7"/>
+    </row>
+    <row r="134" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG134" s="7"/>
+      <c r="BH134" s="7"/>
+      <c r="BI134" s="7"/>
+      <c r="BJ134" s="7"/>
+      <c r="BK134" s="7"/>
+      <c r="BL134" s="7"/>
+      <c r="BM134" s="116"/>
+      <c r="BN134" s="117"/>
+      <c r="BO134" s="117"/>
+      <c r="BP134" s="117"/>
+      <c r="BQ134" s="118"/>
+      <c r="BR134" s="7"/>
+      <c r="BS134" s="7"/>
+      <c r="BT134" s="7"/>
+      <c r="BU134" s="7"/>
+      <c r="BV134" s="7"/>
+      <c r="BW134" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX134" s="129"/>
+      <c r="BY134" s="130"/>
+      <c r="BZ134" s="131"/>
+      <c r="CA134" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB134" s="144"/>
+      <c r="CC134" s="145"/>
+      <c r="CD134" s="146"/>
+      <c r="CE134" s="7"/>
+      <c r="CF134" s="7"/>
+    </row>
+    <row r="135" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG135" s="7"/>
+      <c r="BH135" s="7"/>
+      <c r="BI135" s="7"/>
+      <c r="BJ135" s="7"/>
+      <c r="BK135" s="7"/>
+      <c r="BL135" s="7"/>
+      <c r="BM135" s="116"/>
+      <c r="BN135" s="117"/>
+      <c r="BO135" s="117"/>
+      <c r="BP135" s="117"/>
+      <c r="BQ135" s="118"/>
+      <c r="BR135" s="7"/>
+      <c r="BS135" s="7"/>
+      <c r="BT135" s="7"/>
+      <c r="BU135" s="7"/>
+      <c r="BV135" s="7"/>
+      <c r="BW135" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX135" s="129"/>
+      <c r="BY135" s="130"/>
+      <c r="BZ135" s="131"/>
+      <c r="CA135" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB135" s="144"/>
+      <c r="CC135" s="145"/>
+      <c r="CD135" s="146"/>
+      <c r="CE135" s="7"/>
+      <c r="CF135" s="7"/>
+    </row>
+    <row r="136" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG136" s="7"/>
+      <c r="BH136" s="7"/>
+      <c r="BI136" s="7"/>
+      <c r="BJ136" s="7"/>
+      <c r="BK136" s="7"/>
+      <c r="BL136" s="7"/>
+      <c r="BM136" s="116"/>
+      <c r="BN136" s="117"/>
+      <c r="BO136" s="117"/>
+      <c r="BP136" s="117"/>
+      <c r="BQ136" s="118"/>
+      <c r="BR136" s="7"/>
+      <c r="BS136" s="7"/>
+      <c r="BT136" s="7"/>
+      <c r="BU136" s="7"/>
+      <c r="BV136" s="7"/>
+      <c r="BW136" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX136" s="129"/>
+      <c r="BY136" s="130"/>
+      <c r="BZ136" s="131"/>
+      <c r="CA136" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB136" s="144"/>
+      <c r="CC136" s="145"/>
+      <c r="CD136" s="146"/>
+      <c r="CE136" s="7"/>
+      <c r="CF136" s="7"/>
+    </row>
+    <row r="137" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG137" s="7"/>
+      <c r="BH137" s="7"/>
+      <c r="BI137" s="7"/>
+      <c r="BJ137" s="7"/>
+      <c r="BK137" s="7"/>
+      <c r="BL137" s="7"/>
+      <c r="BM137" s="119"/>
+      <c r="BN137" s="120"/>
+      <c r="BO137" s="120"/>
+      <c r="BP137" s="120"/>
+      <c r="BQ137" s="121"/>
+      <c r="BR137" s="7"/>
+      <c r="BS137" s="7"/>
+      <c r="BT137" s="7"/>
+      <c r="BU137" s="7"/>
+      <c r="BV137" s="7"/>
+      <c r="BW137" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX137" s="132"/>
+      <c r="BY137" s="133"/>
+      <c r="BZ137" s="134"/>
+      <c r="CA137" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB137" s="141"/>
+      <c r="CC137" s="142"/>
+      <c r="CD137" s="143"/>
+      <c r="CE137" s="7"/>
+      <c r="CF137" s="7"/>
+      <c r="AVI137" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="138" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG138" s="7"/>
+      <c r="BH138" s="7"/>
+      <c r="BI138" s="7"/>
+      <c r="BJ138" s="7"/>
+      <c r="BK138" s="7"/>
+      <c r="BL138" s="7"/>
+      <c r="BM138" s="7"/>
+      <c r="BN138" s="7"/>
+      <c r="BO138" s="7"/>
+      <c r="BP138" s="7"/>
+      <c r="BQ138" s="7"/>
+      <c r="BR138" s="7"/>
+      <c r="BS138" s="7"/>
+      <c r="BT138" s="7"/>
+      <c r="BU138" s="7"/>
+      <c r="BV138" s="7"/>
+      <c r="BW138" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX138" s="7"/>
+      <c r="BY138" s="7"/>
+      <c r="BZ138" s="7"/>
+      <c r="CA138" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB138" s="7"/>
+      <c r="CC138" s="7"/>
+      <c r="CD138" s="7"/>
+      <c r="CE138" s="7"/>
+      <c r="CF138" s="7"/>
+    </row>
+    <row r="139" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG139" s="7"/>
+      <c r="BH139" s="7"/>
+      <c r="BI139" s="7"/>
+      <c r="BJ139" s="7"/>
+      <c r="BK139" s="7"/>
+      <c r="BL139" s="7"/>
+      <c r="BM139" s="7"/>
+      <c r="BN139" s="7"/>
+      <c r="BO139" s="7"/>
+      <c r="BP139" s="7"/>
+      <c r="BQ139" s="7"/>
+      <c r="BR139" s="7"/>
+      <c r="BS139" s="7"/>
+      <c r="BT139" s="7"/>
+      <c r="BU139" s="7"/>
+      <c r="BV139" s="7"/>
+      <c r="BW139" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX139" s="7"/>
+      <c r="BY139" s="7"/>
+      <c r="BZ139" s="7"/>
+      <c r="CA139" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB139" s="7"/>
+      <c r="CC139" s="7"/>
+      <c r="CD139" s="7"/>
+      <c r="CE139" s="7"/>
+      <c r="CF139" s="7"/>
+    </row>
+    <row r="140" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG140" s="7"/>
+      <c r="BH140" s="7"/>
+      <c r="BI140" s="7"/>
+      <c r="BJ140" s="7"/>
+      <c r="BK140" s="7"/>
+      <c r="BL140" s="7"/>
+      <c r="BM140" s="7"/>
+      <c r="BN140" s="7"/>
+      <c r="BO140" s="7"/>
+      <c r="BP140" s="7"/>
+      <c r="BQ140" s="7"/>
+      <c r="BR140" s="7"/>
+      <c r="BS140" s="7"/>
+      <c r="BT140" s="7"/>
+      <c r="BU140" s="7"/>
+      <c r="BV140" s="7"/>
+      <c r="BW140" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX140" s="7"/>
+      <c r="BY140" s="7"/>
+      <c r="BZ140" s="7"/>
+      <c r="CA140" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB140" s="7"/>
+      <c r="CC140" s="7"/>
+      <c r="CD140" s="7"/>
+      <c r="CE140" s="7"/>
+      <c r="CF140" s="7"/>
+    </row>
+    <row r="141" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG141" s="7"/>
+      <c r="BH141" s="7"/>
+      <c r="BI141" s="7"/>
+      <c r="BJ141" s="7"/>
+      <c r="BK141" s="7"/>
+      <c r="BL141" s="7"/>
+      <c r="BM141" s="7"/>
+      <c r="BN141" s="7"/>
+      <c r="BO141" s="7"/>
+      <c r="BP141" s="7"/>
+      <c r="BQ141" s="7"/>
+      <c r="BR141" s="7"/>
+      <c r="BS141" s="7"/>
+      <c r="BT141" s="7"/>
+      <c r="BU141" s="7"/>
+      <c r="BV141" s="7"/>
+      <c r="BW141" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX141" s="7"/>
+      <c r="BY141" s="7"/>
+      <c r="BZ141" s="7"/>
+      <c r="CA141" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB141" s="7"/>
+      <c r="CC141" s="7"/>
+      <c r="CD141" s="7"/>
+      <c r="CE141" s="7"/>
+      <c r="CF141" s="7"/>
+    </row>
+    <row r="142" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BG142" s="7"/>
+      <c r="BH142" s="7"/>
+      <c r="BI142" s="7"/>
+      <c r="BJ142" s="7"/>
+      <c r="BK142" s="7"/>
+      <c r="BL142" s="7"/>
+      <c r="BM142" s="7"/>
+      <c r="BN142" s="7"/>
+      <c r="BO142" s="7"/>
+      <c r="BP142" s="7"/>
+      <c r="BQ142" s="7"/>
+      <c r="BR142" s="7"/>
+      <c r="BS142" s="7"/>
+      <c r="BT142" s="7"/>
+      <c r="BU142" s="7"/>
+      <c r="BV142" s="7"/>
+      <c r="BW142" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="BX142" s="7"/>
+      <c r="BY142" s="7"/>
+      <c r="BZ142" s="7"/>
+      <c r="CA142" s="152" t="s">
+        <v>65</v>
+      </c>
+      <c r="CB142" s="7"/>
+      <c r="CC142" s="7"/>
+      <c r="CD142" s="7"/>
+      <c r="CE142" s="7"/>
+      <c r="CF142" s="7"/>
+    </row>
+    <row r="143" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
+      <c r="BM143" s="7"/>
+      <c r="BN143" s="7"/>
+      <c r="BO143" s="7"/>
+      <c r="BP143" s="7"/>
+      <c r="BQ143" s="7"/>
+      <c r="BR143" s="7"/>
+      <c r="BS143" s="7"/>
+      <c r="BT143" s="7"/>
+      <c r="BU143" s="7"/>
+      <c r="BV143" s="7"/>
+      <c r="BW143" s="7"/>
+      <c r="BX143" s="7"/>
+      <c r="BY143" s="7"/>
+      <c r="BZ143" s="7"/>
+      <c r="CA143" s="7"/>
+      <c r="CB143" s="7"/>
+      <c r="CC143" s="7"/>
+      <c r="CD143" s="7"/>
+      <c r="CE143" s="7"/>
+      <c r="CF143" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="67">
+    <mergeCell ref="BH76:BV78"/>
+    <mergeCell ref="BX76:BZ78"/>
+    <mergeCell ref="CB76:CD78"/>
+    <mergeCell ref="BH123:BH125"/>
+    <mergeCell ref="BV123:BV125"/>
+    <mergeCell ref="BT123:BT125"/>
+    <mergeCell ref="BJ123:BJ125"/>
+    <mergeCell ref="BM132:BQ136"/>
+    <mergeCell ref="BX131:BZ137"/>
+    <mergeCell ref="BP111:BV115"/>
+    <mergeCell ref="CB132:CD136"/>
+    <mergeCell ref="BL82:BL83"/>
+    <mergeCell ref="CC82:CC83"/>
+    <mergeCell ref="BI98:BU102"/>
     <mergeCell ref="AM33:AQ34"/>
     <mergeCell ref="AN63:AX64"/>
     <mergeCell ref="AN65:AX66"/>
@@ -4040,7 +9077,7 @@
     <mergeCell ref="T38:T39"/>
     <mergeCell ref="S34:U34"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/report-vis.xlsx
+++ b/report-vis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\! CS\Y2\AI is taking over\cw\ai-garbage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B037B311-49D5-42FC-82BA-677DCFB74D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9EBF03-7430-4448-B72C-40484726A902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-12645" windowWidth="29040" windowHeight="15840" xr2:uid="{82DBE9BC-AC51-4988-B415-6B972F3134D5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
   <si>
     <t>sub-01</t>
   </si>
@@ -146,70 +146,16 @@
     <t>(165400 samples across the 10 subjects)</t>
   </si>
   <si>
-    <t>Test Subject</t>
-  </si>
-  <si>
-    <t>Train Subjects</t>
-  </si>
-  <si>
-    <t>Validation Subject</t>
-  </si>
-  <si>
     <t>Key:</t>
   </si>
   <si>
-    <t>5 Train Samples per class</t>
-  </si>
-  <si>
-    <t>3 Validation Samples per class</t>
-  </si>
-  <si>
-    <t>2 Test Samples per class</t>
-  </si>
-  <si>
-    <t>Each Class For Each Subject:</t>
-  </si>
-  <si>
     <t>TRAINING is performed using the TRAIN SAMPLES for the TRAIN SUBJECTS</t>
-  </si>
-  <si>
-    <t>VALIDATION is performed using the VALIDATION SAMPLES for the VALIDATION SUBJECT</t>
   </si>
   <si>
     <t>TESTING is performed using the TEST SAMPLES for the TEST SUBJECT</t>
   </si>
   <si>
     <t>a</t>
-  </si>
-  <si>
-    <t>SV</t>
-  </si>
-  <si>
-    <t>STt</t>
-  </si>
-  <si>
-    <t>STr1</t>
-  </si>
-  <si>
-    <t>STr2</t>
-  </si>
-  <si>
-    <t>STr3</t>
-  </si>
-  <si>
-    <t>STr4</t>
-  </si>
-  <si>
-    <t>STr5</t>
-  </si>
-  <si>
-    <t>STr6</t>
-  </si>
-  <si>
-    <t>STr7</t>
-  </si>
-  <si>
-    <t>STr8</t>
   </si>
   <si>
     <t>Fit Preprocessors</t>
@@ -233,23 +179,78 @@
     <t>W8</t>
   </si>
   <si>
-    <t>|</t>
-  </si>
-  <si>
-    <t>Fine-Tune using
-Validation Set</t>
-  </si>
-  <si>
     <t>Test Final Model</t>
   </si>
   <si>
-    <t>TRAINING</t>
+    <t>For Each Class:</t>
   </si>
   <si>
-    <t>VALIDATION</t>
+    <t>FINE TUNING is performed using the FINE TUNING SAMPLES from the TEST SUBJECT</t>
   </si>
   <si>
-    <t>TESTING</t>
+    <t>W9</t>
+  </si>
+  <si>
+    <t>W3</t>
+  </si>
+  <si>
+    <t>Fine-Tuning:
+Domain
+Adaptation</t>
+  </si>
+  <si>
+    <t>SS1</t>
+  </si>
+  <si>
+    <t>SS2</t>
+  </si>
+  <si>
+    <t>SS3</t>
+  </si>
+  <si>
+    <t>SS4</t>
+  </si>
+  <si>
+    <t>SS5</t>
+  </si>
+  <si>
+    <t>SS6</t>
+  </si>
+  <si>
+    <t>SS7</t>
+  </si>
+  <si>
+    <t>SS8</t>
+  </si>
+  <si>
+    <t>SS9</t>
+  </si>
+  <si>
+    <t>FINE-TUNE</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>(all other data is unused)</t>
+  </si>
+  <si>
+    <t>2 Fine Tuning Samples from the Target Subject</t>
+  </si>
+  <si>
+    <t>2 Test Samples from the Target Subject</t>
+  </si>
+  <si>
+    <t>6 Train Samples per Source Subject</t>
+  </si>
+  <si>
+    <t>Target Subject</t>
+  </si>
+  <si>
+    <t>Source Subjects</t>
+  </si>
+  <si>
+    <t>ST</t>
   </si>
   <si>
     <r>
@@ -272,21 +273,27 @@
       <rPr>
         <b/>
         <i/>
-        <sz val="14"/>
+        <sz val="16"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>avg</t>
+      <t>general</t>
     </r>
+  </si>
+  <si>
+    <t>TRAINING (SOURCE) SUBJECTS</t>
+  </si>
+  <si>
+    <t>TEST (TARGET) SUBJECT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,9 +409,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="17.5"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <i/>
-      <sz val="14"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -903,219 +917,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1125,14 +970,8 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1143,18 +982,14 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1172,22 +1007,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1196,72 +1019,281 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1271,10 +1303,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFECF6AE"/>
       <color rgb="FFFBA9F7"/>
       <color rgb="FFEF7F7F"/>
       <color rgb="FF7DF977"/>
-      <color rgb="FFECF6AE"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2018,16 +2050,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>76</xdr:col>
-      <xdr:colOff>56029</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>50539</xdr:rowOff>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>164886</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>76</xdr:col>
-      <xdr:colOff>533216</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>32473</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>168729</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2042,8 +2074,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="45833179" y="17081239"/>
-          <a:ext cx="477187" cy="2883161"/>
+          <a:off x="47165999" y="16535400"/>
+          <a:ext cx="477187" cy="3302454"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -2078,16 +2110,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>80</xdr:col>
-      <xdr:colOff>55806</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>48634</xdr:rowOff>
+      <xdr:col>81</xdr:col>
+      <xdr:colOff>77578</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>117232</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>80</xdr:col>
-      <xdr:colOff>550138</xdr:colOff>
+      <xdr:col>81</xdr:col>
+      <xdr:colOff>571910</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2102,8 +2134,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="47052156" y="17079334"/>
-          <a:ext cx="494332" cy="2885066"/>
+          <a:off x="49513793" y="16969155"/>
+          <a:ext cx="494332" cy="3009900"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -2978,14 +3010,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>66</xdr:col>
-      <xdr:colOff>69588</xdr:colOff>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>69586</xdr:colOff>
       <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>66</xdr:col>
-      <xdr:colOff>542965</xdr:colOff>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>542963</xdr:colOff>
       <xdr:row>129</xdr:row>
       <xdr:rowOff>117230</xdr:rowOff>
     </xdr:to>
@@ -3002,8 +3034,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="40360338" y="23726775"/>
-          <a:ext cx="473377" cy="479180"/>
+          <a:off x="40978100" y="24111857"/>
+          <a:ext cx="473377" cy="487344"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -3399,15 +3431,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>59</xdr:col>
-      <xdr:colOff>18378</xdr:colOff>
+      <xdr:colOff>18377</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>174025</xdr:rowOff>
+      <xdr:rowOff>174026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>74</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>8164</xdr:colOff>
       <xdr:row>127</xdr:row>
-      <xdr:rowOff>77390</xdr:rowOff>
+      <xdr:rowOff>70758</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3422,8 +3454,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35903816" y="23456697"/>
-          <a:ext cx="9089903" cy="81959"/>
+          <a:off x="36044648" y="23760647"/>
+          <a:ext cx="10352987" cy="79068"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3518,14 +3550,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>73</xdr:col>
-      <xdr:colOff>535782</xdr:colOff>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>541213</xdr:colOff>
       <xdr:row>126</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>74</xdr:col>
-      <xdr:colOff>1838</xdr:colOff>
+      <xdr:col>76</xdr:col>
+      <xdr:colOff>7269</xdr:colOff>
       <xdr:row>126</xdr:row>
       <xdr:rowOff>168733</xdr:rowOff>
     </xdr:to>
@@ -3542,8 +3574,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="44922282" y="23377922"/>
-          <a:ext cx="73275" cy="73483"/>
+          <a:off x="46321084" y="23681871"/>
+          <a:ext cx="75656" cy="73483"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3578,16 +3610,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>76</xdr:col>
-      <xdr:colOff>59839</xdr:colOff>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>201353</xdr:colOff>
       <xdr:row>117</xdr:row>
-      <xdr:rowOff>46728</xdr:rowOff>
+      <xdr:rowOff>68499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>76</xdr:col>
-      <xdr:colOff>533216</xdr:colOff>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>65130</xdr:colOff>
       <xdr:row>129</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
+      <xdr:rowOff>122624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3602,8 +3634,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="45510898" y="21606846"/>
-          <a:ext cx="473377" cy="2384948"/>
+          <a:off x="47205867" y="22188270"/>
+          <a:ext cx="473377" cy="2416325"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -3638,16 +3670,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>69</xdr:col>
-      <xdr:colOff>57667</xdr:colOff>
+      <xdr:col>70</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
       <xdr:row>132</xdr:row>
-      <xdr:rowOff>58202</xdr:rowOff>
+      <xdr:rowOff>58199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>74</xdr:col>
-      <xdr:colOff>503468</xdr:colOff>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>555173</xdr:colOff>
       <xdr:row>134</xdr:row>
-      <xdr:rowOff>169181</xdr:rowOff>
+      <xdr:rowOff>169178</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3662,10 +3694,490 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="43883596" y="22703166"/>
-          <a:ext cx="464764" cy="3507408"/>
+          <a:off x="44336454" y="23572403"/>
+          <a:ext cx="481093" cy="3526972"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>79</xdr:col>
+      <xdr:colOff>54432</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>40786</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>79</xdr:col>
+      <xdr:colOff>550005</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Arrow: Down 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BDD8F75-8BA8-4503-8063-BD1C45DE56D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="47878669" y="24157513"/>
+          <a:ext cx="478100" cy="495573"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Arrow: Down 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD0D97B1-E692-4B52-9C43-3FB3F26858E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44640657" y="17350586"/>
+          <a:ext cx="480997" cy="555745"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Arrow: Down 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E75694D3-F14A-45B0-BA37-424BA4A7E08E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44640657" y="17350586"/>
+          <a:ext cx="480997" cy="555745"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Arrow: Down 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4142A0E5-B327-4FEA-B846-CEF6420A9EF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44640657" y="19756329"/>
+          <a:ext cx="480997" cy="555745"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Arrow: Down 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{736A42B9-5201-4192-BC5D-28AA9255F6D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44640657" y="19756329"/>
+          <a:ext cx="480997" cy="555745"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Arrow: Down 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6460A211-A743-4534-9526-23DCFB4459DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44640657" y="22162071"/>
+          <a:ext cx="480997" cy="555746"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>74543</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>42300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>555540</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>42874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Arrow: Down 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E834F8F7-D9F6-462A-8E0B-B6F3608A20B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="44640657" y="22162071"/>
+          <a:ext cx="480997" cy="555746"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>78</xdr:col>
+      <xdr:colOff>555172</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>119743</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66C2A9D9-67BD-29BC-7E12-989D915EDC7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="47286863" y="16285029"/>
+          <a:ext cx="879022" cy="246289"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
@@ -3699,22 +4211,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>80</xdr:col>
-      <xdr:colOff>74743</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>51227</xdr:rowOff>
+      <xdr:colOff>35169</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>46892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>80</xdr:col>
-      <xdr:colOff>551930</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>99637</xdr:rowOff>
+      <xdr:col>81</xdr:col>
+      <xdr:colOff>451339</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>112205</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="Arrow: Down 47">
+        <xdr:cNvPr id="51" name="Rectangle 50">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE49285-461A-4257-988B-A399549137A0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4389FA2-4E35-4BB3-AA67-2BA6D6EEB5EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3722,10 +4234,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="49114886" y="21373620"/>
-          <a:ext cx="477187" cy="2361624"/>
+          <a:off x="48861784" y="16717107"/>
+          <a:ext cx="1025770" cy="247021"/>
         </a:xfrm>
-        <a:prstGeom prst="downArrow">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
@@ -3758,32 +4270,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>78</xdr:col>
-      <xdr:colOff>54432</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>40786</xdr:rowOff>
+      <xdr:col>81</xdr:col>
+      <xdr:colOff>74743</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>51227</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>78</xdr:col>
-      <xdr:colOff>550005</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>81</xdr:col>
+      <xdr:colOff>551930</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>99637</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="Arrow: Down 49">
+        <xdr:cNvPr id="52" name="Arrow: Down 51">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BDD8F75-8BA8-4503-8063-BD1C45DE56D1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57344222-3FAA-429E-A8AC-972A04CD1118}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="16200000">
-          <a:off x="47878669" y="24157513"/>
-          <a:ext cx="478100" cy="495573"/>
+        <a:xfrm>
+          <a:off x="48905496" y="21530662"/>
+          <a:ext cx="477187" cy="2352340"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
           <a:avLst/>
@@ -4223,11 +4735,11 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="15" t="s">
+      <c r="N33" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
+      <c r="O33" s="137"/>
+      <c r="P33" s="137"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
@@ -4248,13 +4760,13 @@
       <c r="AJ33" s="7"/>
       <c r="AK33" s="7"/>
       <c r="AL33" s="7"/>
-      <c r="AM33" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AN33" s="15"/>
-      <c r="AO33" s="15"/>
-      <c r="AP33" s="15"/>
-      <c r="AQ33" s="15"/>
+      <c r="AM33" s="81" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN33" s="81"/>
+      <c r="AO33" s="81"/>
+      <c r="AP33" s="81"/>
+      <c r="AQ33" s="81"/>
       <c r="AR33" s="7"/>
       <c r="AS33" s="7"/>
       <c r="AT33" s="7"/>
@@ -4272,27 +4784,27 @@
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
+      <c r="F34" s="132"/>
+      <c r="G34" s="132"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="132"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
+      <c r="N34" s="137"/>
+      <c r="O34" s="137"/>
+      <c r="P34" s="137"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
-      <c r="S34" s="15" t="s">
+      <c r="S34" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
+      <c r="T34" s="82"/>
+      <c r="U34" s="82"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
@@ -4300,25 +4812,25 @@
       <c r="AB34" s="7"/>
       <c r="AC34" s="7"/>
       <c r="AD34" s="7"/>
-      <c r="AE34" s="8" t="s">
+      <c r="AE34" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="AF34" s="9"/>
-      <c r="AG34" s="9"/>
-      <c r="AH34" s="9"/>
-      <c r="AI34" s="9"/>
+      <c r="AF34" s="132"/>
+      <c r="AG34" s="132"/>
+      <c r="AH34" s="132"/>
+      <c r="AI34" s="132"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="7"/>
       <c r="AL34" s="7"/>
-      <c r="AM34" s="15"/>
-      <c r="AN34" s="15"/>
-      <c r="AO34" s="15"/>
-      <c r="AP34" s="15"/>
-      <c r="AQ34" s="15"/>
+      <c r="AM34" s="81"/>
+      <c r="AN34" s="81"/>
+      <c r="AO34" s="81"/>
+      <c r="AP34" s="81"/>
+      <c r="AQ34" s="81"/>
       <c r="AR34" s="7"/>
-      <c r="AS34" s="15"/>
-      <c r="AT34" s="23"/>
-      <c r="AU34" s="23"/>
+      <c r="AS34" s="81"/>
+      <c r="AT34" s="82"/>
+      <c r="AU34" s="82"/>
       <c r="AV34" s="7"/>
       <c r="AW34" s="7"/>
       <c r="AX34" s="7"/>
@@ -4332,11 +4844,11 @@
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="132"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -4356,11 +4868,11 @@
       <c r="AB35" s="7"/>
       <c r="AC35" s="7"/>
       <c r="AD35" s="7"/>
-      <c r="AE35" s="9"/>
-      <c r="AF35" s="9"/>
-      <c r="AG35" s="9"/>
-      <c r="AH35" s="9"/>
-      <c r="AI35" s="9"/>
+      <c r="AE35" s="132"/>
+      <c r="AF35" s="132"/>
+      <c r="AG35" s="132"/>
+      <c r="AH35" s="132"/>
+      <c r="AI35" s="132"/>
       <c r="AJ35" s="7"/>
       <c r="AK35" s="7"/>
       <c r="AL35" s="7"/>
@@ -4450,20 +4962,20 @@
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
-      <c r="O37" s="35" t="s">
+      <c r="O37" s="14" t="s">
         <v>13</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
-      <c r="T37" s="36" t="s">
+      <c r="T37" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="U37" s="37" t="s">
+      <c r="U37" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="V37" s="37"/>
+      <c r="V37" s="131"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -4480,16 +4992,16 @@
       <c r="AL37" s="7"/>
       <c r="AM37" s="7"/>
       <c r="AN37" s="7"/>
-      <c r="AO37" s="35" t="s">
+      <c r="AO37" s="14" t="s">
         <v>29</v>
       </c>
       <c r="AP37" s="7"/>
       <c r="AQ37" s="7"/>
       <c r="AR37" s="7"/>
       <c r="AS37" s="7"/>
-      <c r="AT37" s="29"/>
-      <c r="AU37" s="37"/>
-      <c r="AV37" s="37"/>
+      <c r="AT37" s="7"/>
+      <c r="AU37" s="131"/>
+      <c r="AV37" s="131"/>
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
       <c r="AY37" s="7"/>
@@ -4522,50 +5034,50 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
-      <c r="O38" s="34"/>
+      <c r="O38" s="13"/>
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="40" t="s">
+      <c r="T38" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="U38" s="37"/>
-      <c r="V38" s="37"/>
+      <c r="U38" s="131"/>
+      <c r="V38" s="131"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
       <c r="AB38" s="7"/>
       <c r="AC38" s="1" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AD38" s="6"/>
       <c r="AE38" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="AF38" s="6"/>
       <c r="AG38" s="1" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="AH38" s="6"/>
       <c r="AI38" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="AJ38" s="6"/>
       <c r="AK38" s="1" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="AL38" s="7"/>
       <c r="AM38" s="7"/>
       <c r="AN38" s="7"/>
-      <c r="AO38" s="72"/>
+      <c r="AO38" s="74"/>
       <c r="AP38" s="7"/>
       <c r="AQ38" s="7"/>
       <c r="AR38" s="7"/>
       <c r="AS38" s="7"/>
-      <c r="AT38" s="51"/>
-      <c r="AU38" s="37"/>
-      <c r="AV38" s="37"/>
+      <c r="AT38" s="132"/>
+      <c r="AU38" s="131"/>
+      <c r="AV38" s="131"/>
       <c r="AW38" s="7"/>
       <c r="AX38" s="7"/>
       <c r="AY38" s="7"/>
@@ -4584,41 +5096,41 @@
       <c r="H39" s="6"/>
       <c r="I39" s="3"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="13"/>
+      <c r="K39" s="9"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
-      <c r="O39" s="34"/>
+      <c r="O39" s="13"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="37"/>
-      <c r="V39" s="37"/>
+      <c r="T39" s="149"/>
+      <c r="U39" s="131"/>
+      <c r="V39" s="131"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="AB39" s="7"/>
-      <c r="AC39" s="49"/>
+      <c r="AC39" s="124"/>
       <c r="AD39" s="6"/>
-      <c r="AE39" s="3"/>
+      <c r="AE39" s="17"/>
       <c r="AF39" s="6"/>
-      <c r="AG39" s="43"/>
+      <c r="AG39" s="17"/>
       <c r="AH39" s="6"/>
-      <c r="AI39" s="43"/>
+      <c r="AI39" s="17"/>
       <c r="AJ39" s="6"/>
-      <c r="AK39" s="40"/>
+      <c r="AK39" s="100"/>
       <c r="AL39" s="7"/>
       <c r="AM39" s="7"/>
       <c r="AN39" s="7"/>
-      <c r="AO39" s="72"/>
+      <c r="AO39" s="74"/>
       <c r="AP39" s="7"/>
       <c r="AQ39" s="7"/>
       <c r="AR39" s="7"/>
       <c r="AS39" s="7"/>
-      <c r="AT39" s="51"/>
-      <c r="AU39" s="37"/>
-      <c r="AV39" s="37"/>
+      <c r="AT39" s="132"/>
+      <c r="AU39" s="131"/>
+      <c r="AV39" s="131"/>
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
@@ -4641,28 +5153,28 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
-      <c r="O40" s="14" t="s">
+      <c r="O40" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="37"/>
-      <c r="V40" s="37"/>
+      <c r="T40" s="155"/>
+      <c r="U40" s="131"/>
+      <c r="V40" s="131"/>
       <c r="W40" s="7"/>
       <c r="X40" s="7"/>
       <c r="AB40" s="7"/>
-      <c r="AC40" s="49"/>
+      <c r="AC40" s="124"/>
       <c r="AD40" s="6"/>
-      <c r="AE40" s="3"/>
+      <c r="AE40" s="17"/>
       <c r="AF40" s="6"/>
-      <c r="AG40" s="43"/>
+      <c r="AG40" s="17"/>
       <c r="AH40" s="6"/>
-      <c r="AI40" s="43"/>
+      <c r="AI40" s="17"/>
       <c r="AJ40" s="6"/>
-      <c r="AK40" s="40"/>
+      <c r="AK40" s="100"/>
       <c r="AL40" s="7"/>
       <c r="AM40" s="7"/>
       <c r="AN40" s="7"/>
@@ -4673,9 +5185,9 @@
       <c r="AQ40" s="7"/>
       <c r="AR40" s="7"/>
       <c r="AS40" s="7"/>
-      <c r="AT40" s="50"/>
-      <c r="AU40" s="37"/>
-      <c r="AV40" s="37"/>
+      <c r="AT40" s="7"/>
+      <c r="AU40" s="131"/>
+      <c r="AV40" s="131"/>
       <c r="AW40" s="7"/>
       <c r="AX40" s="7"/>
       <c r="AY40" s="7"/>
@@ -4698,39 +5210,39 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="10" t="s">
+      <c r="O41" s="138" t="s">
         <v>15</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
-      <c r="T41" s="30"/>
+      <c r="T41" s="155"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="AB41" s="7"/>
-      <c r="AC41" s="46"/>
+      <c r="AC41" s="19"/>
       <c r="AD41" s="6"/>
-      <c r="AE41" s="3"/>
+      <c r="AE41" s="17"/>
       <c r="AF41" s="6"/>
-      <c r="AG41" s="43"/>
+      <c r="AG41" s="17"/>
       <c r="AH41" s="6"/>
-      <c r="AI41" s="43"/>
+      <c r="AI41" s="17"/>
       <c r="AJ41" s="6"/>
-      <c r="AK41" s="43"/>
+      <c r="AK41" s="17"/>
       <c r="AL41" s="7"/>
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
-      <c r="AO41" s="74" t="s">
+      <c r="AO41" s="133" t="s">
         <v>15</v>
       </c>
       <c r="AP41" s="7"/>
       <c r="AQ41" s="7"/>
       <c r="AR41" s="7"/>
       <c r="AS41" s="7"/>
-      <c r="AT41" s="50"/>
+      <c r="AT41" s="7"/>
       <c r="AU41" s="7"/>
       <c r="AV41" s="7"/>
       <c r="AW41" s="7"/>
@@ -4755,35 +5267,35 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="10"/>
+      <c r="O42" s="138"/>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
-      <c r="T42" s="30"/>
+      <c r="T42" s="155"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
       <c r="X42" s="7"/>
       <c r="AB42" s="7"/>
-      <c r="AC42" s="46"/>
+      <c r="AC42" s="19"/>
       <c r="AD42" s="6"/>
-      <c r="AE42" s="3"/>
+      <c r="AE42" s="17"/>
       <c r="AF42" s="6"/>
-      <c r="AG42" s="43"/>
+      <c r="AG42" s="17"/>
       <c r="AH42" s="6"/>
-      <c r="AI42" s="43"/>
+      <c r="AI42" s="17"/>
       <c r="AJ42" s="6"/>
-      <c r="AK42" s="43"/>
+      <c r="AK42" s="17"/>
       <c r="AL42" s="7"/>
       <c r="AM42" s="7"/>
       <c r="AN42" s="7"/>
-      <c r="AO42" s="74"/>
+      <c r="AO42" s="133"/>
       <c r="AP42" s="7"/>
       <c r="AQ42" s="7"/>
       <c r="AR42" s="7"/>
       <c r="AS42" s="7"/>
-      <c r="AT42" s="50"/>
+      <c r="AT42" s="7"/>
       <c r="AU42" s="7"/>
       <c r="AV42" s="7"/>
       <c r="AW42" s="7"/>
@@ -4808,41 +5320,39 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="129" t="s">
         <v>23</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
-      <c r="T43" s="30"/>
+      <c r="T43" s="155"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="AB43" s="7"/>
-      <c r="AC43" s="46"/>
+      <c r="AC43" s="19"/>
       <c r="AD43" s="6"/>
-      <c r="AE43" s="3"/>
+      <c r="AE43" s="17"/>
       <c r="AF43" s="6"/>
-      <c r="AG43" s="43"/>
+      <c r="AG43" s="17"/>
       <c r="AH43" s="6"/>
-      <c r="AI43" s="43"/>
+      <c r="AI43" s="17"/>
       <c r="AJ43" s="6"/>
-      <c r="AK43" s="43"/>
+      <c r="AK43" s="17"/>
       <c r="AL43" s="7"/>
       <c r="AM43" s="7"/>
       <c r="AN43" s="7"/>
-      <c r="AO43" s="75" t="s">
+      <c r="AO43" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="AP43" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ43" s="52"/>
-      <c r="AR43" s="52"/>
-      <c r="AS43" s="52"/>
-      <c r="AT43" s="50"/>
+      <c r="AP43" s="7"/>
+      <c r="AQ43" s="7"/>
+      <c r="AR43" s="7"/>
+      <c r="AS43" s="7"/>
+      <c r="AT43" s="7"/>
       <c r="AU43" s="7"/>
       <c r="AV43" s="7"/>
       <c r="AW43" s="7"/>
@@ -4867,41 +5377,41 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
-      <c r="O44" s="12"/>
+      <c r="O44" s="130"/>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
-      <c r="T44" s="30"/>
-      <c r="U44" s="31" t="s">
+      <c r="T44" s="155"/>
+      <c r="U44" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="V44" s="32"/>
-      <c r="W44" s="32"/>
-      <c r="X44" s="32"/>
+      <c r="V44" s="136"/>
+      <c r="W44" s="136"/>
+      <c r="X44" s="136"/>
       <c r="AB44" s="7"/>
-      <c r="AC44" s="46"/>
+      <c r="AC44" s="19"/>
       <c r="AD44" s="6"/>
-      <c r="AE44" s="3"/>
+      <c r="AE44" s="17"/>
       <c r="AF44" s="6"/>
-      <c r="AG44" s="43"/>
+      <c r="AG44" s="17"/>
       <c r="AH44" s="6"/>
-      <c r="AI44" s="43"/>
+      <c r="AI44" s="17"/>
       <c r="AJ44" s="6"/>
-      <c r="AK44" s="43"/>
+      <c r="AK44" s="17"/>
       <c r="AL44" s="7"/>
       <c r="AM44" s="7"/>
       <c r="AN44" s="7"/>
-      <c r="AO44" s="76"/>
-      <c r="AP44" s="52"/>
-      <c r="AQ44" s="52"/>
-      <c r="AR44" s="52"/>
-      <c r="AS44" s="52"/>
-      <c r="AT44" s="50"/>
-      <c r="AU44" s="32"/>
-      <c r="AV44" s="32"/>
-      <c r="AW44" s="32"/>
-      <c r="AX44" s="32"/>
+      <c r="AO44" s="135"/>
+      <c r="AP44" s="7"/>
+      <c r="AQ44" s="7"/>
+      <c r="AR44" s="7"/>
+      <c r="AS44" s="7"/>
+      <c r="AT44" s="7"/>
+      <c r="AU44" s="136"/>
+      <c r="AV44" s="136"/>
+      <c r="AW44" s="136"/>
+      <c r="AX44" s="136"/>
       <c r="AY44" s="7"/>
       <c r="AZ44" s="7"/>
       <c r="BA44" s="7"/>
@@ -4922,43 +5432,45 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="11" t="s">
+      <c r="O45" s="129" t="s">
         <v>22</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="32"/>
-      <c r="W45" s="32"/>
-      <c r="X45" s="32"/>
+      <c r="T45" s="155"/>
+      <c r="U45" s="152"/>
+      <c r="V45" s="136"/>
+      <c r="W45" s="136"/>
+      <c r="X45" s="136"/>
       <c r="AB45" s="7"/>
-      <c r="AC45" s="46"/>
+      <c r="AC45" s="19"/>
       <c r="AD45" s="6"/>
-      <c r="AE45" s="3"/>
+      <c r="AE45" s="17"/>
       <c r="AF45" s="6"/>
-      <c r="AG45" s="43"/>
+      <c r="AG45" s="17"/>
       <c r="AH45" s="6"/>
-      <c r="AI45" s="43"/>
+      <c r="AI45" s="17"/>
       <c r="AJ45" s="6"/>
-      <c r="AK45" s="43"/>
+      <c r="AK45" s="17"/>
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
       <c r="AN45" s="7"/>
-      <c r="AO45" s="75" t="s">
+      <c r="AO45" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="AP45" s="7"/>
-      <c r="AQ45" s="7"/>
-      <c r="AR45" s="7"/>
-      <c r="AS45" s="7"/>
-      <c r="AT45" s="50"/>
-      <c r="AU45" s="32"/>
-      <c r="AV45" s="32"/>
-      <c r="AW45" s="32"/>
-      <c r="AX45" s="32"/>
+      <c r="AP45" s="150" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ45" s="151"/>
+      <c r="AR45" s="151"/>
+      <c r="AS45" s="151"/>
+      <c r="AT45" s="151"/>
+      <c r="AU45" s="136"/>
+      <c r="AV45" s="136"/>
+      <c r="AW45" s="136"/>
+      <c r="AX45" s="136"/>
       <c r="AY45" s="7"/>
       <c r="AZ45" s="7"/>
       <c r="BA45" s="7"/>
@@ -4989,50 +5501,50 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="12"/>
+      <c r="O46" s="130"/>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="24" t="s">
+      <c r="T46" s="155"/>
+      <c r="U46" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
+      <c r="V46" s="137"/>
+      <c r="W46" s="137"/>
       <c r="X46" s="7"/>
       <c r="AB46" s="7"/>
-      <c r="AC46" s="47">
+      <c r="AC46" s="20">
         <v>1654</v>
       </c>
       <c r="AD46" s="6"/>
-      <c r="AE46" s="3">
+      <c r="AE46" s="17">
         <v>1654</v>
       </c>
       <c r="AF46" s="6"/>
-      <c r="AG46" s="43">
+      <c r="AG46" s="17">
         <v>1654</v>
       </c>
       <c r="AH46" s="6"/>
-      <c r="AI46" s="43">
+      <c r="AI46" s="17">
         <v>1654</v>
       </c>
       <c r="AJ46" s="6"/>
-      <c r="AK46" s="43">
+      <c r="AK46" s="17">
         <v>1654</v>
       </c>
       <c r="AL46" s="7"/>
       <c r="AM46" s="7"/>
       <c r="AN46" s="7"/>
-      <c r="AO46" s="76"/>
-      <c r="AP46" s="7"/>
-      <c r="AQ46" s="7"/>
-      <c r="AR46" s="7"/>
-      <c r="AS46" s="7"/>
-      <c r="AT46" s="50"/>
-      <c r="AU46" s="50"/>
-      <c r="AV46" s="16"/>
-      <c r="AW46" s="16"/>
+      <c r="AO46" s="135"/>
+      <c r="AP46" s="150"/>
+      <c r="AQ46" s="151"/>
+      <c r="AR46" s="151"/>
+      <c r="AS46" s="151"/>
+      <c r="AT46" s="151"/>
+      <c r="AU46" s="137"/>
+      <c r="AV46" s="137"/>
+      <c r="AW46" s="137"/>
       <c r="AX46" s="7"/>
       <c r="AY46" s="7"/>
       <c r="AZ46" s="7"/>
@@ -5064,49 +5576,49 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="10" t="s">
+      <c r="O47" s="138" t="s">
         <v>21</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7"/>
       <c r="S47" s="7"/>
-      <c r="T47" s="30"/>
+      <c r="T47" s="155"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
       <c r="AB47" s="7"/>
-      <c r="AC47" s="47" t="s">
+      <c r="AC47" s="20" t="s">
         <v>10</v>
       </c>
       <c r="AD47" s="6"/>
-      <c r="AE47" s="3" t="s">
+      <c r="AE47" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AF47" s="6"/>
-      <c r="AG47" s="43" t="s">
+      <c r="AG47" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AH47" s="6"/>
-      <c r="AI47" s="43" t="s">
+      <c r="AI47" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AJ47" s="6"/>
-      <c r="AK47" s="43" t="s">
+      <c r="AK47" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AL47" s="7"/>
       <c r="AM47" s="7"/>
       <c r="AN47" s="7"/>
-      <c r="AO47" s="74" t="s">
+      <c r="AO47" s="133" t="s">
         <v>21</v>
       </c>
       <c r="AP47" s="7"/>
       <c r="AQ47" s="7"/>
       <c r="AR47" s="7"/>
       <c r="AS47" s="7"/>
-      <c r="AT47" s="50"/>
+      <c r="AT47" s="7"/>
       <c r="AU47" s="7"/>
       <c r="AV47" s="7"/>
       <c r="AW47" s="7"/>
@@ -5141,47 +5653,47 @@
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="27" t="s">
+      <c r="O48" s="138"/>
+      <c r="P48" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="Q48" s="28"/>
-      <c r="R48" s="28"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="30"/>
+      <c r="Q48" s="144"/>
+      <c r="R48" s="144"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="155"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
       <c r="X48" s="7"/>
       <c r="AB48" s="7"/>
-      <c r="AC48" s="47" t="s">
+      <c r="AC48" s="20" t="s">
         <v>11</v>
       </c>
       <c r="AD48" s="6"/>
-      <c r="AE48" s="3" t="s">
+      <c r="AE48" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AF48" s="6"/>
-      <c r="AG48" s="43" t="s">
+      <c r="AG48" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AH48" s="6"/>
-      <c r="AI48" s="43" t="s">
+      <c r="AI48" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AJ48" s="6"/>
-      <c r="AK48" s="43" t="s">
+      <c r="AK48" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AL48" s="7"/>
       <c r="AM48" s="7"/>
       <c r="AN48" s="7"/>
-      <c r="AO48" s="74"/>
-      <c r="AP48" s="27"/>
-      <c r="AQ48" s="28"/>
-      <c r="AR48" s="28"/>
-      <c r="AS48" s="29"/>
-      <c r="AT48" s="50"/>
+      <c r="AO48" s="133"/>
+      <c r="AP48" s="143"/>
+      <c r="AQ48" s="144"/>
+      <c r="AR48" s="144"/>
+      <c r="AS48" s="7"/>
+      <c r="AT48" s="7"/>
       <c r="AU48" s="7"/>
       <c r="AV48" s="7"/>
       <c r="AW48" s="7"/>
@@ -5192,7 +5704,7 @@
       <c r="BB48" s="7"/>
       <c r="BC48" s="7"/>
     </row>
-    <row r="49" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="7"/>
       <c r="C49" s="2"/>
       <c r="D49" s="6"/>
@@ -5206,52 +5718,52 @@
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="10" t="s">
+      <c r="O49" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="26" t="s">
+      <c r="P49" s="144"/>
+      <c r="Q49" s="144"/>
+      <c r="R49" s="144"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="155"/>
+      <c r="U49" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
-      <c r="X49" s="33"/>
+      <c r="V49" s="143"/>
+      <c r="W49" s="143"/>
+      <c r="X49" s="143"/>
       <c r="AB49" s="7"/>
-      <c r="AC49" s="46"/>
+      <c r="AC49" s="19"/>
       <c r="AD49" s="6"/>
-      <c r="AE49" s="3"/>
+      <c r="AE49" s="17"/>
       <c r="AF49" s="6"/>
-      <c r="AG49" s="43"/>
+      <c r="AG49" s="17"/>
       <c r="AH49" s="6"/>
-      <c r="AI49" s="43"/>
+      <c r="AI49" s="17"/>
       <c r="AJ49" s="6"/>
-      <c r="AK49" s="43"/>
+      <c r="AK49" s="17"/>
       <c r="AL49" s="7"/>
       <c r="AM49" s="7"/>
       <c r="AN49" s="7"/>
-      <c r="AO49" s="77" t="s">
+      <c r="AO49" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="AP49" s="28"/>
-      <c r="AQ49" s="28"/>
-      <c r="AR49" s="28"/>
-      <c r="AS49" s="29"/>
-      <c r="AT49" s="50"/>
-      <c r="AU49" s="27"/>
-      <c r="AV49" s="33"/>
-      <c r="AW49" s="33"/>
-      <c r="AX49" s="33"/>
+      <c r="AP49" s="144"/>
+      <c r="AQ49" s="144"/>
+      <c r="AR49" s="144"/>
+      <c r="AS49" s="7"/>
+      <c r="AT49" s="7"/>
+      <c r="AU49" s="72"/>
+      <c r="AV49" s="72"/>
+      <c r="AW49" s="72"/>
+      <c r="AX49" s="72"/>
       <c r="AY49" s="7"/>
       <c r="AZ49" s="7"/>
       <c r="BA49" s="7"/>
       <c r="BB49" s="7"/>
       <c r="BC49" s="7"/>
     </row>
-    <row r="50" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="7"/>
       <c r="C50" s="2"/>
       <c r="D50" s="6"/>
@@ -5265,46 +5777,46 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="10"/>
+      <c r="O50" s="138"/>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
-      <c r="T50" s="20"/>
-      <c r="U50" s="26"/>
-      <c r="V50" s="33"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33"/>
+      <c r="T50" s="12"/>
+      <c r="U50" s="153"/>
+      <c r="V50" s="143"/>
+      <c r="W50" s="143"/>
+      <c r="X50" s="143"/>
       <c r="AB50" s="7"/>
-      <c r="AC50" s="46"/>
+      <c r="AC50" s="19"/>
       <c r="AD50" s="6"/>
-      <c r="AE50" s="3"/>
+      <c r="AE50" s="17"/>
       <c r="AF50" s="6"/>
-      <c r="AG50" s="43"/>
+      <c r="AG50" s="17"/>
       <c r="AH50" s="6"/>
-      <c r="AI50" s="43"/>
+      <c r="AI50" s="17"/>
       <c r="AJ50" s="6"/>
-      <c r="AK50" s="43"/>
+      <c r="AK50" s="17"/>
       <c r="AL50" s="7"/>
       <c r="AM50" s="7"/>
       <c r="AN50" s="7"/>
-      <c r="AO50" s="77"/>
+      <c r="AO50" s="133"/>
       <c r="AP50" s="7"/>
       <c r="AQ50" s="7"/>
       <c r="AR50" s="7"/>
       <c r="AS50" s="7"/>
-      <c r="AT50" s="29"/>
-      <c r="AU50" s="27"/>
-      <c r="AV50" s="33"/>
-      <c r="AW50" s="33"/>
-      <c r="AX50" s="33"/>
+      <c r="AT50" s="7"/>
+      <c r="AU50" s="72"/>
+      <c r="AV50" s="72"/>
+      <c r="AW50" s="72"/>
+      <c r="AX50" s="72"/>
       <c r="AY50" s="7"/>
       <c r="AZ50" s="7"/>
       <c r="BA50" s="7"/>
       <c r="BB50" s="7"/>
       <c r="BC50" s="7"/>
     </row>
-    <row r="51" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="7"/>
       <c r="C51" s="2"/>
       <c r="D51" s="6"/>
@@ -5318,52 +5830,50 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="11" t="s">
+      <c r="O51" s="129" t="s">
         <v>20</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
       <c r="S51" s="7"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="26"/>
-      <c r="V51" s="33"/>
-      <c r="W51" s="33"/>
-      <c r="X51" s="33"/>
+      <c r="T51" s="141"/>
+      <c r="U51" s="153"/>
+      <c r="V51" s="143"/>
+      <c r="W51" s="143"/>
+      <c r="X51" s="143"/>
       <c r="AB51" s="7"/>
-      <c r="AC51" s="46"/>
+      <c r="AC51" s="19"/>
       <c r="AD51" s="6"/>
-      <c r="AE51" s="3"/>
+      <c r="AE51" s="17"/>
       <c r="AF51" s="6"/>
-      <c r="AG51" s="43"/>
+      <c r="AG51" s="17"/>
       <c r="AH51" s="6"/>
-      <c r="AI51" s="43"/>
+      <c r="AI51" s="17"/>
       <c r="AJ51" s="6"/>
-      <c r="AK51" s="43"/>
+      <c r="AK51" s="17"/>
       <c r="AL51" s="7"/>
       <c r="AM51" s="7"/>
       <c r="AN51" s="7"/>
-      <c r="AO51" s="78" t="s">
+      <c r="AO51" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="AP51" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ51" s="37"/>
-      <c r="AR51" s="37"/>
-      <c r="AS51" s="37"/>
-      <c r="AT51" s="50"/>
-      <c r="AU51" s="27"/>
-      <c r="AV51" s="33"/>
-      <c r="AW51" s="33"/>
-      <c r="AX51" s="33"/>
+      <c r="AP51" s="7"/>
+      <c r="AQ51" s="7"/>
+      <c r="AR51" s="7"/>
+      <c r="AS51" s="7"/>
+      <c r="AT51" s="7"/>
+      <c r="AU51" s="7"/>
+      <c r="AV51" s="72"/>
+      <c r="AW51" s="72"/>
+      <c r="AX51" s="72"/>
       <c r="AY51" s="7"/>
       <c r="AZ51" s="7"/>
       <c r="BA51" s="7"/>
       <c r="BB51" s="7"/>
       <c r="BC51" s="7"/>
     </row>
-    <row r="52" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="7"/>
       <c r="C52" s="2"/>
       <c r="D52" s="6"/>
@@ -5377,48 +5887,50 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="12"/>
+      <c r="O52" s="130"/>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
-      <c r="T52" s="18"/>
-      <c r="U52" s="26" t="s">
+      <c r="T52" s="141"/>
+      <c r="U52" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="V52" s="33"/>
-      <c r="W52" s="33"/>
-      <c r="X52" s="33"/>
+      <c r="V52" s="143"/>
+      <c r="W52" s="143"/>
+      <c r="X52" s="143"/>
       <c r="AB52" s="7"/>
-      <c r="AC52" s="46"/>
+      <c r="AC52" s="19"/>
       <c r="AD52" s="6"/>
-      <c r="AE52" s="3"/>
+      <c r="AE52" s="17"/>
       <c r="AF52" s="6"/>
-      <c r="AG52" s="43"/>
+      <c r="AG52" s="17"/>
       <c r="AH52" s="6"/>
-      <c r="AI52" s="43"/>
+      <c r="AI52" s="17"/>
       <c r="AJ52" s="6"/>
-      <c r="AK52" s="43"/>
+      <c r="AK52" s="17"/>
       <c r="AL52" s="7"/>
       <c r="AM52" s="7"/>
       <c r="AN52" s="7"/>
-      <c r="AO52" s="79"/>
-      <c r="AP52" s="52"/>
-      <c r="AQ52" s="37"/>
-      <c r="AR52" s="37"/>
-      <c r="AS52" s="37"/>
-      <c r="AT52" s="50"/>
-      <c r="AU52" s="27"/>
-      <c r="AV52" s="33"/>
-      <c r="AW52" s="33"/>
-      <c r="AX52" s="33"/>
+      <c r="AO52" s="126"/>
+      <c r="AP52" s="148" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ52" s="131"/>
+      <c r="AR52" s="131"/>
+      <c r="AS52" s="131"/>
+      <c r="AT52" s="131"/>
+      <c r="AU52" s="131"/>
+      <c r="AV52" s="72"/>
+      <c r="AW52" s="72"/>
+      <c r="AX52" s="72"/>
       <c r="AY52" s="7"/>
       <c r="AZ52" s="7"/>
       <c r="BA52" s="7"/>
       <c r="BB52" s="7"/>
       <c r="BC52" s="7"/>
     </row>
-    <row r="53" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="7"/>
       <c r="C53" s="2"/>
       <c r="D53" s="6"/>
@@ -5432,50 +5944,50 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="11" t="s">
+      <c r="O53" s="129" t="s">
         <v>16</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
       <c r="S53" s="7"/>
-      <c r="T53" s="18"/>
-      <c r="U53" s="26"/>
-      <c r="V53" s="33"/>
-      <c r="W53" s="33"/>
-      <c r="X53" s="33"/>
+      <c r="T53" s="141"/>
+      <c r="U53" s="153"/>
+      <c r="V53" s="143"/>
+      <c r="W53" s="143"/>
+      <c r="X53" s="143"/>
       <c r="AB53" s="7"/>
-      <c r="AC53" s="46"/>
+      <c r="AC53" s="19"/>
       <c r="AD53" s="6"/>
-      <c r="AE53" s="3"/>
+      <c r="AE53" s="17"/>
       <c r="AF53" s="6"/>
-      <c r="AG53" s="43"/>
+      <c r="AG53" s="17"/>
       <c r="AH53" s="6"/>
-      <c r="AI53" s="43"/>
+      <c r="AI53" s="17"/>
       <c r="AJ53" s="6"/>
-      <c r="AK53" s="43"/>
+      <c r="AK53" s="17"/>
       <c r="AL53" s="7"/>
       <c r="AM53" s="7"/>
       <c r="AN53" s="7"/>
-      <c r="AO53" s="78" t="s">
+      <c r="AO53" s="125" t="s">
         <v>16</v>
       </c>
-      <c r="AP53" s="7"/>
-      <c r="AQ53" s="7"/>
-      <c r="AR53" s="7"/>
-      <c r="AS53" s="7"/>
-      <c r="AT53" s="50"/>
-      <c r="AU53" s="27"/>
-      <c r="AV53" s="33"/>
-      <c r="AW53" s="33"/>
-      <c r="AX53" s="33"/>
+      <c r="AP53" s="148"/>
+      <c r="AQ53" s="131"/>
+      <c r="AR53" s="131"/>
+      <c r="AS53" s="131"/>
+      <c r="AT53" s="131"/>
+      <c r="AU53" s="131"/>
+      <c r="AV53" s="72"/>
+      <c r="AW53" s="72"/>
+      <c r="AX53" s="72"/>
       <c r="AY53" s="7"/>
       <c r="AZ53" s="7"/>
       <c r="BA53" s="7"/>
       <c r="BB53" s="7"/>
       <c r="BC53" s="7"/>
     </row>
-    <row r="54" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="7"/>
       <c r="C54" s="4"/>
       <c r="D54" s="6"/>
@@ -5489,39 +6001,39 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="12"/>
+      <c r="O54" s="130"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
-      <c r="T54" s="18"/>
-      <c r="U54" s="26"/>
-      <c r="V54" s="33"/>
-      <c r="W54" s="33"/>
-      <c r="X54" s="33"/>
+      <c r="T54" s="141"/>
+      <c r="U54" s="153"/>
+      <c r="V54" s="143"/>
+      <c r="W54" s="143"/>
+      <c r="X54" s="143"/>
       <c r="AB54" s="7"/>
-      <c r="AC54" s="48"/>
+      <c r="AC54" s="21"/>
       <c r="AD54" s="6"/>
-      <c r="AE54" s="5"/>
+      <c r="AE54" s="18"/>
       <c r="AF54" s="6"/>
-      <c r="AG54" s="44"/>
+      <c r="AG54" s="18"/>
       <c r="AH54" s="6"/>
-      <c r="AI54" s="44"/>
+      <c r="AI54" s="18"/>
       <c r="AJ54" s="6"/>
-      <c r="AK54" s="44"/>
+      <c r="AK54" s="18"/>
       <c r="AL54" s="7"/>
       <c r="AM54" s="7"/>
       <c r="AN54" s="7"/>
-      <c r="AO54" s="79"/>
-      <c r="AP54" s="7"/>
-      <c r="AQ54" s="7"/>
-      <c r="AR54" s="7"/>
-      <c r="AS54" s="7"/>
-      <c r="AT54" s="50"/>
-      <c r="AU54" s="27"/>
-      <c r="AV54" s="33"/>
-      <c r="AW54" s="33"/>
-      <c r="AX54" s="33"/>
+      <c r="AO54" s="126"/>
+      <c r="AP54" s="71"/>
+      <c r="AQ54" s="70"/>
+      <c r="AR54" s="70"/>
+      <c r="AS54" s="70"/>
+      <c r="AT54" s="70"/>
+      <c r="AU54" s="70"/>
+      <c r="AV54" s="72"/>
+      <c r="AW54" s="72"/>
+      <c r="AX54" s="72"/>
       <c r="AY54" s="7"/>
       <c r="AZ54" s="7"/>
       <c r="BA54" s="7"/>
@@ -5542,14 +6054,14 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="11" t="s">
+      <c r="O55" s="129" t="s">
         <v>17</v>
       </c>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
       <c r="S55" s="7"/>
-      <c r="T55" s="19"/>
+      <c r="T55" s="142"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
       <c r="W55" s="7"/>
@@ -5567,14 +6079,14 @@
       <c r="AL55" s="7"/>
       <c r="AM55" s="7"/>
       <c r="AN55" s="7"/>
-      <c r="AO55" s="80" t="s">
+      <c r="AO55" s="127" t="s">
         <v>17</v>
       </c>
       <c r="AP55" s="7"/>
       <c r="AQ55" s="7"/>
       <c r="AR55" s="7"/>
       <c r="AS55" s="7"/>
-      <c r="AT55" s="50"/>
+      <c r="AT55" s="7"/>
       <c r="AU55" s="7"/>
       <c r="AV55" s="7"/>
       <c r="AW55" s="7"/>
@@ -5585,7 +6097,7 @@
       <c r="BB55" s="7"/>
       <c r="BC55" s="7"/>
     </row>
-    <row r="56" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="7"/>
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
@@ -5599,7 +6111,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="12"/>
+      <c r="O56" s="130"/>
       <c r="P56" s="7"/>
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
@@ -5622,14 +6134,14 @@
       <c r="AL56" s="7"/>
       <c r="AM56" s="7"/>
       <c r="AN56" s="7"/>
-      <c r="AO56" s="81"/>
-      <c r="AP56" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ56" s="25"/>
-      <c r="AR56" s="25"/>
-      <c r="AS56" s="25"/>
-      <c r="AT56" s="7"/>
+      <c r="AO56" s="128"/>
+      <c r="AP56" s="148" t="s">
+        <v>66</v>
+      </c>
+      <c r="AQ56" s="131"/>
+      <c r="AR56" s="131"/>
+      <c r="AS56" s="131"/>
+      <c r="AT56" s="131"/>
       <c r="AU56" s="7"/>
       <c r="AV56" s="7"/>
       <c r="AW56" s="7"/>
@@ -5664,7 +6176,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="11" t="s">
+      <c r="O57" s="129" t="s">
         <v>18</v>
       </c>
       <c r="P57" s="7"/>
@@ -5678,35 +6190,35 @@
       <c r="X57" s="7"/>
       <c r="AB57" s="7"/>
       <c r="AC57" s="1" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="AD57" s="6"/>
       <c r="AE57" s="1" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="AF57" s="6"/>
       <c r="AG57" s="1" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="AH57" s="6"/>
       <c r="AI57" s="1" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="AJ57" s="6"/>
       <c r="AK57" s="1" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="AL57" s="7"/>
       <c r="AM57" s="7"/>
       <c r="AN57" s="7"/>
-      <c r="AO57" s="80" t="s">
+      <c r="AO57" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="AP57" s="28"/>
-      <c r="AQ57" s="25"/>
-      <c r="AR57" s="25"/>
-      <c r="AS57" s="25"/>
-      <c r="AT57" s="7"/>
+      <c r="AP57" s="148"/>
+      <c r="AQ57" s="131"/>
+      <c r="AR57" s="131"/>
+      <c r="AS57" s="131"/>
+      <c r="AT57" s="131"/>
       <c r="AU57" s="7"/>
       <c r="AV57" s="7"/>
       <c r="AW57" s="7"/>
@@ -5731,7 +6243,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="12"/>
+      <c r="O58" s="130"/>
       <c r="P58" s="7"/>
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
@@ -5742,19 +6254,19 @@
       <c r="W58" s="7"/>
       <c r="X58" s="7"/>
       <c r="AB58" s="7"/>
-      <c r="AC58" s="43"/>
+      <c r="AC58" s="17"/>
       <c r="AD58" s="6"/>
-      <c r="AE58" s="43"/>
+      <c r="AE58" s="17"/>
       <c r="AF58" s="6"/>
-      <c r="AG58" s="43"/>
+      <c r="AG58" s="17"/>
       <c r="AH58" s="6"/>
-      <c r="AI58" s="43"/>
+      <c r="AI58" s="17"/>
       <c r="AJ58" s="6"/>
-      <c r="AK58" s="43"/>
+      <c r="AK58" s="17"/>
       <c r="AL58" s="7"/>
       <c r="AM58" s="7"/>
       <c r="AN58" s="7"/>
-      <c r="AO58" s="82"/>
+      <c r="AO58" s="139"/>
       <c r="AP58" s="7"/>
       <c r="AQ58" s="7"/>
       <c r="AR58" s="7"/>
@@ -5795,15 +6307,15 @@
       <c r="W59" s="7"/>
       <c r="X59" s="7"/>
       <c r="AB59" s="7"/>
-      <c r="AC59" s="43"/>
+      <c r="AC59" s="17"/>
       <c r="AD59" s="6"/>
-      <c r="AE59" s="43"/>
+      <c r="AE59" s="17"/>
       <c r="AF59" s="6"/>
-      <c r="AG59" s="43"/>
+      <c r="AG59" s="17"/>
       <c r="AH59" s="6"/>
-      <c r="AI59" s="43"/>
+      <c r="AI59" s="17"/>
       <c r="AJ59" s="6"/>
-      <c r="AK59" s="43"/>
+      <c r="AK59" s="17"/>
       <c r="AL59" s="7"/>
       <c r="AM59" s="7"/>
       <c r="AN59" s="7"/>
@@ -5836,42 +6348,42 @@
       <c r="K60" s="3"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-      <c r="N60" s="22" t="s">
+      <c r="N60" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="O60" s="22"/>
-      <c r="P60" s="22"/>
+      <c r="O60" s="140"/>
+      <c r="P60" s="140"/>
       <c r="Q60" s="7"/>
-      <c r="R60" s="22" t="s">
+      <c r="R60" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="S60" s="22"/>
-      <c r="T60" s="22"/>
-      <c r="U60" s="22"/>
-      <c r="V60" s="22"/>
+      <c r="S60" s="140"/>
+      <c r="T60" s="140"/>
+      <c r="U60" s="140"/>
+      <c r="V60" s="140"/>
       <c r="W60" s="7"/>
       <c r="X60" s="7"/>
       <c r="AB60" s="7"/>
-      <c r="AC60" s="43"/>
+      <c r="AC60" s="17"/>
       <c r="AD60" s="6"/>
-      <c r="AE60" s="43"/>
+      <c r="AE60" s="17"/>
       <c r="AF60" s="6"/>
-      <c r="AG60" s="43"/>
+      <c r="AG60" s="17"/>
       <c r="AH60" s="6"/>
-      <c r="AI60" s="43"/>
+      <c r="AI60" s="17"/>
       <c r="AJ60" s="6"/>
-      <c r="AK60" s="43"/>
+      <c r="AK60" s="17"/>
       <c r="AL60" s="7"/>
       <c r="AM60" s="7"/>
-      <c r="AN60" s="38"/>
-      <c r="AO60" s="38"/>
-      <c r="AP60" s="38"/>
+      <c r="AN60" s="16"/>
+      <c r="AO60" s="16"/>
+      <c r="AP60" s="16"/>
       <c r="AQ60" s="7"/>
-      <c r="AR60" s="38"/>
-      <c r="AS60" s="38"/>
-      <c r="AT60" s="38"/>
-      <c r="AU60" s="38"/>
-      <c r="AV60" s="38"/>
+      <c r="AR60" s="16"/>
+      <c r="AS60" s="16"/>
+      <c r="AT60" s="16"/>
+      <c r="AU60" s="16"/>
+      <c r="AV60" s="16"/>
       <c r="AW60" s="7"/>
       <c r="AX60" s="7"/>
       <c r="AY60" s="7"/>
@@ -5893,42 +6405,42 @@
       <c r="K61" s="3"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
+      <c r="N61" s="140"/>
+      <c r="O61" s="140"/>
+      <c r="P61" s="140"/>
       <c r="Q61" s="7"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="22"/>
-      <c r="V61" s="22"/>
+      <c r="R61" s="140"/>
+      <c r="S61" s="140"/>
+      <c r="T61" s="140"/>
+      <c r="U61" s="140"/>
+      <c r="V61" s="140"/>
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
       <c r="AB61" s="7"/>
-      <c r="AC61" s="43"/>
+      <c r="AC61" s="17"/>
       <c r="AD61" s="6"/>
-      <c r="AE61" s="43"/>
+      <c r="AE61" s="17"/>
       <c r="AF61" s="6"/>
-      <c r="AG61" s="43"/>
+      <c r="AG61" s="17"/>
       <c r="AH61" s="6"/>
-      <c r="AI61" s="43"/>
+      <c r="AI61" s="17"/>
       <c r="AJ61" s="6"/>
-      <c r="AK61" s="43"/>
+      <c r="AK61" s="17"/>
       <c r="AL61" s="7"/>
       <c r="AM61" s="7"/>
-      <c r="AN61" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO61" s="55"/>
-      <c r="AP61" s="55"/>
-      <c r="AQ61" s="55"/>
-      <c r="AR61" s="55"/>
-      <c r="AS61" s="55"/>
-      <c r="AT61" s="55"/>
-      <c r="AU61" s="55"/>
-      <c r="AV61" s="55"/>
-      <c r="AW61" s="55"/>
-      <c r="AX61" s="56"/>
+      <c r="AN61" s="118" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO61" s="119"/>
+      <c r="AP61" s="119"/>
+      <c r="AQ61" s="119"/>
+      <c r="AR61" s="119"/>
+      <c r="AS61" s="119"/>
+      <c r="AT61" s="119"/>
+      <c r="AU61" s="119"/>
+      <c r="AV61" s="119"/>
+      <c r="AW61" s="119"/>
+      <c r="AX61" s="120"/>
       <c r="AY61" s="7"/>
       <c r="AZ61" s="7"/>
       <c r="BA61" s="7"/>
@@ -5952,38 +6464,38 @@
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
       <c r="Q62" s="7"/>
-      <c r="R62" s="39" t="s">
+      <c r="R62" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="S62" s="39"/>
-      <c r="T62" s="39"/>
-      <c r="U62" s="39"/>
-      <c r="V62" s="39"/>
+      <c r="S62" s="137"/>
+      <c r="T62" s="137"/>
+      <c r="U62" s="137"/>
+      <c r="V62" s="137"/>
       <c r="W62" s="7"/>
       <c r="X62" s="7"/>
       <c r="AB62" s="7"/>
-      <c r="AC62" s="43"/>
+      <c r="AC62" s="17"/>
       <c r="AD62" s="6"/>
-      <c r="AE62" s="43"/>
+      <c r="AE62" s="17"/>
       <c r="AF62" s="6"/>
-      <c r="AG62" s="43"/>
+      <c r="AG62" s="17"/>
       <c r="AH62" s="6"/>
-      <c r="AI62" s="43"/>
+      <c r="AI62" s="17"/>
       <c r="AJ62" s="6"/>
-      <c r="AK62" s="43"/>
+      <c r="AK62" s="17"/>
       <c r="AL62" s="7"/>
       <c r="AM62" s="7"/>
-      <c r="AN62" s="57"/>
-      <c r="AO62" s="53"/>
-      <c r="AP62" s="53"/>
-      <c r="AQ62" s="53"/>
-      <c r="AR62" s="53"/>
-      <c r="AS62" s="53"/>
-      <c r="AT62" s="53"/>
-      <c r="AU62" s="53"/>
-      <c r="AV62" s="53"/>
-      <c r="AW62" s="53"/>
-      <c r="AX62" s="58"/>
+      <c r="AN62" s="121"/>
+      <c r="AO62" s="122"/>
+      <c r="AP62" s="122"/>
+      <c r="AQ62" s="122"/>
+      <c r="AR62" s="122"/>
+      <c r="AS62" s="122"/>
+      <c r="AT62" s="122"/>
+      <c r="AU62" s="122"/>
+      <c r="AV62" s="122"/>
+      <c r="AW62" s="122"/>
+      <c r="AX62" s="123"/>
       <c r="AY62" s="7"/>
       <c r="AZ62" s="7"/>
       <c r="BA62" s="7"/>
@@ -6015,30 +6527,30 @@
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
       <c r="AB63" s="7"/>
-      <c r="AC63" s="43"/>
+      <c r="AC63" s="17"/>
       <c r="AD63" s="6"/>
-      <c r="AE63" s="43"/>
+      <c r="AE63" s="17"/>
       <c r="AF63" s="6"/>
-      <c r="AG63" s="43"/>
+      <c r="AG63" s="17"/>
       <c r="AH63" s="6"/>
-      <c r="AI63" s="43"/>
+      <c r="AI63" s="17"/>
       <c r="AJ63" s="6"/>
-      <c r="AK63" s="43"/>
+      <c r="AK63" s="17"/>
       <c r="AL63" s="7"/>
       <c r="AM63" s="7"/>
-      <c r="AN63" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO63" s="66"/>
-      <c r="AP63" s="66"/>
-      <c r="AQ63" s="66"/>
-      <c r="AR63" s="66"/>
-      <c r="AS63" s="66"/>
-      <c r="AT63" s="66"/>
-      <c r="AU63" s="66"/>
-      <c r="AV63" s="66"/>
-      <c r="AW63" s="66"/>
-      <c r="AX63" s="67"/>
+      <c r="AN63" s="109" t="s">
+        <v>49</v>
+      </c>
+      <c r="AO63" s="110"/>
+      <c r="AP63" s="110"/>
+      <c r="AQ63" s="110"/>
+      <c r="AR63" s="110"/>
+      <c r="AS63" s="110"/>
+      <c r="AT63" s="110"/>
+      <c r="AU63" s="110"/>
+      <c r="AV63" s="110"/>
+      <c r="AW63" s="110"/>
+      <c r="AX63" s="111"/>
       <c r="AY63" s="7"/>
       <c r="AZ63" s="7"/>
       <c r="BA63" s="7"/>
@@ -6080,38 +6592,38 @@
       <c r="W64" s="7"/>
       <c r="X64" s="7"/>
       <c r="AB64" s="7"/>
-      <c r="AC64" s="43">
+      <c r="AC64" s="17">
         <v>1654</v>
       </c>
       <c r="AD64" s="6"/>
-      <c r="AE64" s="43">
+      <c r="AE64" s="17">
         <v>1654</v>
       </c>
       <c r="AF64" s="6"/>
-      <c r="AG64" s="43">
+      <c r="AG64" s="17">
         <v>1654</v>
       </c>
       <c r="AH64" s="6"/>
-      <c r="AI64" s="43">
+      <c r="AI64" s="17">
         <v>1654</v>
       </c>
       <c r="AJ64" s="6"/>
-      <c r="AK64" s="43">
+      <c r="AK64" s="17">
         <v>1654</v>
       </c>
       <c r="AL64" s="7"/>
       <c r="AM64" s="7"/>
-      <c r="AN64" s="65"/>
-      <c r="AO64" s="66"/>
-      <c r="AP64" s="66"/>
-      <c r="AQ64" s="66"/>
-      <c r="AR64" s="66"/>
-      <c r="AS64" s="66"/>
-      <c r="AT64" s="66"/>
-      <c r="AU64" s="66"/>
-      <c r="AV64" s="66"/>
-      <c r="AW64" s="66"/>
-      <c r="AX64" s="67"/>
+      <c r="AN64" s="109"/>
+      <c r="AO64" s="110"/>
+      <c r="AP64" s="110"/>
+      <c r="AQ64" s="110"/>
+      <c r="AR64" s="110"/>
+      <c r="AS64" s="110"/>
+      <c r="AT64" s="110"/>
+      <c r="AU64" s="110"/>
+      <c r="AV64" s="110"/>
+      <c r="AW64" s="110"/>
+      <c r="AX64" s="111"/>
       <c r="AY64" s="7"/>
       <c r="AZ64" s="7"/>
       <c r="BA64" s="7"/>
@@ -6153,40 +6665,40 @@
       <c r="W65" s="7"/>
       <c r="X65" s="7"/>
       <c r="AB65" s="7"/>
-      <c r="AC65" s="43" t="s">
+      <c r="AC65" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AD65" s="6"/>
-      <c r="AE65" s="43" t="s">
+      <c r="AE65" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AF65" s="6"/>
-      <c r="AG65" s="43" t="s">
+      <c r="AG65" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AH65" s="6"/>
-      <c r="AI65" s="43" t="s">
+      <c r="AI65" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AJ65" s="6"/>
-      <c r="AK65" s="43" t="s">
+      <c r="AK65" s="17" t="s">
         <v>10</v>
       </c>
       <c r="AL65" s="7"/>
       <c r="AM65" s="7"/>
-      <c r="AN65" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="AO65" s="60"/>
-      <c r="AP65" s="60"/>
-      <c r="AQ65" s="60"/>
-      <c r="AR65" s="60"/>
-      <c r="AS65" s="60"/>
-      <c r="AT65" s="60"/>
-      <c r="AU65" s="60"/>
-      <c r="AV65" s="60"/>
-      <c r="AW65" s="60"/>
-      <c r="AX65" s="61"/>
+      <c r="AN65" s="112" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO65" s="113"/>
+      <c r="AP65" s="113"/>
+      <c r="AQ65" s="113"/>
+      <c r="AR65" s="113"/>
+      <c r="AS65" s="113"/>
+      <c r="AT65" s="113"/>
+      <c r="AU65" s="113"/>
+      <c r="AV65" s="113"/>
+      <c r="AW65" s="113"/>
+      <c r="AX65" s="114"/>
       <c r="AY65" s="7"/>
       <c r="AZ65" s="7"/>
       <c r="BA65" s="7"/>
@@ -6228,38 +6740,38 @@
       <c r="W66" s="7"/>
       <c r="X66" s="7"/>
       <c r="AB66" s="7"/>
-      <c r="AC66" s="43" t="s">
+      <c r="AC66" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AD66" s="6"/>
-      <c r="AE66" s="43" t="s">
+      <c r="AE66" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AF66" s="6"/>
-      <c r="AG66" s="43" t="s">
+      <c r="AG66" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AH66" s="6"/>
-      <c r="AI66" s="43" t="s">
+      <c r="AI66" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AJ66" s="6"/>
-      <c r="AK66" s="43" t="s">
+      <c r="AK66" s="17" t="s">
         <v>11</v>
       </c>
       <c r="AL66" s="7"/>
       <c r="AM66" s="7"/>
-      <c r="AN66" s="62"/>
-      <c r="AO66" s="63"/>
-      <c r="AP66" s="63"/>
-      <c r="AQ66" s="63"/>
-      <c r="AR66" s="63"/>
-      <c r="AS66" s="63"/>
-      <c r="AT66" s="63"/>
-      <c r="AU66" s="63"/>
-      <c r="AV66" s="63"/>
-      <c r="AW66" s="63"/>
-      <c r="AX66" s="64"/>
+      <c r="AN66" s="115"/>
+      <c r="AO66" s="116"/>
+      <c r="AP66" s="116"/>
+      <c r="AQ66" s="116"/>
+      <c r="AR66" s="116"/>
+      <c r="AS66" s="116"/>
+      <c r="AT66" s="116"/>
+      <c r="AU66" s="116"/>
+      <c r="AV66" s="116"/>
+      <c r="AW66" s="116"/>
+      <c r="AX66" s="117"/>
       <c r="AY66" s="7"/>
       <c r="AZ66" s="7"/>
       <c r="BA66" s="7"/>
@@ -6291,28 +6803,30 @@
       <c r="W67" s="7"/>
       <c r="X67" s="7"/>
       <c r="AB67" s="7"/>
-      <c r="AC67" s="43"/>
+      <c r="AC67" s="17"/>
       <c r="AD67" s="6"/>
-      <c r="AE67" s="43"/>
+      <c r="AE67" s="17"/>
       <c r="AF67" s="6"/>
-      <c r="AG67" s="43"/>
+      <c r="AG67" s="17"/>
       <c r="AH67" s="6"/>
-      <c r="AI67" s="43"/>
+      <c r="AI67" s="17"/>
       <c r="AJ67" s="6"/>
-      <c r="AK67" s="43"/>
+      <c r="AK67" s="17"/>
       <c r="AL67" s="7"/>
       <c r="AM67" s="7"/>
-      <c r="AN67" s="7"/>
-      <c r="AO67" s="7"/>
-      <c r="AP67" s="7"/>
-      <c r="AQ67" s="7"/>
-      <c r="AR67" s="7"/>
-      <c r="AS67" s="7"/>
-      <c r="AT67" s="7"/>
-      <c r="AU67" s="7"/>
-      <c r="AV67" s="7"/>
-      <c r="AW67" s="7"/>
-      <c r="AX67" s="7"/>
+      <c r="AN67" s="146" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO67" s="147"/>
+      <c r="AP67" s="147"/>
+      <c r="AQ67" s="147"/>
+      <c r="AR67" s="147"/>
+      <c r="AS67" s="147"/>
+      <c r="AT67" s="147"/>
+      <c r="AU67" s="147"/>
+      <c r="AV67" s="147"/>
+      <c r="AW67" s="147"/>
+      <c r="AX67" s="147"/>
       <c r="AY67" s="7"/>
       <c r="AZ67" s="7"/>
       <c r="BA67" s="7"/>
@@ -6344,28 +6858,28 @@
       <c r="W68" s="7"/>
       <c r="X68" s="7"/>
       <c r="AB68" s="7"/>
-      <c r="AC68" s="43"/>
+      <c r="AC68" s="17"/>
       <c r="AD68" s="6"/>
-      <c r="AE68" s="43"/>
+      <c r="AE68" s="17"/>
       <c r="AF68" s="6"/>
-      <c r="AG68" s="43"/>
+      <c r="AG68" s="17"/>
       <c r="AH68" s="6"/>
-      <c r="AI68" s="43"/>
+      <c r="AI68" s="17"/>
       <c r="AJ68" s="6"/>
-      <c r="AK68" s="43"/>
+      <c r="AK68" s="17"/>
       <c r="AL68" s="7"/>
       <c r="AM68" s="7"/>
-      <c r="AN68" s="7"/>
-      <c r="AO68" s="7"/>
-      <c r="AP68" s="7"/>
-      <c r="AQ68" s="7"/>
-      <c r="AR68" s="7"/>
-      <c r="AS68" s="7"/>
-      <c r="AT68" s="7"/>
-      <c r="AU68" s="7"/>
-      <c r="AV68" s="7"/>
-      <c r="AW68" s="7"/>
-      <c r="AX68" s="7"/>
+      <c r="AN68" s="137"/>
+      <c r="AO68" s="137"/>
+      <c r="AP68" s="137"/>
+      <c r="AQ68" s="137"/>
+      <c r="AR68" s="137"/>
+      <c r="AS68" s="137"/>
+      <c r="AT68" s="137"/>
+      <c r="AU68" s="137"/>
+      <c r="AV68" s="137"/>
+      <c r="AW68" s="137"/>
+      <c r="AX68" s="137"/>
       <c r="AY68" s="7"/>
       <c r="AZ68" s="7"/>
       <c r="BA68" s="7"/>
@@ -6397,15 +6911,15 @@
       <c r="W69" s="7"/>
       <c r="X69" s="7"/>
       <c r="AB69" s="7"/>
-      <c r="AC69" s="43"/>
+      <c r="AC69" s="17"/>
       <c r="AD69" s="6"/>
-      <c r="AE69" s="43"/>
+      <c r="AE69" s="17"/>
       <c r="AF69" s="6"/>
-      <c r="AG69" s="43"/>
+      <c r="AG69" s="17"/>
       <c r="AH69" s="6"/>
-      <c r="AI69" s="43"/>
+      <c r="AI69" s="17"/>
       <c r="AJ69" s="6"/>
-      <c r="AK69" s="43"/>
+      <c r="AK69" s="17"/>
       <c r="AL69" s="7"/>
       <c r="AM69" s="7"/>
       <c r="AN69" s="7"/>
@@ -6450,15 +6964,15 @@
       <c r="W70" s="7"/>
       <c r="X70" s="7"/>
       <c r="AB70" s="7"/>
-      <c r="AC70" s="43"/>
+      <c r="AC70" s="17"/>
       <c r="AD70" s="6"/>
-      <c r="AE70" s="43"/>
+      <c r="AE70" s="17"/>
       <c r="AF70" s="6"/>
-      <c r="AG70" s="43"/>
+      <c r="AG70" s="17"/>
       <c r="AH70" s="6"/>
-      <c r="AI70" s="43"/>
+      <c r="AI70" s="17"/>
       <c r="AJ70" s="6"/>
-      <c r="AK70" s="43"/>
+      <c r="AK70" s="17"/>
       <c r="AL70" s="7"/>
       <c r="AM70" s="7"/>
       <c r="AN70" s="7"/>
@@ -6503,15 +7017,15 @@
       <c r="W71" s="7"/>
       <c r="X71" s="7"/>
       <c r="AB71" s="7"/>
-      <c r="AC71" s="43"/>
+      <c r="AC71" s="17"/>
       <c r="AD71" s="6"/>
-      <c r="AE71" s="43"/>
+      <c r="AE71" s="17"/>
       <c r="AF71" s="6"/>
-      <c r="AG71" s="43"/>
+      <c r="AG71" s="17"/>
       <c r="AH71" s="6"/>
-      <c r="AI71" s="43"/>
+      <c r="AI71" s="17"/>
       <c r="AJ71" s="6"/>
-      <c r="AK71" s="43"/>
+      <c r="AK71" s="17"/>
       <c r="AL71" s="7"/>
       <c r="AM71" s="7"/>
       <c r="AN71" s="7"/>
@@ -6556,15 +7070,15 @@
       <c r="W72" s="7"/>
       <c r="X72" s="7"/>
       <c r="AB72" s="7"/>
-      <c r="AC72" s="44"/>
+      <c r="AC72" s="18"/>
       <c r="AD72" s="6"/>
-      <c r="AE72" s="44"/>
+      <c r="AE72" s="18"/>
       <c r="AF72" s="6"/>
-      <c r="AG72" s="44"/>
+      <c r="AG72" s="18"/>
       <c r="AH72" s="6"/>
-      <c r="AI72" s="44"/>
+      <c r="AI72" s="18"/>
       <c r="AJ72" s="6"/>
-      <c r="AK72" s="44"/>
+      <c r="AK72" s="18"/>
       <c r="AL72" s="7"/>
       <c r="AM72" s="7"/>
       <c r="AN72" s="7"/>
@@ -6643,12 +7157,12 @@
       <c r="W74" s="7"/>
       <c r="X74" s="7"/>
       <c r="AB74" s="7"/>
-      <c r="AC74" s="68" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD74" s="83"/>
-      <c r="AE74" s="83"/>
-      <c r="AF74" s="84"/>
+      <c r="AC74" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD74" s="25"/>
+      <c r="AE74" s="25"/>
+      <c r="AF74" s="26"/>
       <c r="AG74" s="7"/>
       <c r="AH74" s="7"/>
       <c r="AI74" s="7"/>
@@ -6675,12 +7189,12 @@
     </row>
     <row r="75" spans="2:84" ht="21" x14ac:dyDescent="0.4">
       <c r="AB75" s="7"/>
-      <c r="AC75" s="69"/>
-      <c r="AD75" s="85" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE75" s="85"/>
-      <c r="AF75" s="86"/>
+      <c r="AC75" s="23"/>
+      <c r="AD75" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE75" s="16"/>
+      <c r="AF75" s="27"/>
       <c r="AG75" s="7"/>
       <c r="AH75" s="7"/>
       <c r="AI75" s="7"/>
@@ -6705,14 +7219,14 @@
       <c r="BB75" s="7"/>
       <c r="BC75" s="7"/>
     </row>
-    <row r="76" spans="2:84" ht="21" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:84" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="AB76" s="7"/>
-      <c r="AC76" s="70"/>
-      <c r="AD76" s="85" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE76" s="85"/>
-      <c r="AF76" s="86"/>
+      <c r="AC76" s="24"/>
+      <c r="AD76" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE76" s="28"/>
+      <c r="AF76" s="29"/>
       <c r="AG76" s="7"/>
       <c r="AH76" s="7"/>
       <c r="AI76" s="7"/>
@@ -6737,50 +7251,42 @@
       <c r="BB76" s="7"/>
       <c r="BC76" s="7"/>
       <c r="BG76" s="7"/>
-      <c r="BH76" s="151" t="s">
-        <v>68</v>
-      </c>
-      <c r="BI76" s="151"/>
-      <c r="BJ76" s="151"/>
-      <c r="BK76" s="151"/>
-      <c r="BL76" s="151"/>
-      <c r="BM76" s="151"/>
-      <c r="BN76" s="151"/>
-      <c r="BO76" s="151"/>
-      <c r="BP76" s="151"/>
-      <c r="BQ76" s="151"/>
-      <c r="BR76" s="151"/>
-      <c r="BS76" s="151"/>
-      <c r="BT76" s="151"/>
-      <c r="BU76" s="151"/>
-      <c r="BV76" s="151"/>
-      <c r="BW76" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX76" s="151" t="s">
-        <v>69</v>
-      </c>
-      <c r="BY76" s="151"/>
-      <c r="BZ76" s="151"/>
-      <c r="CA76" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB76" s="151" t="s">
-        <v>70</v>
-      </c>
-      <c r="CC76" s="151"/>
-      <c r="CD76" s="151"/>
-      <c r="CE76" s="7"/>
-      <c r="CF76" s="7"/>
-    </row>
-    <row r="77" spans="2:84" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="BH76" s="108" t="s">
+        <v>72</v>
+      </c>
+      <c r="BI76" s="108"/>
+      <c r="BJ76" s="108"/>
+      <c r="BK76" s="108"/>
+      <c r="BL76" s="108"/>
+      <c r="BM76" s="108"/>
+      <c r="BN76" s="108"/>
+      <c r="BO76" s="108"/>
+      <c r="BP76" s="108"/>
+      <c r="BQ76" s="108"/>
+      <c r="BR76" s="108"/>
+      <c r="BS76" s="108"/>
+      <c r="BT76" s="108"/>
+      <c r="BU76" s="108"/>
+      <c r="BV76" s="108"/>
+      <c r="BW76" s="10"/>
+      <c r="BX76" s="156"/>
+      <c r="BY76" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ76" s="108"/>
+      <c r="CA76" s="108"/>
+      <c r="CB76" s="108"/>
+      <c r="CC76" s="108"/>
+      <c r="CD76" s="108"/>
+      <c r="CE76" s="108"/>
+      <c r="CF76" s="156"/>
+    </row>
+    <row r="77" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB77" s="7"/>
-      <c r="AC77" s="71"/>
-      <c r="AD77" s="87" t="s">
-        <v>37</v>
-      </c>
-      <c r="AE77" s="87"/>
-      <c r="AF77" s="88"/>
+      <c r="AC77" s="7"/>
+      <c r="AD77" s="7"/>
+      <c r="AE77" s="7"/>
+      <c r="AF77" s="7"/>
       <c r="AG77" s="7"/>
       <c r="AH77" s="7"/>
       <c r="AI77" s="7"/>
@@ -6805,74 +7311,78 @@
       <c r="BB77" s="7"/>
       <c r="BC77" s="7"/>
       <c r="BG77" s="7"/>
-      <c r="BH77" s="151"/>
-      <c r="BI77" s="151"/>
-      <c r="BJ77" s="151"/>
-      <c r="BK77" s="151"/>
-      <c r="BL77" s="151"/>
-      <c r="BM77" s="151"/>
-      <c r="BN77" s="151"/>
-      <c r="BO77" s="151"/>
-      <c r="BP77" s="151"/>
-      <c r="BQ77" s="151"/>
-      <c r="BR77" s="151"/>
-      <c r="BS77" s="151"/>
-      <c r="BT77" s="151"/>
-      <c r="BU77" s="151"/>
-      <c r="BV77" s="151"/>
-      <c r="BW77" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX77" s="151"/>
-      <c r="BY77" s="151"/>
-      <c r="BZ77" s="151"/>
-      <c r="CA77" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB77" s="151"/>
-      <c r="CC77" s="151"/>
-      <c r="CD77" s="151"/>
-      <c r="CE77" s="7"/>
-      <c r="CF77" s="7"/>
-    </row>
-    <row r="78" spans="2:84" x14ac:dyDescent="0.3">
+      <c r="BH77" s="108"/>
+      <c r="BI77" s="108"/>
+      <c r="BJ77" s="108"/>
+      <c r="BK77" s="108"/>
+      <c r="BL77" s="108"/>
+      <c r="BM77" s="108"/>
+      <c r="BN77" s="108"/>
+      <c r="BO77" s="108"/>
+      <c r="BP77" s="108"/>
+      <c r="BQ77" s="108"/>
+      <c r="BR77" s="108"/>
+      <c r="BS77" s="108"/>
+      <c r="BT77" s="108"/>
+      <c r="BU77" s="108"/>
+      <c r="BV77" s="108"/>
+      <c r="BW77" s="10"/>
+      <c r="BX77" s="156"/>
+      <c r="BY77" s="108"/>
+      <c r="BZ77" s="108"/>
+      <c r="CA77" s="108"/>
+      <c r="CB77" s="108"/>
+      <c r="CC77" s="108"/>
+      <c r="CD77" s="108"/>
+      <c r="CE77" s="108"/>
+      <c r="CF77" s="156"/>
+    </row>
+    <row r="78" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AB78" s="7"/>
+      <c r="AC78" s="7"/>
+      <c r="AD78" s="7"/>
+      <c r="AE78" s="7"/>
+      <c r="AF78" s="7"/>
+      <c r="AG78" s="7"/>
       <c r="AY78" s="7"/>
       <c r="AZ78" s="7"/>
       <c r="BA78" s="7"/>
       <c r="BB78" s="7"/>
       <c r="BC78" s="7"/>
       <c r="BG78" s="7"/>
-      <c r="BH78" s="151"/>
-      <c r="BI78" s="151"/>
-      <c r="BJ78" s="151"/>
-      <c r="BK78" s="151"/>
-      <c r="BL78" s="151"/>
-      <c r="BM78" s="151"/>
-      <c r="BN78" s="151"/>
-      <c r="BO78" s="151"/>
-      <c r="BP78" s="151"/>
-      <c r="BQ78" s="151"/>
-      <c r="BR78" s="151"/>
-      <c r="BS78" s="151"/>
-      <c r="BT78" s="151"/>
-      <c r="BU78" s="151"/>
-      <c r="BV78" s="151"/>
-      <c r="BW78" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX78" s="151"/>
-      <c r="BY78" s="151"/>
-      <c r="BZ78" s="151"/>
-      <c r="CA78" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB78" s="151"/>
-      <c r="CC78" s="151"/>
-      <c r="CD78" s="151"/>
-      <c r="CE78" s="7"/>
-      <c r="CF78" s="7"/>
+      <c r="BH78" s="108"/>
+      <c r="BI78" s="108"/>
+      <c r="BJ78" s="108"/>
+      <c r="BK78" s="108"/>
+      <c r="BL78" s="108"/>
+      <c r="BM78" s="108"/>
+      <c r="BN78" s="108"/>
+      <c r="BO78" s="108"/>
+      <c r="BP78" s="108"/>
+      <c r="BQ78" s="108"/>
+      <c r="BR78" s="108"/>
+      <c r="BS78" s="108"/>
+      <c r="BT78" s="108"/>
+      <c r="BU78" s="108"/>
+      <c r="BV78" s="108"/>
+      <c r="BW78" s="10"/>
+      <c r="BX78" s="156"/>
+      <c r="BY78" s="108"/>
+      <c r="BZ78" s="108"/>
+      <c r="CA78" s="108"/>
+      <c r="CB78" s="108"/>
+      <c r="CC78" s="108"/>
+      <c r="CD78" s="108"/>
+      <c r="CE78" s="108"/>
+      <c r="CF78" s="156"/>
     </row>
     <row r="79" spans="2:84" x14ac:dyDescent="0.3">
+      <c r="AB79" s="7"/>
+      <c r="AC79" s="7"/>
+      <c r="AD79" s="7"/>
+      <c r="AE79" s="7"/>
+      <c r="AF79" s="7"/>
+      <c r="AG79" s="7"/>
       <c r="BG79" s="7"/>
       <c r="BH79" s="7"/>
       <c r="BI79" s="7"/>
@@ -6889,19 +7399,15 @@
       <c r="BT79" s="7"/>
       <c r="BU79" s="7"/>
       <c r="BV79" s="7"/>
-      <c r="BW79" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW79" s="10"/>
       <c r="BX79" s="7"/>
-      <c r="BY79" s="7"/>
-      <c r="BZ79" s="7"/>
-      <c r="CA79" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB79" s="7"/>
-      <c r="CC79" s="7"/>
-      <c r="CD79" s="7"/>
-      <c r="CE79" s="7"/>
+      <c r="BY79" s="108"/>
+      <c r="BZ79" s="108"/>
+      <c r="CA79" s="108"/>
+      <c r="CB79" s="108"/>
+      <c r="CC79" s="108"/>
+      <c r="CD79" s="108"/>
+      <c r="CE79" s="108"/>
       <c r="CF79" s="7"/>
     </row>
     <row r="80" spans="2:84" x14ac:dyDescent="0.3">
@@ -6921,15 +7427,11 @@
       <c r="BT80" s="7"/>
       <c r="BU80" s="7"/>
       <c r="BV80" s="7"/>
-      <c r="BW80" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW80" s="10"/>
       <c r="BX80" s="7"/>
       <c r="BY80" s="7"/>
       <c r="BZ80" s="7"/>
-      <c r="CA80" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA80" s="69"/>
       <c r="CB80" s="7"/>
       <c r="CC80" s="7"/>
       <c r="CD80" s="7"/>
@@ -6939,52 +7441,47 @@
     <row r="81" spans="57:94" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="BE81" s="6"/>
       <c r="BG81" s="6"/>
-      <c r="BH81" s="93" t="s">
-        <v>50</v>
+      <c r="BH81" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="BI81" s="6"/>
-      <c r="BJ81" s="93" t="s">
-        <v>51</v>
+      <c r="BJ81" s="33" t="s">
+        <v>54</v>
       </c>
       <c r="BK81" s="6"/>
-      <c r="BL81" s="93" t="s">
-        <v>52</v>
+      <c r="BL81" s="33" t="s">
+        <v>55</v>
       </c>
       <c r="BM81" s="7"/>
-      <c r="BN81" s="93" t="s">
-        <v>53</v>
+      <c r="BN81" s="33" t="s">
+        <v>56</v>
       </c>
       <c r="BO81" s="6"/>
-      <c r="BP81" s="93" t="s">
-        <v>54</v>
+      <c r="BP81" s="33" t="s">
+        <v>57</v>
       </c>
       <c r="BQ81" s="6"/>
-      <c r="BR81" s="93" t="s">
-        <v>55</v>
+      <c r="BR81" s="33" t="s">
+        <v>58</v>
       </c>
       <c r="BS81" s="6"/>
-      <c r="BT81" s="93" t="s">
-        <v>56</v>
+      <c r="BT81" s="33" t="s">
+        <v>59</v>
       </c>
       <c r="BU81" s="6"/>
-      <c r="BV81" s="93" t="s">
-        <v>57</v>
-      </c>
-      <c r="BW81" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX81" s="7"/>
-      <c r="BY81" s="93" t="s">
-        <v>48</v>
+      <c r="BV81" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="BW81" s="10"/>
+      <c r="BX81" s="33" t="s">
+        <v>61</v>
       </c>
       <c r="BZ81" s="7"/>
-      <c r="CA81" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB81" s="7"/>
-      <c r="CC81" s="93" t="s">
-        <v>49</v>
-      </c>
+      <c r="CA81" s="69"/>
+      <c r="CB81" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="CC81" s="7"/>
       <c r="CD81" s="7"/>
       <c r="CE81" s="7"/>
       <c r="CF81" s="7"/>
@@ -6992,32 +7489,28 @@
     <row r="82" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE82" s="6"/>
       <c r="BG82" s="6"/>
-      <c r="BH82" s="43"/>
+      <c r="BH82" s="17"/>
       <c r="BI82" s="6"/>
-      <c r="BJ82" s="43"/>
+      <c r="BJ82" s="17"/>
       <c r="BK82" s="6"/>
-      <c r="BL82" s="40"/>
+      <c r="BL82" s="100"/>
       <c r="BM82" s="7"/>
-      <c r="BN82" s="43"/>
+      <c r="BN82" s="17"/>
       <c r="BO82" s="6"/>
-      <c r="BP82" s="43"/>
+      <c r="BP82" s="17"/>
       <c r="BQ82" s="6"/>
-      <c r="BR82" s="43"/>
+      <c r="BR82" s="17"/>
       <c r="BS82" s="6"/>
-      <c r="BT82" s="43"/>
+      <c r="BT82" s="17"/>
       <c r="BU82" s="6"/>
-      <c r="BV82" s="43"/>
-      <c r="BW82" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX82" s="7"/>
-      <c r="BY82" s="89"/>
+      <c r="BV82" s="17"/>
+      <c r="BW82" s="10"/>
+      <c r="BX82" s="17"/>
+      <c r="BY82" s="7"/>
       <c r="BZ82" s="7"/>
-      <c r="CA82" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB82" s="7"/>
-      <c r="CC82" s="91"/>
+      <c r="CA82" s="69"/>
+      <c r="CB82" s="101"/>
+      <c r="CC82" s="7"/>
       <c r="CD82" s="7"/>
       <c r="CE82" s="7"/>
       <c r="CF82" s="7"/>
@@ -7025,32 +7518,28 @@
     <row r="83" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE83" s="6"/>
       <c r="BG83" s="6"/>
-      <c r="BH83" s="43"/>
+      <c r="BH83" s="17"/>
       <c r="BI83" s="6"/>
-      <c r="BJ83" s="43"/>
+      <c r="BJ83" s="17"/>
       <c r="BK83" s="6"/>
-      <c r="BL83" s="40"/>
+      <c r="BL83" s="100"/>
       <c r="BM83" s="7"/>
-      <c r="BN83" s="43"/>
+      <c r="BN83" s="17"/>
       <c r="BO83" s="6"/>
-      <c r="BP83" s="43"/>
+      <c r="BP83" s="17"/>
       <c r="BQ83" s="6"/>
-      <c r="BR83" s="43"/>
+      <c r="BR83" s="17"/>
       <c r="BS83" s="6"/>
-      <c r="BT83" s="43"/>
+      <c r="BT83" s="17"/>
       <c r="BU83" s="6"/>
-      <c r="BV83" s="43"/>
-      <c r="BW83" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX83" s="7"/>
-      <c r="BY83" s="89"/>
+      <c r="BV83" s="17"/>
+      <c r="BW83" s="10"/>
+      <c r="BX83" s="17"/>
+      <c r="BY83" s="7"/>
       <c r="BZ83" s="7"/>
-      <c r="CA83" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB83" s="7"/>
-      <c r="CC83" s="91"/>
+      <c r="CA83" s="69"/>
+      <c r="CB83" s="101"/>
+      <c r="CC83" s="7"/>
       <c r="CD83" s="7"/>
       <c r="CE83" s="7"/>
       <c r="CF83" s="7"/>
@@ -7058,32 +7547,28 @@
     <row r="84" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE84" s="6"/>
       <c r="BG84" s="6"/>
-      <c r="BH84" s="43"/>
+      <c r="BH84" s="17"/>
       <c r="BI84" s="6"/>
-      <c r="BJ84" s="43"/>
+      <c r="BJ84" s="17"/>
       <c r="BK84" s="6"/>
-      <c r="BL84" s="43"/>
+      <c r="BL84" s="17"/>
       <c r="BM84" s="7"/>
-      <c r="BN84" s="43"/>
+      <c r="BN84" s="17"/>
       <c r="BO84" s="6"/>
-      <c r="BP84" s="43"/>
+      <c r="BP84" s="17"/>
       <c r="BQ84" s="6"/>
-      <c r="BR84" s="43"/>
+      <c r="BR84" s="17"/>
       <c r="BS84" s="6"/>
-      <c r="BT84" s="43"/>
+      <c r="BT84" s="17"/>
       <c r="BU84" s="6"/>
-      <c r="BV84" s="43"/>
-      <c r="BW84" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX84" s="7"/>
-      <c r="BY84" s="89"/>
+      <c r="BV84" s="17"/>
+      <c r="BW84" s="10"/>
+      <c r="BX84" s="17"/>
+      <c r="BY84" s="7"/>
       <c r="BZ84" s="7"/>
-      <c r="CA84" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB84" s="7"/>
-      <c r="CC84" s="92"/>
+      <c r="CA84" s="69"/>
+      <c r="CB84" s="32"/>
+      <c r="CC84" s="7"/>
       <c r="CD84" s="7"/>
       <c r="CE84" s="7"/>
       <c r="CF84" s="7"/>
@@ -7091,32 +7576,28 @@
     <row r="85" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE85" s="6"/>
       <c r="BG85" s="6"/>
-      <c r="BH85" s="43"/>
+      <c r="BH85" s="17"/>
       <c r="BI85" s="6"/>
-      <c r="BJ85" s="43"/>
+      <c r="BJ85" s="17"/>
       <c r="BK85" s="6"/>
-      <c r="BL85" s="43"/>
+      <c r="BL85" s="17"/>
       <c r="BM85" s="7"/>
-      <c r="BN85" s="43"/>
+      <c r="BN85" s="17"/>
       <c r="BO85" s="6"/>
-      <c r="BP85" s="43"/>
+      <c r="BP85" s="17"/>
       <c r="BQ85" s="6"/>
-      <c r="BR85" s="43"/>
+      <c r="BR85" s="17"/>
       <c r="BS85" s="6"/>
-      <c r="BT85" s="43"/>
+      <c r="BT85" s="17"/>
       <c r="BU85" s="6"/>
-      <c r="BV85" s="43"/>
-      <c r="BW85" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX85" s="7"/>
-      <c r="BY85" s="89"/>
+      <c r="BV85" s="17"/>
+      <c r="BW85" s="10"/>
+      <c r="BX85" s="17"/>
+      <c r="BY85" s="7"/>
       <c r="BZ85" s="7"/>
-      <c r="CA85" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB85" s="7"/>
-      <c r="CC85" s="92"/>
+      <c r="CA85" s="69"/>
+      <c r="CB85" s="32"/>
+      <c r="CC85" s="7"/>
       <c r="CD85" s="7"/>
       <c r="CE85" s="7"/>
       <c r="CF85" s="7"/>
@@ -7125,32 +7606,30 @@
     <row r="86" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE86" s="6"/>
       <c r="BG86" s="6"/>
-      <c r="BH86" s="43"/>
+      <c r="BH86" s="17"/>
       <c r="BI86" s="6"/>
-      <c r="BJ86" s="43"/>
+      <c r="BJ86" s="17"/>
       <c r="BK86" s="6"/>
-      <c r="BL86" s="43"/>
+      <c r="BL86" s="17"/>
       <c r="BM86" s="7"/>
-      <c r="BN86" s="43"/>
+      <c r="BN86" s="17"/>
       <c r="BO86" s="6"/>
-      <c r="BP86" s="43"/>
+      <c r="BP86" s="17"/>
       <c r="BQ86" s="6"/>
-      <c r="BR86" s="43"/>
+      <c r="BR86" s="17"/>
       <c r="BS86" s="6"/>
-      <c r="BT86" s="43"/>
+      <c r="BT86" s="17"/>
       <c r="BU86" s="6"/>
-      <c r="BV86" s="43"/>
-      <c r="BW86" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX86" s="7"/>
-      <c r="BY86" s="89"/>
-      <c r="BZ86" s="7"/>
-      <c r="CA86" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB86" s="7"/>
-      <c r="CC86" s="92"/>
+      <c r="BV86" s="17"/>
+      <c r="BW86" s="10"/>
+      <c r="BX86" s="17"/>
+      <c r="BY86" s="7"/>
+      <c r="BZ86" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="CA86" s="104"/>
+      <c r="CB86" s="32"/>
+      <c r="CC86" s="7"/>
       <c r="CD86" s="7"/>
       <c r="CE86" s="7"/>
       <c r="CF86" s="7"/>
@@ -7158,32 +7637,28 @@
     <row r="87" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE87" s="6"/>
       <c r="BG87" s="6"/>
-      <c r="BH87" s="89"/>
+      <c r="BH87" s="17"/>
       <c r="BI87" s="6"/>
-      <c r="BJ87" s="89"/>
+      <c r="BJ87" s="17"/>
       <c r="BK87" s="6"/>
-      <c r="BL87" s="89"/>
+      <c r="BL87" s="17"/>
       <c r="BM87" s="7"/>
-      <c r="BN87" s="89"/>
+      <c r="BN87" s="17"/>
       <c r="BO87" s="6"/>
-      <c r="BP87" s="89"/>
+      <c r="BP87" s="17"/>
       <c r="BQ87" s="6"/>
-      <c r="BR87" s="89"/>
+      <c r="BR87" s="17"/>
       <c r="BS87" s="6"/>
-      <c r="BT87" s="89"/>
+      <c r="BT87" s="17"/>
       <c r="BU87" s="6"/>
-      <c r="BV87" s="89"/>
-      <c r="BW87" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX87" s="7"/>
-      <c r="BY87" s="3"/>
-      <c r="BZ87" s="7"/>
-      <c r="CA87" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB87" s="7"/>
-      <c r="CC87" s="92"/>
+      <c r="BV87" s="17"/>
+      <c r="BW87" s="10"/>
+      <c r="BX87" s="17"/>
+      <c r="BY87" s="7"/>
+      <c r="BZ87" s="103"/>
+      <c r="CA87" s="104"/>
+      <c r="CB87" s="32"/>
+      <c r="CC87" s="7"/>
       <c r="CD87" s="7"/>
       <c r="CE87" s="7"/>
       <c r="CF87" s="7"/>
@@ -7191,104 +7666,93 @@
     <row r="88" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE88" s="6"/>
       <c r="BG88" s="6"/>
-      <c r="BH88" s="89"/>
+      <c r="BH88" s="30"/>
       <c r="BI88" s="6"/>
-      <c r="BJ88" s="89"/>
+      <c r="BJ88" s="30"/>
       <c r="BK88" s="6"/>
-      <c r="BL88" s="89"/>
+      <c r="BL88" s="30"/>
       <c r="BM88" s="7"/>
-      <c r="BN88" s="89"/>
+      <c r="BN88" s="30"/>
       <c r="BO88" s="6"/>
-      <c r="BP88" s="89"/>
+      <c r="BP88" s="30"/>
       <c r="BQ88" s="6"/>
-      <c r="BR88" s="89"/>
+      <c r="BR88" s="30"/>
       <c r="BS88" s="6"/>
-      <c r="BT88" s="89"/>
+      <c r="BT88" s="30"/>
       <c r="BU88" s="6"/>
-      <c r="BV88" s="89"/>
-      <c r="BW88" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX88" s="7"/>
-      <c r="BY88" s="3"/>
+      <c r="BV88" s="30"/>
+      <c r="BW88" s="10"/>
+      <c r="BX88" s="30"/>
+      <c r="BY88" s="7"/>
       <c r="BZ88" s="7"/>
-      <c r="CA88" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB88" s="7"/>
-      <c r="CC88" s="92"/>
-      <c r="CD88" s="7"/>
+      <c r="CA88" s="69"/>
+      <c r="CB88" s="2"/>
+      <c r="CC88" s="105" t="s">
+        <v>63</v>
+      </c>
+      <c r="CD88" s="106"/>
       <c r="CE88" s="7"/>
       <c r="CF88" s="7"/>
     </row>
     <row r="89" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE89" s="6"/>
       <c r="BG89" s="6"/>
-      <c r="BH89" s="89"/>
+      <c r="BH89" s="30"/>
       <c r="BI89" s="6"/>
-      <c r="BJ89" s="89"/>
+      <c r="BJ89" s="30"/>
       <c r="BK89" s="6"/>
-      <c r="BL89" s="89"/>
+      <c r="BL89" s="30"/>
       <c r="BM89" s="7"/>
-      <c r="BN89" s="89"/>
+      <c r="BN89" s="30"/>
       <c r="BO89" s="6"/>
-      <c r="BP89" s="89"/>
+      <c r="BP89" s="30"/>
       <c r="BQ89" s="6"/>
-      <c r="BR89" s="89"/>
+      <c r="BR89" s="30"/>
       <c r="BS89" s="6"/>
-      <c r="BT89" s="89"/>
+      <c r="BT89" s="30"/>
       <c r="BU89" s="6"/>
-      <c r="BV89" s="89"/>
-      <c r="BW89" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX89" s="7"/>
-      <c r="BY89" s="3"/>
+      <c r="BV89" s="30"/>
+      <c r="BW89" s="10"/>
+      <c r="BX89" s="30"/>
+      <c r="BY89" s="7"/>
       <c r="BZ89" s="7"/>
-      <c r="CA89" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB89" s="7"/>
-      <c r="CC89" s="89"/>
-      <c r="CD89" s="7"/>
+      <c r="CA89" s="69"/>
+      <c r="CB89" s="3"/>
+      <c r="CC89" s="107"/>
+      <c r="CD89" s="106"/>
       <c r="CE89" s="7"/>
       <c r="CF89" s="7"/>
       <c r="CJ89" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="CP89" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE90" s="6"/>
       <c r="BG90" s="6"/>
-      <c r="BH90" s="89"/>
+      <c r="BH90" s="30"/>
       <c r="BI90" s="6"/>
-      <c r="BJ90" s="89"/>
+      <c r="BJ90" s="30"/>
       <c r="BK90" s="6"/>
-      <c r="BL90" s="89"/>
+      <c r="BL90" s="30"/>
       <c r="BM90" s="7"/>
-      <c r="BN90" s="89"/>
+      <c r="BN90" s="30"/>
       <c r="BO90" s="6"/>
-      <c r="BP90" s="89"/>
+      <c r="BP90" s="30"/>
       <c r="BQ90" s="6"/>
-      <c r="BR90" s="89"/>
+      <c r="BR90" s="30"/>
       <c r="BS90" s="6"/>
-      <c r="BT90" s="89"/>
+      <c r="BT90" s="30"/>
       <c r="BU90" s="6"/>
-      <c r="BV90" s="89"/>
-      <c r="BW90" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX90" s="7"/>
-      <c r="BY90" s="89"/>
+      <c r="BV90" s="30"/>
+      <c r="BW90" s="10"/>
+      <c r="BX90" s="30"/>
+      <c r="BY90" s="7"/>
       <c r="BZ90" s="7"/>
-      <c r="CA90" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB90" s="7"/>
-      <c r="CC90" s="47"/>
+      <c r="CB90" s="20"/>
+      <c r="CC90" s="7"/>
       <c r="CD90" s="7"/>
       <c r="CE90" s="7"/>
       <c r="CF90" s="7"/>
@@ -7296,32 +7760,28 @@
     <row r="91" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE91" s="6"/>
       <c r="BG91" s="6"/>
-      <c r="BH91" s="90"/>
+      <c r="BH91" s="31"/>
       <c r="BI91" s="6"/>
-      <c r="BJ91" s="90"/>
+      <c r="BJ91" s="31"/>
       <c r="BK91" s="6"/>
-      <c r="BL91" s="90"/>
+      <c r="BL91" s="31"/>
       <c r="BM91" s="7"/>
-      <c r="BN91" s="90"/>
+      <c r="BN91" s="31"/>
       <c r="BO91" s="6"/>
-      <c r="BP91" s="90"/>
+      <c r="BP91" s="31"/>
       <c r="BQ91" s="6"/>
-      <c r="BR91" s="90"/>
+      <c r="BR91" s="31"/>
       <c r="BS91" s="6"/>
-      <c r="BT91" s="90"/>
+      <c r="BT91" s="31"/>
       <c r="BU91" s="6"/>
-      <c r="BV91" s="90"/>
-      <c r="BW91" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX91" s="7"/>
-      <c r="BY91" s="90"/>
+      <c r="BV91" s="31"/>
+      <c r="BW91" s="10"/>
+      <c r="BX91" s="31"/>
+      <c r="BY91" s="7"/>
       <c r="BZ91" s="7"/>
-      <c r="CA91" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB91" s="7"/>
-      <c r="CC91" s="48"/>
+      <c r="CA91" s="69"/>
+      <c r="CB91" s="21"/>
+      <c r="CC91" s="7"/>
       <c r="CD91" s="7"/>
       <c r="CE91" s="7"/>
       <c r="CF91" s="7"/>
@@ -7344,15 +7804,11 @@
       <c r="BT92" s="7"/>
       <c r="BU92" s="7"/>
       <c r="BV92" s="7"/>
-      <c r="BW92" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW92" s="10"/>
       <c r="BX92" s="7"/>
       <c r="BY92" s="7"/>
       <c r="BZ92" s="7"/>
-      <c r="CA92" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA92" s="69"/>
       <c r="CB92" s="7"/>
       <c r="CC92" s="7"/>
       <c r="CD92" s="7"/>
@@ -7377,15 +7833,11 @@
       <c r="BT93" s="7"/>
       <c r="BU93" s="7"/>
       <c r="BV93" s="7"/>
-      <c r="BW93" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW93" s="10"/>
       <c r="BX93" s="7"/>
       <c r="BY93" s="7"/>
       <c r="BZ93" s="7"/>
-      <c r="CA93" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA93" s="69"/>
       <c r="CB93" s="7"/>
       <c r="CC93" s="7"/>
       <c r="CD93" s="7"/>
@@ -7410,15 +7862,11 @@
       <c r="BT94" s="7"/>
       <c r="BU94" s="7"/>
       <c r="BV94" s="7"/>
-      <c r="BW94" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW94" s="10"/>
       <c r="BX94" s="7"/>
       <c r="BY94" s="7"/>
       <c r="BZ94" s="7"/>
-      <c r="CA94" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA94" s="69"/>
       <c r="CB94" s="7"/>
       <c r="CC94" s="7"/>
       <c r="CD94" s="7"/>
@@ -7443,15 +7891,11 @@
       <c r="BT95" s="7"/>
       <c r="BU95" s="7"/>
       <c r="BV95" s="7"/>
-      <c r="BW95" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW95" s="10"/>
       <c r="BX95" s="7"/>
       <c r="BY95" s="7"/>
       <c r="BZ95" s="7"/>
-      <c r="CA95" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA95" s="69"/>
       <c r="CB95" s="7"/>
       <c r="CC95" s="7"/>
       <c r="CD95" s="7"/>
@@ -7461,30 +7905,26 @@
     <row r="96" spans="57:94" x14ac:dyDescent="0.3">
       <c r="BE96" s="6"/>
       <c r="BG96" s="6"/>
-      <c r="BH96" s="97"/>
-      <c r="BI96" s="98"/>
-      <c r="BJ96" s="98"/>
-      <c r="BK96" s="98"/>
-      <c r="BL96" s="98"/>
-      <c r="BM96" s="98"/>
-      <c r="BN96" s="98"/>
-      <c r="BO96" s="98"/>
-      <c r="BP96" s="98"/>
-      <c r="BQ96" s="98"/>
-      <c r="BR96" s="98"/>
-      <c r="BS96" s="98"/>
-      <c r="BT96" s="98"/>
-      <c r="BU96" s="98"/>
-      <c r="BV96" s="99"/>
-      <c r="BW96" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX96" s="7"/>
+      <c r="BH96" s="36"/>
+      <c r="BI96" s="37"/>
+      <c r="BJ96" s="37"/>
+      <c r="BK96" s="37"/>
+      <c r="BL96" s="37"/>
+      <c r="BM96" s="37"/>
+      <c r="BN96" s="37"/>
+      <c r="BO96" s="37"/>
+      <c r="BP96" s="37"/>
+      <c r="BQ96" s="37"/>
+      <c r="BR96" s="37"/>
+      <c r="BS96" s="37"/>
+      <c r="BT96" s="37"/>
+      <c r="BU96" s="37"/>
+      <c r="BV96" s="37"/>
+      <c r="BW96" s="77"/>
+      <c r="BX96" s="38"/>
       <c r="BY96" s="7"/>
       <c r="BZ96" s="7"/>
-      <c r="CA96" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA96" s="69"/>
       <c r="CB96" s="7"/>
       <c r="CC96" s="7"/>
       <c r="CD96" s="7"/>
@@ -7492,192 +7932,168 @@
       <c r="CF96" s="7"/>
     </row>
     <row r="97" spans="59:84" x14ac:dyDescent="0.3">
-      <c r="BH97" s="100"/>
-      <c r="BI97" s="101"/>
-      <c r="BJ97" s="101"/>
-      <c r="BK97" s="101"/>
-      <c r="BL97" s="101"/>
-      <c r="BM97" s="101"/>
-      <c r="BN97" s="101"/>
-      <c r="BO97" s="101"/>
-      <c r="BP97" s="101"/>
-      <c r="BQ97" s="101"/>
-      <c r="BR97" s="101"/>
-      <c r="BS97" s="101"/>
-      <c r="BT97" s="101"/>
-      <c r="BU97" s="101"/>
-      <c r="BV97" s="102"/>
-      <c r="BW97" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX97" s="7"/>
+      <c r="BH97" s="39"/>
+      <c r="BI97" s="75"/>
+      <c r="BJ97" s="75"/>
+      <c r="BK97" s="75"/>
+      <c r="BL97" s="75"/>
+      <c r="BM97" s="75"/>
+      <c r="BN97" s="75"/>
+      <c r="BO97" s="75"/>
+      <c r="BP97" s="75"/>
+      <c r="BQ97" s="75"/>
+      <c r="BR97" s="75"/>
+      <c r="BS97" s="75"/>
+      <c r="BT97" s="75"/>
+      <c r="BU97" s="75"/>
+      <c r="BV97" s="75"/>
+      <c r="BW97" s="76"/>
+      <c r="BX97" s="40"/>
       <c r="BY97" s="7"/>
       <c r="BZ97" s="7"/>
-      <c r="CA97" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA97" s="69"/>
       <c r="CB97" s="7"/>
       <c r="CC97" s="7"/>
       <c r="CD97" s="7"/>
       <c r="CE97" s="7"/>
       <c r="CF97" s="7"/>
     </row>
-    <row r="98" spans="59:84" x14ac:dyDescent="0.3">
+    <row r="98" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG98" s="7"/>
-      <c r="BH98" s="100"/>
-      <c r="BI98" s="103" t="s">
-        <v>58</v>
-      </c>
-      <c r="BJ98" s="103"/>
-      <c r="BK98" s="103"/>
-      <c r="BL98" s="103"/>
-      <c r="BM98" s="103"/>
-      <c r="BN98" s="103"/>
-      <c r="BO98" s="103"/>
-      <c r="BP98" s="103"/>
-      <c r="BQ98" s="103"/>
-      <c r="BR98" s="103"/>
-      <c r="BS98" s="103"/>
-      <c r="BT98" s="103"/>
-      <c r="BU98" s="103"/>
+      <c r="BH98" s="39"/>
+      <c r="BI98" s="102" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ98" s="102"/>
+      <c r="BK98" s="102"/>
+      <c r="BL98" s="102"/>
+      <c r="BM98" s="102"/>
+      <c r="BN98" s="102"/>
+      <c r="BO98" s="102"/>
+      <c r="BP98" s="102"/>
+      <c r="BQ98" s="102"/>
+      <c r="BR98" s="102"/>
+      <c r="BS98" s="102"/>
+      <c r="BT98" s="102"/>
+      <c r="BU98" s="102"/>
       <c r="BV98" s="102"/>
-      <c r="BW98" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX98" s="7"/>
+      <c r="BW98" s="102"/>
+      <c r="BX98" s="40"/>
       <c r="BY98" s="7"/>
       <c r="BZ98" s="7"/>
-      <c r="CA98" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA98" s="69"/>
       <c r="CB98" s="7"/>
       <c r="CC98" s="7"/>
       <c r="CD98" s="7"/>
       <c r="CE98" s="7"/>
       <c r="CF98" s="7"/>
     </row>
-    <row r="99" spans="59:84" x14ac:dyDescent="0.3">
+    <row r="99" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG99" s="7"/>
-      <c r="BH99" s="100"/>
-      <c r="BI99" s="103"/>
-      <c r="BJ99" s="103"/>
-      <c r="BK99" s="103"/>
-      <c r="BL99" s="103"/>
-      <c r="BM99" s="103"/>
-      <c r="BN99" s="103"/>
-      <c r="BO99" s="103"/>
-      <c r="BP99" s="103"/>
-      <c r="BQ99" s="103"/>
-      <c r="BR99" s="103"/>
-      <c r="BS99" s="103"/>
-      <c r="BT99" s="103"/>
-      <c r="BU99" s="103"/>
+      <c r="BH99" s="39"/>
+      <c r="BI99" s="102"/>
+      <c r="BJ99" s="102"/>
+      <c r="BK99" s="102"/>
+      <c r="BL99" s="102"/>
+      <c r="BM99" s="102"/>
+      <c r="BN99" s="102"/>
+      <c r="BO99" s="102"/>
+      <c r="BP99" s="102"/>
+      <c r="BQ99" s="102"/>
+      <c r="BR99" s="102"/>
+      <c r="BS99" s="102"/>
+      <c r="BT99" s="102"/>
+      <c r="BU99" s="102"/>
       <c r="BV99" s="102"/>
-      <c r="BW99" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX99" s="7"/>
+      <c r="BW99" s="102"/>
+      <c r="BX99" s="40"/>
       <c r="BY99" s="7"/>
       <c r="BZ99" s="7"/>
-      <c r="CA99" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA99" s="69"/>
       <c r="CB99" s="7"/>
       <c r="CC99" s="7"/>
       <c r="CD99" s="7"/>
       <c r="CE99" s="7"/>
       <c r="CF99" s="7"/>
     </row>
-    <row r="100" spans="59:84" x14ac:dyDescent="0.3">
+    <row r="100" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG100" s="7"/>
-      <c r="BH100" s="100"/>
-      <c r="BI100" s="103"/>
-      <c r="BJ100" s="103"/>
-      <c r="BK100" s="103"/>
-      <c r="BL100" s="103"/>
-      <c r="BM100" s="103"/>
-      <c r="BN100" s="103"/>
-      <c r="BO100" s="103"/>
-      <c r="BP100" s="103"/>
-      <c r="BQ100" s="103"/>
-      <c r="BR100" s="103"/>
-      <c r="BS100" s="103"/>
-      <c r="BT100" s="103"/>
-      <c r="BU100" s="103"/>
+      <c r="BH100" s="39"/>
+      <c r="BI100" s="102"/>
+      <c r="BJ100" s="102"/>
+      <c r="BK100" s="102"/>
+      <c r="BL100" s="102"/>
+      <c r="BM100" s="102"/>
+      <c r="BN100" s="102"/>
+      <c r="BO100" s="102"/>
+      <c r="BP100" s="102"/>
+      <c r="BQ100" s="102"/>
+      <c r="BR100" s="102"/>
+      <c r="BS100" s="102"/>
+      <c r="BT100" s="102"/>
+      <c r="BU100" s="102"/>
       <c r="BV100" s="102"/>
-      <c r="BW100" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX100" s="7"/>
+      <c r="BW100" s="102"/>
+      <c r="BX100" s="40"/>
       <c r="BY100" s="7"/>
       <c r="BZ100" s="7"/>
-      <c r="CA100" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA100" s="69"/>
       <c r="CB100" s="7"/>
       <c r="CC100" s="7"/>
       <c r="CD100" s="7"/>
       <c r="CE100" s="7"/>
       <c r="CF100" s="7"/>
     </row>
-    <row r="101" spans="59:84" x14ac:dyDescent="0.3">
+    <row r="101" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG101" s="7"/>
-      <c r="BH101" s="100"/>
-      <c r="BI101" s="103"/>
-      <c r="BJ101" s="103"/>
-      <c r="BK101" s="103"/>
-      <c r="BL101" s="103"/>
-      <c r="BM101" s="103"/>
-      <c r="BN101" s="103"/>
-      <c r="BO101" s="103"/>
-      <c r="BP101" s="103"/>
-      <c r="BQ101" s="103"/>
-      <c r="BR101" s="103"/>
-      <c r="BS101" s="103"/>
-      <c r="BT101" s="103"/>
-      <c r="BU101" s="103"/>
+      <c r="BH101" s="39"/>
+      <c r="BI101" s="102"/>
+      <c r="BJ101" s="102"/>
+      <c r="BK101" s="102"/>
+      <c r="BL101" s="102"/>
+      <c r="BM101" s="102"/>
+      <c r="BN101" s="102"/>
+      <c r="BO101" s="102"/>
+      <c r="BP101" s="102"/>
+      <c r="BQ101" s="102"/>
+      <c r="BR101" s="102"/>
+      <c r="BS101" s="102"/>
+      <c r="BT101" s="102"/>
+      <c r="BU101" s="102"/>
       <c r="BV101" s="102"/>
-      <c r="BW101" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX101" s="7"/>
+      <c r="BW101" s="102"/>
+      <c r="BX101" s="40"/>
       <c r="BY101" s="7"/>
       <c r="BZ101" s="7"/>
-      <c r="CA101" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA101" s="69"/>
       <c r="CB101" s="7"/>
       <c r="CC101" s="7"/>
       <c r="CD101" s="7"/>
       <c r="CE101" s="7"/>
       <c r="CF101" s="7"/>
     </row>
-    <row r="102" spans="59:84" x14ac:dyDescent="0.3">
+    <row r="102" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG102" s="7"/>
-      <c r="BH102" s="100"/>
-      <c r="BI102" s="103"/>
-      <c r="BJ102" s="103"/>
-      <c r="BK102" s="103"/>
-      <c r="BL102" s="103"/>
-      <c r="BM102" s="103"/>
-      <c r="BN102" s="103"/>
-      <c r="BO102" s="103"/>
-      <c r="BP102" s="103"/>
-      <c r="BQ102" s="103"/>
-      <c r="BR102" s="103"/>
-      <c r="BS102" s="103"/>
-      <c r="BT102" s="103"/>
-      <c r="BU102" s="103"/>
+      <c r="BH102" s="39"/>
+      <c r="BI102" s="102"/>
+      <c r="BJ102" s="102"/>
+      <c r="BK102" s="102"/>
+      <c r="BL102" s="102"/>
+      <c r="BM102" s="102"/>
+      <c r="BN102" s="102"/>
+      <c r="BO102" s="102"/>
+      <c r="BP102" s="102"/>
+      <c r="BQ102" s="102"/>
+      <c r="BR102" s="102"/>
+      <c r="BS102" s="102"/>
+      <c r="BT102" s="102"/>
+      <c r="BU102" s="102"/>
       <c r="BV102" s="102"/>
-      <c r="BW102" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX102" s="7"/>
+      <c r="BW102" s="102"/>
+      <c r="BX102" s="40"/>
       <c r="BY102" s="7"/>
       <c r="BZ102" s="7"/>
-      <c r="CA102" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA102" s="69"/>
       <c r="CB102" s="7"/>
       <c r="CC102" s="7"/>
       <c r="CD102" s="7"/>
@@ -7686,30 +8102,26 @@
     </row>
     <row r="103" spans="59:84" x14ac:dyDescent="0.3">
       <c r="BG103" s="7"/>
-      <c r="BH103" s="100"/>
-      <c r="BI103" s="101"/>
-      <c r="BJ103" s="101"/>
-      <c r="BK103" s="101"/>
-      <c r="BL103" s="101"/>
-      <c r="BM103" s="101"/>
-      <c r="BN103" s="101"/>
-      <c r="BO103" s="101"/>
-      <c r="BP103" s="101"/>
-      <c r="BQ103" s="101"/>
-      <c r="BR103" s="101"/>
-      <c r="BS103" s="101"/>
-      <c r="BT103" s="101"/>
-      <c r="BU103" s="101"/>
-      <c r="BV103" s="102"/>
-      <c r="BW103" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX103" s="7"/>
+      <c r="BH103" s="39"/>
+      <c r="BI103" s="75"/>
+      <c r="BJ103" s="75"/>
+      <c r="BK103" s="75"/>
+      <c r="BL103" s="75"/>
+      <c r="BM103" s="75"/>
+      <c r="BN103" s="75"/>
+      <c r="BO103" s="75"/>
+      <c r="BP103" s="75"/>
+      <c r="BQ103" s="75"/>
+      <c r="BR103" s="75"/>
+      <c r="BS103" s="75"/>
+      <c r="BT103" s="75"/>
+      <c r="BU103" s="75"/>
+      <c r="BV103" s="75"/>
+      <c r="BW103" s="76"/>
+      <c r="BX103" s="40"/>
       <c r="BY103" s="7"/>
       <c r="BZ103" s="7"/>
-      <c r="CA103" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA103" s="69"/>
       <c r="CB103" s="7"/>
       <c r="CC103" s="7"/>
       <c r="CD103" s="7"/>
@@ -7718,30 +8130,26 @@
     </row>
     <row r="104" spans="59:84" x14ac:dyDescent="0.3">
       <c r="BG104" s="7"/>
-      <c r="BH104" s="104"/>
-      <c r="BI104" s="105"/>
-      <c r="BJ104" s="105"/>
-      <c r="BK104" s="105"/>
-      <c r="BL104" s="105"/>
-      <c r="BM104" s="105"/>
-      <c r="BN104" s="105"/>
-      <c r="BO104" s="105"/>
-      <c r="BP104" s="105"/>
-      <c r="BQ104" s="105"/>
-      <c r="BR104" s="105"/>
-      <c r="BS104" s="105"/>
-      <c r="BT104" s="105"/>
-      <c r="BU104" s="105"/>
-      <c r="BV104" s="106"/>
-      <c r="BW104" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX104" s="7"/>
+      <c r="BH104" s="41"/>
+      <c r="BI104" s="42"/>
+      <c r="BJ104" s="42"/>
+      <c r="BK104" s="42"/>
+      <c r="BL104" s="42"/>
+      <c r="BM104" s="42"/>
+      <c r="BN104" s="42"/>
+      <c r="BO104" s="42"/>
+      <c r="BP104" s="42"/>
+      <c r="BQ104" s="42"/>
+      <c r="BR104" s="42"/>
+      <c r="BS104" s="42"/>
+      <c r="BT104" s="42"/>
+      <c r="BU104" s="42"/>
+      <c r="BV104" s="42"/>
+      <c r="BW104" s="78"/>
+      <c r="BX104" s="43"/>
       <c r="BY104" s="7"/>
       <c r="BZ104" s="7"/>
-      <c r="CA104" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA104" s="69"/>
       <c r="CB104" s="7"/>
       <c r="CC104" s="7"/>
       <c r="CD104" s="7"/>
@@ -7765,15 +8173,11 @@
       <c r="BT105" s="7"/>
       <c r="BU105" s="7"/>
       <c r="BV105" s="7"/>
-      <c r="BW105" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW105" s="10"/>
       <c r="BX105" s="7"/>
       <c r="BY105" s="7"/>
       <c r="BZ105" s="7"/>
-      <c r="CA105" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA105" s="69"/>
       <c r="CB105" s="7"/>
       <c r="CC105" s="7"/>
       <c r="CD105" s="7"/>
@@ -7797,15 +8201,11 @@
       <c r="BT106" s="7"/>
       <c r="BU106" s="7"/>
       <c r="BV106" s="7"/>
-      <c r="BW106" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW106" s="10"/>
       <c r="BX106" s="7"/>
       <c r="BY106" s="7"/>
       <c r="BZ106" s="7"/>
-      <c r="CA106" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA106" s="69"/>
       <c r="CB106" s="7"/>
       <c r="CC106" s="7"/>
       <c r="CD106" s="7"/>
@@ -7829,15 +8229,11 @@
       <c r="BT107" s="7"/>
       <c r="BU107" s="7"/>
       <c r="BV107" s="7"/>
-      <c r="BW107" s="42" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW107" s="10"/>
       <c r="BX107" s="7"/>
       <c r="BY107" s="7"/>
       <c r="BZ107" s="7"/>
-      <c r="CA107" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA107" s="69"/>
       <c r="CB107" s="7"/>
       <c r="CC107" s="7"/>
       <c r="CD107" s="7"/>
@@ -7861,15 +8257,11 @@
       <c r="BT108" s="7"/>
       <c r="BU108" s="7"/>
       <c r="BV108" s="7"/>
-      <c r="BW108" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW108" s="10"/>
       <c r="BX108" s="7"/>
       <c r="BY108" s="7"/>
       <c r="BZ108" s="7"/>
-      <c r="CA108" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA108" s="69"/>
       <c r="CB108" s="7"/>
       <c r="CC108" s="7"/>
       <c r="CD108" s="7"/>
@@ -7878,291 +8270,255 @@
     </row>
     <row r="109" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG109" s="7"/>
-      <c r="BH109" s="109"/>
-      <c r="BI109" s="107"/>
-      <c r="BJ109" s="107"/>
-      <c r="BK109" s="107"/>
-      <c r="BL109" s="107"/>
-      <c r="BM109" s="107"/>
-      <c r="BN109" s="107"/>
-      <c r="BO109" s="107"/>
-      <c r="BP109" s="107"/>
-      <c r="BQ109" s="107"/>
-      <c r="BR109" s="107"/>
-      <c r="BS109" s="107"/>
-      <c r="BT109" s="107"/>
-      <c r="BU109" s="107"/>
-      <c r="BV109" s="107"/>
-      <c r="BW109" s="124" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX109" s="114"/>
-      <c r="BY109" s="107"/>
-      <c r="BZ109" s="114"/>
-      <c r="CA109" s="148" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB109" s="114"/>
-      <c r="CC109" s="115"/>
-      <c r="CD109" s="7"/>
+      <c r="BH109" s="46"/>
+      <c r="BI109" s="44"/>
+      <c r="BJ109" s="44"/>
+      <c r="BK109" s="44"/>
+      <c r="BL109" s="44"/>
+      <c r="BM109" s="44"/>
+      <c r="BN109" s="44"/>
+      <c r="BO109" s="44"/>
+      <c r="BP109" s="44"/>
+      <c r="BQ109" s="44"/>
+      <c r="BR109" s="44"/>
+      <c r="BS109" s="44"/>
+      <c r="BT109" s="44"/>
+      <c r="BU109" s="44"/>
+      <c r="BV109" s="44"/>
+      <c r="BW109" s="57"/>
+      <c r="BX109" s="51"/>
+      <c r="BY109" s="44"/>
+      <c r="BZ109" s="51"/>
+      <c r="CA109" s="66"/>
+      <c r="CB109" s="51"/>
+      <c r="CC109" s="51"/>
+      <c r="CD109" s="52"/>
       <c r="CE109" s="7"/>
       <c r="CF109" s="7"/>
     </row>
     <row r="110" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG110" s="7"/>
-      <c r="BH110" s="110"/>
-      <c r="BI110" s="108"/>
-      <c r="BJ110" s="108"/>
-      <c r="BK110" s="108"/>
-      <c r="BL110" s="108"/>
-      <c r="BM110" s="108"/>
-      <c r="BN110" s="108"/>
-      <c r="BO110" s="108"/>
-      <c r="BP110" s="108"/>
-      <c r="BQ110" s="108"/>
-      <c r="BR110" s="108"/>
-      <c r="BS110" s="108"/>
-      <c r="BT110" s="108"/>
-      <c r="BU110" s="108"/>
-      <c r="BV110" s="108"/>
-      <c r="BW110" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX110" s="17"/>
-      <c r="BY110" s="108"/>
-      <c r="BZ110" s="17"/>
-      <c r="CA110" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB110" s="17"/>
-      <c r="CC110" s="135"/>
-      <c r="CD110" s="7"/>
+      <c r="BH110" s="47"/>
+      <c r="BI110" s="45"/>
+      <c r="BJ110" s="45"/>
+      <c r="BK110" s="45"/>
+      <c r="BL110" s="45"/>
+      <c r="BM110" s="45"/>
+      <c r="BN110" s="45"/>
+      <c r="BO110" s="45"/>
+      <c r="BP110" s="45"/>
+      <c r="BQ110" s="45"/>
+      <c r="BR110" s="45"/>
+      <c r="BS110" s="45"/>
+      <c r="BT110" s="45"/>
+      <c r="BU110" s="45"/>
+      <c r="BV110" s="45"/>
+      <c r="BW110" s="56"/>
+      <c r="BX110" s="11"/>
+      <c r="BY110" s="45"/>
+      <c r="BZ110" s="11"/>
+      <c r="CA110" s="67"/>
+      <c r="CB110" s="11"/>
+      <c r="CC110" s="11"/>
+      <c r="CD110" s="59"/>
       <c r="CE110" s="7"/>
       <c r="CF110" s="7"/>
     </row>
     <row r="111" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG111" s="7"/>
-      <c r="BH111" s="110"/>
-      <c r="BI111" s="108"/>
-      <c r="BJ111" s="108"/>
-      <c r="BK111" s="108"/>
-      <c r="BL111" s="108"/>
-      <c r="BM111" s="108"/>
-      <c r="BN111" s="108"/>
-      <c r="BO111" s="108"/>
-      <c r="BP111" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="BQ111" s="136"/>
-      <c r="BR111" s="136"/>
-      <c r="BS111" s="136"/>
-      <c r="BT111" s="136"/>
-      <c r="BU111" s="136"/>
-      <c r="BV111" s="136"/>
-      <c r="BW111" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX111" s="17"/>
-      <c r="BY111" s="108"/>
-      <c r="BZ111" s="17"/>
-      <c r="CA111" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB111" s="17"/>
-      <c r="CC111" s="135"/>
-      <c r="CD111" s="7"/>
+      <c r="BH111" s="47"/>
+      <c r="BI111" s="45"/>
+      <c r="BJ111" s="45"/>
+      <c r="BK111" s="45"/>
+      <c r="BL111" s="45"/>
+      <c r="BM111" s="45"/>
+      <c r="BN111" s="45"/>
+      <c r="BO111" s="45"/>
+      <c r="BP111" s="96" t="s">
+        <v>41</v>
+      </c>
+      <c r="BQ111" s="96"/>
+      <c r="BR111" s="96"/>
+      <c r="BS111" s="96"/>
+      <c r="BT111" s="96"/>
+      <c r="BU111" s="96"/>
+      <c r="BV111" s="96"/>
+      <c r="BW111" s="56"/>
+      <c r="BX111" s="11"/>
+      <c r="BY111" s="45"/>
+      <c r="BZ111" s="11"/>
+      <c r="CA111" s="67"/>
+      <c r="CB111" s="11"/>
+      <c r="CC111" s="11"/>
+      <c r="CD111" s="59"/>
       <c r="CE111" s="7"/>
       <c r="CF111" s="7"/>
     </row>
     <row r="112" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG112" s="7"/>
-      <c r="BH112" s="110"/>
-      <c r="BI112" s="108"/>
-      <c r="BJ112" s="108"/>
-      <c r="BK112" s="108"/>
-      <c r="BL112" s="108"/>
-      <c r="BM112" s="108"/>
-      <c r="BN112" s="108"/>
-      <c r="BO112" s="108"/>
-      <c r="BP112" s="136"/>
-      <c r="BQ112" s="136"/>
-      <c r="BR112" s="136"/>
-      <c r="BS112" s="136"/>
-      <c r="BT112" s="136"/>
-      <c r="BU112" s="136"/>
-      <c r="BV112" s="136"/>
-      <c r="BW112" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX112" s="17"/>
-      <c r="BY112" s="108"/>
-      <c r="BZ112" s="17"/>
-      <c r="CA112" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB112" s="17"/>
-      <c r="CC112" s="135"/>
-      <c r="CD112" s="7"/>
+      <c r="BH112" s="47"/>
+      <c r="BI112" s="45"/>
+      <c r="BJ112" s="45"/>
+      <c r="BK112" s="45"/>
+      <c r="BL112" s="45"/>
+      <c r="BM112" s="45"/>
+      <c r="BN112" s="45"/>
+      <c r="BO112" s="45"/>
+      <c r="BP112" s="96"/>
+      <c r="BQ112" s="96"/>
+      <c r="BR112" s="96"/>
+      <c r="BS112" s="96"/>
+      <c r="BT112" s="96"/>
+      <c r="BU112" s="96"/>
+      <c r="BV112" s="96"/>
+      <c r="BW112" s="56"/>
+      <c r="BX112" s="11"/>
+      <c r="BY112" s="45"/>
+      <c r="BZ112" s="11"/>
+      <c r="CA112" s="67"/>
+      <c r="CB112" s="11"/>
+      <c r="CC112" s="11"/>
+      <c r="CD112" s="59"/>
       <c r="CE112" s="7"/>
       <c r="CF112" s="7"/>
     </row>
     <row r="113" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG113" s="7"/>
-      <c r="BH113" s="110"/>
-      <c r="BI113" s="108"/>
-      <c r="BJ113" s="108"/>
-      <c r="BK113" s="108"/>
-      <c r="BL113" s="108"/>
-      <c r="BM113" s="108"/>
-      <c r="BN113" s="108"/>
-      <c r="BO113" s="108"/>
-      <c r="BP113" s="136"/>
-      <c r="BQ113" s="136"/>
-      <c r="BR113" s="136"/>
-      <c r="BS113" s="136"/>
-      <c r="BT113" s="136"/>
-      <c r="BU113" s="136"/>
-      <c r="BV113" s="136"/>
-      <c r="BW113" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX113" s="17"/>
-      <c r="BY113" s="108"/>
-      <c r="BZ113" s="17"/>
-      <c r="CA113" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB113" s="17"/>
-      <c r="CC113" s="135"/>
-      <c r="CD113" s="7"/>
+      <c r="BH113" s="47"/>
+      <c r="BI113" s="45"/>
+      <c r="BJ113" s="45"/>
+      <c r="BK113" s="45"/>
+      <c r="BL113" s="45"/>
+      <c r="BM113" s="45"/>
+      <c r="BN113" s="45"/>
+      <c r="BO113" s="45"/>
+      <c r="BP113" s="96"/>
+      <c r="BQ113" s="96"/>
+      <c r="BR113" s="96"/>
+      <c r="BS113" s="96"/>
+      <c r="BT113" s="96"/>
+      <c r="BU113" s="96"/>
+      <c r="BV113" s="96"/>
+      <c r="BW113" s="56"/>
+      <c r="BX113" s="11"/>
+      <c r="BY113" s="45"/>
+      <c r="BZ113" s="11"/>
+      <c r="CA113" s="67"/>
+      <c r="CB113" s="11"/>
+      <c r="CC113" s="11"/>
+      <c r="CD113" s="59"/>
       <c r="CE113" s="7"/>
       <c r="CF113" s="7"/>
     </row>
     <row r="114" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG114" s="7"/>
-      <c r="BH114" s="110"/>
-      <c r="BI114" s="108"/>
-      <c r="BJ114" s="108"/>
-      <c r="BK114" s="108"/>
-      <c r="BL114" s="108"/>
-      <c r="BM114" s="108"/>
-      <c r="BN114" s="108"/>
-      <c r="BO114" s="108"/>
-      <c r="BP114" s="136"/>
-      <c r="BQ114" s="136"/>
-      <c r="BR114" s="136"/>
-      <c r="BS114" s="136"/>
-      <c r="BT114" s="136"/>
-      <c r="BU114" s="136"/>
-      <c r="BV114" s="136"/>
-      <c r="BW114" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX114" s="17"/>
-      <c r="BY114" s="108"/>
-      <c r="BZ114" s="17"/>
-      <c r="CA114" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB114" s="17"/>
-      <c r="CC114" s="135"/>
-      <c r="CD114" s="7"/>
+      <c r="BH114" s="47"/>
+      <c r="BI114" s="45"/>
+      <c r="BJ114" s="45"/>
+      <c r="BK114" s="45"/>
+      <c r="BL114" s="45"/>
+      <c r="BM114" s="45"/>
+      <c r="BN114" s="45"/>
+      <c r="BO114" s="45"/>
+      <c r="BP114" s="96"/>
+      <c r="BQ114" s="96"/>
+      <c r="BR114" s="96"/>
+      <c r="BS114" s="96"/>
+      <c r="BT114" s="96"/>
+      <c r="BU114" s="96"/>
+      <c r="BV114" s="96"/>
+      <c r="BW114" s="56"/>
+      <c r="BX114" s="11"/>
+      <c r="BY114" s="45"/>
+      <c r="BZ114" s="11"/>
+      <c r="CA114" s="67"/>
+      <c r="CB114" s="11"/>
+      <c r="CC114" s="11"/>
+      <c r="CD114" s="59"/>
       <c r="CE114" s="7"/>
       <c r="CF114" s="7"/>
     </row>
     <row r="115" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG115" s="7"/>
-      <c r="BH115" s="110"/>
-      <c r="BI115" s="108"/>
-      <c r="BJ115" s="108"/>
-      <c r="BK115" s="108"/>
-      <c r="BL115" s="108"/>
-      <c r="BM115" s="108"/>
-      <c r="BN115" s="108"/>
-      <c r="BO115" s="108"/>
-      <c r="BP115" s="136"/>
-      <c r="BQ115" s="136"/>
-      <c r="BR115" s="136"/>
-      <c r="BS115" s="136"/>
-      <c r="BT115" s="136"/>
-      <c r="BU115" s="136"/>
-      <c r="BV115" s="136"/>
-      <c r="BW115" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX115" s="17"/>
-      <c r="BY115" s="108"/>
-      <c r="BZ115" s="17"/>
-      <c r="CA115" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB115" s="17"/>
-      <c r="CC115" s="135"/>
-      <c r="CD115" s="7"/>
+      <c r="BH115" s="47"/>
+      <c r="BI115" s="45"/>
+      <c r="BJ115" s="45"/>
+      <c r="BK115" s="45"/>
+      <c r="BL115" s="45"/>
+      <c r="BM115" s="45"/>
+      <c r="BN115" s="45"/>
+      <c r="BO115" s="45"/>
+      <c r="BP115" s="96"/>
+      <c r="BQ115" s="96"/>
+      <c r="BR115" s="96"/>
+      <c r="BS115" s="96"/>
+      <c r="BT115" s="96"/>
+      <c r="BU115" s="96"/>
+      <c r="BV115" s="96"/>
+      <c r="BW115" s="56"/>
+      <c r="BX115" s="11"/>
+      <c r="BY115" s="45"/>
+      <c r="BZ115" s="11"/>
+      <c r="CA115" s="67"/>
+      <c r="CB115" s="11"/>
+      <c r="CC115" s="11"/>
+      <c r="CD115" s="59"/>
       <c r="CE115" s="7"/>
       <c r="CF115" s="7"/>
     </row>
     <row r="116" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG116" s="7"/>
-      <c r="BH116" s="110"/>
-      <c r="BI116" s="108"/>
-      <c r="BJ116" s="108"/>
-      <c r="BK116" s="108"/>
-      <c r="BL116" s="108"/>
-      <c r="BM116" s="108"/>
-      <c r="BN116" s="108"/>
-      <c r="BO116" s="108"/>
-      <c r="BP116" s="108"/>
-      <c r="BQ116" s="108"/>
-      <c r="BR116" s="108"/>
-      <c r="BS116" s="108"/>
-      <c r="BT116" s="108"/>
-      <c r="BU116" s="108"/>
-      <c r="BV116" s="108"/>
-      <c r="BW116" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX116" s="17"/>
-      <c r="BY116" s="108"/>
-      <c r="BZ116" s="17"/>
-      <c r="CA116" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB116" s="17"/>
-      <c r="CC116" s="135"/>
-      <c r="CD116" s="7"/>
+      <c r="BH116" s="47"/>
+      <c r="BI116" s="45"/>
+      <c r="BJ116" s="45"/>
+      <c r="BK116" s="45"/>
+      <c r="BL116" s="45"/>
+      <c r="BM116" s="45"/>
+      <c r="BN116" s="45"/>
+      <c r="BO116" s="45"/>
+      <c r="BP116" s="45"/>
+      <c r="BQ116" s="45"/>
+      <c r="BR116" s="45"/>
+      <c r="BS116" s="45"/>
+      <c r="BT116" s="45"/>
+      <c r="BU116" s="45"/>
+      <c r="BV116" s="45"/>
+      <c r="BW116" s="56"/>
+      <c r="BX116" s="11"/>
+      <c r="BY116" s="45"/>
+      <c r="BZ116" s="11"/>
+      <c r="CA116" s="67"/>
+      <c r="CB116" s="11"/>
+      <c r="CC116" s="11"/>
+      <c r="CD116" s="59"/>
       <c r="CE116" s="7"/>
       <c r="CF116" s="7"/>
     </row>
     <row r="117" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG117" s="7"/>
-      <c r="BH117" s="111"/>
-      <c r="BI117" s="112"/>
-      <c r="BJ117" s="112"/>
-      <c r="BK117" s="112"/>
-      <c r="BL117" s="112"/>
-      <c r="BM117" s="112"/>
-      <c r="BN117" s="112"/>
-      <c r="BO117" s="112"/>
-      <c r="BP117" s="112"/>
-      <c r="BQ117" s="112"/>
-      <c r="BR117" s="112"/>
-      <c r="BS117" s="112"/>
-      <c r="BT117" s="112"/>
-      <c r="BU117" s="112"/>
-      <c r="BV117" s="112"/>
-      <c r="BW117" s="125" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX117" s="120"/>
-      <c r="BY117" s="112"/>
-      <c r="BZ117" s="120"/>
-      <c r="CA117" s="150" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB117" s="120"/>
-      <c r="CC117" s="121"/>
-      <c r="CD117" s="7"/>
+      <c r="BH117" s="48"/>
+      <c r="BI117" s="49"/>
+      <c r="BJ117" s="49"/>
+      <c r="BK117" s="49"/>
+      <c r="BL117" s="49"/>
+      <c r="BM117" s="49"/>
+      <c r="BN117" s="49"/>
+      <c r="BO117" s="49"/>
+      <c r="BP117" s="49"/>
+      <c r="BQ117" s="49"/>
+      <c r="BR117" s="49"/>
+      <c r="BS117" s="49"/>
+      <c r="BT117" s="49"/>
+      <c r="BU117" s="49"/>
+      <c r="BV117" s="49"/>
+      <c r="BW117" s="58"/>
+      <c r="BX117" s="54"/>
+      <c r="BY117" s="49"/>
+      <c r="BZ117" s="54"/>
+      <c r="CA117" s="68"/>
+      <c r="CB117" s="54"/>
+      <c r="CC117" s="54"/>
+      <c r="CD117" s="55"/>
       <c r="CE117" s="7"/>
       <c r="CF117" s="7"/>
     </row>
@@ -8183,15 +8539,11 @@
       <c r="BT118" s="7"/>
       <c r="BU118" s="7"/>
       <c r="BV118" s="7"/>
-      <c r="BW118" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW118" s="10"/>
       <c r="BX118" s="7"/>
       <c r="BY118" s="7"/>
       <c r="BZ118" s="7"/>
-      <c r="CA118" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA118" s="69"/>
       <c r="CB118" s="7"/>
       <c r="CC118" s="7"/>
       <c r="CD118" s="7"/>
@@ -8215,15 +8567,11 @@
       <c r="BT119" s="7"/>
       <c r="BU119" s="7"/>
       <c r="BV119" s="7"/>
-      <c r="BW119" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW119" s="10"/>
       <c r="BX119" s="7"/>
       <c r="BY119" s="7"/>
       <c r="BZ119" s="7"/>
-      <c r="CA119" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA119" s="69"/>
       <c r="CB119" s="7"/>
       <c r="CC119" s="7"/>
       <c r="CD119" s="7"/>
@@ -8247,15 +8595,11 @@
       <c r="BT120" s="7"/>
       <c r="BU120" s="7"/>
       <c r="BV120" s="7"/>
-      <c r="BW120" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW120" s="10"/>
       <c r="BX120" s="7"/>
       <c r="BY120" s="7"/>
       <c r="BZ120" s="7"/>
-      <c r="CA120" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA120" s="69"/>
       <c r="CB120" s="7"/>
       <c r="CC120" s="7"/>
       <c r="CD120" s="7"/>
@@ -8279,15 +8623,11 @@
       <c r="BT121" s="7"/>
       <c r="BU121" s="7"/>
       <c r="BV121" s="7"/>
-      <c r="BW121" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW121" s="10"/>
       <c r="BX121" s="7"/>
       <c r="BY121" s="7"/>
       <c r="BZ121" s="7"/>
-      <c r="CA121" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA121" s="69"/>
       <c r="CB121" s="7"/>
       <c r="CC121" s="7"/>
       <c r="CD121" s="7"/>
@@ -8296,30 +8636,26 @@
     </row>
     <row r="122" spans="59:84" x14ac:dyDescent="0.3">
       <c r="BG122" s="7"/>
-      <c r="BH122" s="96"/>
+      <c r="BH122" s="35"/>
       <c r="BI122" s="6"/>
-      <c r="BJ122" s="96"/>
+      <c r="BJ122" s="35"/>
       <c r="BK122" s="6"/>
-      <c r="BL122" s="96"/>
+      <c r="BL122" s="35"/>
       <c r="BM122" s="7"/>
-      <c r="BN122" s="96"/>
+      <c r="BN122" s="35"/>
       <c r="BO122" s="6"/>
-      <c r="BP122" s="96"/>
+      <c r="BP122" s="35"/>
       <c r="BQ122" s="6"/>
-      <c r="BR122" s="96"/>
+      <c r="BR122" s="35"/>
       <c r="BS122" s="6"/>
-      <c r="BT122" s="96"/>
+      <c r="BT122" s="35"/>
       <c r="BU122" s="6"/>
-      <c r="BV122" s="96"/>
-      <c r="BW122" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX122" s="7"/>
+      <c r="BV122" s="35"/>
+      <c r="BW122" s="10"/>
+      <c r="BX122" s="35"/>
       <c r="BY122" s="7"/>
       <c r="BZ122" s="7"/>
-      <c r="CA122" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA122" s="69"/>
       <c r="CB122" s="7"/>
       <c r="CC122" s="7"/>
       <c r="CD122" s="7"/>
@@ -8328,38 +8664,38 @@
     </row>
     <row r="123" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG123" s="7"/>
-      <c r="BH123" s="147" t="s">
-        <v>61</v>
+      <c r="BH123" s="80" t="s">
+        <v>43</v>
       </c>
       <c r="BI123" s="6"/>
-      <c r="BJ123" s="147" t="s">
-        <v>62</v>
+      <c r="BJ123" s="80" t="s">
+        <v>44</v>
       </c>
       <c r="BK123" s="6"/>
-      <c r="BL123" s="43"/>
+      <c r="BL123" s="80" t="s">
+        <v>51</v>
+      </c>
       <c r="BM123" s="7"/>
-      <c r="BN123" s="43"/>
+      <c r="BN123" s="17"/>
       <c r="BO123" s="6"/>
-      <c r="BP123" s="43"/>
+      <c r="BP123" s="17"/>
       <c r="BQ123" s="6"/>
-      <c r="BR123" s="43"/>
+      <c r="BR123" s="17"/>
       <c r="BS123" s="6"/>
-      <c r="BT123" s="147" t="s">
-        <v>63</v>
+      <c r="BT123" s="80" t="s">
+        <v>45</v>
       </c>
       <c r="BU123" s="6"/>
-      <c r="BV123" s="147" t="s">
-        <v>64</v>
-      </c>
-      <c r="BW123" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX123" s="7"/>
+      <c r="BV123" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="BW123" s="10"/>
+      <c r="BX123" s="80" t="s">
+        <v>50</v>
+      </c>
       <c r="BY123" s="7"/>
       <c r="BZ123" s="7"/>
-      <c r="CA123" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA123" s="69"/>
       <c r="CB123" s="7"/>
       <c r="CC123" s="7"/>
       <c r="CD123" s="7"/>
@@ -8368,32 +8704,27 @@
     </row>
     <row r="124" spans="59:84" ht="25.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="BG124" s="7"/>
-      <c r="BH124" s="147"/>
+      <c r="BH124" s="80"/>
       <c r="BI124" s="6"/>
-      <c r="BJ124" s="147"/>
+      <c r="BJ124" s="80"/>
       <c r="BK124" s="6"/>
-      <c r="BL124" s="43"/>
-      <c r="BM124" s="95"/>
-      <c r="BN124" s="43"/>
-      <c r="BO124" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="BP124" s="43"/>
+      <c r="BL124" s="80"/>
+      <c r="BM124" s="34"/>
+      <c r="BN124" s="17"/>
+      <c r="BP124" s="79" t="s">
+        <v>42</v>
+      </c>
       <c r="BQ124" s="6"/>
-      <c r="BR124" s="43"/>
+      <c r="BR124" s="17"/>
       <c r="BS124" s="6"/>
-      <c r="BT124" s="147"/>
+      <c r="BT124" s="80"/>
       <c r="BU124" s="6"/>
-      <c r="BV124" s="147"/>
-      <c r="BW124" s="122" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX124" s="7"/>
+      <c r="BV124" s="80"/>
+      <c r="BW124" s="10"/>
+      <c r="BX124" s="80"/>
       <c r="BY124" s="7"/>
       <c r="BZ124" s="7"/>
-      <c r="CA124" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA124" s="69"/>
       <c r="CB124" s="7"/>
       <c r="CC124" s="7"/>
       <c r="CD124" s="7"/>
@@ -8402,30 +8733,26 @@
     </row>
     <row r="125" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG125" s="7"/>
-      <c r="BH125" s="147"/>
+      <c r="BH125" s="80"/>
       <c r="BI125" s="6"/>
-      <c r="BJ125" s="147"/>
+      <c r="BJ125" s="80"/>
       <c r="BK125" s="6"/>
-      <c r="BL125" s="43"/>
+      <c r="BL125" s="80"/>
       <c r="BM125" s="7"/>
-      <c r="BN125" s="43"/>
+      <c r="BN125" s="17"/>
       <c r="BO125" s="6"/>
-      <c r="BP125" s="43"/>
+      <c r="BP125" s="17"/>
       <c r="BQ125" s="6"/>
-      <c r="BR125" s="43"/>
+      <c r="BR125" s="17"/>
       <c r="BS125" s="6"/>
-      <c r="BT125" s="147"/>
+      <c r="BT125" s="80"/>
       <c r="BU125" s="6"/>
-      <c r="BV125" s="147"/>
-      <c r="BW125" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX125" s="7"/>
+      <c r="BV125" s="80"/>
+      <c r="BW125" s="10"/>
+      <c r="BX125" s="80"/>
       <c r="BY125" s="7"/>
       <c r="BZ125" s="7"/>
-      <c r="CA125" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA125" s="69"/>
       <c r="CB125" s="7"/>
       <c r="CC125" s="7"/>
       <c r="CD125" s="7"/>
@@ -8434,30 +8761,26 @@
     </row>
     <row r="126" spans="59:84" x14ac:dyDescent="0.3">
       <c r="BG126" s="7"/>
-      <c r="BH126" s="44"/>
+      <c r="BH126" s="18"/>
       <c r="BI126" s="6"/>
-      <c r="BJ126" s="44"/>
+      <c r="BJ126" s="18"/>
       <c r="BK126" s="6"/>
-      <c r="BL126" s="44"/>
+      <c r="BL126" s="18"/>
       <c r="BM126" s="7"/>
-      <c r="BN126" s="44"/>
+      <c r="BN126" s="18"/>
       <c r="BO126" s="6"/>
-      <c r="BP126" s="44"/>
+      <c r="BP126" s="18"/>
       <c r="BQ126" s="6"/>
-      <c r="BR126" s="44"/>
+      <c r="BR126" s="18"/>
       <c r="BS126" s="6"/>
-      <c r="BT126" s="44"/>
+      <c r="BT126" s="18"/>
       <c r="BU126" s="6"/>
-      <c r="BV126" s="44"/>
-      <c r="BW126" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX126" s="7"/>
+      <c r="BV126" s="18"/>
+      <c r="BW126" s="10"/>
+      <c r="BX126" s="18"/>
       <c r="BY126" s="7"/>
       <c r="BZ126" s="7"/>
-      <c r="CA126" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA126" s="69"/>
       <c r="CB126" s="7"/>
       <c r="CC126" s="7"/>
       <c r="CD126" s="7"/>
@@ -8481,15 +8804,11 @@
       <c r="BT127" s="7"/>
       <c r="BU127" s="7"/>
       <c r="BV127" s="7"/>
-      <c r="BW127" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW127" s="10"/>
       <c r="BX127" s="7"/>
       <c r="BY127" s="7"/>
       <c r="BZ127" s="7"/>
-      <c r="CA127" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA127" s="69"/>
       <c r="CB127" s="7"/>
       <c r="CC127" s="7"/>
       <c r="CD127" s="7"/>
@@ -8513,15 +8832,11 @@
       <c r="BT128" s="7"/>
       <c r="BU128" s="7"/>
       <c r="BV128" s="7"/>
-      <c r="BW128" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW128" s="10"/>
       <c r="BX128" s="7"/>
       <c r="BY128" s="7"/>
       <c r="BZ128" s="7"/>
-      <c r="CA128" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA128" s="69"/>
       <c r="CB128" s="7"/>
       <c r="CC128" s="7"/>
       <c r="CD128" s="7"/>
@@ -8545,15 +8860,11 @@
       <c r="BT129" s="7"/>
       <c r="BU129" s="7"/>
       <c r="BV129" s="7"/>
-      <c r="BW129" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW129" s="10"/>
       <c r="BX129" s="7"/>
       <c r="BY129" s="7"/>
       <c r="BZ129" s="7"/>
-      <c r="CA129" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA129" s="69"/>
       <c r="CB129" s="7"/>
       <c r="CC129" s="7"/>
       <c r="CD129" s="7"/>
@@ -8577,15 +8888,11 @@
       <c r="BT130" s="7"/>
       <c r="BU130" s="7"/>
       <c r="BV130" s="7"/>
-      <c r="BW130" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW130" s="10"/>
       <c r="BX130" s="7"/>
       <c r="BY130" s="7"/>
       <c r="BZ130" s="7"/>
-      <c r="CA130" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA130" s="69"/>
       <c r="CB130" s="7"/>
       <c r="CC130" s="7"/>
       <c r="CD130" s="7"/>
@@ -8599,31 +8906,27 @@
       <c r="BJ131" s="7"/>
       <c r="BK131" s="7"/>
       <c r="BL131" s="7"/>
-      <c r="BM131" s="113"/>
-      <c r="BN131" s="114"/>
-      <c r="BO131" s="114"/>
-      <c r="BP131" s="114"/>
-      <c r="BQ131" s="115"/>
-      <c r="BR131" s="7"/>
+      <c r="BM131" s="7"/>
+      <c r="BN131" s="50"/>
+      <c r="BO131" s="51"/>
+      <c r="BP131" s="51"/>
+      <c r="BQ131" s="51"/>
+      <c r="BR131" s="52"/>
       <c r="BS131" s="7"/>
       <c r="BT131" s="7"/>
       <c r="BU131" s="7"/>
       <c r="BV131" s="7"/>
-      <c r="BW131" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX131" s="126" t="s">
-        <v>66</v>
-      </c>
-      <c r="BY131" s="127"/>
-      <c r="BZ131" s="128"/>
-      <c r="CA131" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB131" s="138"/>
-      <c r="CC131" s="139"/>
-      <c r="CD131" s="140"/>
-      <c r="CE131" s="7"/>
+      <c r="BW131" s="10"/>
+      <c r="BX131" s="7"/>
+      <c r="BY131" s="87" t="s">
+        <v>52</v>
+      </c>
+      <c r="BZ131" s="88"/>
+      <c r="CA131" s="89"/>
+      <c r="CB131" s="69"/>
+      <c r="CC131" s="60"/>
+      <c r="CD131" s="61"/>
+      <c r="CE131" s="62"/>
       <c r="CF131" s="7"/>
     </row>
     <row r="132" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8633,33 +8936,29 @@
       <c r="BJ132" s="7"/>
       <c r="BK132" s="7"/>
       <c r="BL132" s="7"/>
-      <c r="BM132" s="137" t="s">
+      <c r="BM132" s="7"/>
+      <c r="BN132" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="BN132" s="117"/>
-      <c r="BO132" s="117"/>
-      <c r="BP132" s="117"/>
-      <c r="BQ132" s="118"/>
-      <c r="BR132" s="7"/>
+      <c r="BO132" s="84"/>
+      <c r="BP132" s="84"/>
+      <c r="BQ132" s="84"/>
+      <c r="BR132" s="85"/>
       <c r="BS132" s="7"/>
       <c r="BT132" s="7"/>
       <c r="BU132" s="7"/>
       <c r="BV132" s="7"/>
-      <c r="BW132" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX132" s="129"/>
-      <c r="BY132" s="130"/>
-      <c r="BZ132" s="131"/>
-      <c r="CA132" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB132" s="144" t="s">
-        <v>67</v>
-      </c>
-      <c r="CC132" s="145"/>
-      <c r="CD132" s="146"/>
-      <c r="CE132" s="7"/>
+      <c r="BW132" s="10"/>
+      <c r="BX132" s="7"/>
+      <c r="BY132" s="90"/>
+      <c r="BZ132" s="91"/>
+      <c r="CA132" s="92"/>
+      <c r="CB132" s="69"/>
+      <c r="CC132" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="CD132" s="98"/>
+      <c r="CE132" s="99"/>
       <c r="CF132" s="7"/>
     </row>
     <row r="133" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8669,29 +8968,25 @@
       <c r="BJ133" s="7"/>
       <c r="BK133" s="7"/>
       <c r="BL133" s="7"/>
-      <c r="BM133" s="116"/>
-      <c r="BN133" s="117"/>
-      <c r="BO133" s="117"/>
-      <c r="BP133" s="117"/>
-      <c r="BQ133" s="118"/>
-      <c r="BR133" s="7"/>
+      <c r="BM133" s="7"/>
+      <c r="BN133" s="86"/>
+      <c r="BO133" s="84"/>
+      <c r="BP133" s="84"/>
+      <c r="BQ133" s="84"/>
+      <c r="BR133" s="85"/>
       <c r="BS133" s="7"/>
       <c r="BT133" s="7"/>
       <c r="BU133" s="7"/>
       <c r="BV133" s="7"/>
-      <c r="BW133" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX133" s="129"/>
-      <c r="BY133" s="130"/>
-      <c r="BZ133" s="131"/>
-      <c r="CA133" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB133" s="144"/>
-      <c r="CC133" s="145"/>
-      <c r="CD133" s="146"/>
-      <c r="CE133" s="7"/>
+      <c r="BW133" s="10"/>
+      <c r="BX133" s="7"/>
+      <c r="BY133" s="90"/>
+      <c r="BZ133" s="91"/>
+      <c r="CA133" s="92"/>
+      <c r="CB133" s="69"/>
+      <c r="CC133" s="97"/>
+      <c r="CD133" s="98"/>
+      <c r="CE133" s="99"/>
       <c r="CF133" s="7"/>
     </row>
     <row r="134" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8701,29 +8996,25 @@
       <c r="BJ134" s="7"/>
       <c r="BK134" s="7"/>
       <c r="BL134" s="7"/>
-      <c r="BM134" s="116"/>
-      <c r="BN134" s="117"/>
-      <c r="BO134" s="117"/>
-      <c r="BP134" s="117"/>
-      <c r="BQ134" s="118"/>
-      <c r="BR134" s="7"/>
+      <c r="BM134" s="7"/>
+      <c r="BN134" s="86"/>
+      <c r="BO134" s="84"/>
+      <c r="BP134" s="84"/>
+      <c r="BQ134" s="84"/>
+      <c r="BR134" s="85"/>
       <c r="BS134" s="7"/>
       <c r="BT134" s="7"/>
       <c r="BU134" s="7"/>
       <c r="BV134" s="7"/>
-      <c r="BW134" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX134" s="129"/>
-      <c r="BY134" s="130"/>
-      <c r="BZ134" s="131"/>
-      <c r="CA134" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB134" s="144"/>
-      <c r="CC134" s="145"/>
-      <c r="CD134" s="146"/>
-      <c r="CE134" s="7"/>
+      <c r="BW134" s="10"/>
+      <c r="BX134" s="7"/>
+      <c r="BY134" s="90"/>
+      <c r="BZ134" s="91"/>
+      <c r="CA134" s="92"/>
+      <c r="CB134" s="69"/>
+      <c r="CC134" s="97"/>
+      <c r="CD134" s="98"/>
+      <c r="CE134" s="99"/>
       <c r="CF134" s="7"/>
     </row>
     <row r="135" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8733,29 +9024,25 @@
       <c r="BJ135" s="7"/>
       <c r="BK135" s="7"/>
       <c r="BL135" s="7"/>
-      <c r="BM135" s="116"/>
-      <c r="BN135" s="117"/>
-      <c r="BO135" s="117"/>
-      <c r="BP135" s="117"/>
-      <c r="BQ135" s="118"/>
-      <c r="BR135" s="7"/>
+      <c r="BM135" s="7"/>
+      <c r="BN135" s="86"/>
+      <c r="BO135" s="84"/>
+      <c r="BP135" s="84"/>
+      <c r="BQ135" s="84"/>
+      <c r="BR135" s="85"/>
       <c r="BS135" s="7"/>
       <c r="BT135" s="7"/>
       <c r="BU135" s="7"/>
       <c r="BV135" s="7"/>
-      <c r="BW135" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX135" s="129"/>
-      <c r="BY135" s="130"/>
-      <c r="BZ135" s="131"/>
-      <c r="CA135" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB135" s="144"/>
-      <c r="CC135" s="145"/>
-      <c r="CD135" s="146"/>
-      <c r="CE135" s="7"/>
+      <c r="BW135" s="10"/>
+      <c r="BX135" s="7"/>
+      <c r="BY135" s="90"/>
+      <c r="BZ135" s="91"/>
+      <c r="CA135" s="92"/>
+      <c r="CB135" s="69"/>
+      <c r="CC135" s="97"/>
+      <c r="CD135" s="98"/>
+      <c r="CE135" s="99"/>
       <c r="CF135" s="7"/>
     </row>
     <row r="136" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8765,29 +9052,25 @@
       <c r="BJ136" s="7"/>
       <c r="BK136" s="7"/>
       <c r="BL136" s="7"/>
-      <c r="BM136" s="116"/>
-      <c r="BN136" s="117"/>
-      <c r="BO136" s="117"/>
-      <c r="BP136" s="117"/>
-      <c r="BQ136" s="118"/>
-      <c r="BR136" s="7"/>
+      <c r="BM136" s="7"/>
+      <c r="BN136" s="86"/>
+      <c r="BO136" s="84"/>
+      <c r="BP136" s="84"/>
+      <c r="BQ136" s="84"/>
+      <c r="BR136" s="85"/>
       <c r="BS136" s="7"/>
       <c r="BT136" s="7"/>
       <c r="BU136" s="7"/>
       <c r="BV136" s="7"/>
-      <c r="BW136" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX136" s="129"/>
-      <c r="BY136" s="130"/>
-      <c r="BZ136" s="131"/>
-      <c r="CA136" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB136" s="144"/>
-      <c r="CC136" s="145"/>
-      <c r="CD136" s="146"/>
-      <c r="CE136" s="7"/>
+      <c r="BW136" s="10"/>
+      <c r="BX136" s="7"/>
+      <c r="BY136" s="90"/>
+      <c r="BZ136" s="91"/>
+      <c r="CA136" s="92"/>
+      <c r="CB136" s="69"/>
+      <c r="CC136" s="97"/>
+      <c r="CD136" s="98"/>
+      <c r="CE136" s="99"/>
       <c r="CF136" s="7"/>
     </row>
     <row r="137" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8797,32 +9080,28 @@
       <c r="BJ137" s="7"/>
       <c r="BK137" s="7"/>
       <c r="BL137" s="7"/>
-      <c r="BM137" s="119"/>
-      <c r="BN137" s="120"/>
-      <c r="BO137" s="120"/>
-      <c r="BP137" s="120"/>
-      <c r="BQ137" s="121"/>
-      <c r="BR137" s="7"/>
+      <c r="BM137" s="7"/>
+      <c r="BN137" s="53"/>
+      <c r="BO137" s="54"/>
+      <c r="BP137" s="54"/>
+      <c r="BQ137" s="54"/>
+      <c r="BR137" s="55"/>
       <c r="BS137" s="7"/>
       <c r="BT137" s="7"/>
       <c r="BU137" s="7"/>
       <c r="BV137" s="7"/>
-      <c r="BW137" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="BX137" s="132"/>
-      <c r="BY137" s="133"/>
-      <c r="BZ137" s="134"/>
-      <c r="CA137" s="152" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB137" s="141"/>
-      <c r="CC137" s="142"/>
-      <c r="CD137" s="143"/>
-      <c r="CE137" s="7"/>
+      <c r="BW137" s="10"/>
+      <c r="BX137" s="7"/>
+      <c r="BY137" s="93"/>
+      <c r="BZ137" s="94"/>
+      <c r="CA137" s="95"/>
+      <c r="CB137" s="69"/>
+      <c r="CC137" s="63"/>
+      <c r="CD137" s="64"/>
+      <c r="CE137" s="65"/>
       <c r="CF137" s="7"/>
       <c r="AVI137" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="138" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8842,15 +9121,11 @@
       <c r="BT138" s="7"/>
       <c r="BU138" s="7"/>
       <c r="BV138" s="7"/>
-      <c r="BW138" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW138" s="10"/>
       <c r="BX138" s="7"/>
       <c r="BY138" s="7"/>
       <c r="BZ138" s="7"/>
-      <c r="CA138" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA138" s="69"/>
       <c r="CB138" s="7"/>
       <c r="CC138" s="7"/>
       <c r="CD138" s="7"/>
@@ -8874,15 +9149,11 @@
       <c r="BT139" s="7"/>
       <c r="BU139" s="7"/>
       <c r="BV139" s="7"/>
-      <c r="BW139" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW139" s="10"/>
       <c r="BX139" s="7"/>
       <c r="BY139" s="7"/>
       <c r="BZ139" s="7"/>
-      <c r="CA139" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA139" s="69"/>
       <c r="CB139" s="7"/>
       <c r="CC139" s="7"/>
       <c r="CD139" s="7"/>
@@ -8906,15 +9177,11 @@
       <c r="BT140" s="7"/>
       <c r="BU140" s="7"/>
       <c r="BV140" s="7"/>
-      <c r="BW140" s="45" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW140" s="10"/>
       <c r="BX140" s="7"/>
       <c r="BY140" s="7"/>
       <c r="BZ140" s="7"/>
-      <c r="CA140" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA140" s="69"/>
       <c r="CB140" s="7"/>
       <c r="CC140" s="7"/>
       <c r="CD140" s="7"/>
@@ -8938,15 +9205,11 @@
       <c r="BT141" s="7"/>
       <c r="BU141" s="7"/>
       <c r="BV141" s="7"/>
-      <c r="BW141" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW141" s="10"/>
       <c r="BX141" s="7"/>
       <c r="BY141" s="7"/>
       <c r="BZ141" s="7"/>
-      <c r="CA141" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA141" s="69"/>
       <c r="CB141" s="7"/>
       <c r="CC141" s="7"/>
       <c r="CD141" s="7"/>
@@ -8970,15 +9233,11 @@
       <c r="BT142" s="7"/>
       <c r="BU142" s="7"/>
       <c r="BV142" s="7"/>
-      <c r="BW142" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="BW142" s="10"/>
       <c r="BX142" s="7"/>
       <c r="BY142" s="7"/>
       <c r="BZ142" s="7"/>
-      <c r="CA142" s="152" t="s">
-        <v>65</v>
-      </c>
+      <c r="CA142" s="69"/>
       <c r="CB142" s="7"/>
       <c r="CC142" s="7"/>
       <c r="CD142" s="7"/>
@@ -8996,11 +9255,11 @@
       <c r="BT143" s="7"/>
       <c r="BU143" s="7"/>
       <c r="BV143" s="7"/>
-      <c r="BW143" s="7"/>
+      <c r="BW143" s="10"/>
       <c r="BX143" s="7"/>
       <c r="BY143" s="7"/>
       <c r="BZ143" s="7"/>
-      <c r="CA143" s="7"/>
+      <c r="CA143" s="69"/>
       <c r="CB143" s="7"/>
       <c r="CC143" s="7"/>
       <c r="CD143" s="7"/>
@@ -9009,73 +9268,73 @@
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="BH76:BV78"/>
-    <mergeCell ref="BX76:BZ78"/>
-    <mergeCell ref="CB76:CD78"/>
-    <mergeCell ref="BH123:BH125"/>
-    <mergeCell ref="BV123:BV125"/>
-    <mergeCell ref="BT123:BT125"/>
-    <mergeCell ref="BJ123:BJ125"/>
-    <mergeCell ref="BM132:BQ136"/>
-    <mergeCell ref="BX131:BZ137"/>
-    <mergeCell ref="BP111:BV115"/>
-    <mergeCell ref="CB132:CD136"/>
-    <mergeCell ref="BL82:BL83"/>
-    <mergeCell ref="CC82:CC83"/>
-    <mergeCell ref="BI98:BU102"/>
+    <mergeCell ref="R62:V62"/>
+    <mergeCell ref="U44:X45"/>
+    <mergeCell ref="U49:X51"/>
+    <mergeCell ref="U52:X54"/>
+    <mergeCell ref="U37:V40"/>
+    <mergeCell ref="U46:W46"/>
+    <mergeCell ref="T40:T49"/>
+    <mergeCell ref="E34:I35"/>
+    <mergeCell ref="N33:P34"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="S34:U34"/>
+    <mergeCell ref="AP45:AT46"/>
+    <mergeCell ref="AE34:AI35"/>
+    <mergeCell ref="AP48:AR49"/>
+    <mergeCell ref="AO49:AO50"/>
     <mergeCell ref="AM33:AQ34"/>
-    <mergeCell ref="AN63:AX64"/>
-    <mergeCell ref="AN65:AX66"/>
-    <mergeCell ref="AN61:AX62"/>
-    <mergeCell ref="AC39:AC40"/>
-    <mergeCell ref="AK39:AK40"/>
-    <mergeCell ref="AP43:AS44"/>
-    <mergeCell ref="AP51:AS52"/>
-    <mergeCell ref="AP56:AS57"/>
-    <mergeCell ref="AU49:AX51"/>
-    <mergeCell ref="AO51:AO52"/>
-    <mergeCell ref="AT51:AT55"/>
-    <mergeCell ref="AU52:AX54"/>
-    <mergeCell ref="AO53:AO54"/>
-    <mergeCell ref="AO55:AO56"/>
-    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="AN67:AX68"/>
+    <mergeCell ref="AP56:AT57"/>
+    <mergeCell ref="AP52:AU53"/>
+    <mergeCell ref="N60:P61"/>
+    <mergeCell ref="R60:V61"/>
+    <mergeCell ref="O55:O56"/>
+    <mergeCell ref="O57:O58"/>
+    <mergeCell ref="T51:T55"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="O53:O54"/>
     <mergeCell ref="AU37:AV40"/>
     <mergeCell ref="AT38:AT39"/>
-    <mergeCell ref="AT40:AT49"/>
     <mergeCell ref="AO41:AO42"/>
     <mergeCell ref="AO43:AO44"/>
     <mergeCell ref="AU44:AX45"/>
     <mergeCell ref="AO45:AO46"/>
     <mergeCell ref="AU46:AW46"/>
     <mergeCell ref="AO47:AO48"/>
-    <mergeCell ref="AE34:AI35"/>
-    <mergeCell ref="AP48:AR49"/>
-    <mergeCell ref="AO49:AO50"/>
-    <mergeCell ref="AO57:AO58"/>
-    <mergeCell ref="N60:P61"/>
-    <mergeCell ref="R60:V61"/>
-    <mergeCell ref="R62:V62"/>
-    <mergeCell ref="U44:X45"/>
-    <mergeCell ref="U49:X51"/>
-    <mergeCell ref="U52:X54"/>
-    <mergeCell ref="U37:V40"/>
-    <mergeCell ref="U46:W46"/>
-    <mergeCell ref="O55:O56"/>
-    <mergeCell ref="O57:O58"/>
     <mergeCell ref="O45:O46"/>
-    <mergeCell ref="T40:T49"/>
-    <mergeCell ref="T51:T55"/>
-    <mergeCell ref="P48:R49"/>
     <mergeCell ref="O41:O42"/>
     <mergeCell ref="O43:O44"/>
     <mergeCell ref="O47:O48"/>
     <mergeCell ref="O49:O50"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="E34:I35"/>
-    <mergeCell ref="N33:P34"/>
-    <mergeCell ref="T38:T39"/>
-    <mergeCell ref="S34:U34"/>
+    <mergeCell ref="P48:R49"/>
+    <mergeCell ref="AC39:AC40"/>
+    <mergeCell ref="AK39:AK40"/>
+    <mergeCell ref="AO51:AO52"/>
+    <mergeCell ref="AO53:AO54"/>
+    <mergeCell ref="AO55:AO56"/>
+    <mergeCell ref="CC132:CE136"/>
+    <mergeCell ref="BL82:BL83"/>
+    <mergeCell ref="CB82:CB83"/>
+    <mergeCell ref="BI98:BW102"/>
+    <mergeCell ref="BX123:BX125"/>
+    <mergeCell ref="BL123:BL125"/>
+    <mergeCell ref="BZ86:CA87"/>
+    <mergeCell ref="CC88:CD89"/>
+    <mergeCell ref="BV123:BV125"/>
+    <mergeCell ref="BT123:BT125"/>
+    <mergeCell ref="BJ123:BJ125"/>
+    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="BN132:BR136"/>
+    <mergeCell ref="BY131:CA137"/>
+    <mergeCell ref="BP111:BV115"/>
+    <mergeCell ref="BH76:BV78"/>
+    <mergeCell ref="BH123:BH125"/>
+    <mergeCell ref="AN63:AX64"/>
+    <mergeCell ref="AN65:AX66"/>
+    <mergeCell ref="AN61:AX62"/>
+    <mergeCell ref="AO57:AO58"/>
+    <mergeCell ref="BY76:CE79"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report-vis.xlsx
+++ b/report-vis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\! CS\Y2\AI is taking over\cw\ai-garbage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9EBF03-7430-4448-B72C-40484726A902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A8B363-F5F6-4FC7-AE22-87DEC2D22CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12645" windowWidth="29040" windowHeight="15840" xr2:uid="{82DBE9BC-AC51-4988-B415-6B972F3134D5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{82DBE9BC-AC51-4988-B415-6B972F3134D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="81">
   <si>
     <t>sub-01</t>
   </si>
@@ -288,6 +288,55 @@
   <si>
     <t>TEST (TARGET) SUBJECT</t>
   </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>average acc</t>
+  </si>
+  <si>
+    <t>Average LOSO-CV Accuracy</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Value of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>f</t>
+    </r>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>average accuracy</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Value of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">α </t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -425,7 +474,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -489,6 +538,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -917,7 +984,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1064,14 +1131,143 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1114,39 +1310,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1196,110 +1359,50 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -1318,6 +1421,1845 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$CM$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>average acc</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$CL$11:$CL$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$CM$11:$CM$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>0.314</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.53400000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.754</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.81699999999999995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.84899999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.88800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.90100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.90400000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.90900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.90900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.91100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.91100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.90900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.90600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.90600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.90800000000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.90500000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.90800000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.90800000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CDD6-4A40-9E34-40EBA23A0598}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="125010064"/>
+        <c:axId val="125007184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="125010064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="125007184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="125007184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="125010064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$DA$12:$DA$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$DB$12:$DB$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>0.90300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90500000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.90600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.91200000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-45CA-4CF9-9A33-5CB838930841}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="40215184"/>
+        <c:axId val="40210384"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="40215184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="40210384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="40210384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="40215184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4328,7 +6270,107 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>94</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>102</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>3810</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="54" name="Chart 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81CFCEBF-5DE0-E308-8FCB-394A537755A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>108</xdr:col>
+      <xdr:colOff>31376</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>35858</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>115</xdr:col>
+      <xdr:colOff>336176</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>89646</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="55" name="Chart 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{612C54E1-E97A-2439-62F6-BF81AC5AF536}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E1CA15F9-110A-4944-AC64-DD6572F91D2D}" name="Table1" displayName="Table1" ref="CL10:CM33" totalsRowShown="0">
+  <autoFilter ref="CL10:CM33" xr:uid="{E1CA15F9-110A-4944-AC64-DD6572F91D2D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="CL11:CM33">
+    <sortCondition ref="CL10:CL33"/>
+  </sortState>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7D30BD47-D9DB-4789-B91B-4874D62E0F89}" name="f" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{8A9C92EC-EAE9-4222-8A39-24080A13046F}" name="average acc" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A833F649-C07A-4FB2-B16F-D970E5245707}" name="Table2" displayName="Table2" ref="DA11:DB33" totalsRowShown="0">
+  <autoFilter ref="DA11:DB33" xr:uid="{A833F649-C07A-4FB2-B16F-D970E5245707}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="DA12:DB33">
+    <sortCondition ref="DA11:DA33"/>
+  </sortState>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{04F0382F-8483-4CF8-AD96-1A2F986D9499}" name="alpha"/>
+    <tableColumn id="2" xr3:uid="{11B1233C-9A0D-4199-97DA-01172ED00F6E}" name="average accuracy"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4648,14 +6690,602 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{318B4486-90DF-4557-8364-585FD469B441}">
-  <dimension ref="B31:AVI143"/>
+  <dimension ref="B9:AVI143"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="6" width="8.88671875" customWidth="1"/>
     <col min="20" max="20" width="8.88671875" customWidth="1"/>
     <col min="50" max="50" width="9.77734375" customWidth="1"/>
+    <col min="91" max="91" width="17.6640625" customWidth="1"/>
+    <col min="105" max="105" width="10.5546875" customWidth="1"/>
+    <col min="106" max="106" width="18.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="31" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="9" spans="90:116" x14ac:dyDescent="0.3">
+      <c r="DD9" s="7"/>
+      <c r="DE9" s="7"/>
+      <c r="DF9" s="7"/>
+      <c r="DG9" s="7"/>
+      <c r="DH9" s="7"/>
+      <c r="DI9" s="7"/>
+      <c r="DJ9" s="7"/>
+      <c r="DK9" s="7"/>
+      <c r="DL9" s="7"/>
+    </row>
+    <row r="10" spans="90:116" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="CL10" s="157" t="s">
+        <v>74</v>
+      </c>
+      <c r="CM10" s="158" t="s">
+        <v>75</v>
+      </c>
+      <c r="DD10" s="162" t="s">
+        <v>76</v>
+      </c>
+      <c r="DE10" s="7"/>
+      <c r="DF10" s="7"/>
+      <c r="DG10" s="7"/>
+      <c r="DH10" s="7"/>
+      <c r="DI10" s="7"/>
+      <c r="DJ10" s="7"/>
+      <c r="DK10" s="7"/>
+      <c r="DL10" s="7"/>
+    </row>
+    <row r="11" spans="90:116" x14ac:dyDescent="0.3">
+      <c r="CL11" s="159">
+        <v>100</v>
+      </c>
+      <c r="CM11" s="164">
+        <v>0.314</v>
+      </c>
+      <c r="DA11" t="s">
+        <v>78</v>
+      </c>
+      <c r="DB11" t="s">
+        <v>79</v>
+      </c>
+      <c r="DD11" s="162"/>
+      <c r="DE11" s="7"/>
+      <c r="DF11" s="7"/>
+      <c r="DG11" s="7"/>
+      <c r="DH11" s="7"/>
+      <c r="DI11" s="7"/>
+      <c r="DJ11" s="7"/>
+      <c r="DK11" s="7"/>
+      <c r="DL11" s="7"/>
+    </row>
+    <row r="12" spans="90:116" x14ac:dyDescent="0.3">
+      <c r="CL12" s="160">
+        <v>150</v>
+      </c>
+      <c r="CM12" s="161">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="DA12">
+        <v>0</v>
+      </c>
+      <c r="DB12">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="DD12" s="162"/>
+      <c r="DE12" s="7"/>
+      <c r="DF12" s="7"/>
+      <c r="DG12" s="7"/>
+      <c r="DH12" s="7"/>
+      <c r="DI12" s="7"/>
+      <c r="DJ12" s="7"/>
+      <c r="DK12" s="7"/>
+      <c r="DL12" s="7"/>
+    </row>
+    <row r="13" spans="90:116" x14ac:dyDescent="0.3">
+      <c r="CL13" s="159">
+        <v>200</v>
+      </c>
+      <c r="CM13" s="164">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="DA13">
+        <v>0.1</v>
+      </c>
+      <c r="DB13">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="DD13" s="162"/>
+      <c r="DE13" s="7"/>
+      <c r="DF13" s="7"/>
+      <c r="DG13" s="7"/>
+      <c r="DH13" s="7"/>
+      <c r="DI13" s="7"/>
+      <c r="DJ13" s="7"/>
+      <c r="DK13" s="7"/>
+      <c r="DL13" s="7"/>
+    </row>
+    <row r="14" spans="90:116" x14ac:dyDescent="0.3">
+      <c r="CL14" s="160">
+        <v>250</v>
+      </c>
+      <c r="CM14" s="161">
+        <v>0.754</v>
+      </c>
+      <c r="DA14">
+        <v>0.25</v>
+      </c>
+      <c r="DB14">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="DD14" s="162"/>
+      <c r="DE14" s="7"/>
+      <c r="DF14" s="7"/>
+      <c r="DG14" s="7"/>
+      <c r="DH14" s="7"/>
+      <c r="DI14" s="7"/>
+      <c r="DJ14" s="7"/>
+      <c r="DK14" s="7"/>
+      <c r="DL14" s="7"/>
+    </row>
+    <row r="15" spans="90:116" x14ac:dyDescent="0.3">
+      <c r="CL15" s="159">
+        <v>300</v>
+      </c>
+      <c r="CM15" s="164">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="CO15">
+        <v>565</v>
+      </c>
+      <c r="CQ15" s="7"/>
+      <c r="CR15" s="7"/>
+      <c r="CS15" s="7"/>
+      <c r="CT15" s="7"/>
+      <c r="CU15" s="7"/>
+      <c r="CV15" s="7"/>
+      <c r="CW15" s="7"/>
+      <c r="CX15" s="7"/>
+      <c r="CY15" s="7"/>
+      <c r="DA15">
+        <v>0.5</v>
+      </c>
+      <c r="DB15">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="DD15" s="162"/>
+      <c r="DE15" s="7"/>
+      <c r="DF15" s="7"/>
+      <c r="DG15" s="7"/>
+      <c r="DH15" s="7"/>
+      <c r="DI15" s="7"/>
+      <c r="DJ15" s="7"/>
+      <c r="DK15" s="7"/>
+      <c r="DL15" s="7"/>
+    </row>
+    <row r="16" spans="90:116" x14ac:dyDescent="0.3">
+      <c r="CL16" s="160">
+        <v>350</v>
+      </c>
+      <c r="CM16" s="161">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="CQ16" s="7"/>
+      <c r="CR16" s="7"/>
+      <c r="CS16" s="7"/>
+      <c r="CT16" s="7"/>
+      <c r="CU16" s="7"/>
+      <c r="CV16" s="7"/>
+      <c r="CW16" s="7"/>
+      <c r="CX16" s="7"/>
+      <c r="CY16" s="7"/>
+      <c r="DA16">
+        <v>0.75</v>
+      </c>
+      <c r="DB16">
+        <v>0.91</v>
+      </c>
+      <c r="DD16" s="162"/>
+      <c r="DE16" s="7"/>
+      <c r="DF16" s="7"/>
+      <c r="DG16" s="7"/>
+      <c r="DH16" s="7"/>
+      <c r="DI16" s="7"/>
+      <c r="DJ16" s="7"/>
+      <c r="DK16" s="7"/>
+      <c r="DL16" s="7"/>
+    </row>
+    <row r="17" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL17" s="159">
+        <v>400</v>
+      </c>
+      <c r="CM17" s="164">
+        <v>0.87</v>
+      </c>
+      <c r="CQ17" s="162" t="s">
+        <v>76</v>
+      </c>
+      <c r="CR17" s="7"/>
+      <c r="CS17" s="7"/>
+      <c r="CT17" s="7"/>
+      <c r="CU17" s="7"/>
+      <c r="CV17" s="7"/>
+      <c r="CW17" s="7"/>
+      <c r="CX17" s="7"/>
+      <c r="CY17" s="7"/>
+      <c r="DA17">
+        <v>1</v>
+      </c>
+      <c r="DB17">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD17" s="162"/>
+      <c r="DE17" s="7"/>
+      <c r="DF17" s="7"/>
+      <c r="DG17" s="7"/>
+      <c r="DH17" s="7"/>
+      <c r="DI17" s="7"/>
+      <c r="DJ17" s="7"/>
+      <c r="DK17" s="7"/>
+      <c r="DL17" s="7"/>
+    </row>
+    <row r="18" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL18" s="160">
+        <v>450</v>
+      </c>
+      <c r="CM18" s="161">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="CQ18" s="162"/>
+      <c r="CR18" s="7"/>
+      <c r="CS18" s="7"/>
+      <c r="CT18" s="7"/>
+      <c r="CU18" s="7"/>
+      <c r="CV18" s="7"/>
+      <c r="CW18" s="7"/>
+      <c r="CX18" s="7"/>
+      <c r="CY18" s="7"/>
+      <c r="DA18">
+        <v>1.25</v>
+      </c>
+      <c r="DB18">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD18" s="162"/>
+      <c r="DE18" s="7"/>
+      <c r="DF18" s="7"/>
+      <c r="DG18" s="7"/>
+      <c r="DH18" s="7"/>
+      <c r="DI18" s="7"/>
+      <c r="DJ18" s="7"/>
+      <c r="DK18" s="7"/>
+      <c r="DL18" s="7"/>
+    </row>
+    <row r="19" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL19" s="159">
+        <v>500</v>
+      </c>
+      <c r="CM19" s="164">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="CQ19" s="162"/>
+      <c r="CR19" s="7"/>
+      <c r="CS19" s="7"/>
+      <c r="CT19" s="7"/>
+      <c r="CU19" s="7"/>
+      <c r="CV19" s="7"/>
+      <c r="CW19" s="7"/>
+      <c r="CX19" s="7"/>
+      <c r="CY19" s="7"/>
+      <c r="DA19">
+        <v>1.5</v>
+      </c>
+      <c r="DB19">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD19" s="162"/>
+      <c r="DE19" s="7"/>
+      <c r="DF19" s="7"/>
+      <c r="DG19" s="7"/>
+      <c r="DH19" s="7"/>
+      <c r="DI19" s="7"/>
+      <c r="DJ19" s="7"/>
+      <c r="DK19" s="7"/>
+      <c r="DL19" s="7"/>
+    </row>
+    <row r="20" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL20" s="160">
+        <v>525</v>
+      </c>
+      <c r="CM20" s="161">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="CQ20" s="162"/>
+      <c r="CR20" s="7"/>
+      <c r="CS20" s="7"/>
+      <c r="CT20" s="7"/>
+      <c r="CU20" s="7"/>
+      <c r="CV20" s="7"/>
+      <c r="CW20" s="7"/>
+      <c r="CX20" s="7"/>
+      <c r="CY20" s="7"/>
+      <c r="DA20">
+        <v>1.75</v>
+      </c>
+      <c r="DB20">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD20" s="162"/>
+      <c r="DE20" s="7"/>
+      <c r="DF20" s="7"/>
+      <c r="DG20" s="7"/>
+      <c r="DH20" s="7"/>
+      <c r="DI20" s="7"/>
+      <c r="DJ20" s="7"/>
+      <c r="DK20" s="7"/>
+      <c r="DL20" s="7"/>
+    </row>
+    <row r="21" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL21" s="160">
+        <v>550</v>
+      </c>
+      <c r="CM21" s="161">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="CQ21" s="162"/>
+      <c r="CR21" s="7"/>
+      <c r="CS21" s="7"/>
+      <c r="CT21" s="7"/>
+      <c r="CU21" s="7"/>
+      <c r="CV21" s="7"/>
+      <c r="CW21" s="7"/>
+      <c r="CX21" s="7"/>
+      <c r="CY21" s="7"/>
+      <c r="DA21">
+        <v>2</v>
+      </c>
+      <c r="DB21">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD21" s="162"/>
+      <c r="DE21" s="7"/>
+      <c r="DF21" s="7"/>
+      <c r="DG21" s="7"/>
+      <c r="DH21" s="7"/>
+      <c r="DI21" s="7"/>
+      <c r="DJ21" s="7"/>
+      <c r="DK21" s="7"/>
+      <c r="DL21" s="7"/>
+    </row>
+    <row r="22" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL22" s="160">
+        <v>560</v>
+      </c>
+      <c r="CM22" s="161">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="CQ22" s="162"/>
+      <c r="CR22" s="7"/>
+      <c r="CS22" s="7"/>
+      <c r="CT22" s="7"/>
+      <c r="CU22" s="7"/>
+      <c r="CV22" s="7"/>
+      <c r="CW22" s="7"/>
+      <c r="CX22" s="7"/>
+      <c r="CY22" s="7"/>
+      <c r="DA22">
+        <v>2.25</v>
+      </c>
+      <c r="DB22">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD22" s="162"/>
+      <c r="DE22" s="7"/>
+      <c r="DF22" s="7"/>
+      <c r="DG22" s="7"/>
+      <c r="DH22" s="7"/>
+      <c r="DI22" s="7"/>
+      <c r="DJ22" s="7"/>
+      <c r="DK22" s="7"/>
+      <c r="DL22" s="7"/>
+    </row>
+    <row r="23" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL23" s="159">
+        <v>565</v>
+      </c>
+      <c r="CM23" s="164">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="CQ23" s="162"/>
+      <c r="CR23" s="7"/>
+      <c r="CS23" s="7"/>
+      <c r="CT23" s="7"/>
+      <c r="CU23" s="7"/>
+      <c r="CV23" s="7"/>
+      <c r="CW23" s="7"/>
+      <c r="CX23" s="7"/>
+      <c r="CY23" s="7"/>
+      <c r="DA23">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="DB23">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD23" s="162"/>
+      <c r="DE23" s="7"/>
+      <c r="DF23" s="7"/>
+      <c r="DG23" s="7"/>
+      <c r="DH23" s="7"/>
+      <c r="DI23" s="7"/>
+      <c r="DJ23" s="7"/>
+      <c r="DK23" s="7"/>
+      <c r="DL23" s="7"/>
+    </row>
+    <row r="24" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL24" s="160">
+        <v>570</v>
+      </c>
+      <c r="CM24" s="161">
+        <v>0.91</v>
+      </c>
+      <c r="CQ24" s="162"/>
+      <c r="CR24" s="7"/>
+      <c r="CS24" s="7"/>
+      <c r="CT24" s="7"/>
+      <c r="CU24" s="7"/>
+      <c r="CV24" s="7"/>
+      <c r="CW24" s="7"/>
+      <c r="CX24" s="7"/>
+      <c r="CY24" s="7"/>
+      <c r="DA24">
+        <v>2.75</v>
+      </c>
+      <c r="DB24">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD24" s="162"/>
+      <c r="DE24" s="7"/>
+      <c r="DF24" s="7"/>
+      <c r="DG24" s="7"/>
+      <c r="DH24" s="7"/>
+      <c r="DI24" s="7"/>
+      <c r="DJ24" s="7"/>
+      <c r="DK24" s="7"/>
+      <c r="DL24" s="7"/>
+    </row>
+    <row r="25" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL25" s="159">
+        <v>575</v>
+      </c>
+      <c r="CM25" s="164">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="CQ25" s="162"/>
+      <c r="CR25" s="7"/>
+      <c r="CS25" s="7"/>
+      <c r="CT25" s="7"/>
+      <c r="CU25" s="7"/>
+      <c r="CV25" s="7"/>
+      <c r="CW25" s="7"/>
+      <c r="CX25" s="7"/>
+      <c r="CY25" s="7"/>
+      <c r="DA25">
+        <v>3</v>
+      </c>
+      <c r="DB25">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="DD25" s="7"/>
+      <c r="DE25" s="7"/>
+      <c r="DF25" s="7"/>
+      <c r="DG25" s="7"/>
+      <c r="DH25" s="7"/>
+      <c r="DI25" s="7"/>
+      <c r="DJ25" s="7"/>
+      <c r="DK25" s="7"/>
+      <c r="DL25" s="7"/>
+    </row>
+    <row r="26" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL26" s="160">
+        <v>580</v>
+      </c>
+      <c r="CM26" s="161">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="CQ26" s="162"/>
+      <c r="CR26" s="7"/>
+      <c r="CS26" s="7"/>
+      <c r="CT26" s="7"/>
+      <c r="CU26" s="7"/>
+      <c r="CV26" s="7"/>
+      <c r="CW26" s="7"/>
+      <c r="CX26" s="7"/>
+      <c r="CY26" s="7"/>
+      <c r="DD26" s="7"/>
+      <c r="DE26" s="7"/>
+      <c r="DF26" s="163" t="s">
+        <v>80</v>
+      </c>
+      <c r="DG26" s="163"/>
+      <c r="DH26" s="163"/>
+      <c r="DI26" s="163"/>
+      <c r="DJ26" s="163"/>
+      <c r="DK26" s="163"/>
+      <c r="DL26" s="7"/>
+    </row>
+    <row r="27" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL27" s="160">
+        <v>585</v>
+      </c>
+      <c r="CM27" s="161">
+        <v>0.90900000000000003</v>
+      </c>
+      <c r="CQ27" s="162"/>
+      <c r="CR27" s="7"/>
+      <c r="CS27" s="7"/>
+      <c r="CT27" s="7"/>
+      <c r="CU27" s="7"/>
+      <c r="CV27" s="7"/>
+      <c r="CW27" s="7"/>
+      <c r="CX27" s="7"/>
+      <c r="CY27" s="7"/>
+      <c r="DD27" s="7"/>
+      <c r="DE27" s="7"/>
+      <c r="DF27" s="163"/>
+      <c r="DG27" s="163"/>
+      <c r="DH27" s="163"/>
+      <c r="DI27" s="163"/>
+      <c r="DJ27" s="163"/>
+      <c r="DK27" s="163"/>
+      <c r="DL27" s="7"/>
+    </row>
+    <row r="28" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL28" s="160">
+        <v>590</v>
+      </c>
+      <c r="CM28" s="161">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="CQ28" s="162"/>
+      <c r="CR28" s="7"/>
+      <c r="CS28" s="7"/>
+      <c r="CT28" s="7"/>
+      <c r="CU28" s="7"/>
+      <c r="CV28" s="7"/>
+      <c r="CW28" s="7"/>
+      <c r="CX28" s="7"/>
+      <c r="CY28" s="7"/>
+    </row>
+    <row r="29" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL29" s="159">
+        <v>600</v>
+      </c>
+      <c r="CM29" s="164">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="CQ29" s="162"/>
+      <c r="CR29" s="7"/>
+      <c r="CS29" s="7"/>
+      <c r="CT29" s="7"/>
+      <c r="CU29" s="7"/>
+      <c r="CV29" s="7"/>
+      <c r="CW29" s="7"/>
+      <c r="CX29" s="7"/>
+      <c r="CY29" s="7"/>
+    </row>
+    <row r="30" spans="2:116" x14ac:dyDescent="0.3">
+      <c r="CL30" s="160">
+        <v>650</v>
+      </c>
+      <c r="CM30" s="161">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="CQ30" s="162"/>
+      <c r="CR30" s="7"/>
+      <c r="CS30" s="7"/>
+      <c r="CT30" s="7"/>
+      <c r="CU30" s="7"/>
+      <c r="CV30" s="7"/>
+      <c r="CW30" s="7"/>
+      <c r="CX30" s="7"/>
+      <c r="CY30" s="7"/>
+    </row>
+    <row r="31" spans="2:116" x14ac:dyDescent="0.3">
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
@@ -4667,8 +7297,23 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-    </row>
-    <row r="32" spans="2:55" x14ac:dyDescent="0.3">
+      <c r="CL31" s="159">
+        <v>700</v>
+      </c>
+      <c r="CM31" s="164">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="CQ31" s="7"/>
+      <c r="CR31" s="7"/>
+      <c r="CS31" s="7"/>
+      <c r="CT31" s="7"/>
+      <c r="CU31" s="7"/>
+      <c r="CV31" s="7"/>
+      <c r="CW31" s="7"/>
+      <c r="CX31" s="7"/>
+      <c r="CY31" s="7"/>
+    </row>
+    <row r="32" spans="2:116" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -4721,8 +7366,25 @@
       <c r="BA32" s="7"/>
       <c r="BB32" s="7"/>
       <c r="BC32" s="7"/>
-    </row>
-    <row r="33" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="CL32" s="160">
+        <v>750</v>
+      </c>
+      <c r="CM32" s="161">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="CQ32" s="7"/>
+      <c r="CR32" s="163" t="s">
+        <v>77</v>
+      </c>
+      <c r="CS32" s="163"/>
+      <c r="CT32" s="163"/>
+      <c r="CU32" s="163"/>
+      <c r="CV32" s="163"/>
+      <c r="CW32" s="163"/>
+      <c r="CX32" s="163"/>
+      <c r="CY32" s="7"/>
+    </row>
+    <row r="33" spans="2:103" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -4735,11 +7397,11 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="81" t="s">
+      <c r="N33" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="O33" s="137"/>
-      <c r="P33" s="137"/>
+      <c r="O33" s="81"/>
+      <c r="P33" s="81"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
@@ -4760,13 +7422,13 @@
       <c r="AJ33" s="7"/>
       <c r="AK33" s="7"/>
       <c r="AL33" s="7"/>
-      <c r="AM33" s="81" t="s">
+      <c r="AM33" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="AN33" s="81"/>
-      <c r="AO33" s="81"/>
-      <c r="AP33" s="81"/>
-      <c r="AQ33" s="81"/>
+      <c r="AN33" s="91"/>
+      <c r="AO33" s="91"/>
+      <c r="AP33" s="91"/>
+      <c r="AQ33" s="91"/>
       <c r="AR33" s="7"/>
       <c r="AS33" s="7"/>
       <c r="AT33" s="7"/>
@@ -4779,32 +7441,47 @@
       <c r="BA33" s="7"/>
       <c r="BB33" s="7"/>
       <c r="BC33" s="7"/>
-    </row>
-    <row r="34" spans="2:55" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="CL33" s="159">
+        <v>800</v>
+      </c>
+      <c r="CM33" s="164">
+        <v>0.90800000000000003</v>
+      </c>
+      <c r="CQ33" s="7"/>
+      <c r="CR33" s="163"/>
+      <c r="CS33" s="163"/>
+      <c r="CT33" s="163"/>
+      <c r="CU33" s="163"/>
+      <c r="CV33" s="163"/>
+      <c r="CW33" s="163"/>
+      <c r="CX33" s="163"/>
+      <c r="CY33" s="7"/>
+    </row>
+    <row r="34" spans="2:103" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="145" t="s">
+      <c r="E34" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="132"/>
-      <c r="G34" s="132"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="132"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="137"/>
-      <c r="O34" s="137"/>
-      <c r="P34" s="137"/>
+      <c r="N34" s="81"/>
+      <c r="O34" s="81"/>
+      <c r="P34" s="81"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
-      <c r="S34" s="81" t="s">
+      <c r="S34" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="82"/>
-      <c r="U34" s="82"/>
+      <c r="T34" s="94"/>
+      <c r="U34" s="94"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
@@ -4812,25 +7489,25 @@
       <c r="AB34" s="7"/>
       <c r="AC34" s="7"/>
       <c r="AD34" s="7"/>
-      <c r="AE34" s="145" t="s">
+      <c r="AE34" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="AF34" s="132"/>
-      <c r="AG34" s="132"/>
-      <c r="AH34" s="132"/>
-      <c r="AI34" s="132"/>
+      <c r="AF34" s="90"/>
+      <c r="AG34" s="90"/>
+      <c r="AH34" s="90"/>
+      <c r="AI34" s="90"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="7"/>
       <c r="AL34" s="7"/>
-      <c r="AM34" s="81"/>
-      <c r="AN34" s="81"/>
-      <c r="AO34" s="81"/>
-      <c r="AP34" s="81"/>
-      <c r="AQ34" s="81"/>
+      <c r="AM34" s="91"/>
+      <c r="AN34" s="91"/>
+      <c r="AO34" s="91"/>
+      <c r="AP34" s="91"/>
+      <c r="AQ34" s="91"/>
       <c r="AR34" s="7"/>
-      <c r="AS34" s="81"/>
-      <c r="AT34" s="82"/>
-      <c r="AU34" s="82"/>
+      <c r="AS34" s="91"/>
+      <c r="AT34" s="94"/>
+      <c r="AU34" s="94"/>
       <c r="AV34" s="7"/>
       <c r="AW34" s="7"/>
       <c r="AX34" s="7"/>
@@ -4840,15 +7517,15 @@
       <c r="BB34" s="7"/>
       <c r="BC34" s="7"/>
     </row>
-    <row r="35" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="132"/>
-      <c r="H35" s="132"/>
-      <c r="I35" s="132"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -4868,11 +7545,11 @@
       <c r="AB35" s="7"/>
       <c r="AC35" s="7"/>
       <c r="AD35" s="7"/>
-      <c r="AE35" s="132"/>
-      <c r="AF35" s="132"/>
-      <c r="AG35" s="132"/>
-      <c r="AH35" s="132"/>
-      <c r="AI35" s="132"/>
+      <c r="AE35" s="90"/>
+      <c r="AF35" s="90"/>
+      <c r="AG35" s="90"/>
+      <c r="AH35" s="90"/>
+      <c r="AI35" s="90"/>
       <c r="AJ35" s="7"/>
       <c r="AK35" s="7"/>
       <c r="AL35" s="7"/>
@@ -4894,7 +7571,7 @@
       <c r="BB35" s="7"/>
       <c r="BC35" s="7"/>
     </row>
-    <row r="36" spans="2:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:103" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -4948,7 +7625,7 @@
       <c r="BB36" s="7"/>
       <c r="BC36" s="7"/>
     </row>
-    <row r="37" spans="2:55" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:103" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
@@ -4972,10 +7649,10 @@
       <c r="T37" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="U37" s="131" t="s">
+      <c r="U37" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="V37" s="131"/>
+      <c r="V37" s="86"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -5000,8 +7677,8 @@
       <c r="AR37" s="7"/>
       <c r="AS37" s="7"/>
       <c r="AT37" s="7"/>
-      <c r="AU37" s="131"/>
-      <c r="AV37" s="131"/>
+      <c r="AU37" s="86"/>
+      <c r="AV37" s="86"/>
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
       <c r="AY37" s="7"/>
@@ -5010,7 +7687,7 @@
       <c r="BB37" s="7"/>
       <c r="BC37" s="7"/>
     </row>
-    <row r="38" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B38" s="7"/>
       <c r="C38" s="1" t="s">
         <v>0</v>
@@ -5039,11 +7716,11 @@
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="100" t="s">
+      <c r="T38" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="U38" s="131"/>
-      <c r="V38" s="131"/>
+      <c r="U38" s="86"/>
+      <c r="V38" s="86"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
@@ -5075,9 +7752,9 @@
       <c r="AQ38" s="7"/>
       <c r="AR38" s="7"/>
       <c r="AS38" s="7"/>
-      <c r="AT38" s="132"/>
-      <c r="AU38" s="131"/>
-      <c r="AV38" s="131"/>
+      <c r="AT38" s="90"/>
+      <c r="AU38" s="86"/>
+      <c r="AV38" s="86"/>
       <c r="AW38" s="7"/>
       <c r="AX38" s="7"/>
       <c r="AY38" s="7"/>
@@ -5086,7 +7763,7 @@
       <c r="BB38" s="7"/>
       <c r="BC38" s="7"/>
     </row>
-    <row r="39" spans="2:55" ht="1.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:103" ht="1.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="7"/>
       <c r="C39" s="2"/>
       <c r="D39" s="6"/>
@@ -5105,13 +7782,13 @@
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
-      <c r="T39" s="149"/>
-      <c r="U39" s="131"/>
-      <c r="V39" s="131"/>
+      <c r="T39" s="93"/>
+      <c r="U39" s="86"/>
+      <c r="V39" s="86"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="AB39" s="7"/>
-      <c r="AC39" s="124"/>
+      <c r="AC39" s="110"/>
       <c r="AD39" s="6"/>
       <c r="AE39" s="17"/>
       <c r="AF39" s="6"/>
@@ -5119,7 +7796,7 @@
       <c r="AH39" s="6"/>
       <c r="AI39" s="17"/>
       <c r="AJ39" s="6"/>
-      <c r="AK39" s="100"/>
+      <c r="AK39" s="92"/>
       <c r="AL39" s="7"/>
       <c r="AM39" s="7"/>
       <c r="AN39" s="7"/>
@@ -5128,9 +7805,9 @@
       <c r="AQ39" s="7"/>
       <c r="AR39" s="7"/>
       <c r="AS39" s="7"/>
-      <c r="AT39" s="132"/>
-      <c r="AU39" s="131"/>
-      <c r="AV39" s="131"/>
+      <c r="AT39" s="90"/>
+      <c r="AU39" s="86"/>
+      <c r="AV39" s="86"/>
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
@@ -5139,7 +7816,7 @@
       <c r="BB39" s="7"/>
       <c r="BC39" s="7"/>
     </row>
-    <row r="40" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B40" s="7"/>
       <c r="C40" s="2"/>
       <c r="D40" s="6"/>
@@ -5160,13 +7837,13 @@
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
-      <c r="T40" s="155"/>
-      <c r="U40" s="131"/>
-      <c r="V40" s="131"/>
+      <c r="T40" s="88"/>
+      <c r="U40" s="86"/>
+      <c r="V40" s="86"/>
       <c r="W40" s="7"/>
       <c r="X40" s="7"/>
       <c r="AB40" s="7"/>
-      <c r="AC40" s="124"/>
+      <c r="AC40" s="110"/>
       <c r="AD40" s="6"/>
       <c r="AE40" s="17"/>
       <c r="AF40" s="6"/>
@@ -5174,7 +7851,7 @@
       <c r="AH40" s="6"/>
       <c r="AI40" s="17"/>
       <c r="AJ40" s="6"/>
-      <c r="AK40" s="100"/>
+      <c r="AK40" s="92"/>
       <c r="AL40" s="7"/>
       <c r="AM40" s="7"/>
       <c r="AN40" s="7"/>
@@ -5186,8 +7863,8 @@
       <c r="AR40" s="7"/>
       <c r="AS40" s="7"/>
       <c r="AT40" s="7"/>
-      <c r="AU40" s="131"/>
-      <c r="AV40" s="131"/>
+      <c r="AU40" s="86"/>
+      <c r="AV40" s="86"/>
       <c r="AW40" s="7"/>
       <c r="AX40" s="7"/>
       <c r="AY40" s="7"/>
@@ -5196,7 +7873,7 @@
       <c r="BB40" s="7"/>
       <c r="BC40" s="7"/>
     </row>
-    <row r="41" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B41" s="7"/>
       <c r="C41" s="2"/>
       <c r="D41" s="6"/>
@@ -5210,14 +7887,14 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="138" t="s">
+      <c r="O41" s="109" t="s">
         <v>15</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
-      <c r="T41" s="155"/>
+      <c r="T41" s="88"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
@@ -5235,7 +7912,7 @@
       <c r="AL41" s="7"/>
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
-      <c r="AO41" s="133" t="s">
+      <c r="AO41" s="98" t="s">
         <v>15</v>
       </c>
       <c r="AP41" s="7"/>
@@ -5253,7 +7930,7 @@
       <c r="BB41" s="7"/>
       <c r="BC41" s="7"/>
     </row>
-    <row r="42" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B42" s="7"/>
       <c r="C42" s="2"/>
       <c r="D42" s="6"/>
@@ -5267,12 +7944,12 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="138"/>
+      <c r="O42" s="109"/>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
-      <c r="T42" s="155"/>
+      <c r="T42" s="88"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
@@ -5290,7 +7967,7 @@
       <c r="AL42" s="7"/>
       <c r="AM42" s="7"/>
       <c r="AN42" s="7"/>
-      <c r="AO42" s="133"/>
+      <c r="AO42" s="98"/>
       <c r="AP42" s="7"/>
       <c r="AQ42" s="7"/>
       <c r="AR42" s="7"/>
@@ -5306,7 +7983,7 @@
       <c r="BB42" s="7"/>
       <c r="BC42" s="7"/>
     </row>
-    <row r="43" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:103" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="7"/>
       <c r="C43" s="2"/>
       <c r="D43" s="6"/>
@@ -5320,14 +7997,14 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
-      <c r="O43" s="129" t="s">
+      <c r="O43" s="103" t="s">
         <v>23</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
-      <c r="T43" s="155"/>
+      <c r="T43" s="88"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
@@ -5345,7 +8022,7 @@
       <c r="AL43" s="7"/>
       <c r="AM43" s="7"/>
       <c r="AN43" s="7"/>
-      <c r="AO43" s="134" t="s">
+      <c r="AO43" s="107" t="s">
         <v>23</v>
       </c>
       <c r="AP43" s="7"/>
@@ -5363,7 +8040,7 @@
       <c r="BB43" s="7"/>
       <c r="BC43" s="7"/>
     </row>
-    <row r="44" spans="2:55" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:103" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="7"/>
       <c r="C44" s="2"/>
       <c r="D44" s="6"/>
@@ -5377,18 +8054,18 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
-      <c r="O44" s="130"/>
+      <c r="O44" s="104"/>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
-      <c r="T44" s="155"/>
-      <c r="U44" s="152" t="s">
+      <c r="T44" s="88"/>
+      <c r="U44" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="V44" s="136"/>
-      <c r="W44" s="136"/>
-      <c r="X44" s="136"/>
+      <c r="V44" s="83"/>
+      <c r="W44" s="83"/>
+      <c r="X44" s="83"/>
       <c r="AB44" s="7"/>
       <c r="AC44" s="19"/>
       <c r="AD44" s="6"/>
@@ -5402,23 +8079,23 @@
       <c r="AL44" s="7"/>
       <c r="AM44" s="7"/>
       <c r="AN44" s="7"/>
-      <c r="AO44" s="135"/>
+      <c r="AO44" s="108"/>
       <c r="AP44" s="7"/>
       <c r="AQ44" s="7"/>
       <c r="AR44" s="7"/>
       <c r="AS44" s="7"/>
       <c r="AT44" s="7"/>
-      <c r="AU44" s="136"/>
-      <c r="AV44" s="136"/>
-      <c r="AW44" s="136"/>
-      <c r="AX44" s="136"/>
+      <c r="AU44" s="83"/>
+      <c r="AV44" s="83"/>
+      <c r="AW44" s="83"/>
+      <c r="AX44" s="83"/>
       <c r="AY44" s="7"/>
       <c r="AZ44" s="7"/>
       <c r="BA44" s="7"/>
       <c r="BB44" s="7"/>
       <c r="BC44" s="7"/>
     </row>
-    <row r="45" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B45" s="7"/>
       <c r="C45" s="2"/>
       <c r="D45" s="6"/>
@@ -5432,18 +8109,18 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="129" t="s">
+      <c r="O45" s="103" t="s">
         <v>22</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
-      <c r="T45" s="155"/>
-      <c r="U45" s="152"/>
-      <c r="V45" s="136"/>
-      <c r="W45" s="136"/>
-      <c r="X45" s="136"/>
+      <c r="T45" s="88"/>
+      <c r="U45" s="82"/>
+      <c r="V45" s="83"/>
+      <c r="W45" s="83"/>
+      <c r="X45" s="83"/>
       <c r="AB45" s="7"/>
       <c r="AC45" s="19"/>
       <c r="AD45" s="6"/>
@@ -5457,27 +8134,27 @@
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
       <c r="AN45" s="7"/>
-      <c r="AO45" s="134" t="s">
+      <c r="AO45" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="AP45" s="150" t="s">
+      <c r="AP45" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="AQ45" s="151"/>
-      <c r="AR45" s="151"/>
-      <c r="AS45" s="151"/>
-      <c r="AT45" s="151"/>
-      <c r="AU45" s="136"/>
-      <c r="AV45" s="136"/>
-      <c r="AW45" s="136"/>
-      <c r="AX45" s="136"/>
+      <c r="AQ45" s="96"/>
+      <c r="AR45" s="96"/>
+      <c r="AS45" s="96"/>
+      <c r="AT45" s="96"/>
+      <c r="AU45" s="83"/>
+      <c r="AV45" s="83"/>
+      <c r="AW45" s="83"/>
+      <c r="AX45" s="83"/>
       <c r="AY45" s="7"/>
       <c r="AZ45" s="7"/>
       <c r="BA45" s="7"/>
       <c r="BB45" s="7"/>
       <c r="BC45" s="7"/>
     </row>
-    <row r="46" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B46" s="7"/>
       <c r="C46" s="3">
         <v>1654</v>
@@ -5501,17 +8178,17 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="130"/>
+      <c r="O46" s="104"/>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
-      <c r="T46" s="155"/>
-      <c r="U46" s="154" t="s">
+      <c r="T46" s="88"/>
+      <c r="U46" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="V46" s="137"/>
-      <c r="W46" s="137"/>
+      <c r="V46" s="81"/>
+      <c r="W46" s="81"/>
       <c r="X46" s="7"/>
       <c r="AB46" s="7"/>
       <c r="AC46" s="20">
@@ -5536,15 +8213,15 @@
       <c r="AL46" s="7"/>
       <c r="AM46" s="7"/>
       <c r="AN46" s="7"/>
-      <c r="AO46" s="135"/>
-      <c r="AP46" s="150"/>
-      <c r="AQ46" s="151"/>
-      <c r="AR46" s="151"/>
-      <c r="AS46" s="151"/>
-      <c r="AT46" s="151"/>
-      <c r="AU46" s="137"/>
-      <c r="AV46" s="137"/>
-      <c r="AW46" s="137"/>
+      <c r="AO46" s="108"/>
+      <c r="AP46" s="95"/>
+      <c r="AQ46" s="96"/>
+      <c r="AR46" s="96"/>
+      <c r="AS46" s="96"/>
+      <c r="AT46" s="96"/>
+      <c r="AU46" s="81"/>
+      <c r="AV46" s="81"/>
+      <c r="AW46" s="81"/>
       <c r="AX46" s="7"/>
       <c r="AY46" s="7"/>
       <c r="AZ46" s="7"/>
@@ -5552,7 +8229,7 @@
       <c r="BB46" s="7"/>
       <c r="BC46" s="7"/>
     </row>
-    <row r="47" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B47" s="7"/>
       <c r="C47" s="3" t="s">
         <v>10</v>
@@ -5576,14 +8253,14 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="138" t="s">
+      <c r="O47" s="109" t="s">
         <v>21</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7"/>
       <c r="S47" s="7"/>
-      <c r="T47" s="155"/>
+      <c r="T47" s="88"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
@@ -5611,7 +8288,7 @@
       <c r="AL47" s="7"/>
       <c r="AM47" s="7"/>
       <c r="AN47" s="7"/>
-      <c r="AO47" s="133" t="s">
+      <c r="AO47" s="98" t="s">
         <v>21</v>
       </c>
       <c r="AP47" s="7"/>
@@ -5629,7 +8306,7 @@
       <c r="BB47" s="7"/>
       <c r="BC47" s="7"/>
     </row>
-    <row r="48" spans="2:55" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:103" x14ac:dyDescent="0.3">
       <c r="B48" s="7"/>
       <c r="C48" s="3" t="s">
         <v>11</v>
@@ -5653,14 +8330,14 @@
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="138"/>
-      <c r="P48" s="143" t="s">
+      <c r="O48" s="109"/>
+      <c r="P48" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="Q48" s="144"/>
-      <c r="R48" s="144"/>
+      <c r="Q48" s="97"/>
+      <c r="R48" s="97"/>
       <c r="S48" s="7"/>
-      <c r="T48" s="155"/>
+      <c r="T48" s="88"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
@@ -5688,10 +8365,10 @@
       <c r="AL48" s="7"/>
       <c r="AM48" s="7"/>
       <c r="AN48" s="7"/>
-      <c r="AO48" s="133"/>
-      <c r="AP48" s="143"/>
-      <c r="AQ48" s="144"/>
-      <c r="AR48" s="144"/>
+      <c r="AO48" s="98"/>
+      <c r="AP48" s="85"/>
+      <c r="AQ48" s="97"/>
+      <c r="AR48" s="97"/>
       <c r="AS48" s="7"/>
       <c r="AT48" s="7"/>
       <c r="AU48" s="7"/>
@@ -5718,20 +8395,20 @@
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="138" t="s">
+      <c r="O49" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="144"/>
-      <c r="Q49" s="144"/>
-      <c r="R49" s="144"/>
+      <c r="P49" s="97"/>
+      <c r="Q49" s="97"/>
+      <c r="R49" s="97"/>
       <c r="S49" s="7"/>
-      <c r="T49" s="155"/>
-      <c r="U49" s="153" t="s">
+      <c r="T49" s="88"/>
+      <c r="U49" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="V49" s="143"/>
-      <c r="W49" s="143"/>
-      <c r="X49" s="143"/>
+      <c r="V49" s="85"/>
+      <c r="W49" s="85"/>
+      <c r="X49" s="85"/>
       <c r="AB49" s="7"/>
       <c r="AC49" s="19"/>
       <c r="AD49" s="6"/>
@@ -5745,12 +8422,12 @@
       <c r="AL49" s="7"/>
       <c r="AM49" s="7"/>
       <c r="AN49" s="7"/>
-      <c r="AO49" s="133" t="s">
+      <c r="AO49" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="AP49" s="144"/>
-      <c r="AQ49" s="144"/>
-      <c r="AR49" s="144"/>
+      <c r="AP49" s="97"/>
+      <c r="AQ49" s="97"/>
+      <c r="AR49" s="97"/>
       <c r="AS49" s="7"/>
       <c r="AT49" s="7"/>
       <c r="AU49" s="72"/>
@@ -5777,16 +8454,16 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="138"/>
+      <c r="O50" s="109"/>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
       <c r="T50" s="12"/>
-      <c r="U50" s="153"/>
-      <c r="V50" s="143"/>
-      <c r="W50" s="143"/>
-      <c r="X50" s="143"/>
+      <c r="U50" s="84"/>
+      <c r="V50" s="85"/>
+      <c r="W50" s="85"/>
+      <c r="X50" s="85"/>
       <c r="AB50" s="7"/>
       <c r="AC50" s="19"/>
       <c r="AD50" s="6"/>
@@ -5800,7 +8477,7 @@
       <c r="AL50" s="7"/>
       <c r="AM50" s="7"/>
       <c r="AN50" s="7"/>
-      <c r="AO50" s="133"/>
+      <c r="AO50" s="98"/>
       <c r="AP50" s="7"/>
       <c r="AQ50" s="7"/>
       <c r="AR50" s="7"/>
@@ -5830,18 +8507,18 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="129" t="s">
+      <c r="O51" s="103" t="s">
         <v>20</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
       <c r="S51" s="7"/>
-      <c r="T51" s="141"/>
-      <c r="U51" s="153"/>
-      <c r="V51" s="143"/>
-      <c r="W51" s="143"/>
-      <c r="X51" s="143"/>
+      <c r="T51" s="105"/>
+      <c r="U51" s="84"/>
+      <c r="V51" s="85"/>
+      <c r="W51" s="85"/>
+      <c r="X51" s="85"/>
       <c r="AB51" s="7"/>
       <c r="AC51" s="19"/>
       <c r="AD51" s="6"/>
@@ -5855,7 +8532,7 @@
       <c r="AL51" s="7"/>
       <c r="AM51" s="7"/>
       <c r="AN51" s="7"/>
-      <c r="AO51" s="125" t="s">
+      <c r="AO51" s="111" t="s">
         <v>20</v>
       </c>
       <c r="AP51" s="7"/>
@@ -5887,18 +8564,18 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="130"/>
+      <c r="O52" s="104"/>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
-      <c r="T52" s="141"/>
-      <c r="U52" s="153" t="s">
+      <c r="T52" s="105"/>
+      <c r="U52" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="V52" s="143"/>
-      <c r="W52" s="143"/>
-      <c r="X52" s="143"/>
+      <c r="V52" s="85"/>
+      <c r="W52" s="85"/>
+      <c r="X52" s="85"/>
       <c r="AB52" s="7"/>
       <c r="AC52" s="19"/>
       <c r="AD52" s="6"/>
@@ -5912,15 +8589,15 @@
       <c r="AL52" s="7"/>
       <c r="AM52" s="7"/>
       <c r="AN52" s="7"/>
-      <c r="AO52" s="126"/>
-      <c r="AP52" s="148" t="s">
+      <c r="AO52" s="112"/>
+      <c r="AP52" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="AQ52" s="131"/>
-      <c r="AR52" s="131"/>
-      <c r="AS52" s="131"/>
-      <c r="AT52" s="131"/>
-      <c r="AU52" s="131"/>
+      <c r="AQ52" s="86"/>
+      <c r="AR52" s="86"/>
+      <c r="AS52" s="86"/>
+      <c r="AT52" s="86"/>
+      <c r="AU52" s="86"/>
       <c r="AV52" s="72"/>
       <c r="AW52" s="72"/>
       <c r="AX52" s="72"/>
@@ -5944,18 +8621,18 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="129" t="s">
+      <c r="O53" s="103" t="s">
         <v>16</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
       <c r="S53" s="7"/>
-      <c r="T53" s="141"/>
-      <c r="U53" s="153"/>
-      <c r="V53" s="143"/>
-      <c r="W53" s="143"/>
-      <c r="X53" s="143"/>
+      <c r="T53" s="105"/>
+      <c r="U53" s="84"/>
+      <c r="V53" s="85"/>
+      <c r="W53" s="85"/>
+      <c r="X53" s="85"/>
       <c r="AB53" s="7"/>
       <c r="AC53" s="19"/>
       <c r="AD53" s="6"/>
@@ -5969,15 +8646,15 @@
       <c r="AL53" s="7"/>
       <c r="AM53" s="7"/>
       <c r="AN53" s="7"/>
-      <c r="AO53" s="125" t="s">
+      <c r="AO53" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="AP53" s="148"/>
-      <c r="AQ53" s="131"/>
-      <c r="AR53" s="131"/>
-      <c r="AS53" s="131"/>
-      <c r="AT53" s="131"/>
-      <c r="AU53" s="131"/>
+      <c r="AP53" s="101"/>
+      <c r="AQ53" s="86"/>
+      <c r="AR53" s="86"/>
+      <c r="AS53" s="86"/>
+      <c r="AT53" s="86"/>
+      <c r="AU53" s="86"/>
       <c r="AV53" s="72"/>
       <c r="AW53" s="72"/>
       <c r="AX53" s="72"/>
@@ -6001,16 +8678,16 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="130"/>
+      <c r="O54" s="104"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
-      <c r="T54" s="141"/>
-      <c r="U54" s="153"/>
-      <c r="V54" s="143"/>
-      <c r="W54" s="143"/>
-      <c r="X54" s="143"/>
+      <c r="T54" s="105"/>
+      <c r="U54" s="84"/>
+      <c r="V54" s="85"/>
+      <c r="W54" s="85"/>
+      <c r="X54" s="85"/>
       <c r="AB54" s="7"/>
       <c r="AC54" s="21"/>
       <c r="AD54" s="6"/>
@@ -6024,7 +8701,7 @@
       <c r="AL54" s="7"/>
       <c r="AM54" s="7"/>
       <c r="AN54" s="7"/>
-      <c r="AO54" s="126"/>
+      <c r="AO54" s="112"/>
       <c r="AP54" s="71"/>
       <c r="AQ54" s="70"/>
       <c r="AR54" s="70"/>
@@ -6054,14 +8731,14 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="129" t="s">
+      <c r="O55" s="103" t="s">
         <v>17</v>
       </c>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
       <c r="S55" s="7"/>
-      <c r="T55" s="142"/>
+      <c r="T55" s="106"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
       <c r="W55" s="7"/>
@@ -6079,7 +8756,7 @@
       <c r="AL55" s="7"/>
       <c r="AM55" s="7"/>
       <c r="AN55" s="7"/>
-      <c r="AO55" s="127" t="s">
+      <c r="AO55" s="113" t="s">
         <v>17</v>
       </c>
       <c r="AP55" s="7"/>
@@ -6111,7 +8788,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="130"/>
+      <c r="O56" s="104"/>
       <c r="P56" s="7"/>
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
@@ -6134,14 +8811,14 @@
       <c r="AL56" s="7"/>
       <c r="AM56" s="7"/>
       <c r="AN56" s="7"/>
-      <c r="AO56" s="128"/>
-      <c r="AP56" s="148" t="s">
+      <c r="AO56" s="114"/>
+      <c r="AP56" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="AQ56" s="131"/>
-      <c r="AR56" s="131"/>
-      <c r="AS56" s="131"/>
-      <c r="AT56" s="131"/>
+      <c r="AQ56" s="86"/>
+      <c r="AR56" s="86"/>
+      <c r="AS56" s="86"/>
+      <c r="AT56" s="86"/>
       <c r="AU56" s="7"/>
       <c r="AV56" s="7"/>
       <c r="AW56" s="7"/>
@@ -6176,7 +8853,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="129" t="s">
+      <c r="O57" s="103" t="s">
         <v>18</v>
       </c>
       <c r="P57" s="7"/>
@@ -6211,14 +8888,14 @@
       <c r="AL57" s="7"/>
       <c r="AM57" s="7"/>
       <c r="AN57" s="7"/>
-      <c r="AO57" s="127" t="s">
+      <c r="AO57" s="113" t="s">
         <v>18</v>
       </c>
-      <c r="AP57" s="148"/>
-      <c r="AQ57" s="131"/>
-      <c r="AR57" s="131"/>
-      <c r="AS57" s="131"/>
-      <c r="AT57" s="131"/>
+      <c r="AP57" s="101"/>
+      <c r="AQ57" s="86"/>
+      <c r="AR57" s="86"/>
+      <c r="AS57" s="86"/>
+      <c r="AT57" s="86"/>
       <c r="AU57" s="7"/>
       <c r="AV57" s="7"/>
       <c r="AW57" s="7"/>
@@ -6243,7 +8920,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="130"/>
+      <c r="O58" s="104"/>
       <c r="P58" s="7"/>
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
@@ -6266,7 +8943,7 @@
       <c r="AL58" s="7"/>
       <c r="AM58" s="7"/>
       <c r="AN58" s="7"/>
-      <c r="AO58" s="139"/>
+      <c r="AO58" s="156"/>
       <c r="AP58" s="7"/>
       <c r="AQ58" s="7"/>
       <c r="AR58" s="7"/>
@@ -6348,19 +9025,19 @@
       <c r="K60" s="3"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-      <c r="N60" s="140" t="s">
+      <c r="N60" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="O60" s="140"/>
-      <c r="P60" s="140"/>
+      <c r="O60" s="102"/>
+      <c r="P60" s="102"/>
       <c r="Q60" s="7"/>
-      <c r="R60" s="140" t="s">
+      <c r="R60" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="S60" s="140"/>
-      <c r="T60" s="140"/>
-      <c r="U60" s="140"/>
-      <c r="V60" s="140"/>
+      <c r="S60" s="102"/>
+      <c r="T60" s="102"/>
+      <c r="U60" s="102"/>
+      <c r="V60" s="102"/>
       <c r="W60" s="7"/>
       <c r="X60" s="7"/>
       <c r="AB60" s="7"/>
@@ -6405,15 +9082,15 @@
       <c r="K61" s="3"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-      <c r="N61" s="140"/>
-      <c r="O61" s="140"/>
-      <c r="P61" s="140"/>
+      <c r="N61" s="102"/>
+      <c r="O61" s="102"/>
+      <c r="P61" s="102"/>
       <c r="Q61" s="7"/>
-      <c r="R61" s="140"/>
-      <c r="S61" s="140"/>
-      <c r="T61" s="140"/>
-      <c r="U61" s="140"/>
-      <c r="V61" s="140"/>
+      <c r="R61" s="102"/>
+      <c r="S61" s="102"/>
+      <c r="T61" s="102"/>
+      <c r="U61" s="102"/>
+      <c r="V61" s="102"/>
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
       <c r="AB61" s="7"/>
@@ -6428,19 +9105,19 @@
       <c r="AK61" s="17"/>
       <c r="AL61" s="7"/>
       <c r="AM61" s="7"/>
-      <c r="AN61" s="118" t="s">
+      <c r="AN61" s="150" t="s">
         <v>37</v>
       </c>
-      <c r="AO61" s="119"/>
-      <c r="AP61" s="119"/>
-      <c r="AQ61" s="119"/>
-      <c r="AR61" s="119"/>
-      <c r="AS61" s="119"/>
-      <c r="AT61" s="119"/>
-      <c r="AU61" s="119"/>
-      <c r="AV61" s="119"/>
-      <c r="AW61" s="119"/>
-      <c r="AX61" s="120"/>
+      <c r="AO61" s="151"/>
+      <c r="AP61" s="151"/>
+      <c r="AQ61" s="151"/>
+      <c r="AR61" s="151"/>
+      <c r="AS61" s="151"/>
+      <c r="AT61" s="151"/>
+      <c r="AU61" s="151"/>
+      <c r="AV61" s="151"/>
+      <c r="AW61" s="151"/>
+      <c r="AX61" s="152"/>
       <c r="AY61" s="7"/>
       <c r="AZ61" s="7"/>
       <c r="BA61" s="7"/>
@@ -6464,13 +9141,13 @@
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
       <c r="Q62" s="7"/>
-      <c r="R62" s="137" t="s">
+      <c r="R62" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="S62" s="137"/>
-      <c r="T62" s="137"/>
-      <c r="U62" s="137"/>
-      <c r="V62" s="137"/>
+      <c r="S62" s="81"/>
+      <c r="T62" s="81"/>
+      <c r="U62" s="81"/>
+      <c r="V62" s="81"/>
       <c r="W62" s="7"/>
       <c r="X62" s="7"/>
       <c r="AB62" s="7"/>
@@ -6485,17 +9162,17 @@
       <c r="AK62" s="17"/>
       <c r="AL62" s="7"/>
       <c r="AM62" s="7"/>
-      <c r="AN62" s="121"/>
-      <c r="AO62" s="122"/>
-      <c r="AP62" s="122"/>
-      <c r="AQ62" s="122"/>
-      <c r="AR62" s="122"/>
-      <c r="AS62" s="122"/>
-      <c r="AT62" s="122"/>
-      <c r="AU62" s="122"/>
-      <c r="AV62" s="122"/>
-      <c r="AW62" s="122"/>
-      <c r="AX62" s="123"/>
+      <c r="AN62" s="153"/>
+      <c r="AO62" s="154"/>
+      <c r="AP62" s="154"/>
+      <c r="AQ62" s="154"/>
+      <c r="AR62" s="154"/>
+      <c r="AS62" s="154"/>
+      <c r="AT62" s="154"/>
+      <c r="AU62" s="154"/>
+      <c r="AV62" s="154"/>
+      <c r="AW62" s="154"/>
+      <c r="AX62" s="155"/>
       <c r="AY62" s="7"/>
       <c r="AZ62" s="7"/>
       <c r="BA62" s="7"/>
@@ -6538,19 +9215,19 @@
       <c r="AK63" s="17"/>
       <c r="AL63" s="7"/>
       <c r="AM63" s="7"/>
-      <c r="AN63" s="109" t="s">
+      <c r="AN63" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="AO63" s="110"/>
-      <c r="AP63" s="110"/>
-      <c r="AQ63" s="110"/>
-      <c r="AR63" s="110"/>
-      <c r="AS63" s="110"/>
-      <c r="AT63" s="110"/>
-      <c r="AU63" s="110"/>
-      <c r="AV63" s="110"/>
-      <c r="AW63" s="110"/>
-      <c r="AX63" s="111"/>
+      <c r="AO63" s="142"/>
+      <c r="AP63" s="142"/>
+      <c r="AQ63" s="142"/>
+      <c r="AR63" s="142"/>
+      <c r="AS63" s="142"/>
+      <c r="AT63" s="142"/>
+      <c r="AU63" s="142"/>
+      <c r="AV63" s="142"/>
+      <c r="AW63" s="142"/>
+      <c r="AX63" s="143"/>
       <c r="AY63" s="7"/>
       <c r="AZ63" s="7"/>
       <c r="BA63" s="7"/>
@@ -6613,17 +9290,17 @@
       </c>
       <c r="AL64" s="7"/>
       <c r="AM64" s="7"/>
-      <c r="AN64" s="109"/>
-      <c r="AO64" s="110"/>
-      <c r="AP64" s="110"/>
-      <c r="AQ64" s="110"/>
-      <c r="AR64" s="110"/>
-      <c r="AS64" s="110"/>
-      <c r="AT64" s="110"/>
-      <c r="AU64" s="110"/>
-      <c r="AV64" s="110"/>
-      <c r="AW64" s="110"/>
-      <c r="AX64" s="111"/>
+      <c r="AN64" s="141"/>
+      <c r="AO64" s="142"/>
+      <c r="AP64" s="142"/>
+      <c r="AQ64" s="142"/>
+      <c r="AR64" s="142"/>
+      <c r="AS64" s="142"/>
+      <c r="AT64" s="142"/>
+      <c r="AU64" s="142"/>
+      <c r="AV64" s="142"/>
+      <c r="AW64" s="142"/>
+      <c r="AX64" s="143"/>
       <c r="AY64" s="7"/>
       <c r="AZ64" s="7"/>
       <c r="BA64" s="7"/>
@@ -6686,19 +9363,19 @@
       </c>
       <c r="AL65" s="7"/>
       <c r="AM65" s="7"/>
-      <c r="AN65" s="112" t="s">
+      <c r="AN65" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="AO65" s="113"/>
-      <c r="AP65" s="113"/>
-      <c r="AQ65" s="113"/>
-      <c r="AR65" s="113"/>
-      <c r="AS65" s="113"/>
-      <c r="AT65" s="113"/>
-      <c r="AU65" s="113"/>
-      <c r="AV65" s="113"/>
-      <c r="AW65" s="113"/>
-      <c r="AX65" s="114"/>
+      <c r="AO65" s="145"/>
+      <c r="AP65" s="145"/>
+      <c r="AQ65" s="145"/>
+      <c r="AR65" s="145"/>
+      <c r="AS65" s="145"/>
+      <c r="AT65" s="145"/>
+      <c r="AU65" s="145"/>
+      <c r="AV65" s="145"/>
+      <c r="AW65" s="145"/>
+      <c r="AX65" s="146"/>
       <c r="AY65" s="7"/>
       <c r="AZ65" s="7"/>
       <c r="BA65" s="7"/>
@@ -6761,17 +9438,17 @@
       </c>
       <c r="AL66" s="7"/>
       <c r="AM66" s="7"/>
-      <c r="AN66" s="115"/>
-      <c r="AO66" s="116"/>
-      <c r="AP66" s="116"/>
-      <c r="AQ66" s="116"/>
-      <c r="AR66" s="116"/>
-      <c r="AS66" s="116"/>
-      <c r="AT66" s="116"/>
-      <c r="AU66" s="116"/>
-      <c r="AV66" s="116"/>
-      <c r="AW66" s="116"/>
-      <c r="AX66" s="117"/>
+      <c r="AN66" s="147"/>
+      <c r="AO66" s="148"/>
+      <c r="AP66" s="148"/>
+      <c r="AQ66" s="148"/>
+      <c r="AR66" s="148"/>
+      <c r="AS66" s="148"/>
+      <c r="AT66" s="148"/>
+      <c r="AU66" s="148"/>
+      <c r="AV66" s="148"/>
+      <c r="AW66" s="148"/>
+      <c r="AX66" s="149"/>
       <c r="AY66" s="7"/>
       <c r="AZ66" s="7"/>
       <c r="BA66" s="7"/>
@@ -6814,19 +9491,19 @@
       <c r="AK67" s="17"/>
       <c r="AL67" s="7"/>
       <c r="AM67" s="7"/>
-      <c r="AN67" s="146" t="s">
+      <c r="AN67" s="99" t="s">
         <v>64</v>
       </c>
-      <c r="AO67" s="147"/>
-      <c r="AP67" s="147"/>
-      <c r="AQ67" s="147"/>
-      <c r="AR67" s="147"/>
-      <c r="AS67" s="147"/>
-      <c r="AT67" s="147"/>
-      <c r="AU67" s="147"/>
-      <c r="AV67" s="147"/>
-      <c r="AW67" s="147"/>
-      <c r="AX67" s="147"/>
+      <c r="AO67" s="100"/>
+      <c r="AP67" s="100"/>
+      <c r="AQ67" s="100"/>
+      <c r="AR67" s="100"/>
+      <c r="AS67" s="100"/>
+      <c r="AT67" s="100"/>
+      <c r="AU67" s="100"/>
+      <c r="AV67" s="100"/>
+      <c r="AW67" s="100"/>
+      <c r="AX67" s="100"/>
       <c r="AY67" s="7"/>
       <c r="AZ67" s="7"/>
       <c r="BA67" s="7"/>
@@ -6869,17 +9546,17 @@
       <c r="AK68" s="17"/>
       <c r="AL68" s="7"/>
       <c r="AM68" s="7"/>
-      <c r="AN68" s="137"/>
-      <c r="AO68" s="137"/>
-      <c r="AP68" s="137"/>
-      <c r="AQ68" s="137"/>
-      <c r="AR68" s="137"/>
-      <c r="AS68" s="137"/>
-      <c r="AT68" s="137"/>
-      <c r="AU68" s="137"/>
-      <c r="AV68" s="137"/>
-      <c r="AW68" s="137"/>
-      <c r="AX68" s="137"/>
+      <c r="AN68" s="81"/>
+      <c r="AO68" s="81"/>
+      <c r="AP68" s="81"/>
+      <c r="AQ68" s="81"/>
+      <c r="AR68" s="81"/>
+      <c r="AS68" s="81"/>
+      <c r="AT68" s="81"/>
+      <c r="AU68" s="81"/>
+      <c r="AV68" s="81"/>
+      <c r="AW68" s="81"/>
+      <c r="AX68" s="81"/>
       <c r="AY68" s="7"/>
       <c r="AZ68" s="7"/>
       <c r="BA68" s="7"/>
@@ -7251,35 +9928,35 @@
       <c r="BB76" s="7"/>
       <c r="BC76" s="7"/>
       <c r="BG76" s="7"/>
-      <c r="BH76" s="108" t="s">
+      <c r="BH76" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="BI76" s="108"/>
-      <c r="BJ76" s="108"/>
-      <c r="BK76" s="108"/>
-      <c r="BL76" s="108"/>
-      <c r="BM76" s="108"/>
-      <c r="BN76" s="108"/>
-      <c r="BO76" s="108"/>
-      <c r="BP76" s="108"/>
-      <c r="BQ76" s="108"/>
-      <c r="BR76" s="108"/>
-      <c r="BS76" s="108"/>
-      <c r="BT76" s="108"/>
-      <c r="BU76" s="108"/>
-      <c r="BV76" s="108"/>
+      <c r="BI76" s="140"/>
+      <c r="BJ76" s="140"/>
+      <c r="BK76" s="140"/>
+      <c r="BL76" s="140"/>
+      <c r="BM76" s="140"/>
+      <c r="BN76" s="140"/>
+      <c r="BO76" s="140"/>
+      <c r="BP76" s="140"/>
+      <c r="BQ76" s="140"/>
+      <c r="BR76" s="140"/>
+      <c r="BS76" s="140"/>
+      <c r="BT76" s="140"/>
+      <c r="BU76" s="140"/>
+      <c r="BV76" s="140"/>
       <c r="BW76" s="10"/>
-      <c r="BX76" s="156"/>
-      <c r="BY76" s="108" t="s">
+      <c r="BX76" s="80"/>
+      <c r="BY76" s="140" t="s">
         <v>73</v>
       </c>
-      <c r="BZ76" s="108"/>
-      <c r="CA76" s="108"/>
-      <c r="CB76" s="108"/>
-      <c r="CC76" s="108"/>
-      <c r="CD76" s="108"/>
-      <c r="CE76" s="108"/>
-      <c r="CF76" s="156"/>
+      <c r="BZ76" s="140"/>
+      <c r="CA76" s="140"/>
+      <c r="CB76" s="140"/>
+      <c r="CC76" s="140"/>
+      <c r="CD76" s="140"/>
+      <c r="CE76" s="140"/>
+      <c r="CF76" s="80"/>
     </row>
     <row r="77" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB77" s="7"/>
@@ -7311,31 +9988,31 @@
       <c r="BB77" s="7"/>
       <c r="BC77" s="7"/>
       <c r="BG77" s="7"/>
-      <c r="BH77" s="108"/>
-      <c r="BI77" s="108"/>
-      <c r="BJ77" s="108"/>
-      <c r="BK77" s="108"/>
-      <c r="BL77" s="108"/>
-      <c r="BM77" s="108"/>
-      <c r="BN77" s="108"/>
-      <c r="BO77" s="108"/>
-      <c r="BP77" s="108"/>
-      <c r="BQ77" s="108"/>
-      <c r="BR77" s="108"/>
-      <c r="BS77" s="108"/>
-      <c r="BT77" s="108"/>
-      <c r="BU77" s="108"/>
-      <c r="BV77" s="108"/>
+      <c r="BH77" s="140"/>
+      <c r="BI77" s="140"/>
+      <c r="BJ77" s="140"/>
+      <c r="BK77" s="140"/>
+      <c r="BL77" s="140"/>
+      <c r="BM77" s="140"/>
+      <c r="BN77" s="140"/>
+      <c r="BO77" s="140"/>
+      <c r="BP77" s="140"/>
+      <c r="BQ77" s="140"/>
+      <c r="BR77" s="140"/>
+      <c r="BS77" s="140"/>
+      <c r="BT77" s="140"/>
+      <c r="BU77" s="140"/>
+      <c r="BV77" s="140"/>
       <c r="BW77" s="10"/>
-      <c r="BX77" s="156"/>
-      <c r="BY77" s="108"/>
-      <c r="BZ77" s="108"/>
-      <c r="CA77" s="108"/>
-      <c r="CB77" s="108"/>
-      <c r="CC77" s="108"/>
-      <c r="CD77" s="108"/>
-      <c r="CE77" s="108"/>
-      <c r="CF77" s="156"/>
+      <c r="BX77" s="80"/>
+      <c r="BY77" s="140"/>
+      <c r="BZ77" s="140"/>
+      <c r="CA77" s="140"/>
+      <c r="CB77" s="140"/>
+      <c r="CC77" s="140"/>
+      <c r="CD77" s="140"/>
+      <c r="CE77" s="140"/>
+      <c r="CF77" s="80"/>
     </row>
     <row r="78" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AB78" s="7"/>
@@ -7350,31 +10027,31 @@
       <c r="BB78" s="7"/>
       <c r="BC78" s="7"/>
       <c r="BG78" s="7"/>
-      <c r="BH78" s="108"/>
-      <c r="BI78" s="108"/>
-      <c r="BJ78" s="108"/>
-      <c r="BK78" s="108"/>
-      <c r="BL78" s="108"/>
-      <c r="BM78" s="108"/>
-      <c r="BN78" s="108"/>
-      <c r="BO78" s="108"/>
-      <c r="BP78" s="108"/>
-      <c r="BQ78" s="108"/>
-      <c r="BR78" s="108"/>
-      <c r="BS78" s="108"/>
-      <c r="BT78" s="108"/>
-      <c r="BU78" s="108"/>
-      <c r="BV78" s="108"/>
+      <c r="BH78" s="140"/>
+      <c r="BI78" s="140"/>
+      <c r="BJ78" s="140"/>
+      <c r="BK78" s="140"/>
+      <c r="BL78" s="140"/>
+      <c r="BM78" s="140"/>
+      <c r="BN78" s="140"/>
+      <c r="BO78" s="140"/>
+      <c r="BP78" s="140"/>
+      <c r="BQ78" s="140"/>
+      <c r="BR78" s="140"/>
+      <c r="BS78" s="140"/>
+      <c r="BT78" s="140"/>
+      <c r="BU78" s="140"/>
+      <c r="BV78" s="140"/>
       <c r="BW78" s="10"/>
-      <c r="BX78" s="156"/>
-      <c r="BY78" s="108"/>
-      <c r="BZ78" s="108"/>
-      <c r="CA78" s="108"/>
-      <c r="CB78" s="108"/>
-      <c r="CC78" s="108"/>
-      <c r="CD78" s="108"/>
-      <c r="CE78" s="108"/>
-      <c r="CF78" s="156"/>
+      <c r="BX78" s="80"/>
+      <c r="BY78" s="140"/>
+      <c r="BZ78" s="140"/>
+      <c r="CA78" s="140"/>
+      <c r="CB78" s="140"/>
+      <c r="CC78" s="140"/>
+      <c r="CD78" s="140"/>
+      <c r="CE78" s="140"/>
+      <c r="CF78" s="80"/>
     </row>
     <row r="79" spans="2:84" x14ac:dyDescent="0.3">
       <c r="AB79" s="7"/>
@@ -7401,13 +10078,13 @@
       <c r="BV79" s="7"/>
       <c r="BW79" s="10"/>
       <c r="BX79" s="7"/>
-      <c r="BY79" s="108"/>
-      <c r="BZ79" s="108"/>
-      <c r="CA79" s="108"/>
-      <c r="CB79" s="108"/>
-      <c r="CC79" s="108"/>
-      <c r="CD79" s="108"/>
-      <c r="CE79" s="108"/>
+      <c r="BY79" s="140"/>
+      <c r="BZ79" s="140"/>
+      <c r="CA79" s="140"/>
+      <c r="CB79" s="140"/>
+      <c r="CC79" s="140"/>
+      <c r="CD79" s="140"/>
+      <c r="CE79" s="140"/>
       <c r="CF79" s="7"/>
     </row>
     <row r="80" spans="2:84" x14ac:dyDescent="0.3">
@@ -7493,7 +10170,7 @@
       <c r="BI82" s="6"/>
       <c r="BJ82" s="17"/>
       <c r="BK82" s="6"/>
-      <c r="BL82" s="100"/>
+      <c r="BL82" s="92"/>
       <c r="BM82" s="7"/>
       <c r="BN82" s="17"/>
       <c r="BO82" s="6"/>
@@ -7509,7 +10186,7 @@
       <c r="BY82" s="7"/>
       <c r="BZ82" s="7"/>
       <c r="CA82" s="69"/>
-      <c r="CB82" s="101"/>
+      <c r="CB82" s="118"/>
       <c r="CC82" s="7"/>
       <c r="CD82" s="7"/>
       <c r="CE82" s="7"/>
@@ -7522,7 +10199,7 @@
       <c r="BI83" s="6"/>
       <c r="BJ83" s="17"/>
       <c r="BK83" s="6"/>
-      <c r="BL83" s="100"/>
+      <c r="BL83" s="92"/>
       <c r="BM83" s="7"/>
       <c r="BN83" s="17"/>
       <c r="BO83" s="6"/>
@@ -7538,7 +10215,7 @@
       <c r="BY83" s="7"/>
       <c r="BZ83" s="7"/>
       <c r="CA83" s="69"/>
-      <c r="CB83" s="101"/>
+      <c r="CB83" s="118"/>
       <c r="CC83" s="7"/>
       <c r="CD83" s="7"/>
       <c r="CE83" s="7"/>
@@ -7624,10 +10301,10 @@
       <c r="BW86" s="10"/>
       <c r="BX86" s="17"/>
       <c r="BY86" s="7"/>
-      <c r="BZ86" s="103" t="s">
+      <c r="BZ86" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="CA86" s="104"/>
+      <c r="CA86" s="122"/>
       <c r="CB86" s="32"/>
       <c r="CC86" s="7"/>
       <c r="CD86" s="7"/>
@@ -7655,8 +10332,8 @@
       <c r="BW87" s="10"/>
       <c r="BX87" s="17"/>
       <c r="BY87" s="7"/>
-      <c r="BZ87" s="103"/>
-      <c r="CA87" s="104"/>
+      <c r="BZ87" s="121"/>
+      <c r="CA87" s="122"/>
       <c r="CB87" s="32"/>
       <c r="CC87" s="7"/>
       <c r="CD87" s="7"/>
@@ -7687,10 +10364,10 @@
       <c r="BZ88" s="7"/>
       <c r="CA88" s="69"/>
       <c r="CB88" s="2"/>
-      <c r="CC88" s="105" t="s">
+      <c r="CC88" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="CD88" s="106"/>
+      <c r="CD88" s="124"/>
       <c r="CE88" s="7"/>
       <c r="CF88" s="7"/>
     </row>
@@ -7718,8 +10395,8 @@
       <c r="BZ89" s="7"/>
       <c r="CA89" s="69"/>
       <c r="CB89" s="3"/>
-      <c r="CC89" s="107"/>
-      <c r="CD89" s="106"/>
+      <c r="CC89" s="125"/>
+      <c r="CD89" s="124"/>
       <c r="CE89" s="7"/>
       <c r="CF89" s="7"/>
       <c r="CJ89" t="s">
@@ -7961,23 +10638,23 @@
     <row r="98" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG98" s="7"/>
       <c r="BH98" s="39"/>
-      <c r="BI98" s="102" t="s">
+      <c r="BI98" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="BJ98" s="102"/>
-      <c r="BK98" s="102"/>
-      <c r="BL98" s="102"/>
-      <c r="BM98" s="102"/>
-      <c r="BN98" s="102"/>
-      <c r="BO98" s="102"/>
-      <c r="BP98" s="102"/>
-      <c r="BQ98" s="102"/>
-      <c r="BR98" s="102"/>
-      <c r="BS98" s="102"/>
-      <c r="BT98" s="102"/>
-      <c r="BU98" s="102"/>
-      <c r="BV98" s="102"/>
-      <c r="BW98" s="102"/>
+      <c r="BJ98" s="119"/>
+      <c r="BK98" s="119"/>
+      <c r="BL98" s="119"/>
+      <c r="BM98" s="119"/>
+      <c r="BN98" s="119"/>
+      <c r="BO98" s="119"/>
+      <c r="BP98" s="119"/>
+      <c r="BQ98" s="119"/>
+      <c r="BR98" s="119"/>
+      <c r="BS98" s="119"/>
+      <c r="BT98" s="119"/>
+      <c r="BU98" s="119"/>
+      <c r="BV98" s="119"/>
+      <c r="BW98" s="119"/>
       <c r="BX98" s="40"/>
       <c r="BY98" s="7"/>
       <c r="BZ98" s="7"/>
@@ -7991,21 +10668,21 @@
     <row r="99" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG99" s="7"/>
       <c r="BH99" s="39"/>
-      <c r="BI99" s="102"/>
-      <c r="BJ99" s="102"/>
-      <c r="BK99" s="102"/>
-      <c r="BL99" s="102"/>
-      <c r="BM99" s="102"/>
-      <c r="BN99" s="102"/>
-      <c r="BO99" s="102"/>
-      <c r="BP99" s="102"/>
-      <c r="BQ99" s="102"/>
-      <c r="BR99" s="102"/>
-      <c r="BS99" s="102"/>
-      <c r="BT99" s="102"/>
-      <c r="BU99" s="102"/>
-      <c r="BV99" s="102"/>
-      <c r="BW99" s="102"/>
+      <c r="BI99" s="119"/>
+      <c r="BJ99" s="119"/>
+      <c r="BK99" s="119"/>
+      <c r="BL99" s="119"/>
+      <c r="BM99" s="119"/>
+      <c r="BN99" s="119"/>
+      <c r="BO99" s="119"/>
+      <c r="BP99" s="119"/>
+      <c r="BQ99" s="119"/>
+      <c r="BR99" s="119"/>
+      <c r="BS99" s="119"/>
+      <c r="BT99" s="119"/>
+      <c r="BU99" s="119"/>
+      <c r="BV99" s="119"/>
+      <c r="BW99" s="119"/>
       <c r="BX99" s="40"/>
       <c r="BY99" s="7"/>
       <c r="BZ99" s="7"/>
@@ -8019,21 +10696,21 @@
     <row r="100" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG100" s="7"/>
       <c r="BH100" s="39"/>
-      <c r="BI100" s="102"/>
-      <c r="BJ100" s="102"/>
-      <c r="BK100" s="102"/>
-      <c r="BL100" s="102"/>
-      <c r="BM100" s="102"/>
-      <c r="BN100" s="102"/>
-      <c r="BO100" s="102"/>
-      <c r="BP100" s="102"/>
-      <c r="BQ100" s="102"/>
-      <c r="BR100" s="102"/>
-      <c r="BS100" s="102"/>
-      <c r="BT100" s="102"/>
-      <c r="BU100" s="102"/>
-      <c r="BV100" s="102"/>
-      <c r="BW100" s="102"/>
+      <c r="BI100" s="119"/>
+      <c r="BJ100" s="119"/>
+      <c r="BK100" s="119"/>
+      <c r="BL100" s="119"/>
+      <c r="BM100" s="119"/>
+      <c r="BN100" s="119"/>
+      <c r="BO100" s="119"/>
+      <c r="BP100" s="119"/>
+      <c r="BQ100" s="119"/>
+      <c r="BR100" s="119"/>
+      <c r="BS100" s="119"/>
+      <c r="BT100" s="119"/>
+      <c r="BU100" s="119"/>
+      <c r="BV100" s="119"/>
+      <c r="BW100" s="119"/>
       <c r="BX100" s="40"/>
       <c r="BY100" s="7"/>
       <c r="BZ100" s="7"/>
@@ -8047,21 +10724,21 @@
     <row r="101" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG101" s="7"/>
       <c r="BH101" s="39"/>
-      <c r="BI101" s="102"/>
-      <c r="BJ101" s="102"/>
-      <c r="BK101" s="102"/>
-      <c r="BL101" s="102"/>
-      <c r="BM101" s="102"/>
-      <c r="BN101" s="102"/>
-      <c r="BO101" s="102"/>
-      <c r="BP101" s="102"/>
-      <c r="BQ101" s="102"/>
-      <c r="BR101" s="102"/>
-      <c r="BS101" s="102"/>
-      <c r="BT101" s="102"/>
-      <c r="BU101" s="102"/>
-      <c r="BV101" s="102"/>
-      <c r="BW101" s="102"/>
+      <c r="BI101" s="119"/>
+      <c r="BJ101" s="119"/>
+      <c r="BK101" s="119"/>
+      <c r="BL101" s="119"/>
+      <c r="BM101" s="119"/>
+      <c r="BN101" s="119"/>
+      <c r="BO101" s="119"/>
+      <c r="BP101" s="119"/>
+      <c r="BQ101" s="119"/>
+      <c r="BR101" s="119"/>
+      <c r="BS101" s="119"/>
+      <c r="BT101" s="119"/>
+      <c r="BU101" s="119"/>
+      <c r="BV101" s="119"/>
+      <c r="BW101" s="119"/>
       <c r="BX101" s="40"/>
       <c r="BY101" s="7"/>
       <c r="BZ101" s="7"/>
@@ -8075,21 +10752,21 @@
     <row r="102" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG102" s="7"/>
       <c r="BH102" s="39"/>
-      <c r="BI102" s="102"/>
-      <c r="BJ102" s="102"/>
-      <c r="BK102" s="102"/>
-      <c r="BL102" s="102"/>
-      <c r="BM102" s="102"/>
-      <c r="BN102" s="102"/>
-      <c r="BO102" s="102"/>
-      <c r="BP102" s="102"/>
-      <c r="BQ102" s="102"/>
-      <c r="BR102" s="102"/>
-      <c r="BS102" s="102"/>
-      <c r="BT102" s="102"/>
-      <c r="BU102" s="102"/>
-      <c r="BV102" s="102"/>
-      <c r="BW102" s="102"/>
+      <c r="BI102" s="119"/>
+      <c r="BJ102" s="119"/>
+      <c r="BK102" s="119"/>
+      <c r="BL102" s="119"/>
+      <c r="BM102" s="119"/>
+      <c r="BN102" s="119"/>
+      <c r="BO102" s="119"/>
+      <c r="BP102" s="119"/>
+      <c r="BQ102" s="119"/>
+      <c r="BR102" s="119"/>
+      <c r="BS102" s="119"/>
+      <c r="BT102" s="119"/>
+      <c r="BU102" s="119"/>
+      <c r="BV102" s="119"/>
+      <c r="BW102" s="119"/>
       <c r="BX102" s="40"/>
       <c r="BY102" s="7"/>
       <c r="BZ102" s="7"/>
@@ -8334,15 +11011,15 @@
       <c r="BM111" s="45"/>
       <c r="BN111" s="45"/>
       <c r="BO111" s="45"/>
-      <c r="BP111" s="96" t="s">
+      <c r="BP111" s="139" t="s">
         <v>41</v>
       </c>
-      <c r="BQ111" s="96"/>
-      <c r="BR111" s="96"/>
-      <c r="BS111" s="96"/>
-      <c r="BT111" s="96"/>
-      <c r="BU111" s="96"/>
-      <c r="BV111" s="96"/>
+      <c r="BQ111" s="139"/>
+      <c r="BR111" s="139"/>
+      <c r="BS111" s="139"/>
+      <c r="BT111" s="139"/>
+      <c r="BU111" s="139"/>
+      <c r="BV111" s="139"/>
       <c r="BW111" s="56"/>
       <c r="BX111" s="11"/>
       <c r="BY111" s="45"/>
@@ -8364,13 +11041,13 @@
       <c r="BM112" s="45"/>
       <c r="BN112" s="45"/>
       <c r="BO112" s="45"/>
-      <c r="BP112" s="96"/>
-      <c r="BQ112" s="96"/>
-      <c r="BR112" s="96"/>
-      <c r="BS112" s="96"/>
-      <c r="BT112" s="96"/>
-      <c r="BU112" s="96"/>
-      <c r="BV112" s="96"/>
+      <c r="BP112" s="139"/>
+      <c r="BQ112" s="139"/>
+      <c r="BR112" s="139"/>
+      <c r="BS112" s="139"/>
+      <c r="BT112" s="139"/>
+      <c r="BU112" s="139"/>
+      <c r="BV112" s="139"/>
       <c r="BW112" s="56"/>
       <c r="BX112" s="11"/>
       <c r="BY112" s="45"/>
@@ -8392,13 +11069,13 @@
       <c r="BM113" s="45"/>
       <c r="BN113" s="45"/>
       <c r="BO113" s="45"/>
-      <c r="BP113" s="96"/>
-      <c r="BQ113" s="96"/>
-      <c r="BR113" s="96"/>
-      <c r="BS113" s="96"/>
-      <c r="BT113" s="96"/>
-      <c r="BU113" s="96"/>
-      <c r="BV113" s="96"/>
+      <c r="BP113" s="139"/>
+      <c r="BQ113" s="139"/>
+      <c r="BR113" s="139"/>
+      <c r="BS113" s="139"/>
+      <c r="BT113" s="139"/>
+      <c r="BU113" s="139"/>
+      <c r="BV113" s="139"/>
       <c r="BW113" s="56"/>
       <c r="BX113" s="11"/>
       <c r="BY113" s="45"/>
@@ -8420,13 +11097,13 @@
       <c r="BM114" s="45"/>
       <c r="BN114" s="45"/>
       <c r="BO114" s="45"/>
-      <c r="BP114" s="96"/>
-      <c r="BQ114" s="96"/>
-      <c r="BR114" s="96"/>
-      <c r="BS114" s="96"/>
-      <c r="BT114" s="96"/>
-      <c r="BU114" s="96"/>
-      <c r="BV114" s="96"/>
+      <c r="BP114" s="139"/>
+      <c r="BQ114" s="139"/>
+      <c r="BR114" s="139"/>
+      <c r="BS114" s="139"/>
+      <c r="BT114" s="139"/>
+      <c r="BU114" s="139"/>
+      <c r="BV114" s="139"/>
       <c r="BW114" s="56"/>
       <c r="BX114" s="11"/>
       <c r="BY114" s="45"/>
@@ -8448,13 +11125,13 @@
       <c r="BM115" s="45"/>
       <c r="BN115" s="45"/>
       <c r="BO115" s="45"/>
-      <c r="BP115" s="96"/>
-      <c r="BQ115" s="96"/>
-      <c r="BR115" s="96"/>
-      <c r="BS115" s="96"/>
-      <c r="BT115" s="96"/>
-      <c r="BU115" s="96"/>
-      <c r="BV115" s="96"/>
+      <c r="BP115" s="139"/>
+      <c r="BQ115" s="139"/>
+      <c r="BR115" s="139"/>
+      <c r="BS115" s="139"/>
+      <c r="BT115" s="139"/>
+      <c r="BU115" s="139"/>
+      <c r="BV115" s="139"/>
       <c r="BW115" s="56"/>
       <c r="BX115" s="11"/>
       <c r="BY115" s="45"/>
@@ -8664,15 +11341,15 @@
     </row>
     <row r="123" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG123" s="7"/>
-      <c r="BH123" s="80" t="s">
+      <c r="BH123" s="120" t="s">
         <v>43</v>
       </c>
       <c r="BI123" s="6"/>
-      <c r="BJ123" s="80" t="s">
+      <c r="BJ123" s="120" t="s">
         <v>44</v>
       </c>
       <c r="BK123" s="6"/>
-      <c r="BL123" s="80" t="s">
+      <c r="BL123" s="120" t="s">
         <v>51</v>
       </c>
       <c r="BM123" s="7"/>
@@ -8682,15 +11359,15 @@
       <c r="BQ123" s="6"/>
       <c r="BR123" s="17"/>
       <c r="BS123" s="6"/>
-      <c r="BT123" s="80" t="s">
+      <c r="BT123" s="120" t="s">
         <v>45</v>
       </c>
       <c r="BU123" s="6"/>
-      <c r="BV123" s="80" t="s">
+      <c r="BV123" s="120" t="s">
         <v>46</v>
       </c>
       <c r="BW123" s="10"/>
-      <c r="BX123" s="80" t="s">
+      <c r="BX123" s="120" t="s">
         <v>50</v>
       </c>
       <c r="BY123" s="7"/>
@@ -8704,11 +11381,11 @@
     </row>
     <row r="124" spans="59:84" ht="25.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="BG124" s="7"/>
-      <c r="BH124" s="80"/>
+      <c r="BH124" s="120"/>
       <c r="BI124" s="6"/>
-      <c r="BJ124" s="80"/>
+      <c r="BJ124" s="120"/>
       <c r="BK124" s="6"/>
-      <c r="BL124" s="80"/>
+      <c r="BL124" s="120"/>
       <c r="BM124" s="34"/>
       <c r="BN124" s="17"/>
       <c r="BP124" s="79" t="s">
@@ -8717,11 +11394,11 @@
       <c r="BQ124" s="6"/>
       <c r="BR124" s="17"/>
       <c r="BS124" s="6"/>
-      <c r="BT124" s="80"/>
+      <c r="BT124" s="120"/>
       <c r="BU124" s="6"/>
-      <c r="BV124" s="80"/>
+      <c r="BV124" s="120"/>
       <c r="BW124" s="10"/>
-      <c r="BX124" s="80"/>
+      <c r="BX124" s="120"/>
       <c r="BY124" s="7"/>
       <c r="BZ124" s="7"/>
       <c r="CA124" s="69"/>
@@ -8733,11 +11410,11 @@
     </row>
     <row r="125" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG125" s="7"/>
-      <c r="BH125" s="80"/>
+      <c r="BH125" s="120"/>
       <c r="BI125" s="6"/>
-      <c r="BJ125" s="80"/>
+      <c r="BJ125" s="120"/>
       <c r="BK125" s="6"/>
-      <c r="BL125" s="80"/>
+      <c r="BL125" s="120"/>
       <c r="BM125" s="7"/>
       <c r="BN125" s="17"/>
       <c r="BO125" s="6"/>
@@ -8745,11 +11422,11 @@
       <c r="BQ125" s="6"/>
       <c r="BR125" s="17"/>
       <c r="BS125" s="6"/>
-      <c r="BT125" s="80"/>
+      <c r="BT125" s="120"/>
       <c r="BU125" s="6"/>
-      <c r="BV125" s="80"/>
+      <c r="BV125" s="120"/>
       <c r="BW125" s="10"/>
-      <c r="BX125" s="80"/>
+      <c r="BX125" s="120"/>
       <c r="BY125" s="7"/>
       <c r="BZ125" s="7"/>
       <c r="CA125" s="69"/>
@@ -8918,11 +11595,11 @@
       <c r="BV131" s="7"/>
       <c r="BW131" s="10"/>
       <c r="BX131" s="7"/>
-      <c r="BY131" s="87" t="s">
+      <c r="BY131" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="BZ131" s="88"/>
-      <c r="CA131" s="89"/>
+      <c r="BZ131" s="131"/>
+      <c r="CA131" s="132"/>
       <c r="CB131" s="69"/>
       <c r="CC131" s="60"/>
       <c r="CD131" s="61"/>
@@ -8937,28 +11614,28 @@
       <c r="BK132" s="7"/>
       <c r="BL132" s="7"/>
       <c r="BM132" s="7"/>
-      <c r="BN132" s="83" t="s">
+      <c r="BN132" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="BO132" s="84"/>
-      <c r="BP132" s="84"/>
-      <c r="BQ132" s="84"/>
-      <c r="BR132" s="85"/>
+      <c r="BO132" s="127"/>
+      <c r="BP132" s="127"/>
+      <c r="BQ132" s="127"/>
+      <c r="BR132" s="128"/>
       <c r="BS132" s="7"/>
       <c r="BT132" s="7"/>
       <c r="BU132" s="7"/>
       <c r="BV132" s="7"/>
       <c r="BW132" s="10"/>
       <c r="BX132" s="7"/>
-      <c r="BY132" s="90"/>
-      <c r="BZ132" s="91"/>
-      <c r="CA132" s="92"/>
+      <c r="BY132" s="133"/>
+      <c r="BZ132" s="134"/>
+      <c r="CA132" s="135"/>
       <c r="CB132" s="69"/>
-      <c r="CC132" s="97" t="s">
+      <c r="CC132" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="CD132" s="98"/>
-      <c r="CE132" s="99"/>
+      <c r="CD132" s="116"/>
+      <c r="CE132" s="117"/>
       <c r="CF132" s="7"/>
     </row>
     <row r="133" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8969,24 +11646,24 @@
       <c r="BK133" s="7"/>
       <c r="BL133" s="7"/>
       <c r="BM133" s="7"/>
-      <c r="BN133" s="86"/>
-      <c r="BO133" s="84"/>
-      <c r="BP133" s="84"/>
-      <c r="BQ133" s="84"/>
-      <c r="BR133" s="85"/>
+      <c r="BN133" s="129"/>
+      <c r="BO133" s="127"/>
+      <c r="BP133" s="127"/>
+      <c r="BQ133" s="127"/>
+      <c r="BR133" s="128"/>
       <c r="BS133" s="7"/>
       <c r="BT133" s="7"/>
       <c r="BU133" s="7"/>
       <c r="BV133" s="7"/>
       <c r="BW133" s="10"/>
       <c r="BX133" s="7"/>
-      <c r="BY133" s="90"/>
-      <c r="BZ133" s="91"/>
-      <c r="CA133" s="92"/>
+      <c r="BY133" s="133"/>
+      <c r="BZ133" s="134"/>
+      <c r="CA133" s="135"/>
       <c r="CB133" s="69"/>
-      <c r="CC133" s="97"/>
-      <c r="CD133" s="98"/>
-      <c r="CE133" s="99"/>
+      <c r="CC133" s="115"/>
+      <c r="CD133" s="116"/>
+      <c r="CE133" s="117"/>
       <c r="CF133" s="7"/>
     </row>
     <row r="134" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -8997,24 +11674,24 @@
       <c r="BK134" s="7"/>
       <c r="BL134" s="7"/>
       <c r="BM134" s="7"/>
-      <c r="BN134" s="86"/>
-      <c r="BO134" s="84"/>
-      <c r="BP134" s="84"/>
-      <c r="BQ134" s="84"/>
-      <c r="BR134" s="85"/>
+      <c r="BN134" s="129"/>
+      <c r="BO134" s="127"/>
+      <c r="BP134" s="127"/>
+      <c r="BQ134" s="127"/>
+      <c r="BR134" s="128"/>
       <c r="BS134" s="7"/>
       <c r="BT134" s="7"/>
       <c r="BU134" s="7"/>
       <c r="BV134" s="7"/>
       <c r="BW134" s="10"/>
       <c r="BX134" s="7"/>
-      <c r="BY134" s="90"/>
-      <c r="BZ134" s="91"/>
-      <c r="CA134" s="92"/>
+      <c r="BY134" s="133"/>
+      <c r="BZ134" s="134"/>
+      <c r="CA134" s="135"/>
       <c r="CB134" s="69"/>
-      <c r="CC134" s="97"/>
-      <c r="CD134" s="98"/>
-      <c r="CE134" s="99"/>
+      <c r="CC134" s="115"/>
+      <c r="CD134" s="116"/>
+      <c r="CE134" s="117"/>
       <c r="CF134" s="7"/>
     </row>
     <row r="135" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -9025,24 +11702,24 @@
       <c r="BK135" s="7"/>
       <c r="BL135" s="7"/>
       <c r="BM135" s="7"/>
-      <c r="BN135" s="86"/>
-      <c r="BO135" s="84"/>
-      <c r="BP135" s="84"/>
-      <c r="BQ135" s="84"/>
-      <c r="BR135" s="85"/>
+      <c r="BN135" s="129"/>
+      <c r="BO135" s="127"/>
+      <c r="BP135" s="127"/>
+      <c r="BQ135" s="127"/>
+      <c r="BR135" s="128"/>
       <c r="BS135" s="7"/>
       <c r="BT135" s="7"/>
       <c r="BU135" s="7"/>
       <c r="BV135" s="7"/>
       <c r="BW135" s="10"/>
       <c r="BX135" s="7"/>
-      <c r="BY135" s="90"/>
-      <c r="BZ135" s="91"/>
-      <c r="CA135" s="92"/>
+      <c r="BY135" s="133"/>
+      <c r="BZ135" s="134"/>
+      <c r="CA135" s="135"/>
       <c r="CB135" s="69"/>
-      <c r="CC135" s="97"/>
-      <c r="CD135" s="98"/>
-      <c r="CE135" s="99"/>
+      <c r="CC135" s="115"/>
+      <c r="CD135" s="116"/>
+      <c r="CE135" s="117"/>
       <c r="CF135" s="7"/>
     </row>
     <row r="136" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -9053,24 +11730,24 @@
       <c r="BK136" s="7"/>
       <c r="BL136" s="7"/>
       <c r="BM136" s="7"/>
-      <c r="BN136" s="86"/>
-      <c r="BO136" s="84"/>
-      <c r="BP136" s="84"/>
-      <c r="BQ136" s="84"/>
-      <c r="BR136" s="85"/>
+      <c r="BN136" s="129"/>
+      <c r="BO136" s="127"/>
+      <c r="BP136" s="127"/>
+      <c r="BQ136" s="127"/>
+      <c r="BR136" s="128"/>
       <c r="BS136" s="7"/>
       <c r="BT136" s="7"/>
       <c r="BU136" s="7"/>
       <c r="BV136" s="7"/>
       <c r="BW136" s="10"/>
       <c r="BX136" s="7"/>
-      <c r="BY136" s="90"/>
-      <c r="BZ136" s="91"/>
-      <c r="CA136" s="92"/>
+      <c r="BY136" s="133"/>
+      <c r="BZ136" s="134"/>
+      <c r="CA136" s="135"/>
       <c r="CB136" s="69"/>
-      <c r="CC136" s="97"/>
-      <c r="CD136" s="98"/>
-      <c r="CE136" s="99"/>
+      <c r="CC136" s="115"/>
+      <c r="CD136" s="116"/>
+      <c r="CE136" s="117"/>
       <c r="CF136" s="7"/>
     </row>
     <row r="137" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -9092,9 +11769,9 @@
       <c r="BV137" s="7"/>
       <c r="BW137" s="10"/>
       <c r="BX137" s="7"/>
-      <c r="BY137" s="93"/>
-      <c r="BZ137" s="94"/>
-      <c r="CA137" s="95"/>
+      <c r="BY137" s="136"/>
+      <c r="BZ137" s="137"/>
+      <c r="CA137" s="138"/>
       <c r="CB137" s="69"/>
       <c r="CC137" s="63"/>
       <c r="CD137" s="64"/>
@@ -9267,51 +11944,17 @@
       <c r="CF143" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="R62:V62"/>
-    <mergeCell ref="U44:X45"/>
-    <mergeCell ref="U49:X51"/>
-    <mergeCell ref="U52:X54"/>
-    <mergeCell ref="U37:V40"/>
-    <mergeCell ref="U46:W46"/>
-    <mergeCell ref="T40:T49"/>
-    <mergeCell ref="E34:I35"/>
-    <mergeCell ref="N33:P34"/>
-    <mergeCell ref="T38:T39"/>
-    <mergeCell ref="S34:U34"/>
-    <mergeCell ref="AP45:AT46"/>
-    <mergeCell ref="AE34:AI35"/>
-    <mergeCell ref="AP48:AR49"/>
-    <mergeCell ref="AO49:AO50"/>
-    <mergeCell ref="AM33:AQ34"/>
-    <mergeCell ref="AN67:AX68"/>
-    <mergeCell ref="AP56:AT57"/>
-    <mergeCell ref="AP52:AU53"/>
-    <mergeCell ref="N60:P61"/>
-    <mergeCell ref="R60:V61"/>
-    <mergeCell ref="O55:O56"/>
-    <mergeCell ref="O57:O58"/>
-    <mergeCell ref="T51:T55"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="AU37:AV40"/>
-    <mergeCell ref="AT38:AT39"/>
-    <mergeCell ref="AO41:AO42"/>
-    <mergeCell ref="AO43:AO44"/>
-    <mergeCell ref="AU44:AX45"/>
-    <mergeCell ref="AO45:AO46"/>
-    <mergeCell ref="AU46:AW46"/>
-    <mergeCell ref="AO47:AO48"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P48:R49"/>
-    <mergeCell ref="AC39:AC40"/>
-    <mergeCell ref="AK39:AK40"/>
-    <mergeCell ref="AO51:AO52"/>
-    <mergeCell ref="AO53:AO54"/>
+  <mergeCells count="71">
+    <mergeCell ref="CR32:CX33"/>
+    <mergeCell ref="DD10:DD24"/>
+    <mergeCell ref="DF26:DK27"/>
+    <mergeCell ref="CQ17:CQ30"/>
+    <mergeCell ref="BY76:CE79"/>
+    <mergeCell ref="BH123:BH125"/>
+    <mergeCell ref="AN63:AX64"/>
+    <mergeCell ref="AN65:AX66"/>
+    <mergeCell ref="AN61:AX62"/>
+    <mergeCell ref="AO57:AO58"/>
     <mergeCell ref="AO55:AO56"/>
     <mergeCell ref="CC132:CE136"/>
     <mergeCell ref="BL82:BL83"/>
@@ -9324,21 +11967,63 @@
     <mergeCell ref="BV123:BV125"/>
     <mergeCell ref="BT123:BT125"/>
     <mergeCell ref="BJ123:BJ125"/>
-    <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BN132:BR136"/>
     <mergeCell ref="BY131:CA137"/>
     <mergeCell ref="BP111:BV115"/>
     <mergeCell ref="BH76:BV78"/>
-    <mergeCell ref="BH123:BH125"/>
-    <mergeCell ref="AN63:AX64"/>
-    <mergeCell ref="AN65:AX66"/>
-    <mergeCell ref="AN61:AX62"/>
-    <mergeCell ref="AO57:AO58"/>
-    <mergeCell ref="BY76:CE79"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P48:R49"/>
+    <mergeCell ref="AC39:AC40"/>
+    <mergeCell ref="AK39:AK40"/>
+    <mergeCell ref="N60:P61"/>
+    <mergeCell ref="R60:V61"/>
+    <mergeCell ref="O55:O56"/>
+    <mergeCell ref="O57:O58"/>
+    <mergeCell ref="T51:T55"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="AP48:AR49"/>
+    <mergeCell ref="AO49:AO50"/>
+    <mergeCell ref="AM33:AQ34"/>
+    <mergeCell ref="AN67:AX68"/>
+    <mergeCell ref="AP56:AT57"/>
+    <mergeCell ref="AP52:AU53"/>
+    <mergeCell ref="AU37:AV40"/>
+    <mergeCell ref="AT38:AT39"/>
+    <mergeCell ref="AO41:AO42"/>
+    <mergeCell ref="AO43:AO44"/>
+    <mergeCell ref="AU44:AX45"/>
+    <mergeCell ref="AO45:AO46"/>
+    <mergeCell ref="AU46:AW46"/>
+    <mergeCell ref="AO47:AO48"/>
+    <mergeCell ref="AO51:AO52"/>
+    <mergeCell ref="AO53:AO54"/>
+    <mergeCell ref="E34:I35"/>
+    <mergeCell ref="N33:P34"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="S34:U34"/>
+    <mergeCell ref="AP45:AT46"/>
+    <mergeCell ref="AE34:AI35"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="R62:V62"/>
+    <mergeCell ref="U44:X45"/>
+    <mergeCell ref="U49:X51"/>
+    <mergeCell ref="U52:X54"/>
+    <mergeCell ref="U37:V40"/>
+    <mergeCell ref="U46:W46"/>
+    <mergeCell ref="T40:T49"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <tableParts count="2">
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/report-vis.xlsx
+++ b/report-vis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\! CS\Y2\AI is taking over\cw\ai-garbage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A8B363-F5F6-4FC7-AE22-87DEC2D22CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D96942-2F04-4413-99B8-843452D433D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{82DBE9BC-AC51-4988-B415-6B972F3134D5}"/>
+    <workbookView xWindow="28680" yWindow="-12645" windowWidth="29040" windowHeight="15840" xr2:uid="{82DBE9BC-AC51-4988-B415-6B972F3134D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1134,103 +1134,79 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1245,13 +1221,13 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1311,73 +1287,97 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6342,6 +6342,682 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>117</xdr:col>
+      <xdr:colOff>13855</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>41563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>135</xdr:col>
+      <xdr:colOff>478675</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>20781</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Picture 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32602446-A3D8-485B-FAE2-7E0F6BA02A9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="72736364" y="1482436"/>
+          <a:ext cx="11430000" cy="9525000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>135</xdr:col>
+      <xdr:colOff>415637</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>27709</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>154</xdr:col>
+      <xdr:colOff>263237</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>10737</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{951542AB-2907-E09B-8A20-AE4CC8F62BBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="84110946" y="1468582"/>
+          <a:ext cx="11430000" cy="9525000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>124</xdr:col>
+      <xdr:colOff>332509</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>3463</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>129</xdr:col>
+      <xdr:colOff>526473</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>128155</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="TextBox 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E512BE3A-8B85-88A0-8C07-6848FE46394D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="77351659" y="1527463"/>
+          <a:ext cx="3241964" cy="696192"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2800"/>
+            <a:t>PR Curve (Baseline)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>143</xdr:col>
+      <xdr:colOff>207824</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9697</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>148</xdr:col>
+      <xdr:colOff>401788</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="TextBox 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B31F4764-D6FD-4C54-AFB3-F21468921FFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="88809374" y="1533697"/>
+          <a:ext cx="3241964" cy="714203"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2800"/>
+            <a:t>PR Curve (Improved)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>116</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>140</xdr:col>
+      <xdr:colOff>383015</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>25753</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{465CD6EB-85C7-6DA3-8418-4F63A77C3359}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="72713850" y="11620500"/>
+          <a:ext cx="14441915" cy="7078063"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>116</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>140</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>99059</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2B8BF71-A327-5F2D-D449-3030574C348B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="72618600" y="18611849"/>
+          <a:ext cx="14687550" cy="7343775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>124</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>135</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="TextBox 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{673ECAEA-1AC0-8504-15C6-96F4598A9014}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="77038200" y="18630900"/>
+          <a:ext cx="6819900" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200"/>
+            <a:t>Average</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" baseline="0"/>
+            <a:t> Precision per class  (Improved)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>124</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>135</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="TextBox 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2DE14C1-70A6-4823-9197-3AC2B901E8D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="77057250" y="11544300"/>
+          <a:ext cx="6819900" cy="628650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200"/>
+            <a:t>Average</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200" baseline="0"/>
+            <a:t> Precision per class  (Baseline)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>169</xdr:col>
+      <xdr:colOff>244116</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>69273</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>195</xdr:col>
+      <xdr:colOff>176242</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>257869</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E198CA6-6ABA-5BED-BA76-452681DF549E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="104118571" y="11170228"/>
+          <a:ext cx="15691671" cy="10943186"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>144</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>66677</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>169</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>200027</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50708172-EC5E-BC1E-8FE3-21A71BA13214}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="88046379" y="12204248"/>
+          <a:ext cx="14967857" cy="11808279"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>150</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>76202</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>161</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>156212</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="TextBox 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7CB22A2-B04B-4337-97D9-80D7624AC525}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="91371964" y="12213773"/>
+          <a:ext cx="6852557" cy="651510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200"/>
+            <a:t>Confusion Matrix - 100 classes (baseline)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>173</xdr:col>
+      <xdr:colOff>571501</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>12962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>188</xdr:col>
+      <xdr:colOff>515736</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>25034</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="TextBox 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41ED4E4-EC38-4713-A8EC-6AAEF1A75ECE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106870501" y="11287098"/>
+          <a:ext cx="9036280" cy="548936"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="3200"/>
+            <a:t>Confusion Matrix - 100 classes (improved)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6713,13 +7389,13 @@
       <c r="DL9" s="7"/>
     </row>
     <row r="10" spans="90:116" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="CL10" s="157" t="s">
+      <c r="CL10" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="CM10" s="158" t="s">
+      <c r="CM10" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="DD10" s="162" t="s">
+      <c r="DD10" s="88" t="s">
         <v>76</v>
       </c>
       <c r="DE10" s="7"/>
@@ -6732,10 +7408,10 @@
       <c r="DL10" s="7"/>
     </row>
     <row r="11" spans="90:116" x14ac:dyDescent="0.3">
-      <c r="CL11" s="159">
+      <c r="CL11" s="83">
         <v>100</v>
       </c>
-      <c r="CM11" s="164">
+      <c r="CM11" s="86">
         <v>0.314</v>
       </c>
       <c r="DA11" t="s">
@@ -6744,7 +7420,7 @@
       <c r="DB11" t="s">
         <v>79</v>
       </c>
-      <c r="DD11" s="162"/>
+      <c r="DD11" s="88"/>
       <c r="DE11" s="7"/>
       <c r="DF11" s="7"/>
       <c r="DG11" s="7"/>
@@ -6755,10 +7431,10 @@
       <c r="DL11" s="7"/>
     </row>
     <row r="12" spans="90:116" x14ac:dyDescent="0.3">
-      <c r="CL12" s="160">
+      <c r="CL12" s="84">
         <v>150</v>
       </c>
-      <c r="CM12" s="161">
+      <c r="CM12" s="85">
         <v>0.53400000000000003</v>
       </c>
       <c r="DA12">
@@ -6767,7 +7443,7 @@
       <c r="DB12">
         <v>0.90300000000000002</v>
       </c>
-      <c r="DD12" s="162"/>
+      <c r="DD12" s="88"/>
       <c r="DE12" s="7"/>
       <c r="DF12" s="7"/>
       <c r="DG12" s="7"/>
@@ -6778,10 +7454,10 @@
       <c r="DL12" s="7"/>
     </row>
     <row r="13" spans="90:116" x14ac:dyDescent="0.3">
-      <c r="CL13" s="159">
+      <c r="CL13" s="83">
         <v>200</v>
       </c>
-      <c r="CM13" s="164">
+      <c r="CM13" s="86">
         <v>0.65700000000000003</v>
       </c>
       <c r="DA13">
@@ -6790,7 +7466,7 @@
       <c r="DB13">
         <v>0.90500000000000003</v>
       </c>
-      <c r="DD13" s="162"/>
+      <c r="DD13" s="88"/>
       <c r="DE13" s="7"/>
       <c r="DF13" s="7"/>
       <c r="DG13" s="7"/>
@@ -6801,10 +7477,10 @@
       <c r="DL13" s="7"/>
     </row>
     <row r="14" spans="90:116" x14ac:dyDescent="0.3">
-      <c r="CL14" s="160">
+      <c r="CL14" s="84">
         <v>250</v>
       </c>
-      <c r="CM14" s="161">
+      <c r="CM14" s="85">
         <v>0.754</v>
       </c>
       <c r="DA14">
@@ -6813,7 +7489,7 @@
       <c r="DB14">
         <v>0.90600000000000003</v>
       </c>
-      <c r="DD14" s="162"/>
+      <c r="DD14" s="88"/>
       <c r="DE14" s="7"/>
       <c r="DF14" s="7"/>
       <c r="DG14" s="7"/>
@@ -6824,10 +7500,10 @@
       <c r="DL14" s="7"/>
     </row>
     <row r="15" spans="90:116" x14ac:dyDescent="0.3">
-      <c r="CL15" s="159">
+      <c r="CL15" s="83">
         <v>300</v>
       </c>
-      <c r="CM15" s="164">
+      <c r="CM15" s="86">
         <v>0.81699999999999995</v>
       </c>
       <c r="CO15">
@@ -6848,7 +7524,7 @@
       <c r="DB15">
         <v>0.90900000000000003</v>
       </c>
-      <c r="DD15" s="162"/>
+      <c r="DD15" s="88"/>
       <c r="DE15" s="7"/>
       <c r="DF15" s="7"/>
       <c r="DG15" s="7"/>
@@ -6859,10 +7535,10 @@
       <c r="DL15" s="7"/>
     </row>
     <row r="16" spans="90:116" x14ac:dyDescent="0.3">
-      <c r="CL16" s="160">
+      <c r="CL16" s="84">
         <v>350</v>
       </c>
-      <c r="CM16" s="161">
+      <c r="CM16" s="85">
         <v>0.84899999999999998</v>
       </c>
       <c r="CQ16" s="7"/>
@@ -6880,7 +7556,7 @@
       <c r="DB16">
         <v>0.91</v>
       </c>
-      <c r="DD16" s="162"/>
+      <c r="DD16" s="88"/>
       <c r="DE16" s="7"/>
       <c r="DF16" s="7"/>
       <c r="DG16" s="7"/>
@@ -6891,13 +7567,13 @@
       <c r="DL16" s="7"/>
     </row>
     <row r="17" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL17" s="159">
+      <c r="CL17" s="83">
         <v>400</v>
       </c>
-      <c r="CM17" s="164">
+      <c r="CM17" s="86">
         <v>0.87</v>
       </c>
-      <c r="CQ17" s="162" t="s">
+      <c r="CQ17" s="88" t="s">
         <v>76</v>
       </c>
       <c r="CR17" s="7"/>
@@ -6914,7 +7590,7 @@
       <c r="DB17">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD17" s="162"/>
+      <c r="DD17" s="88"/>
       <c r="DE17" s="7"/>
       <c r="DF17" s="7"/>
       <c r="DG17" s="7"/>
@@ -6925,13 +7601,13 @@
       <c r="DL17" s="7"/>
     </row>
     <row r="18" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL18" s="160">
+      <c r="CL18" s="84">
         <v>450</v>
       </c>
-      <c r="CM18" s="161">
+      <c r="CM18" s="85">
         <v>0.88800000000000001</v>
       </c>
-      <c r="CQ18" s="162"/>
+      <c r="CQ18" s="88"/>
       <c r="CR18" s="7"/>
       <c r="CS18" s="7"/>
       <c r="CT18" s="7"/>
@@ -6946,7 +7622,7 @@
       <c r="DB18">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD18" s="162"/>
+      <c r="DD18" s="88"/>
       <c r="DE18" s="7"/>
       <c r="DF18" s="7"/>
       <c r="DG18" s="7"/>
@@ -6957,13 +7633,13 @@
       <c r="DL18" s="7"/>
     </row>
     <row r="19" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL19" s="159">
+      <c r="CL19" s="83">
         <v>500</v>
       </c>
-      <c r="CM19" s="164">
+      <c r="CM19" s="86">
         <v>0.90100000000000002</v>
       </c>
-      <c r="CQ19" s="162"/>
+      <c r="CQ19" s="88"/>
       <c r="CR19" s="7"/>
       <c r="CS19" s="7"/>
       <c r="CT19" s="7"/>
@@ -6978,7 +7654,7 @@
       <c r="DB19">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD19" s="162"/>
+      <c r="DD19" s="88"/>
       <c r="DE19" s="7"/>
       <c r="DF19" s="7"/>
       <c r="DG19" s="7"/>
@@ -6989,13 +7665,13 @@
       <c r="DL19" s="7"/>
     </row>
     <row r="20" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL20" s="160">
+      <c r="CL20" s="84">
         <v>525</v>
       </c>
-      <c r="CM20" s="161">
+      <c r="CM20" s="85">
         <v>0.90400000000000003</v>
       </c>
-      <c r="CQ20" s="162"/>
+      <c r="CQ20" s="88"/>
       <c r="CR20" s="7"/>
       <c r="CS20" s="7"/>
       <c r="CT20" s="7"/>
@@ -7010,7 +7686,7 @@
       <c r="DB20">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD20" s="162"/>
+      <c r="DD20" s="88"/>
       <c r="DE20" s="7"/>
       <c r="DF20" s="7"/>
       <c r="DG20" s="7"/>
@@ -7021,13 +7697,13 @@
       <c r="DL20" s="7"/>
     </row>
     <row r="21" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL21" s="160">
+      <c r="CL21" s="84">
         <v>550</v>
       </c>
-      <c r="CM21" s="161">
+      <c r="CM21" s="85">
         <v>0.90900000000000003</v>
       </c>
-      <c r="CQ21" s="162"/>
+      <c r="CQ21" s="88"/>
       <c r="CR21" s="7"/>
       <c r="CS21" s="7"/>
       <c r="CT21" s="7"/>
@@ -7042,7 +7718,7 @@
       <c r="DB21">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD21" s="162"/>
+      <c r="DD21" s="88"/>
       <c r="DE21" s="7"/>
       <c r="DF21" s="7"/>
       <c r="DG21" s="7"/>
@@ -7053,13 +7729,13 @@
       <c r="DL21" s="7"/>
     </row>
     <row r="22" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL22" s="160">
+      <c r="CL22" s="84">
         <v>560</v>
       </c>
-      <c r="CM22" s="161">
+      <c r="CM22" s="85">
         <v>0.90900000000000003</v>
       </c>
-      <c r="CQ22" s="162"/>
+      <c r="CQ22" s="88"/>
       <c r="CR22" s="7"/>
       <c r="CS22" s="7"/>
       <c r="CT22" s="7"/>
@@ -7074,7 +7750,7 @@
       <c r="DB22">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD22" s="162"/>
+      <c r="DD22" s="88"/>
       <c r="DE22" s="7"/>
       <c r="DF22" s="7"/>
       <c r="DG22" s="7"/>
@@ -7085,13 +7761,13 @@
       <c r="DL22" s="7"/>
     </row>
     <row r="23" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL23" s="159">
+      <c r="CL23" s="83">
         <v>565</v>
       </c>
-      <c r="CM23" s="164">
+      <c r="CM23" s="86">
         <v>0.91200000000000003</v>
       </c>
-      <c r="CQ23" s="162"/>
+      <c r="CQ23" s="88"/>
       <c r="CR23" s="7"/>
       <c r="CS23" s="7"/>
       <c r="CT23" s="7"/>
@@ -7106,7 +7782,7 @@
       <c r="DB23">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD23" s="162"/>
+      <c r="DD23" s="88"/>
       <c r="DE23" s="7"/>
       <c r="DF23" s="7"/>
       <c r="DG23" s="7"/>
@@ -7117,13 +7793,13 @@
       <c r="DL23" s="7"/>
     </row>
     <row r="24" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL24" s="160">
+      <c r="CL24" s="84">
         <v>570</v>
       </c>
-      <c r="CM24" s="161">
+      <c r="CM24" s="85">
         <v>0.91</v>
       </c>
-      <c r="CQ24" s="162"/>
+      <c r="CQ24" s="88"/>
       <c r="CR24" s="7"/>
       <c r="CS24" s="7"/>
       <c r="CT24" s="7"/>
@@ -7138,7 +7814,7 @@
       <c r="DB24">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD24" s="162"/>
+      <c r="DD24" s="88"/>
       <c r="DE24" s="7"/>
       <c r="DF24" s="7"/>
       <c r="DG24" s="7"/>
@@ -7149,13 +7825,13 @@
       <c r="DL24" s="7"/>
     </row>
     <row r="25" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL25" s="159">
+      <c r="CL25" s="83">
         <v>575</v>
       </c>
-      <c r="CM25" s="164">
+      <c r="CM25" s="86">
         <v>0.91100000000000003</v>
       </c>
-      <c r="CQ25" s="162"/>
+      <c r="CQ25" s="88"/>
       <c r="CR25" s="7"/>
       <c r="CS25" s="7"/>
       <c r="CT25" s="7"/>
@@ -7181,13 +7857,13 @@
       <c r="DL25" s="7"/>
     </row>
     <row r="26" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL26" s="160">
+      <c r="CL26" s="84">
         <v>580</v>
       </c>
-      <c r="CM26" s="161">
+      <c r="CM26" s="85">
         <v>0.91100000000000003</v>
       </c>
-      <c r="CQ26" s="162"/>
+      <c r="CQ26" s="88"/>
       <c r="CR26" s="7"/>
       <c r="CS26" s="7"/>
       <c r="CT26" s="7"/>
@@ -7198,24 +7874,24 @@
       <c r="CY26" s="7"/>
       <c r="DD26" s="7"/>
       <c r="DE26" s="7"/>
-      <c r="DF26" s="163" t="s">
+      <c r="DF26" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="DG26" s="163"/>
-      <c r="DH26" s="163"/>
-      <c r="DI26" s="163"/>
-      <c r="DJ26" s="163"/>
-      <c r="DK26" s="163"/>
+      <c r="DG26" s="87"/>
+      <c r="DH26" s="87"/>
+      <c r="DI26" s="87"/>
+      <c r="DJ26" s="87"/>
+      <c r="DK26" s="87"/>
       <c r="DL26" s="7"/>
     </row>
     <row r="27" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL27" s="160">
+      <c r="CL27" s="84">
         <v>585</v>
       </c>
-      <c r="CM27" s="161">
+      <c r="CM27" s="85">
         <v>0.90900000000000003</v>
       </c>
-      <c r="CQ27" s="162"/>
+      <c r="CQ27" s="88"/>
       <c r="CR27" s="7"/>
       <c r="CS27" s="7"/>
       <c r="CT27" s="7"/>
@@ -7226,22 +7902,22 @@
       <c r="CY27" s="7"/>
       <c r="DD27" s="7"/>
       <c r="DE27" s="7"/>
-      <c r="DF27" s="163"/>
-      <c r="DG27" s="163"/>
-      <c r="DH27" s="163"/>
-      <c r="DI27" s="163"/>
-      <c r="DJ27" s="163"/>
-      <c r="DK27" s="163"/>
+      <c r="DF27" s="87"/>
+      <c r="DG27" s="87"/>
+      <c r="DH27" s="87"/>
+      <c r="DI27" s="87"/>
+      <c r="DJ27" s="87"/>
+      <c r="DK27" s="87"/>
       <c r="DL27" s="7"/>
     </row>
     <row r="28" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL28" s="160">
+      <c r="CL28" s="84">
         <v>590</v>
       </c>
-      <c r="CM28" s="161">
+      <c r="CM28" s="85">
         <v>0.90600000000000003</v>
       </c>
-      <c r="CQ28" s="162"/>
+      <c r="CQ28" s="88"/>
       <c r="CR28" s="7"/>
       <c r="CS28" s="7"/>
       <c r="CT28" s="7"/>
@@ -7252,13 +7928,13 @@
       <c r="CY28" s="7"/>
     </row>
     <row r="29" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL29" s="159">
+      <c r="CL29" s="83">
         <v>600</v>
       </c>
-      <c r="CM29" s="164">
+      <c r="CM29" s="86">
         <v>0.90600000000000003</v>
       </c>
-      <c r="CQ29" s="162"/>
+      <c r="CQ29" s="88"/>
       <c r="CR29" s="7"/>
       <c r="CS29" s="7"/>
       <c r="CT29" s="7"/>
@@ -7269,13 +7945,13 @@
       <c r="CY29" s="7"/>
     </row>
     <row r="30" spans="2:116" x14ac:dyDescent="0.3">
-      <c r="CL30" s="160">
+      <c r="CL30" s="84">
         <v>650</v>
       </c>
-      <c r="CM30" s="161">
+      <c r="CM30" s="85">
         <v>0.90800000000000003</v>
       </c>
-      <c r="CQ30" s="162"/>
+      <c r="CQ30" s="88"/>
       <c r="CR30" s="7"/>
       <c r="CS30" s="7"/>
       <c r="CT30" s="7"/>
@@ -7297,10 +7973,10 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="CL31" s="159">
+      <c r="CL31" s="83">
         <v>700</v>
       </c>
-      <c r="CM31" s="164">
+      <c r="CM31" s="86">
         <v>0.90500000000000003</v>
       </c>
       <c r="CQ31" s="7"/>
@@ -7366,22 +8042,22 @@
       <c r="BA32" s="7"/>
       <c r="BB32" s="7"/>
       <c r="BC32" s="7"/>
-      <c r="CL32" s="160">
+      <c r="CL32" s="84">
         <v>750</v>
       </c>
-      <c r="CM32" s="161">
+      <c r="CM32" s="85">
         <v>0.90800000000000003</v>
       </c>
       <c r="CQ32" s="7"/>
-      <c r="CR32" s="163" t="s">
+      <c r="CR32" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="CS32" s="163"/>
-      <c r="CT32" s="163"/>
-      <c r="CU32" s="163"/>
-      <c r="CV32" s="163"/>
-      <c r="CW32" s="163"/>
-      <c r="CX32" s="163"/>
+      <c r="CS32" s="87"/>
+      <c r="CT32" s="87"/>
+      <c r="CU32" s="87"/>
+      <c r="CV32" s="87"/>
+      <c r="CW32" s="87"/>
+      <c r="CX32" s="87"/>
       <c r="CY32" s="7"/>
     </row>
     <row r="33" spans="2:103" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -7397,11 +8073,11 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="91" t="s">
+      <c r="N33" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="O33" s="81"/>
-      <c r="P33" s="81"/>
+      <c r="O33" s="147"/>
+      <c r="P33" s="147"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
@@ -7422,13 +8098,13 @@
       <c r="AJ33" s="7"/>
       <c r="AK33" s="7"/>
       <c r="AL33" s="7"/>
-      <c r="AM33" s="91" t="s">
+      <c r="AM33" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="AN33" s="91"/>
-      <c r="AO33" s="91"/>
-      <c r="AP33" s="91"/>
-      <c r="AQ33" s="91"/>
+      <c r="AN33" s="144"/>
+      <c r="AO33" s="144"/>
+      <c r="AP33" s="144"/>
+      <c r="AQ33" s="144"/>
       <c r="AR33" s="7"/>
       <c r="AS33" s="7"/>
       <c r="AT33" s="7"/>
@@ -7441,47 +8117,47 @@
       <c r="BA33" s="7"/>
       <c r="BB33" s="7"/>
       <c r="BC33" s="7"/>
-      <c r="CL33" s="159">
+      <c r="CL33" s="83">
         <v>800</v>
       </c>
-      <c r="CM33" s="164">
+      <c r="CM33" s="86">
         <v>0.90800000000000003</v>
       </c>
       <c r="CQ33" s="7"/>
-      <c r="CR33" s="163"/>
-      <c r="CS33" s="163"/>
-      <c r="CT33" s="163"/>
-      <c r="CU33" s="163"/>
-      <c r="CV33" s="163"/>
-      <c r="CW33" s="163"/>
-      <c r="CX33" s="163"/>
+      <c r="CR33" s="87"/>
+      <c r="CS33" s="87"/>
+      <c r="CT33" s="87"/>
+      <c r="CU33" s="87"/>
+      <c r="CV33" s="87"/>
+      <c r="CW33" s="87"/>
+      <c r="CX33" s="87"/>
       <c r="CY33" s="7"/>
     </row>
     <row r="34" spans="2:103" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="89" t="s">
+      <c r="E34" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="90"/>
-      <c r="I34" s="90"/>
+      <c r="F34" s="150"/>
+      <c r="G34" s="150"/>
+      <c r="H34" s="150"/>
+      <c r="I34" s="150"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="81"/>
-      <c r="O34" s="81"/>
-      <c r="P34" s="81"/>
+      <c r="N34" s="147"/>
+      <c r="O34" s="147"/>
+      <c r="P34" s="147"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
-      <c r="S34" s="91" t="s">
+      <c r="S34" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="94"/>
-      <c r="U34" s="94"/>
+      <c r="T34" s="158"/>
+      <c r="U34" s="158"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
@@ -7489,25 +8165,25 @@
       <c r="AB34" s="7"/>
       <c r="AC34" s="7"/>
       <c r="AD34" s="7"/>
-      <c r="AE34" s="89" t="s">
+      <c r="AE34" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="AF34" s="90"/>
-      <c r="AG34" s="90"/>
-      <c r="AH34" s="90"/>
-      <c r="AI34" s="90"/>
+      <c r="AF34" s="150"/>
+      <c r="AG34" s="150"/>
+      <c r="AH34" s="150"/>
+      <c r="AI34" s="150"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="7"/>
       <c r="AL34" s="7"/>
-      <c r="AM34" s="91"/>
-      <c r="AN34" s="91"/>
-      <c r="AO34" s="91"/>
-      <c r="AP34" s="91"/>
-      <c r="AQ34" s="91"/>
+      <c r="AM34" s="144"/>
+      <c r="AN34" s="144"/>
+      <c r="AO34" s="144"/>
+      <c r="AP34" s="144"/>
+      <c r="AQ34" s="144"/>
       <c r="AR34" s="7"/>
-      <c r="AS34" s="91"/>
-      <c r="AT34" s="94"/>
-      <c r="AU34" s="94"/>
+      <c r="AS34" s="144"/>
+      <c r="AT34" s="158"/>
+      <c r="AU34" s="158"/>
       <c r="AV34" s="7"/>
       <c r="AW34" s="7"/>
       <c r="AX34" s="7"/>
@@ -7521,11 +8197,11 @@
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="90"/>
-      <c r="I35" s="90"/>
+      <c r="E35" s="150"/>
+      <c r="F35" s="150"/>
+      <c r="G35" s="150"/>
+      <c r="H35" s="150"/>
+      <c r="I35" s="150"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -7545,11 +8221,11 @@
       <c r="AB35" s="7"/>
       <c r="AC35" s="7"/>
       <c r="AD35" s="7"/>
-      <c r="AE35" s="90"/>
-      <c r="AF35" s="90"/>
-      <c r="AG35" s="90"/>
-      <c r="AH35" s="90"/>
-      <c r="AI35" s="90"/>
+      <c r="AE35" s="150"/>
+      <c r="AF35" s="150"/>
+      <c r="AG35" s="150"/>
+      <c r="AH35" s="150"/>
+      <c r="AI35" s="150"/>
       <c r="AJ35" s="7"/>
       <c r="AK35" s="7"/>
       <c r="AL35" s="7"/>
@@ -7649,10 +8325,10 @@
       <c r="T37" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="U37" s="86" t="s">
+      <c r="U37" s="149" t="s">
         <v>31</v>
       </c>
-      <c r="V37" s="86"/>
+      <c r="V37" s="149"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -7677,8 +8353,8 @@
       <c r="AR37" s="7"/>
       <c r="AS37" s="7"/>
       <c r="AT37" s="7"/>
-      <c r="AU37" s="86"/>
-      <c r="AV37" s="86"/>
+      <c r="AU37" s="149"/>
+      <c r="AV37" s="149"/>
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
       <c r="AY37" s="7"/>
@@ -7716,11 +8392,11 @@
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="92" t="s">
+      <c r="T38" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="U38" s="86"/>
-      <c r="V38" s="86"/>
+      <c r="U38" s="149"/>
+      <c r="V38" s="149"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
@@ -7752,9 +8428,9 @@
       <c r="AQ38" s="7"/>
       <c r="AR38" s="7"/>
       <c r="AS38" s="7"/>
-      <c r="AT38" s="90"/>
-      <c r="AU38" s="86"/>
-      <c r="AV38" s="86"/>
+      <c r="AT38" s="150"/>
+      <c r="AU38" s="149"/>
+      <c r="AV38" s="149"/>
       <c r="AW38" s="7"/>
       <c r="AX38" s="7"/>
       <c r="AY38" s="7"/>
@@ -7782,13 +8458,13 @@
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
-      <c r="T39" s="93"/>
-      <c r="U39" s="86"/>
-      <c r="V39" s="86"/>
+      <c r="T39" s="157"/>
+      <c r="U39" s="149"/>
+      <c r="V39" s="149"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="AB39" s="7"/>
-      <c r="AC39" s="110"/>
+      <c r="AC39" s="137"/>
       <c r="AD39" s="6"/>
       <c r="AE39" s="17"/>
       <c r="AF39" s="6"/>
@@ -7796,7 +8472,7 @@
       <c r="AH39" s="6"/>
       <c r="AI39" s="17"/>
       <c r="AJ39" s="6"/>
-      <c r="AK39" s="92"/>
+      <c r="AK39" s="112"/>
       <c r="AL39" s="7"/>
       <c r="AM39" s="7"/>
       <c r="AN39" s="7"/>
@@ -7805,9 +8481,9 @@
       <c r="AQ39" s="7"/>
       <c r="AR39" s="7"/>
       <c r="AS39" s="7"/>
-      <c r="AT39" s="90"/>
-      <c r="AU39" s="86"/>
-      <c r="AV39" s="86"/>
+      <c r="AT39" s="150"/>
+      <c r="AU39" s="149"/>
+      <c r="AV39" s="149"/>
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
@@ -7837,13 +8513,13 @@
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
-      <c r="T40" s="88"/>
-      <c r="U40" s="86"/>
-      <c r="V40" s="86"/>
+      <c r="T40" s="164"/>
+      <c r="U40" s="149"/>
+      <c r="V40" s="149"/>
       <c r="W40" s="7"/>
       <c r="X40" s="7"/>
       <c r="AB40" s="7"/>
-      <c r="AC40" s="110"/>
+      <c r="AC40" s="137"/>
       <c r="AD40" s="6"/>
       <c r="AE40" s="17"/>
       <c r="AF40" s="6"/>
@@ -7851,7 +8527,7 @@
       <c r="AH40" s="6"/>
       <c r="AI40" s="17"/>
       <c r="AJ40" s="6"/>
-      <c r="AK40" s="92"/>
+      <c r="AK40" s="112"/>
       <c r="AL40" s="7"/>
       <c r="AM40" s="7"/>
       <c r="AN40" s="7"/>
@@ -7863,8 +8539,8 @@
       <c r="AR40" s="7"/>
       <c r="AS40" s="7"/>
       <c r="AT40" s="7"/>
-      <c r="AU40" s="86"/>
-      <c r="AV40" s="86"/>
+      <c r="AU40" s="149"/>
+      <c r="AV40" s="149"/>
       <c r="AW40" s="7"/>
       <c r="AX40" s="7"/>
       <c r="AY40" s="7"/>
@@ -7887,14 +8563,14 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="109" t="s">
+      <c r="O41" s="134" t="s">
         <v>15</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
-      <c r="T41" s="88"/>
+      <c r="T41" s="164"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
@@ -7912,7 +8588,7 @@
       <c r="AL41" s="7"/>
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
-      <c r="AO41" s="98" t="s">
+      <c r="AO41" s="143" t="s">
         <v>15</v>
       </c>
       <c r="AP41" s="7"/>
@@ -7944,12 +8620,12 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="109"/>
+      <c r="O42" s="134"/>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
-      <c r="T42" s="88"/>
+      <c r="T42" s="164"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
@@ -7967,7 +8643,7 @@
       <c r="AL42" s="7"/>
       <c r="AM42" s="7"/>
       <c r="AN42" s="7"/>
-      <c r="AO42" s="98"/>
+      <c r="AO42" s="143"/>
       <c r="AP42" s="7"/>
       <c r="AQ42" s="7"/>
       <c r="AR42" s="7"/>
@@ -7997,14 +8673,14 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
-      <c r="O43" s="103" t="s">
+      <c r="O43" s="139" t="s">
         <v>23</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
-      <c r="T43" s="88"/>
+      <c r="T43" s="164"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
@@ -8022,7 +8698,7 @@
       <c r="AL43" s="7"/>
       <c r="AM43" s="7"/>
       <c r="AN43" s="7"/>
-      <c r="AO43" s="107" t="s">
+      <c r="AO43" s="151" t="s">
         <v>23</v>
       </c>
       <c r="AP43" s="7"/>
@@ -8054,18 +8730,18 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
-      <c r="O44" s="104"/>
+      <c r="O44" s="140"/>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
-      <c r="T44" s="88"/>
-      <c r="U44" s="82" t="s">
+      <c r="T44" s="164"/>
+      <c r="U44" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="V44" s="83"/>
-      <c r="W44" s="83"/>
-      <c r="X44" s="83"/>
+      <c r="V44" s="153"/>
+      <c r="W44" s="153"/>
+      <c r="X44" s="153"/>
       <c r="AB44" s="7"/>
       <c r="AC44" s="19"/>
       <c r="AD44" s="6"/>
@@ -8079,16 +8755,16 @@
       <c r="AL44" s="7"/>
       <c r="AM44" s="7"/>
       <c r="AN44" s="7"/>
-      <c r="AO44" s="108"/>
+      <c r="AO44" s="152"/>
       <c r="AP44" s="7"/>
       <c r="AQ44" s="7"/>
       <c r="AR44" s="7"/>
       <c r="AS44" s="7"/>
       <c r="AT44" s="7"/>
-      <c r="AU44" s="83"/>
-      <c r="AV44" s="83"/>
-      <c r="AW44" s="83"/>
-      <c r="AX44" s="83"/>
+      <c r="AU44" s="153"/>
+      <c r="AV44" s="153"/>
+      <c r="AW44" s="153"/>
+      <c r="AX44" s="153"/>
       <c r="AY44" s="7"/>
       <c r="AZ44" s="7"/>
       <c r="BA44" s="7"/>
@@ -8109,18 +8785,18 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="103" t="s">
+      <c r="O45" s="139" t="s">
         <v>22</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
-      <c r="T45" s="88"/>
-      <c r="U45" s="82"/>
-      <c r="V45" s="83"/>
-      <c r="W45" s="83"/>
-      <c r="X45" s="83"/>
+      <c r="T45" s="164"/>
+      <c r="U45" s="161"/>
+      <c r="V45" s="153"/>
+      <c r="W45" s="153"/>
+      <c r="X45" s="153"/>
       <c r="AB45" s="7"/>
       <c r="AC45" s="19"/>
       <c r="AD45" s="6"/>
@@ -8134,20 +8810,20 @@
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
       <c r="AN45" s="7"/>
-      <c r="AO45" s="107" t="s">
+      <c r="AO45" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="AP45" s="95" t="s">
+      <c r="AP45" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="AQ45" s="96"/>
-      <c r="AR45" s="96"/>
-      <c r="AS45" s="96"/>
-      <c r="AT45" s="96"/>
-      <c r="AU45" s="83"/>
-      <c r="AV45" s="83"/>
-      <c r="AW45" s="83"/>
-      <c r="AX45" s="83"/>
+      <c r="AQ45" s="160"/>
+      <c r="AR45" s="160"/>
+      <c r="AS45" s="160"/>
+      <c r="AT45" s="160"/>
+      <c r="AU45" s="153"/>
+      <c r="AV45" s="153"/>
+      <c r="AW45" s="153"/>
+      <c r="AX45" s="153"/>
       <c r="AY45" s="7"/>
       <c r="AZ45" s="7"/>
       <c r="BA45" s="7"/>
@@ -8178,17 +8854,17 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="104"/>
+      <c r="O46" s="140"/>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
-      <c r="T46" s="88"/>
-      <c r="U46" s="87" t="s">
+      <c r="T46" s="164"/>
+      <c r="U46" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="V46" s="81"/>
-      <c r="W46" s="81"/>
+      <c r="V46" s="147"/>
+      <c r="W46" s="147"/>
       <c r="X46" s="7"/>
       <c r="AB46" s="7"/>
       <c r="AC46" s="20">
@@ -8213,15 +8889,15 @@
       <c r="AL46" s="7"/>
       <c r="AM46" s="7"/>
       <c r="AN46" s="7"/>
-      <c r="AO46" s="108"/>
-      <c r="AP46" s="95"/>
-      <c r="AQ46" s="96"/>
-      <c r="AR46" s="96"/>
-      <c r="AS46" s="96"/>
-      <c r="AT46" s="96"/>
-      <c r="AU46" s="81"/>
-      <c r="AV46" s="81"/>
-      <c r="AW46" s="81"/>
+      <c r="AO46" s="152"/>
+      <c r="AP46" s="159"/>
+      <c r="AQ46" s="160"/>
+      <c r="AR46" s="160"/>
+      <c r="AS46" s="160"/>
+      <c r="AT46" s="160"/>
+      <c r="AU46" s="147"/>
+      <c r="AV46" s="147"/>
+      <c r="AW46" s="147"/>
       <c r="AX46" s="7"/>
       <c r="AY46" s="7"/>
       <c r="AZ46" s="7"/>
@@ -8253,14 +8929,14 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="109" t="s">
+      <c r="O47" s="134" t="s">
         <v>21</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7"/>
       <c r="S47" s="7"/>
-      <c r="T47" s="88"/>
+      <c r="T47" s="164"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
@@ -8288,7 +8964,7 @@
       <c r="AL47" s="7"/>
       <c r="AM47" s="7"/>
       <c r="AN47" s="7"/>
-      <c r="AO47" s="98" t="s">
+      <c r="AO47" s="143" t="s">
         <v>21</v>
       </c>
       <c r="AP47" s="7"/>
@@ -8330,14 +9006,14 @@
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="109"/>
-      <c r="P48" s="85" t="s">
+      <c r="O48" s="134"/>
+      <c r="P48" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="Q48" s="97"/>
-      <c r="R48" s="97"/>
+      <c r="Q48" s="136"/>
+      <c r="R48" s="136"/>
       <c r="S48" s="7"/>
-      <c r="T48" s="88"/>
+      <c r="T48" s="164"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
@@ -8365,10 +9041,10 @@
       <c r="AL48" s="7"/>
       <c r="AM48" s="7"/>
       <c r="AN48" s="7"/>
-      <c r="AO48" s="98"/>
-      <c r="AP48" s="85"/>
-      <c r="AQ48" s="97"/>
-      <c r="AR48" s="97"/>
+      <c r="AO48" s="143"/>
+      <c r="AP48" s="135"/>
+      <c r="AQ48" s="136"/>
+      <c r="AR48" s="136"/>
       <c r="AS48" s="7"/>
       <c r="AT48" s="7"/>
       <c r="AU48" s="7"/>
@@ -8395,20 +9071,20 @@
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="109" t="s">
+      <c r="O49" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="97"/>
-      <c r="Q49" s="97"/>
-      <c r="R49" s="97"/>
+      <c r="P49" s="136"/>
+      <c r="Q49" s="136"/>
+      <c r="R49" s="136"/>
       <c r="S49" s="7"/>
-      <c r="T49" s="88"/>
-      <c r="U49" s="84" t="s">
+      <c r="T49" s="164"/>
+      <c r="U49" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="V49" s="85"/>
-      <c r="W49" s="85"/>
-      <c r="X49" s="85"/>
+      <c r="V49" s="135"/>
+      <c r="W49" s="135"/>
+      <c r="X49" s="135"/>
       <c r="AB49" s="7"/>
       <c r="AC49" s="19"/>
       <c r="AD49" s="6"/>
@@ -8422,12 +9098,12 @@
       <c r="AL49" s="7"/>
       <c r="AM49" s="7"/>
       <c r="AN49" s="7"/>
-      <c r="AO49" s="98" t="s">
+      <c r="AO49" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="AP49" s="97"/>
-      <c r="AQ49" s="97"/>
-      <c r="AR49" s="97"/>
+      <c r="AP49" s="136"/>
+      <c r="AQ49" s="136"/>
+      <c r="AR49" s="136"/>
       <c r="AS49" s="7"/>
       <c r="AT49" s="7"/>
       <c r="AU49" s="72"/>
@@ -8454,16 +9130,16 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="109"/>
+      <c r="O50" s="134"/>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
       <c r="T50" s="12"/>
-      <c r="U50" s="84"/>
-      <c r="V50" s="85"/>
-      <c r="W50" s="85"/>
-      <c r="X50" s="85"/>
+      <c r="U50" s="162"/>
+      <c r="V50" s="135"/>
+      <c r="W50" s="135"/>
+      <c r="X50" s="135"/>
       <c r="AB50" s="7"/>
       <c r="AC50" s="19"/>
       <c r="AD50" s="6"/>
@@ -8477,7 +9153,7 @@
       <c r="AL50" s="7"/>
       <c r="AM50" s="7"/>
       <c r="AN50" s="7"/>
-      <c r="AO50" s="98"/>
+      <c r="AO50" s="143"/>
       <c r="AP50" s="7"/>
       <c r="AQ50" s="7"/>
       <c r="AR50" s="7"/>
@@ -8507,18 +9183,18 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="103" t="s">
+      <c r="O51" s="139" t="s">
         <v>20</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
       <c r="S51" s="7"/>
-      <c r="T51" s="105"/>
-      <c r="U51" s="84"/>
-      <c r="V51" s="85"/>
-      <c r="W51" s="85"/>
-      <c r="X51" s="85"/>
+      <c r="T51" s="141"/>
+      <c r="U51" s="162"/>
+      <c r="V51" s="135"/>
+      <c r="W51" s="135"/>
+      <c r="X51" s="135"/>
       <c r="AB51" s="7"/>
       <c r="AC51" s="19"/>
       <c r="AD51" s="6"/>
@@ -8532,7 +9208,7 @@
       <c r="AL51" s="7"/>
       <c r="AM51" s="7"/>
       <c r="AN51" s="7"/>
-      <c r="AO51" s="111" t="s">
+      <c r="AO51" s="154" t="s">
         <v>20</v>
       </c>
       <c r="AP51" s="7"/>
@@ -8564,18 +9240,18 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="104"/>
+      <c r="O52" s="140"/>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
-      <c r="T52" s="105"/>
-      <c r="U52" s="84" t="s">
+      <c r="T52" s="141"/>
+      <c r="U52" s="162" t="s">
         <v>26</v>
       </c>
-      <c r="V52" s="85"/>
-      <c r="W52" s="85"/>
-      <c r="X52" s="85"/>
+      <c r="V52" s="135"/>
+      <c r="W52" s="135"/>
+      <c r="X52" s="135"/>
       <c r="AB52" s="7"/>
       <c r="AC52" s="19"/>
       <c r="AD52" s="6"/>
@@ -8589,15 +9265,15 @@
       <c r="AL52" s="7"/>
       <c r="AM52" s="7"/>
       <c r="AN52" s="7"/>
-      <c r="AO52" s="112"/>
-      <c r="AP52" s="101" t="s">
+      <c r="AO52" s="155"/>
+      <c r="AP52" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="AQ52" s="86"/>
-      <c r="AR52" s="86"/>
-      <c r="AS52" s="86"/>
-      <c r="AT52" s="86"/>
-      <c r="AU52" s="86"/>
+      <c r="AQ52" s="149"/>
+      <c r="AR52" s="149"/>
+      <c r="AS52" s="149"/>
+      <c r="AT52" s="149"/>
+      <c r="AU52" s="149"/>
       <c r="AV52" s="72"/>
       <c r="AW52" s="72"/>
       <c r="AX52" s="72"/>
@@ -8621,18 +9297,18 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="103" t="s">
+      <c r="O53" s="139" t="s">
         <v>16</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
       <c r="S53" s="7"/>
-      <c r="T53" s="105"/>
-      <c r="U53" s="84"/>
-      <c r="V53" s="85"/>
-      <c r="W53" s="85"/>
-      <c r="X53" s="85"/>
+      <c r="T53" s="141"/>
+      <c r="U53" s="162"/>
+      <c r="V53" s="135"/>
+      <c r="W53" s="135"/>
+      <c r="X53" s="135"/>
       <c r="AB53" s="7"/>
       <c r="AC53" s="19"/>
       <c r="AD53" s="6"/>
@@ -8646,15 +9322,15 @@
       <c r="AL53" s="7"/>
       <c r="AM53" s="7"/>
       <c r="AN53" s="7"/>
-      <c r="AO53" s="111" t="s">
+      <c r="AO53" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="AP53" s="101"/>
-      <c r="AQ53" s="86"/>
-      <c r="AR53" s="86"/>
-      <c r="AS53" s="86"/>
-      <c r="AT53" s="86"/>
-      <c r="AU53" s="86"/>
+      <c r="AP53" s="148"/>
+      <c r="AQ53" s="149"/>
+      <c r="AR53" s="149"/>
+      <c r="AS53" s="149"/>
+      <c r="AT53" s="149"/>
+      <c r="AU53" s="149"/>
       <c r="AV53" s="72"/>
       <c r="AW53" s="72"/>
       <c r="AX53" s="72"/>
@@ -8678,16 +9354,16 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="104"/>
+      <c r="O54" s="140"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
-      <c r="T54" s="105"/>
-      <c r="U54" s="84"/>
-      <c r="V54" s="85"/>
-      <c r="W54" s="85"/>
-      <c r="X54" s="85"/>
+      <c r="T54" s="141"/>
+      <c r="U54" s="162"/>
+      <c r="V54" s="135"/>
+      <c r="W54" s="135"/>
+      <c r="X54" s="135"/>
       <c r="AB54" s="7"/>
       <c r="AC54" s="21"/>
       <c r="AD54" s="6"/>
@@ -8701,7 +9377,7 @@
       <c r="AL54" s="7"/>
       <c r="AM54" s="7"/>
       <c r="AN54" s="7"/>
-      <c r="AO54" s="112"/>
+      <c r="AO54" s="155"/>
       <c r="AP54" s="71"/>
       <c r="AQ54" s="70"/>
       <c r="AR54" s="70"/>
@@ -8731,14 +9407,14 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="103" t="s">
+      <c r="O55" s="139" t="s">
         <v>17</v>
       </c>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
       <c r="S55" s="7"/>
-      <c r="T55" s="106"/>
+      <c r="T55" s="142"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
       <c r="W55" s="7"/>
@@ -8756,7 +9432,7 @@
       <c r="AL55" s="7"/>
       <c r="AM55" s="7"/>
       <c r="AN55" s="7"/>
-      <c r="AO55" s="113" t="s">
+      <c r="AO55" s="106" t="s">
         <v>17</v>
       </c>
       <c r="AP55" s="7"/>
@@ -8788,7 +9464,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="104"/>
+      <c r="O56" s="140"/>
       <c r="P56" s="7"/>
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
@@ -8811,14 +9487,14 @@
       <c r="AL56" s="7"/>
       <c r="AM56" s="7"/>
       <c r="AN56" s="7"/>
-      <c r="AO56" s="114"/>
-      <c r="AP56" s="101" t="s">
+      <c r="AO56" s="108"/>
+      <c r="AP56" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="AQ56" s="86"/>
-      <c r="AR56" s="86"/>
-      <c r="AS56" s="86"/>
-      <c r="AT56" s="86"/>
+      <c r="AQ56" s="149"/>
+      <c r="AR56" s="149"/>
+      <c r="AS56" s="149"/>
+      <c r="AT56" s="149"/>
       <c r="AU56" s="7"/>
       <c r="AV56" s="7"/>
       <c r="AW56" s="7"/>
@@ -8853,7 +9529,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="103" t="s">
+      <c r="O57" s="139" t="s">
         <v>18</v>
       </c>
       <c r="P57" s="7"/>
@@ -8888,14 +9564,14 @@
       <c r="AL57" s="7"/>
       <c r="AM57" s="7"/>
       <c r="AN57" s="7"/>
-      <c r="AO57" s="113" t="s">
+      <c r="AO57" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="AP57" s="101"/>
-      <c r="AQ57" s="86"/>
-      <c r="AR57" s="86"/>
-      <c r="AS57" s="86"/>
-      <c r="AT57" s="86"/>
+      <c r="AP57" s="148"/>
+      <c r="AQ57" s="149"/>
+      <c r="AR57" s="149"/>
+      <c r="AS57" s="149"/>
+      <c r="AT57" s="149"/>
       <c r="AU57" s="7"/>
       <c r="AV57" s="7"/>
       <c r="AW57" s="7"/>
@@ -8920,7 +9596,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="104"/>
+      <c r="O58" s="140"/>
       <c r="P58" s="7"/>
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
@@ -8943,7 +9619,7 @@
       <c r="AL58" s="7"/>
       <c r="AM58" s="7"/>
       <c r="AN58" s="7"/>
-      <c r="AO58" s="156"/>
+      <c r="AO58" s="107"/>
       <c r="AP58" s="7"/>
       <c r="AQ58" s="7"/>
       <c r="AR58" s="7"/>
@@ -9025,19 +9701,19 @@
       <c r="K60" s="3"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-      <c r="N60" s="102" t="s">
+      <c r="N60" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="O60" s="102"/>
-      <c r="P60" s="102"/>
+      <c r="O60" s="138"/>
+      <c r="P60" s="138"/>
       <c r="Q60" s="7"/>
-      <c r="R60" s="102" t="s">
+      <c r="R60" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="S60" s="102"/>
-      <c r="T60" s="102"/>
-      <c r="U60" s="102"/>
-      <c r="V60" s="102"/>
+      <c r="S60" s="138"/>
+      <c r="T60" s="138"/>
+      <c r="U60" s="138"/>
+      <c r="V60" s="138"/>
       <c r="W60" s="7"/>
       <c r="X60" s="7"/>
       <c r="AB60" s="7"/>
@@ -9082,15 +9758,15 @@
       <c r="K61" s="3"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-      <c r="N61" s="102"/>
-      <c r="O61" s="102"/>
-      <c r="P61" s="102"/>
+      <c r="N61" s="138"/>
+      <c r="O61" s="138"/>
+      <c r="P61" s="138"/>
       <c r="Q61" s="7"/>
-      <c r="R61" s="102"/>
-      <c r="S61" s="102"/>
-      <c r="T61" s="102"/>
-      <c r="U61" s="102"/>
-      <c r="V61" s="102"/>
+      <c r="R61" s="138"/>
+      <c r="S61" s="138"/>
+      <c r="T61" s="138"/>
+      <c r="U61" s="138"/>
+      <c r="V61" s="138"/>
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
       <c r="AB61" s="7"/>
@@ -9105,19 +9781,19 @@
       <c r="AK61" s="17"/>
       <c r="AL61" s="7"/>
       <c r="AM61" s="7"/>
-      <c r="AN61" s="150" t="s">
+      <c r="AN61" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="AO61" s="151"/>
-      <c r="AP61" s="151"/>
-      <c r="AQ61" s="151"/>
-      <c r="AR61" s="151"/>
-      <c r="AS61" s="151"/>
-      <c r="AT61" s="151"/>
-      <c r="AU61" s="151"/>
-      <c r="AV61" s="151"/>
-      <c r="AW61" s="151"/>
-      <c r="AX61" s="152"/>
+      <c r="AO61" s="101"/>
+      <c r="AP61" s="101"/>
+      <c r="AQ61" s="101"/>
+      <c r="AR61" s="101"/>
+      <c r="AS61" s="101"/>
+      <c r="AT61" s="101"/>
+      <c r="AU61" s="101"/>
+      <c r="AV61" s="101"/>
+      <c r="AW61" s="101"/>
+      <c r="AX61" s="102"/>
       <c r="AY61" s="7"/>
       <c r="AZ61" s="7"/>
       <c r="BA61" s="7"/>
@@ -9141,13 +9817,13 @@
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
       <c r="Q62" s="7"/>
-      <c r="R62" s="81" t="s">
+      <c r="R62" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="S62" s="81"/>
-      <c r="T62" s="81"/>
-      <c r="U62" s="81"/>
-      <c r="V62" s="81"/>
+      <c r="S62" s="147"/>
+      <c r="T62" s="147"/>
+      <c r="U62" s="147"/>
+      <c r="V62" s="147"/>
       <c r="W62" s="7"/>
       <c r="X62" s="7"/>
       <c r="AB62" s="7"/>
@@ -9162,17 +9838,17 @@
       <c r="AK62" s="17"/>
       <c r="AL62" s="7"/>
       <c r="AM62" s="7"/>
-      <c r="AN62" s="153"/>
-      <c r="AO62" s="154"/>
-      <c r="AP62" s="154"/>
-      <c r="AQ62" s="154"/>
-      <c r="AR62" s="154"/>
-      <c r="AS62" s="154"/>
-      <c r="AT62" s="154"/>
-      <c r="AU62" s="154"/>
-      <c r="AV62" s="154"/>
-      <c r="AW62" s="154"/>
-      <c r="AX62" s="155"/>
+      <c r="AN62" s="103"/>
+      <c r="AO62" s="104"/>
+      <c r="AP62" s="104"/>
+      <c r="AQ62" s="104"/>
+      <c r="AR62" s="104"/>
+      <c r="AS62" s="104"/>
+      <c r="AT62" s="104"/>
+      <c r="AU62" s="104"/>
+      <c r="AV62" s="104"/>
+      <c r="AW62" s="104"/>
+      <c r="AX62" s="105"/>
       <c r="AY62" s="7"/>
       <c r="AZ62" s="7"/>
       <c r="BA62" s="7"/>
@@ -9215,19 +9891,19 @@
       <c r="AK63" s="17"/>
       <c r="AL63" s="7"/>
       <c r="AM63" s="7"/>
-      <c r="AN63" s="141" t="s">
+      <c r="AN63" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="AO63" s="142"/>
-      <c r="AP63" s="142"/>
-      <c r="AQ63" s="142"/>
-      <c r="AR63" s="142"/>
-      <c r="AS63" s="142"/>
-      <c r="AT63" s="142"/>
-      <c r="AU63" s="142"/>
-      <c r="AV63" s="142"/>
-      <c r="AW63" s="142"/>
-      <c r="AX63" s="143"/>
+      <c r="AO63" s="92"/>
+      <c r="AP63" s="92"/>
+      <c r="AQ63" s="92"/>
+      <c r="AR63" s="92"/>
+      <c r="AS63" s="92"/>
+      <c r="AT63" s="92"/>
+      <c r="AU63" s="92"/>
+      <c r="AV63" s="92"/>
+      <c r="AW63" s="92"/>
+      <c r="AX63" s="93"/>
       <c r="AY63" s="7"/>
       <c r="AZ63" s="7"/>
       <c r="BA63" s="7"/>
@@ -9290,17 +9966,17 @@
       </c>
       <c r="AL64" s="7"/>
       <c r="AM64" s="7"/>
-      <c r="AN64" s="141"/>
-      <c r="AO64" s="142"/>
-      <c r="AP64" s="142"/>
-      <c r="AQ64" s="142"/>
-      <c r="AR64" s="142"/>
-      <c r="AS64" s="142"/>
-      <c r="AT64" s="142"/>
-      <c r="AU64" s="142"/>
-      <c r="AV64" s="142"/>
-      <c r="AW64" s="142"/>
-      <c r="AX64" s="143"/>
+      <c r="AN64" s="91"/>
+      <c r="AO64" s="92"/>
+      <c r="AP64" s="92"/>
+      <c r="AQ64" s="92"/>
+      <c r="AR64" s="92"/>
+      <c r="AS64" s="92"/>
+      <c r="AT64" s="92"/>
+      <c r="AU64" s="92"/>
+      <c r="AV64" s="92"/>
+      <c r="AW64" s="92"/>
+      <c r="AX64" s="93"/>
       <c r="AY64" s="7"/>
       <c r="AZ64" s="7"/>
       <c r="BA64" s="7"/>
@@ -9363,19 +10039,19 @@
       </c>
       <c r="AL65" s="7"/>
       <c r="AM65" s="7"/>
-      <c r="AN65" s="144" t="s">
+      <c r="AN65" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="AO65" s="145"/>
-      <c r="AP65" s="145"/>
-      <c r="AQ65" s="145"/>
-      <c r="AR65" s="145"/>
-      <c r="AS65" s="145"/>
-      <c r="AT65" s="145"/>
-      <c r="AU65" s="145"/>
-      <c r="AV65" s="145"/>
-      <c r="AW65" s="145"/>
-      <c r="AX65" s="146"/>
+      <c r="AO65" s="95"/>
+      <c r="AP65" s="95"/>
+      <c r="AQ65" s="95"/>
+      <c r="AR65" s="95"/>
+      <c r="AS65" s="95"/>
+      <c r="AT65" s="95"/>
+      <c r="AU65" s="95"/>
+      <c r="AV65" s="95"/>
+      <c r="AW65" s="95"/>
+      <c r="AX65" s="96"/>
       <c r="AY65" s="7"/>
       <c r="AZ65" s="7"/>
       <c r="BA65" s="7"/>
@@ -9438,17 +10114,17 @@
       </c>
       <c r="AL66" s="7"/>
       <c r="AM66" s="7"/>
-      <c r="AN66" s="147"/>
-      <c r="AO66" s="148"/>
-      <c r="AP66" s="148"/>
-      <c r="AQ66" s="148"/>
-      <c r="AR66" s="148"/>
-      <c r="AS66" s="148"/>
-      <c r="AT66" s="148"/>
-      <c r="AU66" s="148"/>
-      <c r="AV66" s="148"/>
-      <c r="AW66" s="148"/>
-      <c r="AX66" s="149"/>
+      <c r="AN66" s="97"/>
+      <c r="AO66" s="98"/>
+      <c r="AP66" s="98"/>
+      <c r="AQ66" s="98"/>
+      <c r="AR66" s="98"/>
+      <c r="AS66" s="98"/>
+      <c r="AT66" s="98"/>
+      <c r="AU66" s="98"/>
+      <c r="AV66" s="98"/>
+      <c r="AW66" s="98"/>
+      <c r="AX66" s="99"/>
       <c r="AY66" s="7"/>
       <c r="AZ66" s="7"/>
       <c r="BA66" s="7"/>
@@ -9491,19 +10167,19 @@
       <c r="AK67" s="17"/>
       <c r="AL67" s="7"/>
       <c r="AM67" s="7"/>
-      <c r="AN67" s="99" t="s">
+      <c r="AN67" s="145" t="s">
         <v>64</v>
       </c>
-      <c r="AO67" s="100"/>
-      <c r="AP67" s="100"/>
-      <c r="AQ67" s="100"/>
-      <c r="AR67" s="100"/>
-      <c r="AS67" s="100"/>
-      <c r="AT67" s="100"/>
-      <c r="AU67" s="100"/>
-      <c r="AV67" s="100"/>
-      <c r="AW67" s="100"/>
-      <c r="AX67" s="100"/>
+      <c r="AO67" s="146"/>
+      <c r="AP67" s="146"/>
+      <c r="AQ67" s="146"/>
+      <c r="AR67" s="146"/>
+      <c r="AS67" s="146"/>
+      <c r="AT67" s="146"/>
+      <c r="AU67" s="146"/>
+      <c r="AV67" s="146"/>
+      <c r="AW67" s="146"/>
+      <c r="AX67" s="146"/>
       <c r="AY67" s="7"/>
       <c r="AZ67" s="7"/>
       <c r="BA67" s="7"/>
@@ -9546,17 +10222,17 @@
       <c r="AK68" s="17"/>
       <c r="AL68" s="7"/>
       <c r="AM68" s="7"/>
-      <c r="AN68" s="81"/>
-      <c r="AO68" s="81"/>
-      <c r="AP68" s="81"/>
-      <c r="AQ68" s="81"/>
-      <c r="AR68" s="81"/>
-      <c r="AS68" s="81"/>
-      <c r="AT68" s="81"/>
-      <c r="AU68" s="81"/>
-      <c r="AV68" s="81"/>
-      <c r="AW68" s="81"/>
-      <c r="AX68" s="81"/>
+      <c r="AN68" s="147"/>
+      <c r="AO68" s="147"/>
+      <c r="AP68" s="147"/>
+      <c r="AQ68" s="147"/>
+      <c r="AR68" s="147"/>
+      <c r="AS68" s="147"/>
+      <c r="AT68" s="147"/>
+      <c r="AU68" s="147"/>
+      <c r="AV68" s="147"/>
+      <c r="AW68" s="147"/>
+      <c r="AX68" s="147"/>
       <c r="AY68" s="7"/>
       <c r="AZ68" s="7"/>
       <c r="BA68" s="7"/>
@@ -9928,34 +10604,34 @@
       <c r="BB76" s="7"/>
       <c r="BC76" s="7"/>
       <c r="BG76" s="7"/>
-      <c r="BH76" s="140" t="s">
+      <c r="BH76" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="BI76" s="140"/>
-      <c r="BJ76" s="140"/>
-      <c r="BK76" s="140"/>
-      <c r="BL76" s="140"/>
-      <c r="BM76" s="140"/>
-      <c r="BN76" s="140"/>
-      <c r="BO76" s="140"/>
-      <c r="BP76" s="140"/>
-      <c r="BQ76" s="140"/>
-      <c r="BR76" s="140"/>
-      <c r="BS76" s="140"/>
-      <c r="BT76" s="140"/>
-      <c r="BU76" s="140"/>
-      <c r="BV76" s="140"/>
+      <c r="BI76" s="89"/>
+      <c r="BJ76" s="89"/>
+      <c r="BK76" s="89"/>
+      <c r="BL76" s="89"/>
+      <c r="BM76" s="89"/>
+      <c r="BN76" s="89"/>
+      <c r="BO76" s="89"/>
+      <c r="BP76" s="89"/>
+      <c r="BQ76" s="89"/>
+      <c r="BR76" s="89"/>
+      <c r="BS76" s="89"/>
+      <c r="BT76" s="89"/>
+      <c r="BU76" s="89"/>
+      <c r="BV76" s="89"/>
       <c r="BW76" s="10"/>
       <c r="BX76" s="80"/>
-      <c r="BY76" s="140" t="s">
+      <c r="BY76" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="BZ76" s="140"/>
-      <c r="CA76" s="140"/>
-      <c r="CB76" s="140"/>
-      <c r="CC76" s="140"/>
-      <c r="CD76" s="140"/>
-      <c r="CE76" s="140"/>
+      <c r="BZ76" s="89"/>
+      <c r="CA76" s="89"/>
+      <c r="CB76" s="89"/>
+      <c r="CC76" s="89"/>
+      <c r="CD76" s="89"/>
+      <c r="CE76" s="89"/>
       <c r="CF76" s="80"/>
     </row>
     <row r="77" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -9988,30 +10664,30 @@
       <c r="BB77" s="7"/>
       <c r="BC77" s="7"/>
       <c r="BG77" s="7"/>
-      <c r="BH77" s="140"/>
-      <c r="BI77" s="140"/>
-      <c r="BJ77" s="140"/>
-      <c r="BK77" s="140"/>
-      <c r="BL77" s="140"/>
-      <c r="BM77" s="140"/>
-      <c r="BN77" s="140"/>
-      <c r="BO77" s="140"/>
-      <c r="BP77" s="140"/>
-      <c r="BQ77" s="140"/>
-      <c r="BR77" s="140"/>
-      <c r="BS77" s="140"/>
-      <c r="BT77" s="140"/>
-      <c r="BU77" s="140"/>
-      <c r="BV77" s="140"/>
+      <c r="BH77" s="89"/>
+      <c r="BI77" s="89"/>
+      <c r="BJ77" s="89"/>
+      <c r="BK77" s="89"/>
+      <c r="BL77" s="89"/>
+      <c r="BM77" s="89"/>
+      <c r="BN77" s="89"/>
+      <c r="BO77" s="89"/>
+      <c r="BP77" s="89"/>
+      <c r="BQ77" s="89"/>
+      <c r="BR77" s="89"/>
+      <c r="BS77" s="89"/>
+      <c r="BT77" s="89"/>
+      <c r="BU77" s="89"/>
+      <c r="BV77" s="89"/>
       <c r="BW77" s="10"/>
       <c r="BX77" s="80"/>
-      <c r="BY77" s="140"/>
-      <c r="BZ77" s="140"/>
-      <c r="CA77" s="140"/>
-      <c r="CB77" s="140"/>
-      <c r="CC77" s="140"/>
-      <c r="CD77" s="140"/>
-      <c r="CE77" s="140"/>
+      <c r="BY77" s="89"/>
+      <c r="BZ77" s="89"/>
+      <c r="CA77" s="89"/>
+      <c r="CB77" s="89"/>
+      <c r="CC77" s="89"/>
+      <c r="CD77" s="89"/>
+      <c r="CE77" s="89"/>
       <c r="CF77" s="80"/>
     </row>
     <row r="78" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -10027,30 +10703,30 @@
       <c r="BB78" s="7"/>
       <c r="BC78" s="7"/>
       <c r="BG78" s="7"/>
-      <c r="BH78" s="140"/>
-      <c r="BI78" s="140"/>
-      <c r="BJ78" s="140"/>
-      <c r="BK78" s="140"/>
-      <c r="BL78" s="140"/>
-      <c r="BM78" s="140"/>
-      <c r="BN78" s="140"/>
-      <c r="BO78" s="140"/>
-      <c r="BP78" s="140"/>
-      <c r="BQ78" s="140"/>
-      <c r="BR78" s="140"/>
-      <c r="BS78" s="140"/>
-      <c r="BT78" s="140"/>
-      <c r="BU78" s="140"/>
-      <c r="BV78" s="140"/>
+      <c r="BH78" s="89"/>
+      <c r="BI78" s="89"/>
+      <c r="BJ78" s="89"/>
+      <c r="BK78" s="89"/>
+      <c r="BL78" s="89"/>
+      <c r="BM78" s="89"/>
+      <c r="BN78" s="89"/>
+      <c r="BO78" s="89"/>
+      <c r="BP78" s="89"/>
+      <c r="BQ78" s="89"/>
+      <c r="BR78" s="89"/>
+      <c r="BS78" s="89"/>
+      <c r="BT78" s="89"/>
+      <c r="BU78" s="89"/>
+      <c r="BV78" s="89"/>
       <c r="BW78" s="10"/>
       <c r="BX78" s="80"/>
-      <c r="BY78" s="140"/>
-      <c r="BZ78" s="140"/>
-      <c r="CA78" s="140"/>
-      <c r="CB78" s="140"/>
-      <c r="CC78" s="140"/>
-      <c r="CD78" s="140"/>
-      <c r="CE78" s="140"/>
+      <c r="BY78" s="89"/>
+      <c r="BZ78" s="89"/>
+      <c r="CA78" s="89"/>
+      <c r="CB78" s="89"/>
+      <c r="CC78" s="89"/>
+      <c r="CD78" s="89"/>
+      <c r="CE78" s="89"/>
       <c r="CF78" s="80"/>
     </row>
     <row r="79" spans="2:84" x14ac:dyDescent="0.3">
@@ -10078,13 +10754,13 @@
       <c r="BV79" s="7"/>
       <c r="BW79" s="10"/>
       <c r="BX79" s="7"/>
-      <c r="BY79" s="140"/>
-      <c r="BZ79" s="140"/>
-      <c r="CA79" s="140"/>
-      <c r="CB79" s="140"/>
-      <c r="CC79" s="140"/>
-      <c r="CD79" s="140"/>
-      <c r="CE79" s="140"/>
+      <c r="BY79" s="89"/>
+      <c r="BZ79" s="89"/>
+      <c r="CA79" s="89"/>
+      <c r="CB79" s="89"/>
+      <c r="CC79" s="89"/>
+      <c r="CD79" s="89"/>
+      <c r="CE79" s="89"/>
       <c r="CF79" s="7"/>
     </row>
     <row r="80" spans="2:84" x14ac:dyDescent="0.3">
@@ -10170,7 +10846,7 @@
       <c r="BI82" s="6"/>
       <c r="BJ82" s="17"/>
       <c r="BK82" s="6"/>
-      <c r="BL82" s="92"/>
+      <c r="BL82" s="112"/>
       <c r="BM82" s="7"/>
       <c r="BN82" s="17"/>
       <c r="BO82" s="6"/>
@@ -10186,7 +10862,7 @@
       <c r="BY82" s="7"/>
       <c r="BZ82" s="7"/>
       <c r="CA82" s="69"/>
-      <c r="CB82" s="118"/>
+      <c r="CB82" s="113"/>
       <c r="CC82" s="7"/>
       <c r="CD82" s="7"/>
       <c r="CE82" s="7"/>
@@ -10199,7 +10875,7 @@
       <c r="BI83" s="6"/>
       <c r="BJ83" s="17"/>
       <c r="BK83" s="6"/>
-      <c r="BL83" s="92"/>
+      <c r="BL83" s="112"/>
       <c r="BM83" s="7"/>
       <c r="BN83" s="17"/>
       <c r="BO83" s="6"/>
@@ -10215,7 +10891,7 @@
       <c r="BY83" s="7"/>
       <c r="BZ83" s="7"/>
       <c r="CA83" s="69"/>
-      <c r="CB83" s="118"/>
+      <c r="CB83" s="113"/>
       <c r="CC83" s="7"/>
       <c r="CD83" s="7"/>
       <c r="CE83" s="7"/>
@@ -10301,10 +10977,10 @@
       <c r="BW86" s="10"/>
       <c r="BX86" s="17"/>
       <c r="BY86" s="7"/>
-      <c r="BZ86" s="121" t="s">
+      <c r="BZ86" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="CA86" s="122"/>
+      <c r="CA86" s="116"/>
       <c r="CB86" s="32"/>
       <c r="CC86" s="7"/>
       <c r="CD86" s="7"/>
@@ -10332,8 +11008,8 @@
       <c r="BW87" s="10"/>
       <c r="BX87" s="17"/>
       <c r="BY87" s="7"/>
-      <c r="BZ87" s="121"/>
-      <c r="CA87" s="122"/>
+      <c r="BZ87" s="115"/>
+      <c r="CA87" s="116"/>
       <c r="CB87" s="32"/>
       <c r="CC87" s="7"/>
       <c r="CD87" s="7"/>
@@ -10364,10 +11040,10 @@
       <c r="BZ88" s="7"/>
       <c r="CA88" s="69"/>
       <c r="CB88" s="2"/>
-      <c r="CC88" s="123" t="s">
+      <c r="CC88" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="CD88" s="124"/>
+      <c r="CD88" s="118"/>
       <c r="CE88" s="7"/>
       <c r="CF88" s="7"/>
     </row>
@@ -10395,8 +11071,8 @@
       <c r="BZ89" s="7"/>
       <c r="CA89" s="69"/>
       <c r="CB89" s="3"/>
-      <c r="CC89" s="125"/>
-      <c r="CD89" s="124"/>
+      <c r="CC89" s="119"/>
+      <c r="CD89" s="118"/>
       <c r="CE89" s="7"/>
       <c r="CF89" s="7"/>
       <c r="CJ89" t="s">
@@ -10638,23 +11314,23 @@
     <row r="98" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG98" s="7"/>
       <c r="BH98" s="39"/>
-      <c r="BI98" s="119" t="s">
+      <c r="BI98" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="BJ98" s="119"/>
-      <c r="BK98" s="119"/>
-      <c r="BL98" s="119"/>
-      <c r="BM98" s="119"/>
-      <c r="BN98" s="119"/>
-      <c r="BO98" s="119"/>
-      <c r="BP98" s="119"/>
-      <c r="BQ98" s="119"/>
-      <c r="BR98" s="119"/>
-      <c r="BS98" s="119"/>
-      <c r="BT98" s="119"/>
-      <c r="BU98" s="119"/>
-      <c r="BV98" s="119"/>
-      <c r="BW98" s="119"/>
+      <c r="BJ98" s="114"/>
+      <c r="BK98" s="114"/>
+      <c r="BL98" s="114"/>
+      <c r="BM98" s="114"/>
+      <c r="BN98" s="114"/>
+      <c r="BO98" s="114"/>
+      <c r="BP98" s="114"/>
+      <c r="BQ98" s="114"/>
+      <c r="BR98" s="114"/>
+      <c r="BS98" s="114"/>
+      <c r="BT98" s="114"/>
+      <c r="BU98" s="114"/>
+      <c r="BV98" s="114"/>
+      <c r="BW98" s="114"/>
       <c r="BX98" s="40"/>
       <c r="BY98" s="7"/>
       <c r="BZ98" s="7"/>
@@ -10668,21 +11344,21 @@
     <row r="99" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG99" s="7"/>
       <c r="BH99" s="39"/>
-      <c r="BI99" s="119"/>
-      <c r="BJ99" s="119"/>
-      <c r="BK99" s="119"/>
-      <c r="BL99" s="119"/>
-      <c r="BM99" s="119"/>
-      <c r="BN99" s="119"/>
-      <c r="BO99" s="119"/>
-      <c r="BP99" s="119"/>
-      <c r="BQ99" s="119"/>
-      <c r="BR99" s="119"/>
-      <c r="BS99" s="119"/>
-      <c r="BT99" s="119"/>
-      <c r="BU99" s="119"/>
-      <c r="BV99" s="119"/>
-      <c r="BW99" s="119"/>
+      <c r="BI99" s="114"/>
+      <c r="BJ99" s="114"/>
+      <c r="BK99" s="114"/>
+      <c r="BL99" s="114"/>
+      <c r="BM99" s="114"/>
+      <c r="BN99" s="114"/>
+      <c r="BO99" s="114"/>
+      <c r="BP99" s="114"/>
+      <c r="BQ99" s="114"/>
+      <c r="BR99" s="114"/>
+      <c r="BS99" s="114"/>
+      <c r="BT99" s="114"/>
+      <c r="BU99" s="114"/>
+      <c r="BV99" s="114"/>
+      <c r="BW99" s="114"/>
       <c r="BX99" s="40"/>
       <c r="BY99" s="7"/>
       <c r="BZ99" s="7"/>
@@ -10696,21 +11372,21 @@
     <row r="100" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG100" s="7"/>
       <c r="BH100" s="39"/>
-      <c r="BI100" s="119"/>
-      <c r="BJ100" s="119"/>
-      <c r="BK100" s="119"/>
-      <c r="BL100" s="119"/>
-      <c r="BM100" s="119"/>
-      <c r="BN100" s="119"/>
-      <c r="BO100" s="119"/>
-      <c r="BP100" s="119"/>
-      <c r="BQ100" s="119"/>
-      <c r="BR100" s="119"/>
-      <c r="BS100" s="119"/>
-      <c r="BT100" s="119"/>
-      <c r="BU100" s="119"/>
-      <c r="BV100" s="119"/>
-      <c r="BW100" s="119"/>
+      <c r="BI100" s="114"/>
+      <c r="BJ100" s="114"/>
+      <c r="BK100" s="114"/>
+      <c r="BL100" s="114"/>
+      <c r="BM100" s="114"/>
+      <c r="BN100" s="114"/>
+      <c r="BO100" s="114"/>
+      <c r="BP100" s="114"/>
+      <c r="BQ100" s="114"/>
+      <c r="BR100" s="114"/>
+      <c r="BS100" s="114"/>
+      <c r="BT100" s="114"/>
+      <c r="BU100" s="114"/>
+      <c r="BV100" s="114"/>
+      <c r="BW100" s="114"/>
       <c r="BX100" s="40"/>
       <c r="BY100" s="7"/>
       <c r="BZ100" s="7"/>
@@ -10724,21 +11400,21 @@
     <row r="101" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG101" s="7"/>
       <c r="BH101" s="39"/>
-      <c r="BI101" s="119"/>
-      <c r="BJ101" s="119"/>
-      <c r="BK101" s="119"/>
-      <c r="BL101" s="119"/>
-      <c r="BM101" s="119"/>
-      <c r="BN101" s="119"/>
-      <c r="BO101" s="119"/>
-      <c r="BP101" s="119"/>
-      <c r="BQ101" s="119"/>
-      <c r="BR101" s="119"/>
-      <c r="BS101" s="119"/>
-      <c r="BT101" s="119"/>
-      <c r="BU101" s="119"/>
-      <c r="BV101" s="119"/>
-      <c r="BW101" s="119"/>
+      <c r="BI101" s="114"/>
+      <c r="BJ101" s="114"/>
+      <c r="BK101" s="114"/>
+      <c r="BL101" s="114"/>
+      <c r="BM101" s="114"/>
+      <c r="BN101" s="114"/>
+      <c r="BO101" s="114"/>
+      <c r="BP101" s="114"/>
+      <c r="BQ101" s="114"/>
+      <c r="BR101" s="114"/>
+      <c r="BS101" s="114"/>
+      <c r="BT101" s="114"/>
+      <c r="BU101" s="114"/>
+      <c r="BV101" s="114"/>
+      <c r="BW101" s="114"/>
       <c r="BX101" s="40"/>
       <c r="BY101" s="7"/>
       <c r="BZ101" s="7"/>
@@ -10752,21 +11428,21 @@
     <row r="102" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG102" s="7"/>
       <c r="BH102" s="39"/>
-      <c r="BI102" s="119"/>
-      <c r="BJ102" s="119"/>
-      <c r="BK102" s="119"/>
-      <c r="BL102" s="119"/>
-      <c r="BM102" s="119"/>
-      <c r="BN102" s="119"/>
-      <c r="BO102" s="119"/>
-      <c r="BP102" s="119"/>
-      <c r="BQ102" s="119"/>
-      <c r="BR102" s="119"/>
-      <c r="BS102" s="119"/>
-      <c r="BT102" s="119"/>
-      <c r="BU102" s="119"/>
-      <c r="BV102" s="119"/>
-      <c r="BW102" s="119"/>
+      <c r="BI102" s="114"/>
+      <c r="BJ102" s="114"/>
+      <c r="BK102" s="114"/>
+      <c r="BL102" s="114"/>
+      <c r="BM102" s="114"/>
+      <c r="BN102" s="114"/>
+      <c r="BO102" s="114"/>
+      <c r="BP102" s="114"/>
+      <c r="BQ102" s="114"/>
+      <c r="BR102" s="114"/>
+      <c r="BS102" s="114"/>
+      <c r="BT102" s="114"/>
+      <c r="BU102" s="114"/>
+      <c r="BV102" s="114"/>
+      <c r="BW102" s="114"/>
       <c r="BX102" s="40"/>
       <c r="BY102" s="7"/>
       <c r="BZ102" s="7"/>
@@ -11011,15 +11687,15 @@
       <c r="BM111" s="45"/>
       <c r="BN111" s="45"/>
       <c r="BO111" s="45"/>
-      <c r="BP111" s="139" t="s">
+      <c r="BP111" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="BQ111" s="139"/>
-      <c r="BR111" s="139"/>
-      <c r="BS111" s="139"/>
-      <c r="BT111" s="139"/>
-      <c r="BU111" s="139"/>
-      <c r="BV111" s="139"/>
+      <c r="BQ111" s="133"/>
+      <c r="BR111" s="133"/>
+      <c r="BS111" s="133"/>
+      <c r="BT111" s="133"/>
+      <c r="BU111" s="133"/>
+      <c r="BV111" s="133"/>
       <c r="BW111" s="56"/>
       <c r="BX111" s="11"/>
       <c r="BY111" s="45"/>
@@ -11041,13 +11717,13 @@
       <c r="BM112" s="45"/>
       <c r="BN112" s="45"/>
       <c r="BO112" s="45"/>
-      <c r="BP112" s="139"/>
-      <c r="BQ112" s="139"/>
-      <c r="BR112" s="139"/>
-      <c r="BS112" s="139"/>
-      <c r="BT112" s="139"/>
-      <c r="BU112" s="139"/>
-      <c r="BV112" s="139"/>
+      <c r="BP112" s="133"/>
+      <c r="BQ112" s="133"/>
+      <c r="BR112" s="133"/>
+      <c r="BS112" s="133"/>
+      <c r="BT112" s="133"/>
+      <c r="BU112" s="133"/>
+      <c r="BV112" s="133"/>
       <c r="BW112" s="56"/>
       <c r="BX112" s="11"/>
       <c r="BY112" s="45"/>
@@ -11069,13 +11745,13 @@
       <c r="BM113" s="45"/>
       <c r="BN113" s="45"/>
       <c r="BO113" s="45"/>
-      <c r="BP113" s="139"/>
-      <c r="BQ113" s="139"/>
-      <c r="BR113" s="139"/>
-      <c r="BS113" s="139"/>
-      <c r="BT113" s="139"/>
-      <c r="BU113" s="139"/>
-      <c r="BV113" s="139"/>
+      <c r="BP113" s="133"/>
+      <c r="BQ113" s="133"/>
+      <c r="BR113" s="133"/>
+      <c r="BS113" s="133"/>
+      <c r="BT113" s="133"/>
+      <c r="BU113" s="133"/>
+      <c r="BV113" s="133"/>
       <c r="BW113" s="56"/>
       <c r="BX113" s="11"/>
       <c r="BY113" s="45"/>
@@ -11097,13 +11773,13 @@
       <c r="BM114" s="45"/>
       <c r="BN114" s="45"/>
       <c r="BO114" s="45"/>
-      <c r="BP114" s="139"/>
-      <c r="BQ114" s="139"/>
-      <c r="BR114" s="139"/>
-      <c r="BS114" s="139"/>
-      <c r="BT114" s="139"/>
-      <c r="BU114" s="139"/>
-      <c r="BV114" s="139"/>
+      <c r="BP114" s="133"/>
+      <c r="BQ114" s="133"/>
+      <c r="BR114" s="133"/>
+      <c r="BS114" s="133"/>
+      <c r="BT114" s="133"/>
+      <c r="BU114" s="133"/>
+      <c r="BV114" s="133"/>
       <c r="BW114" s="56"/>
       <c r="BX114" s="11"/>
       <c r="BY114" s="45"/>
@@ -11125,13 +11801,13 @@
       <c r="BM115" s="45"/>
       <c r="BN115" s="45"/>
       <c r="BO115" s="45"/>
-      <c r="BP115" s="139"/>
-      <c r="BQ115" s="139"/>
-      <c r="BR115" s="139"/>
-      <c r="BS115" s="139"/>
-      <c r="BT115" s="139"/>
-      <c r="BU115" s="139"/>
-      <c r="BV115" s="139"/>
+      <c r="BP115" s="133"/>
+      <c r="BQ115" s="133"/>
+      <c r="BR115" s="133"/>
+      <c r="BS115" s="133"/>
+      <c r="BT115" s="133"/>
+      <c r="BU115" s="133"/>
+      <c r="BV115" s="133"/>
       <c r="BW115" s="56"/>
       <c r="BX115" s="11"/>
       <c r="BY115" s="45"/>
@@ -11341,15 +12017,15 @@
     </row>
     <row r="123" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG123" s="7"/>
-      <c r="BH123" s="120" t="s">
+      <c r="BH123" s="90" t="s">
         <v>43</v>
       </c>
       <c r="BI123" s="6"/>
-      <c r="BJ123" s="120" t="s">
+      <c r="BJ123" s="90" t="s">
         <v>44</v>
       </c>
       <c r="BK123" s="6"/>
-      <c r="BL123" s="120" t="s">
+      <c r="BL123" s="90" t="s">
         <v>51</v>
       </c>
       <c r="BM123" s="7"/>
@@ -11359,15 +12035,15 @@
       <c r="BQ123" s="6"/>
       <c r="BR123" s="17"/>
       <c r="BS123" s="6"/>
-      <c r="BT123" s="120" t="s">
+      <c r="BT123" s="90" t="s">
         <v>45</v>
       </c>
       <c r="BU123" s="6"/>
-      <c r="BV123" s="120" t="s">
+      <c r="BV123" s="90" t="s">
         <v>46</v>
       </c>
       <c r="BW123" s="10"/>
-      <c r="BX123" s="120" t="s">
+      <c r="BX123" s="90" t="s">
         <v>50</v>
       </c>
       <c r="BY123" s="7"/>
@@ -11381,11 +12057,11 @@
     </row>
     <row r="124" spans="59:84" ht="25.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="BG124" s="7"/>
-      <c r="BH124" s="120"/>
+      <c r="BH124" s="90"/>
       <c r="BI124" s="6"/>
-      <c r="BJ124" s="120"/>
+      <c r="BJ124" s="90"/>
       <c r="BK124" s="6"/>
-      <c r="BL124" s="120"/>
+      <c r="BL124" s="90"/>
       <c r="BM124" s="34"/>
       <c r="BN124" s="17"/>
       <c r="BP124" s="79" t="s">
@@ -11394,11 +12070,11 @@
       <c r="BQ124" s="6"/>
       <c r="BR124" s="17"/>
       <c r="BS124" s="6"/>
-      <c r="BT124" s="120"/>
+      <c r="BT124" s="90"/>
       <c r="BU124" s="6"/>
-      <c r="BV124" s="120"/>
+      <c r="BV124" s="90"/>
       <c r="BW124" s="10"/>
-      <c r="BX124" s="120"/>
+      <c r="BX124" s="90"/>
       <c r="BY124" s="7"/>
       <c r="BZ124" s="7"/>
       <c r="CA124" s="69"/>
@@ -11410,11 +12086,11 @@
     </row>
     <row r="125" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG125" s="7"/>
-      <c r="BH125" s="120"/>
+      <c r="BH125" s="90"/>
       <c r="BI125" s="6"/>
-      <c r="BJ125" s="120"/>
+      <c r="BJ125" s="90"/>
       <c r="BK125" s="6"/>
-      <c r="BL125" s="120"/>
+      <c r="BL125" s="90"/>
       <c r="BM125" s="7"/>
       <c r="BN125" s="17"/>
       <c r="BO125" s="6"/>
@@ -11422,11 +12098,11 @@
       <c r="BQ125" s="6"/>
       <c r="BR125" s="17"/>
       <c r="BS125" s="6"/>
-      <c r="BT125" s="120"/>
+      <c r="BT125" s="90"/>
       <c r="BU125" s="6"/>
-      <c r="BV125" s="120"/>
+      <c r="BV125" s="90"/>
       <c r="BW125" s="10"/>
-      <c r="BX125" s="120"/>
+      <c r="BX125" s="90"/>
       <c r="BY125" s="7"/>
       <c r="BZ125" s="7"/>
       <c r="CA125" s="69"/>
@@ -11595,11 +12271,11 @@
       <c r="BV131" s="7"/>
       <c r="BW131" s="10"/>
       <c r="BX131" s="7"/>
-      <c r="BY131" s="130" t="s">
+      <c r="BY131" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="BZ131" s="131"/>
-      <c r="CA131" s="132"/>
+      <c r="BZ131" s="125"/>
+      <c r="CA131" s="126"/>
       <c r="CB131" s="69"/>
       <c r="CC131" s="60"/>
       <c r="CD131" s="61"/>
@@ -11614,28 +12290,28 @@
       <c r="BK132" s="7"/>
       <c r="BL132" s="7"/>
       <c r="BM132" s="7"/>
-      <c r="BN132" s="126" t="s">
+      <c r="BN132" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="BO132" s="127"/>
-      <c r="BP132" s="127"/>
-      <c r="BQ132" s="127"/>
-      <c r="BR132" s="128"/>
+      <c r="BO132" s="121"/>
+      <c r="BP132" s="121"/>
+      <c r="BQ132" s="121"/>
+      <c r="BR132" s="122"/>
       <c r="BS132" s="7"/>
       <c r="BT132" s="7"/>
       <c r="BU132" s="7"/>
       <c r="BV132" s="7"/>
       <c r="BW132" s="10"/>
       <c r="BX132" s="7"/>
-      <c r="BY132" s="133"/>
-      <c r="BZ132" s="134"/>
-      <c r="CA132" s="135"/>
+      <c r="BY132" s="127"/>
+      <c r="BZ132" s="128"/>
+      <c r="CA132" s="129"/>
       <c r="CB132" s="69"/>
-      <c r="CC132" s="115" t="s">
+      <c r="CC132" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="CD132" s="116"/>
-      <c r="CE132" s="117"/>
+      <c r="CD132" s="110"/>
+      <c r="CE132" s="111"/>
       <c r="CF132" s="7"/>
     </row>
     <row r="133" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -11646,24 +12322,24 @@
       <c r="BK133" s="7"/>
       <c r="BL133" s="7"/>
       <c r="BM133" s="7"/>
-      <c r="BN133" s="129"/>
-      <c r="BO133" s="127"/>
-      <c r="BP133" s="127"/>
-      <c r="BQ133" s="127"/>
-      <c r="BR133" s="128"/>
+      <c r="BN133" s="123"/>
+      <c r="BO133" s="121"/>
+      <c r="BP133" s="121"/>
+      <c r="BQ133" s="121"/>
+      <c r="BR133" s="122"/>
       <c r="BS133" s="7"/>
       <c r="BT133" s="7"/>
       <c r="BU133" s="7"/>
       <c r="BV133" s="7"/>
       <c r="BW133" s="10"/>
       <c r="BX133" s="7"/>
-      <c r="BY133" s="133"/>
-      <c r="BZ133" s="134"/>
-      <c r="CA133" s="135"/>
+      <c r="BY133" s="127"/>
+      <c r="BZ133" s="128"/>
+      <c r="CA133" s="129"/>
       <c r="CB133" s="69"/>
-      <c r="CC133" s="115"/>
-      <c r="CD133" s="116"/>
-      <c r="CE133" s="117"/>
+      <c r="CC133" s="109"/>
+      <c r="CD133" s="110"/>
+      <c r="CE133" s="111"/>
       <c r="CF133" s="7"/>
     </row>
     <row r="134" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -11674,24 +12350,24 @@
       <c r="BK134" s="7"/>
       <c r="BL134" s="7"/>
       <c r="BM134" s="7"/>
-      <c r="BN134" s="129"/>
-      <c r="BO134" s="127"/>
-      <c r="BP134" s="127"/>
-      <c r="BQ134" s="127"/>
-      <c r="BR134" s="128"/>
+      <c r="BN134" s="123"/>
+      <c r="BO134" s="121"/>
+      <c r="BP134" s="121"/>
+      <c r="BQ134" s="121"/>
+      <c r="BR134" s="122"/>
       <c r="BS134" s="7"/>
       <c r="BT134" s="7"/>
       <c r="BU134" s="7"/>
       <c r="BV134" s="7"/>
       <c r="BW134" s="10"/>
       <c r="BX134" s="7"/>
-      <c r="BY134" s="133"/>
-      <c r="BZ134" s="134"/>
-      <c r="CA134" s="135"/>
+      <c r="BY134" s="127"/>
+      <c r="BZ134" s="128"/>
+      <c r="CA134" s="129"/>
       <c r="CB134" s="69"/>
-      <c r="CC134" s="115"/>
-      <c r="CD134" s="116"/>
-      <c r="CE134" s="117"/>
+      <c r="CC134" s="109"/>
+      <c r="CD134" s="110"/>
+      <c r="CE134" s="111"/>
       <c r="CF134" s="7"/>
     </row>
     <row r="135" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -11702,24 +12378,24 @@
       <c r="BK135" s="7"/>
       <c r="BL135" s="7"/>
       <c r="BM135" s="7"/>
-      <c r="BN135" s="129"/>
-      <c r="BO135" s="127"/>
-      <c r="BP135" s="127"/>
-      <c r="BQ135" s="127"/>
-      <c r="BR135" s="128"/>
+      <c r="BN135" s="123"/>
+      <c r="BO135" s="121"/>
+      <c r="BP135" s="121"/>
+      <c r="BQ135" s="121"/>
+      <c r="BR135" s="122"/>
       <c r="BS135" s="7"/>
       <c r="BT135" s="7"/>
       <c r="BU135" s="7"/>
       <c r="BV135" s="7"/>
       <c r="BW135" s="10"/>
       <c r="BX135" s="7"/>
-      <c r="BY135" s="133"/>
-      <c r="BZ135" s="134"/>
-      <c r="CA135" s="135"/>
+      <c r="BY135" s="127"/>
+      <c r="BZ135" s="128"/>
+      <c r="CA135" s="129"/>
       <c r="CB135" s="69"/>
-      <c r="CC135" s="115"/>
-      <c r="CD135" s="116"/>
-      <c r="CE135" s="117"/>
+      <c r="CC135" s="109"/>
+      <c r="CD135" s="110"/>
+      <c r="CE135" s="111"/>
       <c r="CF135" s="7"/>
     </row>
     <row r="136" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -11730,24 +12406,24 @@
       <c r="BK136" s="7"/>
       <c r="BL136" s="7"/>
       <c r="BM136" s="7"/>
-      <c r="BN136" s="129"/>
-      <c r="BO136" s="127"/>
-      <c r="BP136" s="127"/>
-      <c r="BQ136" s="127"/>
-      <c r="BR136" s="128"/>
+      <c r="BN136" s="123"/>
+      <c r="BO136" s="121"/>
+      <c r="BP136" s="121"/>
+      <c r="BQ136" s="121"/>
+      <c r="BR136" s="122"/>
       <c r="BS136" s="7"/>
       <c r="BT136" s="7"/>
       <c r="BU136" s="7"/>
       <c r="BV136" s="7"/>
       <c r="BW136" s="10"/>
       <c r="BX136" s="7"/>
-      <c r="BY136" s="133"/>
-      <c r="BZ136" s="134"/>
-      <c r="CA136" s="135"/>
+      <c r="BY136" s="127"/>
+      <c r="BZ136" s="128"/>
+      <c r="CA136" s="129"/>
       <c r="CB136" s="69"/>
-      <c r="CC136" s="115"/>
-      <c r="CD136" s="116"/>
-      <c r="CE136" s="117"/>
+      <c r="CC136" s="109"/>
+      <c r="CD136" s="110"/>
+      <c r="CE136" s="111"/>
       <c r="CF136" s="7"/>
     </row>
     <row r="137" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -11769,9 +12445,9 @@
       <c r="BV137" s="7"/>
       <c r="BW137" s="10"/>
       <c r="BX137" s="7"/>
-      <c r="BY137" s="136"/>
-      <c r="BZ137" s="137"/>
-      <c r="CA137" s="138"/>
+      <c r="BY137" s="130"/>
+      <c r="BZ137" s="131"/>
+      <c r="CA137" s="132"/>
       <c r="CB137" s="69"/>
       <c r="CC137" s="63"/>
       <c r="CD137" s="64"/>
@@ -11945,16 +12621,51 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="CR32:CX33"/>
-    <mergeCell ref="DD10:DD24"/>
-    <mergeCell ref="DF26:DK27"/>
-    <mergeCell ref="CQ17:CQ30"/>
-    <mergeCell ref="BY76:CE79"/>
-    <mergeCell ref="BH123:BH125"/>
-    <mergeCell ref="AN63:AX64"/>
-    <mergeCell ref="AN65:AX66"/>
-    <mergeCell ref="AN61:AX62"/>
-    <mergeCell ref="AO57:AO58"/>
+    <mergeCell ref="R62:V62"/>
+    <mergeCell ref="U44:X45"/>
+    <mergeCell ref="U49:X51"/>
+    <mergeCell ref="U52:X54"/>
+    <mergeCell ref="U37:V40"/>
+    <mergeCell ref="U46:W46"/>
+    <mergeCell ref="T40:T49"/>
+    <mergeCell ref="E34:I35"/>
+    <mergeCell ref="N33:P34"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="S34:U34"/>
+    <mergeCell ref="AP45:AT46"/>
+    <mergeCell ref="AE34:AI35"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="AP48:AR49"/>
+    <mergeCell ref="AO49:AO50"/>
+    <mergeCell ref="AM33:AQ34"/>
+    <mergeCell ref="AN67:AX68"/>
+    <mergeCell ref="AP56:AT57"/>
+    <mergeCell ref="AP52:AU53"/>
+    <mergeCell ref="AU37:AV40"/>
+    <mergeCell ref="AT38:AT39"/>
+    <mergeCell ref="AO41:AO42"/>
+    <mergeCell ref="AO43:AO44"/>
+    <mergeCell ref="AU44:AX45"/>
+    <mergeCell ref="AO45:AO46"/>
+    <mergeCell ref="AU46:AW46"/>
+    <mergeCell ref="AO47:AO48"/>
+    <mergeCell ref="AO51:AO52"/>
+    <mergeCell ref="AO53:AO54"/>
+    <mergeCell ref="N60:P61"/>
+    <mergeCell ref="R60:V61"/>
+    <mergeCell ref="O55:O56"/>
+    <mergeCell ref="O57:O58"/>
+    <mergeCell ref="T51:T55"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P48:R49"/>
+    <mergeCell ref="AC39:AC40"/>
+    <mergeCell ref="AK39:AK40"/>
     <mergeCell ref="AO55:AO56"/>
     <mergeCell ref="CC132:CE136"/>
     <mergeCell ref="BL82:BL83"/>
@@ -11971,51 +12682,16 @@
     <mergeCell ref="BY131:CA137"/>
     <mergeCell ref="BP111:BV115"/>
     <mergeCell ref="BH76:BV78"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P48:R49"/>
-    <mergeCell ref="AC39:AC40"/>
-    <mergeCell ref="AK39:AK40"/>
-    <mergeCell ref="N60:P61"/>
-    <mergeCell ref="R60:V61"/>
-    <mergeCell ref="O55:O56"/>
-    <mergeCell ref="O57:O58"/>
-    <mergeCell ref="T51:T55"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="AP48:AR49"/>
-    <mergeCell ref="AO49:AO50"/>
-    <mergeCell ref="AM33:AQ34"/>
-    <mergeCell ref="AN67:AX68"/>
-    <mergeCell ref="AP56:AT57"/>
-    <mergeCell ref="AP52:AU53"/>
-    <mergeCell ref="AU37:AV40"/>
-    <mergeCell ref="AT38:AT39"/>
-    <mergeCell ref="AO41:AO42"/>
-    <mergeCell ref="AO43:AO44"/>
-    <mergeCell ref="AU44:AX45"/>
-    <mergeCell ref="AO45:AO46"/>
-    <mergeCell ref="AU46:AW46"/>
-    <mergeCell ref="AO47:AO48"/>
-    <mergeCell ref="AO51:AO52"/>
-    <mergeCell ref="AO53:AO54"/>
-    <mergeCell ref="E34:I35"/>
-    <mergeCell ref="N33:P34"/>
-    <mergeCell ref="T38:T39"/>
-    <mergeCell ref="S34:U34"/>
-    <mergeCell ref="AP45:AT46"/>
-    <mergeCell ref="AE34:AI35"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="AS34:AU34"/>
-    <mergeCell ref="R62:V62"/>
-    <mergeCell ref="U44:X45"/>
-    <mergeCell ref="U49:X51"/>
-    <mergeCell ref="U52:X54"/>
-    <mergeCell ref="U37:V40"/>
-    <mergeCell ref="U46:W46"/>
-    <mergeCell ref="T40:T49"/>
+    <mergeCell ref="BH123:BH125"/>
+    <mergeCell ref="AN63:AX64"/>
+    <mergeCell ref="AN65:AX66"/>
+    <mergeCell ref="AN61:AX62"/>
+    <mergeCell ref="AO57:AO58"/>
+    <mergeCell ref="CR32:CX33"/>
+    <mergeCell ref="DD10:DD24"/>
+    <mergeCell ref="DF26:DK27"/>
+    <mergeCell ref="CQ17:CQ30"/>
+    <mergeCell ref="BY76:CE79"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report-vis.xlsx
+++ b/report-vis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\! CS\Y2\AI is taking over\cw\ai-garbage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D96942-2F04-4413-99B8-843452D433D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D671CB22-4633-4DCE-818E-3D99FFDF49A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-12645" windowWidth="29040" windowHeight="15840" xr2:uid="{82DBE9BC-AC51-4988-B415-6B972F3134D5}"/>
   </bookViews>
@@ -167,18 +167,6 @@
     <t>Fit Subject-Specific Classifiers</t>
   </si>
   <si>
-    <t>W1</t>
-  </si>
-  <si>
-    <t>W2</t>
-  </si>
-  <si>
-    <t>W7</t>
-  </si>
-  <si>
-    <t>W8</t>
-  </si>
-  <si>
     <t>Test Final Model</t>
   </si>
   <si>
@@ -186,12 +174,6 @@
   </si>
   <si>
     <t>FINE TUNING is performed using the FINE TUNING SAMPLES from the TEST SUBJECT</t>
-  </si>
-  <si>
-    <t>W9</t>
-  </si>
-  <si>
-    <t>W3</t>
   </si>
   <si>
     <t>Fine-Tuning:
@@ -253,36 +235,6 @@
     <t>ST</t>
   </si>
   <si>
-    <r>
-      <t>Initialise Generalised Classifier
-with</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> W</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>general</t>
-    </r>
-  </si>
-  <si>
     <t>TRAINING (SOURCE) SUBJECTS</t>
   </si>
   <si>
@@ -337,12 +289,48 @@
       <t xml:space="preserve">α </t>
     </r>
   </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <r>
+      <t>Initialise Generalised Classifier
+M</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>general</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,15 +431,6 @@
       <b/>
       <u/>
       <sz val="26"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="18"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1146,67 +1125,103 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1221,13 +1236,13 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1287,98 +1302,62 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7390,13 +7369,13 @@
     </row>
     <row r="10" spans="90:116" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="CL10" s="81" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="CM10" s="82" t="s">
-        <v>75</v>
-      </c>
-      <c r="DD10" s="88" t="s">
-        <v>76</v>
+        <v>68</v>
+      </c>
+      <c r="DD10" s="164" t="s">
+        <v>69</v>
       </c>
       <c r="DE10" s="7"/>
       <c r="DF10" s="7"/>
@@ -7415,12 +7394,12 @@
         <v>0.314</v>
       </c>
       <c r="DA11" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="DB11" t="s">
-        <v>79</v>
-      </c>
-      <c r="DD11" s="88"/>
+        <v>72</v>
+      </c>
+      <c r="DD11" s="164"/>
       <c r="DE11" s="7"/>
       <c r="DF11" s="7"/>
       <c r="DG11" s="7"/>
@@ -7443,7 +7422,7 @@
       <c r="DB12">
         <v>0.90300000000000002</v>
       </c>
-      <c r="DD12" s="88"/>
+      <c r="DD12" s="164"/>
       <c r="DE12" s="7"/>
       <c r="DF12" s="7"/>
       <c r="DG12" s="7"/>
@@ -7466,7 +7445,7 @@
       <c r="DB13">
         <v>0.90500000000000003</v>
       </c>
-      <c r="DD13" s="88"/>
+      <c r="DD13" s="164"/>
       <c r="DE13" s="7"/>
       <c r="DF13" s="7"/>
       <c r="DG13" s="7"/>
@@ -7489,7 +7468,7 @@
       <c r="DB14">
         <v>0.90600000000000003</v>
       </c>
-      <c r="DD14" s="88"/>
+      <c r="DD14" s="164"/>
       <c r="DE14" s="7"/>
       <c r="DF14" s="7"/>
       <c r="DG14" s="7"/>
@@ -7524,7 +7503,7 @@
       <c r="DB15">
         <v>0.90900000000000003</v>
       </c>
-      <c r="DD15" s="88"/>
+      <c r="DD15" s="164"/>
       <c r="DE15" s="7"/>
       <c r="DF15" s="7"/>
       <c r="DG15" s="7"/>
@@ -7556,7 +7535,7 @@
       <c r="DB16">
         <v>0.91</v>
       </c>
-      <c r="DD16" s="88"/>
+      <c r="DD16" s="164"/>
       <c r="DE16" s="7"/>
       <c r="DF16" s="7"/>
       <c r="DG16" s="7"/>
@@ -7573,8 +7552,8 @@
       <c r="CM17" s="86">
         <v>0.87</v>
       </c>
-      <c r="CQ17" s="88" t="s">
-        <v>76</v>
+      <c r="CQ17" s="164" t="s">
+        <v>69</v>
       </c>
       <c r="CR17" s="7"/>
       <c r="CS17" s="7"/>
@@ -7590,7 +7569,7 @@
       <c r="DB17">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD17" s="88"/>
+      <c r="DD17" s="164"/>
       <c r="DE17" s="7"/>
       <c r="DF17" s="7"/>
       <c r="DG17" s="7"/>
@@ -7607,7 +7586,7 @@
       <c r="CM18" s="85">
         <v>0.88800000000000001</v>
       </c>
-      <c r="CQ18" s="88"/>
+      <c r="CQ18" s="164"/>
       <c r="CR18" s="7"/>
       <c r="CS18" s="7"/>
       <c r="CT18" s="7"/>
@@ -7622,7 +7601,7 @@
       <c r="DB18">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD18" s="88"/>
+      <c r="DD18" s="164"/>
       <c r="DE18" s="7"/>
       <c r="DF18" s="7"/>
       <c r="DG18" s="7"/>
@@ -7639,7 +7618,7 @@
       <c r="CM19" s="86">
         <v>0.90100000000000002</v>
       </c>
-      <c r="CQ19" s="88"/>
+      <c r="CQ19" s="164"/>
       <c r="CR19" s="7"/>
       <c r="CS19" s="7"/>
       <c r="CT19" s="7"/>
@@ -7654,7 +7633,7 @@
       <c r="DB19">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD19" s="88"/>
+      <c r="DD19" s="164"/>
       <c r="DE19" s="7"/>
       <c r="DF19" s="7"/>
       <c r="DG19" s="7"/>
@@ -7671,7 +7650,7 @@
       <c r="CM20" s="85">
         <v>0.90400000000000003</v>
       </c>
-      <c r="CQ20" s="88"/>
+      <c r="CQ20" s="164"/>
       <c r="CR20" s="7"/>
       <c r="CS20" s="7"/>
       <c r="CT20" s="7"/>
@@ -7686,7 +7665,7 @@
       <c r="DB20">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD20" s="88"/>
+      <c r="DD20" s="164"/>
       <c r="DE20" s="7"/>
       <c r="DF20" s="7"/>
       <c r="DG20" s="7"/>
@@ -7703,7 +7682,7 @@
       <c r="CM21" s="85">
         <v>0.90900000000000003</v>
       </c>
-      <c r="CQ21" s="88"/>
+      <c r="CQ21" s="164"/>
       <c r="CR21" s="7"/>
       <c r="CS21" s="7"/>
       <c r="CT21" s="7"/>
@@ -7718,7 +7697,7 @@
       <c r="DB21">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD21" s="88"/>
+      <c r="DD21" s="164"/>
       <c r="DE21" s="7"/>
       <c r="DF21" s="7"/>
       <c r="DG21" s="7"/>
@@ -7735,7 +7714,7 @@
       <c r="CM22" s="85">
         <v>0.90900000000000003</v>
       </c>
-      <c r="CQ22" s="88"/>
+      <c r="CQ22" s="164"/>
       <c r="CR22" s="7"/>
       <c r="CS22" s="7"/>
       <c r="CT22" s="7"/>
@@ -7750,7 +7729,7 @@
       <c r="DB22">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD22" s="88"/>
+      <c r="DD22" s="164"/>
       <c r="DE22" s="7"/>
       <c r="DF22" s="7"/>
       <c r="DG22" s="7"/>
@@ -7767,7 +7746,7 @@
       <c r="CM23" s="86">
         <v>0.91200000000000003</v>
       </c>
-      <c r="CQ23" s="88"/>
+      <c r="CQ23" s="164"/>
       <c r="CR23" s="7"/>
       <c r="CS23" s="7"/>
       <c r="CT23" s="7"/>
@@ -7782,7 +7761,7 @@
       <c r="DB23">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD23" s="88"/>
+      <c r="DD23" s="164"/>
       <c r="DE23" s="7"/>
       <c r="DF23" s="7"/>
       <c r="DG23" s="7"/>
@@ -7799,7 +7778,7 @@
       <c r="CM24" s="85">
         <v>0.91</v>
       </c>
-      <c r="CQ24" s="88"/>
+      <c r="CQ24" s="164"/>
       <c r="CR24" s="7"/>
       <c r="CS24" s="7"/>
       <c r="CT24" s="7"/>
@@ -7814,7 +7793,7 @@
       <c r="DB24">
         <v>0.91200000000000003</v>
       </c>
-      <c r="DD24" s="88"/>
+      <c r="DD24" s="164"/>
       <c r="DE24" s="7"/>
       <c r="DF24" s="7"/>
       <c r="DG24" s="7"/>
@@ -7831,7 +7810,7 @@
       <c r="CM25" s="86">
         <v>0.91100000000000003</v>
       </c>
-      <c r="CQ25" s="88"/>
+      <c r="CQ25" s="164"/>
       <c r="CR25" s="7"/>
       <c r="CS25" s="7"/>
       <c r="CT25" s="7"/>
@@ -7863,7 +7842,7 @@
       <c r="CM26" s="85">
         <v>0.91100000000000003</v>
       </c>
-      <c r="CQ26" s="88"/>
+      <c r="CQ26" s="164"/>
       <c r="CR26" s="7"/>
       <c r="CS26" s="7"/>
       <c r="CT26" s="7"/>
@@ -7874,14 +7853,14 @@
       <c r="CY26" s="7"/>
       <c r="DD26" s="7"/>
       <c r="DE26" s="7"/>
-      <c r="DF26" s="87" t="s">
-        <v>80</v>
-      </c>
-      <c r="DG26" s="87"/>
-      <c r="DH26" s="87"/>
-      <c r="DI26" s="87"/>
-      <c r="DJ26" s="87"/>
-      <c r="DK26" s="87"/>
+      <c r="DF26" s="163" t="s">
+        <v>73</v>
+      </c>
+      <c r="DG26" s="163"/>
+      <c r="DH26" s="163"/>
+      <c r="DI26" s="163"/>
+      <c r="DJ26" s="163"/>
+      <c r="DK26" s="163"/>
       <c r="DL26" s="7"/>
     </row>
     <row r="27" spans="2:116" x14ac:dyDescent="0.3">
@@ -7891,7 +7870,7 @@
       <c r="CM27" s="85">
         <v>0.90900000000000003</v>
       </c>
-      <c r="CQ27" s="88"/>
+      <c r="CQ27" s="164"/>
       <c r="CR27" s="7"/>
       <c r="CS27" s="7"/>
       <c r="CT27" s="7"/>
@@ -7902,12 +7881,12 @@
       <c r="CY27" s="7"/>
       <c r="DD27" s="7"/>
       <c r="DE27" s="7"/>
-      <c r="DF27" s="87"/>
-      <c r="DG27" s="87"/>
-      <c r="DH27" s="87"/>
-      <c r="DI27" s="87"/>
-      <c r="DJ27" s="87"/>
-      <c r="DK27" s="87"/>
+      <c r="DF27" s="163"/>
+      <c r="DG27" s="163"/>
+      <c r="DH27" s="163"/>
+      <c r="DI27" s="163"/>
+      <c r="DJ27" s="163"/>
+      <c r="DK27" s="163"/>
       <c r="DL27" s="7"/>
     </row>
     <row r="28" spans="2:116" x14ac:dyDescent="0.3">
@@ -7917,7 +7896,7 @@
       <c r="CM28" s="85">
         <v>0.90600000000000003</v>
       </c>
-      <c r="CQ28" s="88"/>
+      <c r="CQ28" s="164"/>
       <c r="CR28" s="7"/>
       <c r="CS28" s="7"/>
       <c r="CT28" s="7"/>
@@ -7934,7 +7913,7 @@
       <c r="CM29" s="86">
         <v>0.90600000000000003</v>
       </c>
-      <c r="CQ29" s="88"/>
+      <c r="CQ29" s="164"/>
       <c r="CR29" s="7"/>
       <c r="CS29" s="7"/>
       <c r="CT29" s="7"/>
@@ -7951,7 +7930,7 @@
       <c r="CM30" s="85">
         <v>0.90800000000000003</v>
       </c>
-      <c r="CQ30" s="88"/>
+      <c r="CQ30" s="164"/>
       <c r="CR30" s="7"/>
       <c r="CS30" s="7"/>
       <c r="CT30" s="7"/>
@@ -8049,15 +8028,15 @@
         <v>0.90800000000000003</v>
       </c>
       <c r="CQ32" s="7"/>
-      <c r="CR32" s="87" t="s">
-        <v>77</v>
-      </c>
-      <c r="CS32" s="87"/>
-      <c r="CT32" s="87"/>
-      <c r="CU32" s="87"/>
-      <c r="CV32" s="87"/>
-      <c r="CW32" s="87"/>
-      <c r="CX32" s="87"/>
+      <c r="CR32" s="163" t="s">
+        <v>70</v>
+      </c>
+      <c r="CS32" s="163"/>
+      <c r="CT32" s="163"/>
+      <c r="CU32" s="163"/>
+      <c r="CV32" s="163"/>
+      <c r="CW32" s="163"/>
+      <c r="CX32" s="163"/>
       <c r="CY32" s="7"/>
     </row>
     <row r="33" spans="2:103" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -8073,11 +8052,11 @@
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="144" t="s">
+      <c r="N33" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="O33" s="147"/>
-      <c r="P33" s="147"/>
+      <c r="O33" s="87"/>
+      <c r="P33" s="87"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
@@ -8098,13 +8077,13 @@
       <c r="AJ33" s="7"/>
       <c r="AK33" s="7"/>
       <c r="AL33" s="7"/>
-      <c r="AM33" s="144" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN33" s="144"/>
-      <c r="AO33" s="144"/>
-      <c r="AP33" s="144"/>
-      <c r="AQ33" s="144"/>
+      <c r="AM33" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN33" s="97"/>
+      <c r="AO33" s="97"/>
+      <c r="AP33" s="97"/>
+      <c r="AQ33" s="97"/>
       <c r="AR33" s="7"/>
       <c r="AS33" s="7"/>
       <c r="AT33" s="7"/>
@@ -8124,40 +8103,40 @@
         <v>0.90800000000000003</v>
       </c>
       <c r="CQ33" s="7"/>
-      <c r="CR33" s="87"/>
-      <c r="CS33" s="87"/>
-      <c r="CT33" s="87"/>
-      <c r="CU33" s="87"/>
-      <c r="CV33" s="87"/>
-      <c r="CW33" s="87"/>
-      <c r="CX33" s="87"/>
+      <c r="CR33" s="163"/>
+      <c r="CS33" s="163"/>
+      <c r="CT33" s="163"/>
+      <c r="CU33" s="163"/>
+      <c r="CV33" s="163"/>
+      <c r="CW33" s="163"/>
+      <c r="CX33" s="163"/>
       <c r="CY33" s="7"/>
     </row>
     <row r="34" spans="2:103" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="156" t="s">
+      <c r="E34" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="150"/>
-      <c r="G34" s="150"/>
-      <c r="H34" s="150"/>
-      <c r="I34" s="150"/>
+      <c r="F34" s="96"/>
+      <c r="G34" s="96"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="96"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="147"/>
-      <c r="O34" s="147"/>
-      <c r="P34" s="147"/>
+      <c r="N34" s="87"/>
+      <c r="O34" s="87"/>
+      <c r="P34" s="87"/>
       <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
-      <c r="S34" s="144" t="s">
+      <c r="S34" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="158"/>
-      <c r="U34" s="158"/>
+      <c r="T34" s="100"/>
+      <c r="U34" s="100"/>
       <c r="V34" s="7"/>
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
@@ -8165,25 +8144,25 @@
       <c r="AB34" s="7"/>
       <c r="AC34" s="7"/>
       <c r="AD34" s="7"/>
-      <c r="AE34" s="156" t="s">
+      <c r="AE34" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="AF34" s="150"/>
-      <c r="AG34" s="150"/>
-      <c r="AH34" s="150"/>
-      <c r="AI34" s="150"/>
+      <c r="AF34" s="96"/>
+      <c r="AG34" s="96"/>
+      <c r="AH34" s="96"/>
+      <c r="AI34" s="96"/>
       <c r="AJ34" s="7"/>
       <c r="AK34" s="7"/>
       <c r="AL34" s="7"/>
-      <c r="AM34" s="144"/>
-      <c r="AN34" s="144"/>
-      <c r="AO34" s="144"/>
-      <c r="AP34" s="144"/>
-      <c r="AQ34" s="144"/>
+      <c r="AM34" s="97"/>
+      <c r="AN34" s="97"/>
+      <c r="AO34" s="97"/>
+      <c r="AP34" s="97"/>
+      <c r="AQ34" s="97"/>
       <c r="AR34" s="7"/>
-      <c r="AS34" s="144"/>
-      <c r="AT34" s="158"/>
-      <c r="AU34" s="158"/>
+      <c r="AS34" s="97"/>
+      <c r="AT34" s="100"/>
+      <c r="AU34" s="100"/>
       <c r="AV34" s="7"/>
       <c r="AW34" s="7"/>
       <c r="AX34" s="7"/>
@@ -8197,11 +8176,11 @@
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="150"/>
-      <c r="F35" s="150"/>
-      <c r="G35" s="150"/>
-      <c r="H35" s="150"/>
-      <c r="I35" s="150"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="96"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="96"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -8221,11 +8200,11 @@
       <c r="AB35" s="7"/>
       <c r="AC35" s="7"/>
       <c r="AD35" s="7"/>
-      <c r="AE35" s="150"/>
-      <c r="AF35" s="150"/>
-      <c r="AG35" s="150"/>
-      <c r="AH35" s="150"/>
-      <c r="AI35" s="150"/>
+      <c r="AE35" s="96"/>
+      <c r="AF35" s="96"/>
+      <c r="AG35" s="96"/>
+      <c r="AH35" s="96"/>
+      <c r="AI35" s="96"/>
       <c r="AJ35" s="7"/>
       <c r="AK35" s="7"/>
       <c r="AL35" s="7"/>
@@ -8325,10 +8304,10 @@
       <c r="T37" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="U37" s="149" t="s">
+      <c r="U37" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="V37" s="149"/>
+      <c r="V37" s="92"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -8353,8 +8332,8 @@
       <c r="AR37" s="7"/>
       <c r="AS37" s="7"/>
       <c r="AT37" s="7"/>
-      <c r="AU37" s="149"/>
-      <c r="AV37" s="149"/>
+      <c r="AU37" s="92"/>
+      <c r="AV37" s="92"/>
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
       <c r="AY37" s="7"/>
@@ -8392,33 +8371,33 @@
       <c r="Q38" s="7"/>
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
-      <c r="T38" s="112" t="s">
+      <c r="T38" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="U38" s="149"/>
-      <c r="V38" s="149"/>
+      <c r="U38" s="92"/>
+      <c r="V38" s="92"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
       <c r="AB38" s="7"/>
       <c r="AC38" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="AD38" s="6"/>
       <c r="AE38" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="AF38" s="6"/>
       <c r="AG38" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="AH38" s="6"/>
       <c r="AI38" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AJ38" s="6"/>
       <c r="AK38" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="AL38" s="7"/>
       <c r="AM38" s="7"/>
@@ -8428,9 +8407,9 @@
       <c r="AQ38" s="7"/>
       <c r="AR38" s="7"/>
       <c r="AS38" s="7"/>
-      <c r="AT38" s="150"/>
-      <c r="AU38" s="149"/>
-      <c r="AV38" s="149"/>
+      <c r="AT38" s="96"/>
+      <c r="AU38" s="92"/>
+      <c r="AV38" s="92"/>
       <c r="AW38" s="7"/>
       <c r="AX38" s="7"/>
       <c r="AY38" s="7"/>
@@ -8458,13 +8437,13 @@
       <c r="Q39" s="7"/>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
-      <c r="T39" s="157"/>
-      <c r="U39" s="149"/>
-      <c r="V39" s="149"/>
+      <c r="T39" s="99"/>
+      <c r="U39" s="92"/>
+      <c r="V39" s="92"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="AB39" s="7"/>
-      <c r="AC39" s="137"/>
+      <c r="AC39" s="118"/>
       <c r="AD39" s="6"/>
       <c r="AE39" s="17"/>
       <c r="AF39" s="6"/>
@@ -8472,7 +8451,7 @@
       <c r="AH39" s="6"/>
       <c r="AI39" s="17"/>
       <c r="AJ39" s="6"/>
-      <c r="AK39" s="112"/>
+      <c r="AK39" s="98"/>
       <c r="AL39" s="7"/>
       <c r="AM39" s="7"/>
       <c r="AN39" s="7"/>
@@ -8481,9 +8460,9 @@
       <c r="AQ39" s="7"/>
       <c r="AR39" s="7"/>
       <c r="AS39" s="7"/>
-      <c r="AT39" s="150"/>
-      <c r="AU39" s="149"/>
-      <c r="AV39" s="149"/>
+      <c r="AT39" s="96"/>
+      <c r="AU39" s="92"/>
+      <c r="AV39" s="92"/>
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
@@ -8513,13 +8492,13 @@
       <c r="Q40" s="7"/>
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
-      <c r="T40" s="164"/>
-      <c r="U40" s="149"/>
-      <c r="V40" s="149"/>
+      <c r="T40" s="94"/>
+      <c r="U40" s="92"/>
+      <c r="V40" s="92"/>
       <c r="W40" s="7"/>
       <c r="X40" s="7"/>
       <c r="AB40" s="7"/>
-      <c r="AC40" s="137"/>
+      <c r="AC40" s="118"/>
       <c r="AD40" s="6"/>
       <c r="AE40" s="17"/>
       <c r="AF40" s="6"/>
@@ -8527,7 +8506,7 @@
       <c r="AH40" s="6"/>
       <c r="AI40" s="17"/>
       <c r="AJ40" s="6"/>
-      <c r="AK40" s="112"/>
+      <c r="AK40" s="98"/>
       <c r="AL40" s="7"/>
       <c r="AM40" s="7"/>
       <c r="AN40" s="7"/>
@@ -8539,8 +8518,8 @@
       <c r="AR40" s="7"/>
       <c r="AS40" s="7"/>
       <c r="AT40" s="7"/>
-      <c r="AU40" s="149"/>
-      <c r="AV40" s="149"/>
+      <c r="AU40" s="92"/>
+      <c r="AV40" s="92"/>
       <c r="AW40" s="7"/>
       <c r="AX40" s="7"/>
       <c r="AY40" s="7"/>
@@ -8563,14 +8542,14 @@
       <c r="L41" s="7"/>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="134" t="s">
+      <c r="O41" s="105" t="s">
         <v>15</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
-      <c r="T41" s="164"/>
+      <c r="T41" s="94"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
@@ -8588,7 +8567,7 @@
       <c r="AL41" s="7"/>
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
-      <c r="AO41" s="143" t="s">
+      <c r="AO41" s="107" t="s">
         <v>15</v>
       </c>
       <c r="AP41" s="7"/>
@@ -8620,12 +8599,12 @@
       <c r="L42" s="7"/>
       <c r="M42" s="7"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="134"/>
+      <c r="O42" s="105"/>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
-      <c r="T42" s="164"/>
+      <c r="T42" s="94"/>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
@@ -8643,7 +8622,7 @@
       <c r="AL42" s="7"/>
       <c r="AM42" s="7"/>
       <c r="AN42" s="7"/>
-      <c r="AO42" s="143"/>
+      <c r="AO42" s="107"/>
       <c r="AP42" s="7"/>
       <c r="AQ42" s="7"/>
       <c r="AR42" s="7"/>
@@ -8673,14 +8652,14 @@
       <c r="L43" s="7"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
-      <c r="O43" s="139" t="s">
+      <c r="O43" s="103" t="s">
         <v>23</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
-      <c r="T43" s="164"/>
+      <c r="T43" s="94"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
@@ -8698,7 +8677,7 @@
       <c r="AL43" s="7"/>
       <c r="AM43" s="7"/>
       <c r="AN43" s="7"/>
-      <c r="AO43" s="151" t="s">
+      <c r="AO43" s="111" t="s">
         <v>23</v>
       </c>
       <c r="AP43" s="7"/>
@@ -8730,18 +8709,18 @@
       <c r="L44" s="7"/>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
-      <c r="O44" s="140"/>
+      <c r="O44" s="104"/>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
-      <c r="T44" s="164"/>
-      <c r="U44" s="161" t="s">
+      <c r="T44" s="94"/>
+      <c r="U44" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="V44" s="153"/>
-      <c r="W44" s="153"/>
-      <c r="X44" s="153"/>
+      <c r="V44" s="89"/>
+      <c r="W44" s="89"/>
+      <c r="X44" s="89"/>
       <c r="AB44" s="7"/>
       <c r="AC44" s="19"/>
       <c r="AD44" s="6"/>
@@ -8755,16 +8734,16 @@
       <c r="AL44" s="7"/>
       <c r="AM44" s="7"/>
       <c r="AN44" s="7"/>
-      <c r="AO44" s="152"/>
+      <c r="AO44" s="112"/>
       <c r="AP44" s="7"/>
       <c r="AQ44" s="7"/>
       <c r="AR44" s="7"/>
       <c r="AS44" s="7"/>
       <c r="AT44" s="7"/>
-      <c r="AU44" s="153"/>
-      <c r="AV44" s="153"/>
-      <c r="AW44" s="153"/>
-      <c r="AX44" s="153"/>
+      <c r="AU44" s="89"/>
+      <c r="AV44" s="89"/>
+      <c r="AW44" s="89"/>
+      <c r="AX44" s="89"/>
       <c r="AY44" s="7"/>
       <c r="AZ44" s="7"/>
       <c r="BA44" s="7"/>
@@ -8785,18 +8764,18 @@
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="139" t="s">
+      <c r="O45" s="103" t="s">
         <v>22</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
-      <c r="T45" s="164"/>
-      <c r="U45" s="161"/>
-      <c r="V45" s="153"/>
-      <c r="W45" s="153"/>
-      <c r="X45" s="153"/>
+      <c r="T45" s="94"/>
+      <c r="U45" s="88"/>
+      <c r="V45" s="89"/>
+      <c r="W45" s="89"/>
+      <c r="X45" s="89"/>
       <c r="AB45" s="7"/>
       <c r="AC45" s="19"/>
       <c r="AD45" s="6"/>
@@ -8810,20 +8789,20 @@
       <c r="AL45" s="7"/>
       <c r="AM45" s="7"/>
       <c r="AN45" s="7"/>
-      <c r="AO45" s="151" t="s">
+      <c r="AO45" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="AP45" s="159" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ45" s="160"/>
-      <c r="AR45" s="160"/>
-      <c r="AS45" s="160"/>
-      <c r="AT45" s="160"/>
-      <c r="AU45" s="153"/>
-      <c r="AV45" s="153"/>
-      <c r="AW45" s="153"/>
-      <c r="AX45" s="153"/>
+      <c r="AP45" s="101" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ45" s="102"/>
+      <c r="AR45" s="102"/>
+      <c r="AS45" s="102"/>
+      <c r="AT45" s="102"/>
+      <c r="AU45" s="89"/>
+      <c r="AV45" s="89"/>
+      <c r="AW45" s="89"/>
+      <c r="AX45" s="89"/>
       <c r="AY45" s="7"/>
       <c r="AZ45" s="7"/>
       <c r="BA45" s="7"/>
@@ -8854,17 +8833,17 @@
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="140"/>
+      <c r="O46" s="104"/>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
-      <c r="T46" s="164"/>
-      <c r="U46" s="163" t="s">
+      <c r="T46" s="94"/>
+      <c r="U46" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="V46" s="147"/>
-      <c r="W46" s="147"/>
+      <c r="V46" s="87"/>
+      <c r="W46" s="87"/>
       <c r="X46" s="7"/>
       <c r="AB46" s="7"/>
       <c r="AC46" s="20">
@@ -8889,15 +8868,15 @@
       <c r="AL46" s="7"/>
       <c r="AM46" s="7"/>
       <c r="AN46" s="7"/>
-      <c r="AO46" s="152"/>
-      <c r="AP46" s="159"/>
-      <c r="AQ46" s="160"/>
-      <c r="AR46" s="160"/>
-      <c r="AS46" s="160"/>
-      <c r="AT46" s="160"/>
-      <c r="AU46" s="147"/>
-      <c r="AV46" s="147"/>
-      <c r="AW46" s="147"/>
+      <c r="AO46" s="112"/>
+      <c r="AP46" s="101"/>
+      <c r="AQ46" s="102"/>
+      <c r="AR46" s="102"/>
+      <c r="AS46" s="102"/>
+      <c r="AT46" s="102"/>
+      <c r="AU46" s="87"/>
+      <c r="AV46" s="87"/>
+      <c r="AW46" s="87"/>
       <c r="AX46" s="7"/>
       <c r="AY46" s="7"/>
       <c r="AZ46" s="7"/>
@@ -8929,14 +8908,14 @@
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="134" t="s">
+      <c r="O47" s="105" t="s">
         <v>21</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7"/>
       <c r="S47" s="7"/>
-      <c r="T47" s="164"/>
+      <c r="T47" s="94"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
@@ -8964,7 +8943,7 @@
       <c r="AL47" s="7"/>
       <c r="AM47" s="7"/>
       <c r="AN47" s="7"/>
-      <c r="AO47" s="143" t="s">
+      <c r="AO47" s="107" t="s">
         <v>21</v>
       </c>
       <c r="AP47" s="7"/>
@@ -9006,14 +8985,14 @@
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="134"/>
-      <c r="P48" s="135" t="s">
+      <c r="O48" s="105"/>
+      <c r="P48" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="Q48" s="136"/>
-      <c r="R48" s="136"/>
+      <c r="Q48" s="106"/>
+      <c r="R48" s="106"/>
       <c r="S48" s="7"/>
-      <c r="T48" s="164"/>
+      <c r="T48" s="94"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
@@ -9041,10 +9020,10 @@
       <c r="AL48" s="7"/>
       <c r="AM48" s="7"/>
       <c r="AN48" s="7"/>
-      <c r="AO48" s="143"/>
-      <c r="AP48" s="135"/>
-      <c r="AQ48" s="136"/>
-      <c r="AR48" s="136"/>
+      <c r="AO48" s="107"/>
+      <c r="AP48" s="91"/>
+      <c r="AQ48" s="106"/>
+      <c r="AR48" s="106"/>
       <c r="AS48" s="7"/>
       <c r="AT48" s="7"/>
       <c r="AU48" s="7"/>
@@ -9071,20 +9050,20 @@
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="134" t="s">
+      <c r="O49" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="P49" s="136"/>
-      <c r="Q49" s="136"/>
-      <c r="R49" s="136"/>
+      <c r="P49" s="106"/>
+      <c r="Q49" s="106"/>
+      <c r="R49" s="106"/>
       <c r="S49" s="7"/>
-      <c r="T49" s="164"/>
-      <c r="U49" s="162" t="s">
+      <c r="T49" s="94"/>
+      <c r="U49" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="V49" s="135"/>
-      <c r="W49" s="135"/>
-      <c r="X49" s="135"/>
+      <c r="V49" s="91"/>
+      <c r="W49" s="91"/>
+      <c r="X49" s="91"/>
       <c r="AB49" s="7"/>
       <c r="AC49" s="19"/>
       <c r="AD49" s="6"/>
@@ -9098,12 +9077,12 @@
       <c r="AL49" s="7"/>
       <c r="AM49" s="7"/>
       <c r="AN49" s="7"/>
-      <c r="AO49" s="143" t="s">
+      <c r="AO49" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AP49" s="136"/>
-      <c r="AQ49" s="136"/>
-      <c r="AR49" s="136"/>
+      <c r="AP49" s="106"/>
+      <c r="AQ49" s="106"/>
+      <c r="AR49" s="106"/>
       <c r="AS49" s="7"/>
       <c r="AT49" s="7"/>
       <c r="AU49" s="72"/>
@@ -9130,16 +9109,16 @@
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="134"/>
+      <c r="O50" s="105"/>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
       <c r="T50" s="12"/>
-      <c r="U50" s="162"/>
-      <c r="V50" s="135"/>
-      <c r="W50" s="135"/>
-      <c r="X50" s="135"/>
+      <c r="U50" s="90"/>
+      <c r="V50" s="91"/>
+      <c r="W50" s="91"/>
+      <c r="X50" s="91"/>
       <c r="AB50" s="7"/>
       <c r="AC50" s="19"/>
       <c r="AD50" s="6"/>
@@ -9153,7 +9132,7 @@
       <c r="AL50" s="7"/>
       <c r="AM50" s="7"/>
       <c r="AN50" s="7"/>
-      <c r="AO50" s="143"/>
+      <c r="AO50" s="107"/>
       <c r="AP50" s="7"/>
       <c r="AQ50" s="7"/>
       <c r="AR50" s="7"/>
@@ -9183,18 +9162,18 @@
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="139" t="s">
+      <c r="O51" s="103" t="s">
         <v>20</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
       <c r="S51" s="7"/>
-      <c r="T51" s="141"/>
-      <c r="U51" s="162"/>
-      <c r="V51" s="135"/>
-      <c r="W51" s="135"/>
-      <c r="X51" s="135"/>
+      <c r="T51" s="116"/>
+      <c r="U51" s="90"/>
+      <c r="V51" s="91"/>
+      <c r="W51" s="91"/>
+      <c r="X51" s="91"/>
       <c r="AB51" s="7"/>
       <c r="AC51" s="19"/>
       <c r="AD51" s="6"/>
@@ -9208,7 +9187,7 @@
       <c r="AL51" s="7"/>
       <c r="AM51" s="7"/>
       <c r="AN51" s="7"/>
-      <c r="AO51" s="154" t="s">
+      <c r="AO51" s="113" t="s">
         <v>20</v>
       </c>
       <c r="AP51" s="7"/>
@@ -9240,18 +9219,18 @@
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="140"/>
+      <c r="O52" s="104"/>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
-      <c r="T52" s="141"/>
-      <c r="U52" s="162" t="s">
+      <c r="T52" s="116"/>
+      <c r="U52" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="V52" s="135"/>
-      <c r="W52" s="135"/>
-      <c r="X52" s="135"/>
+      <c r="V52" s="91"/>
+      <c r="W52" s="91"/>
+      <c r="X52" s="91"/>
       <c r="AB52" s="7"/>
       <c r="AC52" s="19"/>
       <c r="AD52" s="6"/>
@@ -9265,15 +9244,15 @@
       <c r="AL52" s="7"/>
       <c r="AM52" s="7"/>
       <c r="AN52" s="7"/>
-      <c r="AO52" s="155"/>
-      <c r="AP52" s="148" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ52" s="149"/>
-      <c r="AR52" s="149"/>
-      <c r="AS52" s="149"/>
-      <c r="AT52" s="149"/>
-      <c r="AU52" s="149"/>
+      <c r="AO52" s="114"/>
+      <c r="AP52" s="110" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ52" s="92"/>
+      <c r="AR52" s="92"/>
+      <c r="AS52" s="92"/>
+      <c r="AT52" s="92"/>
+      <c r="AU52" s="92"/>
       <c r="AV52" s="72"/>
       <c r="AW52" s="72"/>
       <c r="AX52" s="72"/>
@@ -9297,18 +9276,18 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="139" t="s">
+      <c r="O53" s="103" t="s">
         <v>16</v>
       </c>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
       <c r="R53" s="7"/>
       <c r="S53" s="7"/>
-      <c r="T53" s="141"/>
-      <c r="U53" s="162"/>
-      <c r="V53" s="135"/>
-      <c r="W53" s="135"/>
-      <c r="X53" s="135"/>
+      <c r="T53" s="116"/>
+      <c r="U53" s="90"/>
+      <c r="V53" s="91"/>
+      <c r="W53" s="91"/>
+      <c r="X53" s="91"/>
       <c r="AB53" s="7"/>
       <c r="AC53" s="19"/>
       <c r="AD53" s="6"/>
@@ -9322,15 +9301,15 @@
       <c r="AL53" s="7"/>
       <c r="AM53" s="7"/>
       <c r="AN53" s="7"/>
-      <c r="AO53" s="154" t="s">
+      <c r="AO53" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="AP53" s="148"/>
-      <c r="AQ53" s="149"/>
-      <c r="AR53" s="149"/>
-      <c r="AS53" s="149"/>
-      <c r="AT53" s="149"/>
-      <c r="AU53" s="149"/>
+      <c r="AP53" s="110"/>
+      <c r="AQ53" s="92"/>
+      <c r="AR53" s="92"/>
+      <c r="AS53" s="92"/>
+      <c r="AT53" s="92"/>
+      <c r="AU53" s="92"/>
       <c r="AV53" s="72"/>
       <c r="AW53" s="72"/>
       <c r="AX53" s="72"/>
@@ -9354,16 +9333,16 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="140"/>
+      <c r="O54" s="104"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="7"/>
       <c r="R54" s="7"/>
       <c r="S54" s="7"/>
-      <c r="T54" s="141"/>
-      <c r="U54" s="162"/>
-      <c r="V54" s="135"/>
-      <c r="W54" s="135"/>
-      <c r="X54" s="135"/>
+      <c r="T54" s="116"/>
+      <c r="U54" s="90"/>
+      <c r="V54" s="91"/>
+      <c r="W54" s="91"/>
+      <c r="X54" s="91"/>
       <c r="AB54" s="7"/>
       <c r="AC54" s="21"/>
       <c r="AD54" s="6"/>
@@ -9377,7 +9356,7 @@
       <c r="AL54" s="7"/>
       <c r="AM54" s="7"/>
       <c r="AN54" s="7"/>
-      <c r="AO54" s="155"/>
+      <c r="AO54" s="114"/>
       <c r="AP54" s="71"/>
       <c r="AQ54" s="70"/>
       <c r="AR54" s="70"/>
@@ -9407,14 +9386,14 @@
       <c r="L55" s="7"/>
       <c r="M55" s="7"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="139" t="s">
+      <c r="O55" s="103" t="s">
         <v>17</v>
       </c>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
       <c r="S55" s="7"/>
-      <c r="T55" s="142"/>
+      <c r="T55" s="117"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
       <c r="W55" s="7"/>
@@ -9432,7 +9411,7 @@
       <c r="AL55" s="7"/>
       <c r="AM55" s="7"/>
       <c r="AN55" s="7"/>
-      <c r="AO55" s="106" t="s">
+      <c r="AO55" s="119" t="s">
         <v>17</v>
       </c>
       <c r="AP55" s="7"/>
@@ -9464,7 +9443,7 @@
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="140"/>
+      <c r="O56" s="104"/>
       <c r="P56" s="7"/>
       <c r="Q56" s="7"/>
       <c r="R56" s="7"/>
@@ -9487,14 +9466,14 @@
       <c r="AL56" s="7"/>
       <c r="AM56" s="7"/>
       <c r="AN56" s="7"/>
-      <c r="AO56" s="108"/>
-      <c r="AP56" s="148" t="s">
-        <v>66</v>
-      </c>
-      <c r="AQ56" s="149"/>
-      <c r="AR56" s="149"/>
-      <c r="AS56" s="149"/>
-      <c r="AT56" s="149"/>
+      <c r="AO56" s="120"/>
+      <c r="AP56" s="110" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ56" s="92"/>
+      <c r="AR56" s="92"/>
+      <c r="AS56" s="92"/>
+      <c r="AT56" s="92"/>
       <c r="AU56" s="7"/>
       <c r="AV56" s="7"/>
       <c r="AW56" s="7"/>
@@ -9529,7 +9508,7 @@
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="139" t="s">
+      <c r="O57" s="103" t="s">
         <v>18</v>
       </c>
       <c r="P57" s="7"/>
@@ -9543,35 +9522,35 @@
       <c r="X57" s="7"/>
       <c r="AB57" s="7"/>
       <c r="AC57" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="AD57" s="6"/>
       <c r="AE57" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AF57" s="6"/>
       <c r="AG57" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="AH57" s="6"/>
       <c r="AI57" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="AJ57" s="6"/>
       <c r="AK57" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AL57" s="7"/>
       <c r="AM57" s="7"/>
       <c r="AN57" s="7"/>
-      <c r="AO57" s="106" t="s">
+      <c r="AO57" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="AP57" s="148"/>
-      <c r="AQ57" s="149"/>
-      <c r="AR57" s="149"/>
-      <c r="AS57" s="149"/>
-      <c r="AT57" s="149"/>
+      <c r="AP57" s="110"/>
+      <c r="AQ57" s="92"/>
+      <c r="AR57" s="92"/>
+      <c r="AS57" s="92"/>
+      <c r="AT57" s="92"/>
       <c r="AU57" s="7"/>
       <c r="AV57" s="7"/>
       <c r="AW57" s="7"/>
@@ -9596,7 +9575,7 @@
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="140"/>
+      <c r="O58" s="104"/>
       <c r="P58" s="7"/>
       <c r="Q58" s="7"/>
       <c r="R58" s="7"/>
@@ -9619,7 +9598,7 @@
       <c r="AL58" s="7"/>
       <c r="AM58" s="7"/>
       <c r="AN58" s="7"/>
-      <c r="AO58" s="107"/>
+      <c r="AO58" s="162"/>
       <c r="AP58" s="7"/>
       <c r="AQ58" s="7"/>
       <c r="AR58" s="7"/>
@@ -9701,19 +9680,19 @@
       <c r="K60" s="3"/>
       <c r="L60" s="7"/>
       <c r="M60" s="7"/>
-      <c r="N60" s="138" t="s">
+      <c r="N60" s="115" t="s">
         <v>33</v>
       </c>
-      <c r="O60" s="138"/>
-      <c r="P60" s="138"/>
+      <c r="O60" s="115"/>
+      <c r="P60" s="115"/>
       <c r="Q60" s="7"/>
-      <c r="R60" s="138" t="s">
+      <c r="R60" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="S60" s="138"/>
-      <c r="T60" s="138"/>
-      <c r="U60" s="138"/>
-      <c r="V60" s="138"/>
+      <c r="S60" s="115"/>
+      <c r="T60" s="115"/>
+      <c r="U60" s="115"/>
+      <c r="V60" s="115"/>
       <c r="W60" s="7"/>
       <c r="X60" s="7"/>
       <c r="AB60" s="7"/>
@@ -9758,15 +9737,15 @@
       <c r="K61" s="3"/>
       <c r="L61" s="7"/>
       <c r="M61" s="7"/>
-      <c r="N61" s="138"/>
-      <c r="O61" s="138"/>
-      <c r="P61" s="138"/>
+      <c r="N61" s="115"/>
+      <c r="O61" s="115"/>
+      <c r="P61" s="115"/>
       <c r="Q61" s="7"/>
-      <c r="R61" s="138"/>
-      <c r="S61" s="138"/>
-      <c r="T61" s="138"/>
-      <c r="U61" s="138"/>
-      <c r="V61" s="138"/>
+      <c r="R61" s="115"/>
+      <c r="S61" s="115"/>
+      <c r="T61" s="115"/>
+      <c r="U61" s="115"/>
+      <c r="V61" s="115"/>
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
       <c r="AB61" s="7"/>
@@ -9781,19 +9760,19 @@
       <c r="AK61" s="17"/>
       <c r="AL61" s="7"/>
       <c r="AM61" s="7"/>
-      <c r="AN61" s="100" t="s">
+      <c r="AN61" s="156" t="s">
         <v>37</v>
       </c>
-      <c r="AO61" s="101"/>
-      <c r="AP61" s="101"/>
-      <c r="AQ61" s="101"/>
-      <c r="AR61" s="101"/>
-      <c r="AS61" s="101"/>
-      <c r="AT61" s="101"/>
-      <c r="AU61" s="101"/>
-      <c r="AV61" s="101"/>
-      <c r="AW61" s="101"/>
-      <c r="AX61" s="102"/>
+      <c r="AO61" s="157"/>
+      <c r="AP61" s="157"/>
+      <c r="AQ61" s="157"/>
+      <c r="AR61" s="157"/>
+      <c r="AS61" s="157"/>
+      <c r="AT61" s="157"/>
+      <c r="AU61" s="157"/>
+      <c r="AV61" s="157"/>
+      <c r="AW61" s="157"/>
+      <c r="AX61" s="158"/>
       <c r="AY61" s="7"/>
       <c r="AZ61" s="7"/>
       <c r="BA61" s="7"/>
@@ -9817,13 +9796,13 @@
       <c r="O62" s="7"/>
       <c r="P62" s="7"/>
       <c r="Q62" s="7"/>
-      <c r="R62" s="147" t="s">
+      <c r="R62" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="S62" s="147"/>
-      <c r="T62" s="147"/>
-      <c r="U62" s="147"/>
-      <c r="V62" s="147"/>
+      <c r="S62" s="87"/>
+      <c r="T62" s="87"/>
+      <c r="U62" s="87"/>
+      <c r="V62" s="87"/>
       <c r="W62" s="7"/>
       <c r="X62" s="7"/>
       <c r="AB62" s="7"/>
@@ -9838,17 +9817,17 @@
       <c r="AK62" s="17"/>
       <c r="AL62" s="7"/>
       <c r="AM62" s="7"/>
-      <c r="AN62" s="103"/>
-      <c r="AO62" s="104"/>
-      <c r="AP62" s="104"/>
-      <c r="AQ62" s="104"/>
-      <c r="AR62" s="104"/>
-      <c r="AS62" s="104"/>
-      <c r="AT62" s="104"/>
-      <c r="AU62" s="104"/>
-      <c r="AV62" s="104"/>
-      <c r="AW62" s="104"/>
-      <c r="AX62" s="105"/>
+      <c r="AN62" s="159"/>
+      <c r="AO62" s="160"/>
+      <c r="AP62" s="160"/>
+      <c r="AQ62" s="160"/>
+      <c r="AR62" s="160"/>
+      <c r="AS62" s="160"/>
+      <c r="AT62" s="160"/>
+      <c r="AU62" s="160"/>
+      <c r="AV62" s="160"/>
+      <c r="AW62" s="160"/>
+      <c r="AX62" s="161"/>
       <c r="AY62" s="7"/>
       <c r="AZ62" s="7"/>
       <c r="BA62" s="7"/>
@@ -9891,19 +9870,19 @@
       <c r="AK63" s="17"/>
       <c r="AL63" s="7"/>
       <c r="AM63" s="7"/>
-      <c r="AN63" s="91" t="s">
-        <v>49</v>
-      </c>
-      <c r="AO63" s="92"/>
-      <c r="AP63" s="92"/>
-      <c r="AQ63" s="92"/>
-      <c r="AR63" s="92"/>
-      <c r="AS63" s="92"/>
-      <c r="AT63" s="92"/>
-      <c r="AU63" s="92"/>
-      <c r="AV63" s="92"/>
-      <c r="AW63" s="92"/>
-      <c r="AX63" s="93"/>
+      <c r="AN63" s="147" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO63" s="148"/>
+      <c r="AP63" s="148"/>
+      <c r="AQ63" s="148"/>
+      <c r="AR63" s="148"/>
+      <c r="AS63" s="148"/>
+      <c r="AT63" s="148"/>
+      <c r="AU63" s="148"/>
+      <c r="AV63" s="148"/>
+      <c r="AW63" s="148"/>
+      <c r="AX63" s="149"/>
       <c r="AY63" s="7"/>
       <c r="AZ63" s="7"/>
       <c r="BA63" s="7"/>
@@ -9966,17 +9945,17 @@
       </c>
       <c r="AL64" s="7"/>
       <c r="AM64" s="7"/>
-      <c r="AN64" s="91"/>
-      <c r="AO64" s="92"/>
-      <c r="AP64" s="92"/>
-      <c r="AQ64" s="92"/>
-      <c r="AR64" s="92"/>
-      <c r="AS64" s="92"/>
-      <c r="AT64" s="92"/>
-      <c r="AU64" s="92"/>
-      <c r="AV64" s="92"/>
-      <c r="AW64" s="92"/>
-      <c r="AX64" s="93"/>
+      <c r="AN64" s="147"/>
+      <c r="AO64" s="148"/>
+      <c r="AP64" s="148"/>
+      <c r="AQ64" s="148"/>
+      <c r="AR64" s="148"/>
+      <c r="AS64" s="148"/>
+      <c r="AT64" s="148"/>
+      <c r="AU64" s="148"/>
+      <c r="AV64" s="148"/>
+      <c r="AW64" s="148"/>
+      <c r="AX64" s="149"/>
       <c r="AY64" s="7"/>
       <c r="AZ64" s="7"/>
       <c r="BA64" s="7"/>
@@ -10039,19 +10018,19 @@
       </c>
       <c r="AL65" s="7"/>
       <c r="AM65" s="7"/>
-      <c r="AN65" s="94" t="s">
+      <c r="AN65" s="150" t="s">
         <v>38</v>
       </c>
-      <c r="AO65" s="95"/>
-      <c r="AP65" s="95"/>
-      <c r="AQ65" s="95"/>
-      <c r="AR65" s="95"/>
-      <c r="AS65" s="95"/>
-      <c r="AT65" s="95"/>
-      <c r="AU65" s="95"/>
-      <c r="AV65" s="95"/>
-      <c r="AW65" s="95"/>
-      <c r="AX65" s="96"/>
+      <c r="AO65" s="151"/>
+      <c r="AP65" s="151"/>
+      <c r="AQ65" s="151"/>
+      <c r="AR65" s="151"/>
+      <c r="AS65" s="151"/>
+      <c r="AT65" s="151"/>
+      <c r="AU65" s="151"/>
+      <c r="AV65" s="151"/>
+      <c r="AW65" s="151"/>
+      <c r="AX65" s="152"/>
       <c r="AY65" s="7"/>
       <c r="AZ65" s="7"/>
       <c r="BA65" s="7"/>
@@ -10114,17 +10093,17 @@
       </c>
       <c r="AL66" s="7"/>
       <c r="AM66" s="7"/>
-      <c r="AN66" s="97"/>
-      <c r="AO66" s="98"/>
-      <c r="AP66" s="98"/>
-      <c r="AQ66" s="98"/>
-      <c r="AR66" s="98"/>
-      <c r="AS66" s="98"/>
-      <c r="AT66" s="98"/>
-      <c r="AU66" s="98"/>
-      <c r="AV66" s="98"/>
-      <c r="AW66" s="98"/>
-      <c r="AX66" s="99"/>
+      <c r="AN66" s="153"/>
+      <c r="AO66" s="154"/>
+      <c r="AP66" s="154"/>
+      <c r="AQ66" s="154"/>
+      <c r="AR66" s="154"/>
+      <c r="AS66" s="154"/>
+      <c r="AT66" s="154"/>
+      <c r="AU66" s="154"/>
+      <c r="AV66" s="154"/>
+      <c r="AW66" s="154"/>
+      <c r="AX66" s="155"/>
       <c r="AY66" s="7"/>
       <c r="AZ66" s="7"/>
       <c r="BA66" s="7"/>
@@ -10167,19 +10146,19 @@
       <c r="AK67" s="17"/>
       <c r="AL67" s="7"/>
       <c r="AM67" s="7"/>
-      <c r="AN67" s="145" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO67" s="146"/>
-      <c r="AP67" s="146"/>
-      <c r="AQ67" s="146"/>
-      <c r="AR67" s="146"/>
-      <c r="AS67" s="146"/>
-      <c r="AT67" s="146"/>
-      <c r="AU67" s="146"/>
-      <c r="AV67" s="146"/>
-      <c r="AW67" s="146"/>
-      <c r="AX67" s="146"/>
+      <c r="AN67" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO67" s="109"/>
+      <c r="AP67" s="109"/>
+      <c r="AQ67" s="109"/>
+      <c r="AR67" s="109"/>
+      <c r="AS67" s="109"/>
+      <c r="AT67" s="109"/>
+      <c r="AU67" s="109"/>
+      <c r="AV67" s="109"/>
+      <c r="AW67" s="109"/>
+      <c r="AX67" s="109"/>
       <c r="AY67" s="7"/>
       <c r="AZ67" s="7"/>
       <c r="BA67" s="7"/>
@@ -10222,17 +10201,17 @@
       <c r="AK68" s="17"/>
       <c r="AL68" s="7"/>
       <c r="AM68" s="7"/>
-      <c r="AN68" s="147"/>
-      <c r="AO68" s="147"/>
-      <c r="AP68" s="147"/>
-      <c r="AQ68" s="147"/>
-      <c r="AR68" s="147"/>
-      <c r="AS68" s="147"/>
-      <c r="AT68" s="147"/>
-      <c r="AU68" s="147"/>
-      <c r="AV68" s="147"/>
-      <c r="AW68" s="147"/>
-      <c r="AX68" s="147"/>
+      <c r="AN68" s="87"/>
+      <c r="AO68" s="87"/>
+      <c r="AP68" s="87"/>
+      <c r="AQ68" s="87"/>
+      <c r="AR68" s="87"/>
+      <c r="AS68" s="87"/>
+      <c r="AT68" s="87"/>
+      <c r="AU68" s="87"/>
+      <c r="AV68" s="87"/>
+      <c r="AW68" s="87"/>
+      <c r="AX68" s="87"/>
       <c r="AY68" s="7"/>
       <c r="AZ68" s="7"/>
       <c r="BA68" s="7"/>
@@ -10544,7 +10523,7 @@
       <c r="AB75" s="7"/>
       <c r="AC75" s="23"/>
       <c r="AD75" s="16" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="AE75" s="16"/>
       <c r="AF75" s="27"/>
@@ -10576,7 +10555,7 @@
       <c r="AB76" s="7"/>
       <c r="AC76" s="24"/>
       <c r="AD76" s="28" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="AE76" s="28"/>
       <c r="AF76" s="29"/>
@@ -10604,34 +10583,34 @@
       <c r="BB76" s="7"/>
       <c r="BC76" s="7"/>
       <c r="BG76" s="7"/>
-      <c r="BH76" s="89" t="s">
-        <v>72</v>
-      </c>
-      <c r="BI76" s="89"/>
-      <c r="BJ76" s="89"/>
-      <c r="BK76" s="89"/>
-      <c r="BL76" s="89"/>
-      <c r="BM76" s="89"/>
-      <c r="BN76" s="89"/>
-      <c r="BO76" s="89"/>
-      <c r="BP76" s="89"/>
-      <c r="BQ76" s="89"/>
-      <c r="BR76" s="89"/>
-      <c r="BS76" s="89"/>
-      <c r="BT76" s="89"/>
-      <c r="BU76" s="89"/>
-      <c r="BV76" s="89"/>
+      <c r="BH76" s="146" t="s">
+        <v>65</v>
+      </c>
+      <c r="BI76" s="146"/>
+      <c r="BJ76" s="146"/>
+      <c r="BK76" s="146"/>
+      <c r="BL76" s="146"/>
+      <c r="BM76" s="146"/>
+      <c r="BN76" s="146"/>
+      <c r="BO76" s="146"/>
+      <c r="BP76" s="146"/>
+      <c r="BQ76" s="146"/>
+      <c r="BR76" s="146"/>
+      <c r="BS76" s="146"/>
+      <c r="BT76" s="146"/>
+      <c r="BU76" s="146"/>
+      <c r="BV76" s="146"/>
       <c r="BW76" s="10"/>
       <c r="BX76" s="80"/>
-      <c r="BY76" s="89" t="s">
-        <v>73</v>
-      </c>
-      <c r="BZ76" s="89"/>
-      <c r="CA76" s="89"/>
-      <c r="CB76" s="89"/>
-      <c r="CC76" s="89"/>
-      <c r="CD76" s="89"/>
-      <c r="CE76" s="89"/>
+      <c r="BY76" s="146" t="s">
+        <v>66</v>
+      </c>
+      <c r="BZ76" s="146"/>
+      <c r="CA76" s="146"/>
+      <c r="CB76" s="146"/>
+      <c r="CC76" s="146"/>
+      <c r="CD76" s="146"/>
+      <c r="CE76" s="146"/>
       <c r="CF76" s="80"/>
     </row>
     <row r="77" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -10664,30 +10643,30 @@
       <c r="BB77" s="7"/>
       <c r="BC77" s="7"/>
       <c r="BG77" s="7"/>
-      <c r="BH77" s="89"/>
-      <c r="BI77" s="89"/>
-      <c r="BJ77" s="89"/>
-      <c r="BK77" s="89"/>
-      <c r="BL77" s="89"/>
-      <c r="BM77" s="89"/>
-      <c r="BN77" s="89"/>
-      <c r="BO77" s="89"/>
-      <c r="BP77" s="89"/>
-      <c r="BQ77" s="89"/>
-      <c r="BR77" s="89"/>
-      <c r="BS77" s="89"/>
-      <c r="BT77" s="89"/>
-      <c r="BU77" s="89"/>
-      <c r="BV77" s="89"/>
+      <c r="BH77" s="146"/>
+      <c r="BI77" s="146"/>
+      <c r="BJ77" s="146"/>
+      <c r="BK77" s="146"/>
+      <c r="BL77" s="146"/>
+      <c r="BM77" s="146"/>
+      <c r="BN77" s="146"/>
+      <c r="BO77" s="146"/>
+      <c r="BP77" s="146"/>
+      <c r="BQ77" s="146"/>
+      <c r="BR77" s="146"/>
+      <c r="BS77" s="146"/>
+      <c r="BT77" s="146"/>
+      <c r="BU77" s="146"/>
+      <c r="BV77" s="146"/>
       <c r="BW77" s="10"/>
       <c r="BX77" s="80"/>
-      <c r="BY77" s="89"/>
-      <c r="BZ77" s="89"/>
-      <c r="CA77" s="89"/>
-      <c r="CB77" s="89"/>
-      <c r="CC77" s="89"/>
-      <c r="CD77" s="89"/>
-      <c r="CE77" s="89"/>
+      <c r="BY77" s="146"/>
+      <c r="BZ77" s="146"/>
+      <c r="CA77" s="146"/>
+      <c r="CB77" s="146"/>
+      <c r="CC77" s="146"/>
+      <c r="CD77" s="146"/>
+      <c r="CE77" s="146"/>
       <c r="CF77" s="80"/>
     </row>
     <row r="78" spans="2:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -10703,30 +10682,30 @@
       <c r="BB78" s="7"/>
       <c r="BC78" s="7"/>
       <c r="BG78" s="7"/>
-      <c r="BH78" s="89"/>
-      <c r="BI78" s="89"/>
-      <c r="BJ78" s="89"/>
-      <c r="BK78" s="89"/>
-      <c r="BL78" s="89"/>
-      <c r="BM78" s="89"/>
-      <c r="BN78" s="89"/>
-      <c r="BO78" s="89"/>
-      <c r="BP78" s="89"/>
-      <c r="BQ78" s="89"/>
-      <c r="BR78" s="89"/>
-      <c r="BS78" s="89"/>
-      <c r="BT78" s="89"/>
-      <c r="BU78" s="89"/>
-      <c r="BV78" s="89"/>
+      <c r="BH78" s="146"/>
+      <c r="BI78" s="146"/>
+      <c r="BJ78" s="146"/>
+      <c r="BK78" s="146"/>
+      <c r="BL78" s="146"/>
+      <c r="BM78" s="146"/>
+      <c r="BN78" s="146"/>
+      <c r="BO78" s="146"/>
+      <c r="BP78" s="146"/>
+      <c r="BQ78" s="146"/>
+      <c r="BR78" s="146"/>
+      <c r="BS78" s="146"/>
+      <c r="BT78" s="146"/>
+      <c r="BU78" s="146"/>
+      <c r="BV78" s="146"/>
       <c r="BW78" s="10"/>
       <c r="BX78" s="80"/>
-      <c r="BY78" s="89"/>
-      <c r="BZ78" s="89"/>
-      <c r="CA78" s="89"/>
-      <c r="CB78" s="89"/>
-      <c r="CC78" s="89"/>
-      <c r="CD78" s="89"/>
-      <c r="CE78" s="89"/>
+      <c r="BY78" s="146"/>
+      <c r="BZ78" s="146"/>
+      <c r="CA78" s="146"/>
+      <c r="CB78" s="146"/>
+      <c r="CC78" s="146"/>
+      <c r="CD78" s="146"/>
+      <c r="CE78" s="146"/>
       <c r="CF78" s="80"/>
     </row>
     <row r="79" spans="2:84" x14ac:dyDescent="0.3">
@@ -10754,13 +10733,13 @@
       <c r="BV79" s="7"/>
       <c r="BW79" s="10"/>
       <c r="BX79" s="7"/>
-      <c r="BY79" s="89"/>
-      <c r="BZ79" s="89"/>
-      <c r="CA79" s="89"/>
-      <c r="CB79" s="89"/>
-      <c r="CC79" s="89"/>
-      <c r="CD79" s="89"/>
-      <c r="CE79" s="89"/>
+      <c r="BY79" s="146"/>
+      <c r="BZ79" s="146"/>
+      <c r="CA79" s="146"/>
+      <c r="CB79" s="146"/>
+      <c r="CC79" s="146"/>
+      <c r="CD79" s="146"/>
+      <c r="CE79" s="146"/>
       <c r="CF79" s="7"/>
     </row>
     <row r="80" spans="2:84" x14ac:dyDescent="0.3">
@@ -10795,44 +10774,44 @@
       <c r="BE81" s="6"/>
       <c r="BG81" s="6"/>
       <c r="BH81" s="33" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="BI81" s="6"/>
       <c r="BJ81" s="33" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="BK81" s="6"/>
       <c r="BL81" s="33" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="BM81" s="7"/>
       <c r="BN81" s="33" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="BO81" s="6"/>
       <c r="BP81" s="33" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="BQ81" s="6"/>
       <c r="BR81" s="33" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="BS81" s="6"/>
       <c r="BT81" s="33" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="BU81" s="6"/>
       <c r="BV81" s="33" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="BW81" s="10"/>
       <c r="BX81" s="33" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="BZ81" s="7"/>
       <c r="CA81" s="69"/>
       <c r="CB81" s="33" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="CC81" s="7"/>
       <c r="CD81" s="7"/>
@@ -10846,7 +10825,7 @@
       <c r="BI82" s="6"/>
       <c r="BJ82" s="17"/>
       <c r="BK82" s="6"/>
-      <c r="BL82" s="112"/>
+      <c r="BL82" s="98"/>
       <c r="BM82" s="7"/>
       <c r="BN82" s="17"/>
       <c r="BO82" s="6"/>
@@ -10862,7 +10841,7 @@
       <c r="BY82" s="7"/>
       <c r="BZ82" s="7"/>
       <c r="CA82" s="69"/>
-      <c r="CB82" s="113"/>
+      <c r="CB82" s="124"/>
       <c r="CC82" s="7"/>
       <c r="CD82" s="7"/>
       <c r="CE82" s="7"/>
@@ -10875,7 +10854,7 @@
       <c r="BI83" s="6"/>
       <c r="BJ83" s="17"/>
       <c r="BK83" s="6"/>
-      <c r="BL83" s="112"/>
+      <c r="BL83" s="98"/>
       <c r="BM83" s="7"/>
       <c r="BN83" s="17"/>
       <c r="BO83" s="6"/>
@@ -10891,7 +10870,7 @@
       <c r="BY83" s="7"/>
       <c r="BZ83" s="7"/>
       <c r="CA83" s="69"/>
-      <c r="CB83" s="113"/>
+      <c r="CB83" s="124"/>
       <c r="CC83" s="7"/>
       <c r="CD83" s="7"/>
       <c r="CE83" s="7"/>
@@ -10977,10 +10956,10 @@
       <c r="BW86" s="10"/>
       <c r="BX86" s="17"/>
       <c r="BY86" s="7"/>
-      <c r="BZ86" s="115" t="s">
-        <v>62</v>
-      </c>
-      <c r="CA86" s="116"/>
+      <c r="BZ86" s="127" t="s">
+        <v>56</v>
+      </c>
+      <c r="CA86" s="128"/>
       <c r="CB86" s="32"/>
       <c r="CC86" s="7"/>
       <c r="CD86" s="7"/>
@@ -11008,8 +10987,8 @@
       <c r="BW87" s="10"/>
       <c r="BX87" s="17"/>
       <c r="BY87" s="7"/>
-      <c r="BZ87" s="115"/>
-      <c r="CA87" s="116"/>
+      <c r="BZ87" s="127"/>
+      <c r="CA87" s="128"/>
       <c r="CB87" s="32"/>
       <c r="CC87" s="7"/>
       <c r="CD87" s="7"/>
@@ -11040,10 +11019,10 @@
       <c r="BZ88" s="7"/>
       <c r="CA88" s="69"/>
       <c r="CB88" s="2"/>
-      <c r="CC88" s="117" t="s">
-        <v>63</v>
-      </c>
-      <c r="CD88" s="118"/>
+      <c r="CC88" s="129" t="s">
+        <v>57</v>
+      </c>
+      <c r="CD88" s="130"/>
       <c r="CE88" s="7"/>
       <c r="CF88" s="7"/>
     </row>
@@ -11071,8 +11050,8 @@
       <c r="BZ89" s="7"/>
       <c r="CA89" s="69"/>
       <c r="CB89" s="3"/>
-      <c r="CC89" s="119"/>
-      <c r="CD89" s="118"/>
+      <c r="CC89" s="131"/>
+      <c r="CD89" s="130"/>
       <c r="CE89" s="7"/>
       <c r="CF89" s="7"/>
       <c r="CJ89" t="s">
@@ -11314,23 +11293,23 @@
     <row r="98" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG98" s="7"/>
       <c r="BH98" s="39"/>
-      <c r="BI98" s="114" t="s">
+      <c r="BI98" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="BJ98" s="114"/>
-      <c r="BK98" s="114"/>
-      <c r="BL98" s="114"/>
-      <c r="BM98" s="114"/>
-      <c r="BN98" s="114"/>
-      <c r="BO98" s="114"/>
-      <c r="BP98" s="114"/>
-      <c r="BQ98" s="114"/>
-      <c r="BR98" s="114"/>
-      <c r="BS98" s="114"/>
-      <c r="BT98" s="114"/>
-      <c r="BU98" s="114"/>
-      <c r="BV98" s="114"/>
-      <c r="BW98" s="114"/>
+      <c r="BJ98" s="125"/>
+      <c r="BK98" s="125"/>
+      <c r="BL98" s="125"/>
+      <c r="BM98" s="125"/>
+      <c r="BN98" s="125"/>
+      <c r="BO98" s="125"/>
+      <c r="BP98" s="125"/>
+      <c r="BQ98" s="125"/>
+      <c r="BR98" s="125"/>
+      <c r="BS98" s="125"/>
+      <c r="BT98" s="125"/>
+      <c r="BU98" s="125"/>
+      <c r="BV98" s="125"/>
+      <c r="BW98" s="125"/>
       <c r="BX98" s="40"/>
       <c r="BY98" s="7"/>
       <c r="BZ98" s="7"/>
@@ -11344,21 +11323,21 @@
     <row r="99" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG99" s="7"/>
       <c r="BH99" s="39"/>
-      <c r="BI99" s="114"/>
-      <c r="BJ99" s="114"/>
-      <c r="BK99" s="114"/>
-      <c r="BL99" s="114"/>
-      <c r="BM99" s="114"/>
-      <c r="BN99" s="114"/>
-      <c r="BO99" s="114"/>
-      <c r="BP99" s="114"/>
-      <c r="BQ99" s="114"/>
-      <c r="BR99" s="114"/>
-      <c r="BS99" s="114"/>
-      <c r="BT99" s="114"/>
-      <c r="BU99" s="114"/>
-      <c r="BV99" s="114"/>
-      <c r="BW99" s="114"/>
+      <c r="BI99" s="125"/>
+      <c r="BJ99" s="125"/>
+      <c r="BK99" s="125"/>
+      <c r="BL99" s="125"/>
+      <c r="BM99" s="125"/>
+      <c r="BN99" s="125"/>
+      <c r="BO99" s="125"/>
+      <c r="BP99" s="125"/>
+      <c r="BQ99" s="125"/>
+      <c r="BR99" s="125"/>
+      <c r="BS99" s="125"/>
+      <c r="BT99" s="125"/>
+      <c r="BU99" s="125"/>
+      <c r="BV99" s="125"/>
+      <c r="BW99" s="125"/>
       <c r="BX99" s="40"/>
       <c r="BY99" s="7"/>
       <c r="BZ99" s="7"/>
@@ -11372,21 +11351,21 @@
     <row r="100" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG100" s="7"/>
       <c r="BH100" s="39"/>
-      <c r="BI100" s="114"/>
-      <c r="BJ100" s="114"/>
-      <c r="BK100" s="114"/>
-      <c r="BL100" s="114"/>
-      <c r="BM100" s="114"/>
-      <c r="BN100" s="114"/>
-      <c r="BO100" s="114"/>
-      <c r="BP100" s="114"/>
-      <c r="BQ100" s="114"/>
-      <c r="BR100" s="114"/>
-      <c r="BS100" s="114"/>
-      <c r="BT100" s="114"/>
-      <c r="BU100" s="114"/>
-      <c r="BV100" s="114"/>
-      <c r="BW100" s="114"/>
+      <c r="BI100" s="125"/>
+      <c r="BJ100" s="125"/>
+      <c r="BK100" s="125"/>
+      <c r="BL100" s="125"/>
+      <c r="BM100" s="125"/>
+      <c r="BN100" s="125"/>
+      <c r="BO100" s="125"/>
+      <c r="BP100" s="125"/>
+      <c r="BQ100" s="125"/>
+      <c r="BR100" s="125"/>
+      <c r="BS100" s="125"/>
+      <c r="BT100" s="125"/>
+      <c r="BU100" s="125"/>
+      <c r="BV100" s="125"/>
+      <c r="BW100" s="125"/>
       <c r="BX100" s="40"/>
       <c r="BY100" s="7"/>
       <c r="BZ100" s="7"/>
@@ -11400,21 +11379,21 @@
     <row r="101" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG101" s="7"/>
       <c r="BH101" s="39"/>
-      <c r="BI101" s="114"/>
-      <c r="BJ101" s="114"/>
-      <c r="BK101" s="114"/>
-      <c r="BL101" s="114"/>
-      <c r="BM101" s="114"/>
-      <c r="BN101" s="114"/>
-      <c r="BO101" s="114"/>
-      <c r="BP101" s="114"/>
-      <c r="BQ101" s="114"/>
-      <c r="BR101" s="114"/>
-      <c r="BS101" s="114"/>
-      <c r="BT101" s="114"/>
-      <c r="BU101" s="114"/>
-      <c r="BV101" s="114"/>
-      <c r="BW101" s="114"/>
+      <c r="BI101" s="125"/>
+      <c r="BJ101" s="125"/>
+      <c r="BK101" s="125"/>
+      <c r="BL101" s="125"/>
+      <c r="BM101" s="125"/>
+      <c r="BN101" s="125"/>
+      <c r="BO101" s="125"/>
+      <c r="BP101" s="125"/>
+      <c r="BQ101" s="125"/>
+      <c r="BR101" s="125"/>
+      <c r="BS101" s="125"/>
+      <c r="BT101" s="125"/>
+      <c r="BU101" s="125"/>
+      <c r="BV101" s="125"/>
+      <c r="BW101" s="125"/>
       <c r="BX101" s="40"/>
       <c r="BY101" s="7"/>
       <c r="BZ101" s="7"/>
@@ -11428,21 +11407,21 @@
     <row r="102" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG102" s="7"/>
       <c r="BH102" s="39"/>
-      <c r="BI102" s="114"/>
-      <c r="BJ102" s="114"/>
-      <c r="BK102" s="114"/>
-      <c r="BL102" s="114"/>
-      <c r="BM102" s="114"/>
-      <c r="BN102" s="114"/>
-      <c r="BO102" s="114"/>
-      <c r="BP102" s="114"/>
-      <c r="BQ102" s="114"/>
-      <c r="BR102" s="114"/>
-      <c r="BS102" s="114"/>
-      <c r="BT102" s="114"/>
-      <c r="BU102" s="114"/>
-      <c r="BV102" s="114"/>
-      <c r="BW102" s="114"/>
+      <c r="BI102" s="125"/>
+      <c r="BJ102" s="125"/>
+      <c r="BK102" s="125"/>
+      <c r="BL102" s="125"/>
+      <c r="BM102" s="125"/>
+      <c r="BN102" s="125"/>
+      <c r="BO102" s="125"/>
+      <c r="BP102" s="125"/>
+      <c r="BQ102" s="125"/>
+      <c r="BR102" s="125"/>
+      <c r="BS102" s="125"/>
+      <c r="BT102" s="125"/>
+      <c r="BU102" s="125"/>
+      <c r="BV102" s="125"/>
+      <c r="BW102" s="125"/>
       <c r="BX102" s="40"/>
       <c r="BY102" s="7"/>
       <c r="BZ102" s="7"/>
@@ -11687,15 +11666,15 @@
       <c r="BM111" s="45"/>
       <c r="BN111" s="45"/>
       <c r="BO111" s="45"/>
-      <c r="BP111" s="133" t="s">
+      <c r="BP111" s="145" t="s">
         <v>41</v>
       </c>
-      <c r="BQ111" s="133"/>
-      <c r="BR111" s="133"/>
-      <c r="BS111" s="133"/>
-      <c r="BT111" s="133"/>
-      <c r="BU111" s="133"/>
-      <c r="BV111" s="133"/>
+      <c r="BQ111" s="145"/>
+      <c r="BR111" s="145"/>
+      <c r="BS111" s="145"/>
+      <c r="BT111" s="145"/>
+      <c r="BU111" s="145"/>
+      <c r="BV111" s="145"/>
       <c r="BW111" s="56"/>
       <c r="BX111" s="11"/>
       <c r="BY111" s="45"/>
@@ -11717,13 +11696,13 @@
       <c r="BM112" s="45"/>
       <c r="BN112" s="45"/>
       <c r="BO112" s="45"/>
-      <c r="BP112" s="133"/>
-      <c r="BQ112" s="133"/>
-      <c r="BR112" s="133"/>
-      <c r="BS112" s="133"/>
-      <c r="BT112" s="133"/>
-      <c r="BU112" s="133"/>
-      <c r="BV112" s="133"/>
+      <c r="BP112" s="145"/>
+      <c r="BQ112" s="145"/>
+      <c r="BR112" s="145"/>
+      <c r="BS112" s="145"/>
+      <c r="BT112" s="145"/>
+      <c r="BU112" s="145"/>
+      <c r="BV112" s="145"/>
       <c r="BW112" s="56"/>
       <c r="BX112" s="11"/>
       <c r="BY112" s="45"/>
@@ -11745,13 +11724,13 @@
       <c r="BM113" s="45"/>
       <c r="BN113" s="45"/>
       <c r="BO113" s="45"/>
-      <c r="BP113" s="133"/>
-      <c r="BQ113" s="133"/>
-      <c r="BR113" s="133"/>
-      <c r="BS113" s="133"/>
-      <c r="BT113" s="133"/>
-      <c r="BU113" s="133"/>
-      <c r="BV113" s="133"/>
+      <c r="BP113" s="145"/>
+      <c r="BQ113" s="145"/>
+      <c r="BR113" s="145"/>
+      <c r="BS113" s="145"/>
+      <c r="BT113" s="145"/>
+      <c r="BU113" s="145"/>
+      <c r="BV113" s="145"/>
       <c r="BW113" s="56"/>
       <c r="BX113" s="11"/>
       <c r="BY113" s="45"/>
@@ -11773,13 +11752,13 @@
       <c r="BM114" s="45"/>
       <c r="BN114" s="45"/>
       <c r="BO114" s="45"/>
-      <c r="BP114" s="133"/>
-      <c r="BQ114" s="133"/>
-      <c r="BR114" s="133"/>
-      <c r="BS114" s="133"/>
-      <c r="BT114" s="133"/>
-      <c r="BU114" s="133"/>
-      <c r="BV114" s="133"/>
+      <c r="BP114" s="145"/>
+      <c r="BQ114" s="145"/>
+      <c r="BR114" s="145"/>
+      <c r="BS114" s="145"/>
+      <c r="BT114" s="145"/>
+      <c r="BU114" s="145"/>
+      <c r="BV114" s="145"/>
       <c r="BW114" s="56"/>
       <c r="BX114" s="11"/>
       <c r="BY114" s="45"/>
@@ -11801,13 +11780,13 @@
       <c r="BM115" s="45"/>
       <c r="BN115" s="45"/>
       <c r="BO115" s="45"/>
-      <c r="BP115" s="133"/>
-      <c r="BQ115" s="133"/>
-      <c r="BR115" s="133"/>
-      <c r="BS115" s="133"/>
-      <c r="BT115" s="133"/>
-      <c r="BU115" s="133"/>
-      <c r="BV115" s="133"/>
+      <c r="BP115" s="145"/>
+      <c r="BQ115" s="145"/>
+      <c r="BR115" s="145"/>
+      <c r="BS115" s="145"/>
+      <c r="BT115" s="145"/>
+      <c r="BU115" s="145"/>
+      <c r="BV115" s="145"/>
       <c r="BW115" s="56"/>
       <c r="BX115" s="11"/>
       <c r="BY115" s="45"/>
@@ -12017,16 +11996,16 @@
     </row>
     <row r="123" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG123" s="7"/>
-      <c r="BH123" s="90" t="s">
-        <v>43</v>
+      <c r="BH123" s="126" t="s">
+        <v>74</v>
       </c>
       <c r="BI123" s="6"/>
-      <c r="BJ123" s="90" t="s">
-        <v>44</v>
+      <c r="BJ123" s="126" t="s">
+        <v>75</v>
       </c>
       <c r="BK123" s="6"/>
-      <c r="BL123" s="90" t="s">
-        <v>51</v>
+      <c r="BL123" s="126" t="s">
+        <v>76</v>
       </c>
       <c r="BM123" s="7"/>
       <c r="BN123" s="17"/>
@@ -12035,16 +12014,16 @@
       <c r="BQ123" s="6"/>
       <c r="BR123" s="17"/>
       <c r="BS123" s="6"/>
-      <c r="BT123" s="90" t="s">
-        <v>45</v>
+      <c r="BT123" s="126" t="s">
+        <v>77</v>
       </c>
       <c r="BU123" s="6"/>
-      <c r="BV123" s="90" t="s">
-        <v>46</v>
+      <c r="BV123" s="126" t="s">
+        <v>78</v>
       </c>
       <c r="BW123" s="10"/>
-      <c r="BX123" s="90" t="s">
-        <v>50</v>
+      <c r="BX123" s="126" t="s">
+        <v>79</v>
       </c>
       <c r="BY123" s="7"/>
       <c r="BZ123" s="7"/>
@@ -12057,11 +12036,11 @@
     </row>
     <row r="124" spans="59:84" ht="25.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="BG124" s="7"/>
-      <c r="BH124" s="90"/>
+      <c r="BH124" s="126"/>
       <c r="BI124" s="6"/>
-      <c r="BJ124" s="90"/>
+      <c r="BJ124" s="126"/>
       <c r="BK124" s="6"/>
-      <c r="BL124" s="90"/>
+      <c r="BL124" s="126"/>
       <c r="BM124" s="34"/>
       <c r="BN124" s="17"/>
       <c r="BP124" s="79" t="s">
@@ -12070,11 +12049,11 @@
       <c r="BQ124" s="6"/>
       <c r="BR124" s="17"/>
       <c r="BS124" s="6"/>
-      <c r="BT124" s="90"/>
+      <c r="BT124" s="126"/>
       <c r="BU124" s="6"/>
-      <c r="BV124" s="90"/>
+      <c r="BV124" s="126"/>
       <c r="BW124" s="10"/>
-      <c r="BX124" s="90"/>
+      <c r="BX124" s="126"/>
       <c r="BY124" s="7"/>
       <c r="BZ124" s="7"/>
       <c r="CA124" s="69"/>
@@ -12086,11 +12065,11 @@
     </row>
     <row r="125" spans="59:84" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="BG125" s="7"/>
-      <c r="BH125" s="90"/>
+      <c r="BH125" s="126"/>
       <c r="BI125" s="6"/>
-      <c r="BJ125" s="90"/>
+      <c r="BJ125" s="126"/>
       <c r="BK125" s="6"/>
-      <c r="BL125" s="90"/>
+      <c r="BL125" s="126"/>
       <c r="BM125" s="7"/>
       <c r="BN125" s="17"/>
       <c r="BO125" s="6"/>
@@ -12098,11 +12077,11 @@
       <c r="BQ125" s="6"/>
       <c r="BR125" s="17"/>
       <c r="BS125" s="6"/>
-      <c r="BT125" s="90"/>
+      <c r="BT125" s="126"/>
       <c r="BU125" s="6"/>
-      <c r="BV125" s="90"/>
+      <c r="BV125" s="126"/>
       <c r="BW125" s="10"/>
-      <c r="BX125" s="90"/>
+      <c r="BX125" s="126"/>
       <c r="BY125" s="7"/>
       <c r="BZ125" s="7"/>
       <c r="CA125" s="69"/>
@@ -12271,11 +12250,11 @@
       <c r="BV131" s="7"/>
       <c r="BW131" s="10"/>
       <c r="BX131" s="7"/>
-      <c r="BY131" s="124" t="s">
-        <v>52</v>
-      </c>
-      <c r="BZ131" s="125"/>
-      <c r="CA131" s="126"/>
+      <c r="BY131" s="136" t="s">
+        <v>46</v>
+      </c>
+      <c r="BZ131" s="137"/>
+      <c r="CA131" s="138"/>
       <c r="CB131" s="69"/>
       <c r="CC131" s="60"/>
       <c r="CD131" s="61"/>
@@ -12290,28 +12269,28 @@
       <c r="BK132" s="7"/>
       <c r="BL132" s="7"/>
       <c r="BM132" s="7"/>
-      <c r="BN132" s="120" t="s">
-        <v>71</v>
-      </c>
-      <c r="BO132" s="121"/>
-      <c r="BP132" s="121"/>
-      <c r="BQ132" s="121"/>
-      <c r="BR132" s="122"/>
+      <c r="BN132" s="132" t="s">
+        <v>80</v>
+      </c>
+      <c r="BO132" s="133"/>
+      <c r="BP132" s="133"/>
+      <c r="BQ132" s="133"/>
+      <c r="BR132" s="134"/>
       <c r="BS132" s="7"/>
       <c r="BT132" s="7"/>
       <c r="BU132" s="7"/>
       <c r="BV132" s="7"/>
       <c r="BW132" s="10"/>
       <c r="BX132" s="7"/>
-      <c r="BY132" s="127"/>
-      <c r="BZ132" s="128"/>
-      <c r="CA132" s="129"/>
+      <c r="BY132" s="139"/>
+      <c r="BZ132" s="140"/>
+      <c r="CA132" s="141"/>
       <c r="CB132" s="69"/>
-      <c r="CC132" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="CD132" s="110"/>
-      <c r="CE132" s="111"/>
+      <c r="CC132" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="CD132" s="122"/>
+      <c r="CE132" s="123"/>
       <c r="CF132" s="7"/>
     </row>
     <row r="133" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -12322,24 +12301,24 @@
       <c r="BK133" s="7"/>
       <c r="BL133" s="7"/>
       <c r="BM133" s="7"/>
-      <c r="BN133" s="123"/>
-      <c r="BO133" s="121"/>
-      <c r="BP133" s="121"/>
-      <c r="BQ133" s="121"/>
-      <c r="BR133" s="122"/>
+      <c r="BN133" s="135"/>
+      <c r="BO133" s="133"/>
+      <c r="BP133" s="133"/>
+      <c r="BQ133" s="133"/>
+      <c r="BR133" s="134"/>
       <c r="BS133" s="7"/>
       <c r="BT133" s="7"/>
       <c r="BU133" s="7"/>
       <c r="BV133" s="7"/>
       <c r="BW133" s="10"/>
       <c r="BX133" s="7"/>
-      <c r="BY133" s="127"/>
-      <c r="BZ133" s="128"/>
-      <c r="CA133" s="129"/>
+      <c r="BY133" s="139"/>
+      <c r="BZ133" s="140"/>
+      <c r="CA133" s="141"/>
       <c r="CB133" s="69"/>
-      <c r="CC133" s="109"/>
-      <c r="CD133" s="110"/>
-      <c r="CE133" s="111"/>
+      <c r="CC133" s="121"/>
+      <c r="CD133" s="122"/>
+      <c r="CE133" s="123"/>
       <c r="CF133" s="7"/>
     </row>
     <row r="134" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -12350,24 +12329,24 @@
       <c r="BK134" s="7"/>
       <c r="BL134" s="7"/>
       <c r="BM134" s="7"/>
-      <c r="BN134" s="123"/>
-      <c r="BO134" s="121"/>
-      <c r="BP134" s="121"/>
-      <c r="BQ134" s="121"/>
-      <c r="BR134" s="122"/>
+      <c r="BN134" s="135"/>
+      <c r="BO134" s="133"/>
+      <c r="BP134" s="133"/>
+      <c r="BQ134" s="133"/>
+      <c r="BR134" s="134"/>
       <c r="BS134" s="7"/>
       <c r="BT134" s="7"/>
       <c r="BU134" s="7"/>
       <c r="BV134" s="7"/>
       <c r="BW134" s="10"/>
       <c r="BX134" s="7"/>
-      <c r="BY134" s="127"/>
-      <c r="BZ134" s="128"/>
-      <c r="CA134" s="129"/>
+      <c r="BY134" s="139"/>
+      <c r="BZ134" s="140"/>
+      <c r="CA134" s="141"/>
       <c r="CB134" s="69"/>
-      <c r="CC134" s="109"/>
-      <c r="CD134" s="110"/>
-      <c r="CE134" s="111"/>
+      <c r="CC134" s="121"/>
+      <c r="CD134" s="122"/>
+      <c r="CE134" s="123"/>
       <c r="CF134" s="7"/>
     </row>
     <row r="135" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -12378,24 +12357,24 @@
       <c r="BK135" s="7"/>
       <c r="BL135" s="7"/>
       <c r="BM135" s="7"/>
-      <c r="BN135" s="123"/>
-      <c r="BO135" s="121"/>
-      <c r="BP135" s="121"/>
-      <c r="BQ135" s="121"/>
-      <c r="BR135" s="122"/>
+      <c r="BN135" s="135"/>
+      <c r="BO135" s="133"/>
+      <c r="BP135" s="133"/>
+      <c r="BQ135" s="133"/>
+      <c r="BR135" s="134"/>
       <c r="BS135" s="7"/>
       <c r="BT135" s="7"/>
       <c r="BU135" s="7"/>
       <c r="BV135" s="7"/>
       <c r="BW135" s="10"/>
       <c r="BX135" s="7"/>
-      <c r="BY135" s="127"/>
-      <c r="BZ135" s="128"/>
-      <c r="CA135" s="129"/>
+      <c r="BY135" s="139"/>
+      <c r="BZ135" s="140"/>
+      <c r="CA135" s="141"/>
       <c r="CB135" s="69"/>
-      <c r="CC135" s="109"/>
-      <c r="CD135" s="110"/>
-      <c r="CE135" s="111"/>
+      <c r="CC135" s="121"/>
+      <c r="CD135" s="122"/>
+      <c r="CE135" s="123"/>
       <c r="CF135" s="7"/>
     </row>
     <row r="136" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -12406,24 +12385,24 @@
       <c r="BK136" s="7"/>
       <c r="BL136" s="7"/>
       <c r="BM136" s="7"/>
-      <c r="BN136" s="123"/>
-      <c r="BO136" s="121"/>
-      <c r="BP136" s="121"/>
-      <c r="BQ136" s="121"/>
-      <c r="BR136" s="122"/>
+      <c r="BN136" s="135"/>
+      <c r="BO136" s="133"/>
+      <c r="BP136" s="133"/>
+      <c r="BQ136" s="133"/>
+      <c r="BR136" s="134"/>
       <c r="BS136" s="7"/>
       <c r="BT136" s="7"/>
       <c r="BU136" s="7"/>
       <c r="BV136" s="7"/>
       <c r="BW136" s="10"/>
       <c r="BX136" s="7"/>
-      <c r="BY136" s="127"/>
-      <c r="BZ136" s="128"/>
-      <c r="CA136" s="129"/>
+      <c r="BY136" s="139"/>
+      <c r="BZ136" s="140"/>
+      <c r="CA136" s="141"/>
       <c r="CB136" s="69"/>
-      <c r="CC136" s="109"/>
-      <c r="CD136" s="110"/>
-      <c r="CE136" s="111"/>
+      <c r="CC136" s="121"/>
+      <c r="CD136" s="122"/>
+      <c r="CE136" s="123"/>
       <c r="CF136" s="7"/>
     </row>
     <row r="137" spans="59:84 1257:1257" x14ac:dyDescent="0.3">
@@ -12445,9 +12424,9 @@
       <c r="BV137" s="7"/>
       <c r="BW137" s="10"/>
       <c r="BX137" s="7"/>
-      <c r="BY137" s="130"/>
-      <c r="BZ137" s="131"/>
-      <c r="CA137" s="132"/>
+      <c r="BY137" s="142"/>
+      <c r="BZ137" s="143"/>
+      <c r="CA137" s="144"/>
       <c r="CB137" s="69"/>
       <c r="CC137" s="63"/>
       <c r="CD137" s="64"/>
@@ -12621,23 +12600,44 @@
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="R62:V62"/>
-    <mergeCell ref="U44:X45"/>
-    <mergeCell ref="U49:X51"/>
-    <mergeCell ref="U52:X54"/>
-    <mergeCell ref="U37:V40"/>
-    <mergeCell ref="U46:W46"/>
-    <mergeCell ref="T40:T49"/>
-    <mergeCell ref="E34:I35"/>
-    <mergeCell ref="N33:P34"/>
-    <mergeCell ref="T38:T39"/>
-    <mergeCell ref="S34:U34"/>
-    <mergeCell ref="AP45:AT46"/>
-    <mergeCell ref="AE34:AI35"/>
-    <mergeCell ref="O45:O46"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="CR32:CX33"/>
+    <mergeCell ref="DD10:DD24"/>
+    <mergeCell ref="DF26:DK27"/>
+    <mergeCell ref="CQ17:CQ30"/>
+    <mergeCell ref="BY76:CE79"/>
+    <mergeCell ref="BH123:BH125"/>
+    <mergeCell ref="AN63:AX64"/>
+    <mergeCell ref="AN65:AX66"/>
+    <mergeCell ref="AN61:AX62"/>
+    <mergeCell ref="AO57:AO58"/>
+    <mergeCell ref="AO55:AO56"/>
+    <mergeCell ref="CC132:CE136"/>
+    <mergeCell ref="BL82:BL83"/>
+    <mergeCell ref="CB82:CB83"/>
+    <mergeCell ref="BI98:BW102"/>
+    <mergeCell ref="BX123:BX125"/>
+    <mergeCell ref="BL123:BL125"/>
+    <mergeCell ref="BZ86:CA87"/>
+    <mergeCell ref="CC88:CD89"/>
+    <mergeCell ref="BV123:BV125"/>
+    <mergeCell ref="BT123:BT125"/>
+    <mergeCell ref="BJ123:BJ125"/>
+    <mergeCell ref="BN132:BR136"/>
+    <mergeCell ref="BY131:CA137"/>
+    <mergeCell ref="BP111:BV115"/>
+    <mergeCell ref="BH76:BV78"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P48:R49"/>
+    <mergeCell ref="AC39:AC40"/>
+    <mergeCell ref="AK39:AK40"/>
+    <mergeCell ref="N60:P61"/>
+    <mergeCell ref="R60:V61"/>
+    <mergeCell ref="O55:O56"/>
+    <mergeCell ref="O57:O58"/>
+    <mergeCell ref="T51:T55"/>
+    <mergeCell ref="O51:O52"/>
+    <mergeCell ref="O53:O54"/>
     <mergeCell ref="AP48:AR49"/>
     <mergeCell ref="AO49:AO50"/>
     <mergeCell ref="AM33:AQ34"/>
@@ -12654,44 +12654,23 @@
     <mergeCell ref="AO47:AO48"/>
     <mergeCell ref="AO51:AO52"/>
     <mergeCell ref="AO53:AO54"/>
-    <mergeCell ref="N60:P61"/>
-    <mergeCell ref="R60:V61"/>
-    <mergeCell ref="O55:O56"/>
-    <mergeCell ref="O57:O58"/>
-    <mergeCell ref="T51:T55"/>
-    <mergeCell ref="O51:O52"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P48:R49"/>
-    <mergeCell ref="AC39:AC40"/>
-    <mergeCell ref="AK39:AK40"/>
-    <mergeCell ref="AO55:AO56"/>
-    <mergeCell ref="CC132:CE136"/>
-    <mergeCell ref="BL82:BL83"/>
-    <mergeCell ref="CB82:CB83"/>
-    <mergeCell ref="BI98:BW102"/>
-    <mergeCell ref="BX123:BX125"/>
-    <mergeCell ref="BL123:BL125"/>
-    <mergeCell ref="BZ86:CA87"/>
-    <mergeCell ref="CC88:CD89"/>
-    <mergeCell ref="BV123:BV125"/>
-    <mergeCell ref="BT123:BT125"/>
-    <mergeCell ref="BJ123:BJ125"/>
-    <mergeCell ref="BN132:BR136"/>
-    <mergeCell ref="BY131:CA137"/>
-    <mergeCell ref="BP111:BV115"/>
-    <mergeCell ref="BH76:BV78"/>
-    <mergeCell ref="BH123:BH125"/>
-    <mergeCell ref="AN63:AX64"/>
-    <mergeCell ref="AN65:AX66"/>
-    <mergeCell ref="AN61:AX62"/>
-    <mergeCell ref="AO57:AO58"/>
-    <mergeCell ref="CR32:CX33"/>
-    <mergeCell ref="DD10:DD24"/>
-    <mergeCell ref="DF26:DK27"/>
-    <mergeCell ref="CQ17:CQ30"/>
-    <mergeCell ref="BY76:CE79"/>
+    <mergeCell ref="E34:I35"/>
+    <mergeCell ref="N33:P34"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="S34:U34"/>
+    <mergeCell ref="AP45:AT46"/>
+    <mergeCell ref="AE34:AI35"/>
+    <mergeCell ref="O45:O46"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="R62:V62"/>
+    <mergeCell ref="U44:X45"/>
+    <mergeCell ref="U49:X51"/>
+    <mergeCell ref="U52:X54"/>
+    <mergeCell ref="U37:V40"/>
+    <mergeCell ref="U46:W46"/>
+    <mergeCell ref="T40:T49"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
